--- a/jogos_2025-08-01.xlsx
+++ b/jogos_2025-08-01.xlsx
@@ -902,7 +902,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mariehamn</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Rukh Vynnyky</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>SK Poltava</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1112,10 +1112,10 @@
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -1166,22 +1166,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rukh Vynnyky</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SK Poltava</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1244,10 +1244,10 @@
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.32</v>
+        <v>2.39</v>
       </c>
       <c r="M27" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="N27" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4028,10 +4028,10 @@
         <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF27" t="n">
         <v>0</v>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.95</v>
+        <v>2.28</v>
       </c>
       <c r="M28" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="N28" t="n">
-        <v>2.29</v>
+        <v>3.05</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4154,10 +4154,10 @@
         <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.7</v>
+        <v>2.39</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.95</v>
+        <v>1.58</v>
       </c>
       <c r="AD28" t="n">
         <v>0</v>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,13 +4238,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4286,10 +4286,10 @@
         <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD29" t="n">
         <v>0</v>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="M30" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N30" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4418,10 +4418,10 @@
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
         <v>0</v>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,13 +4502,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4556,10 +4556,10 @@
         <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
         <v>0</v>
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4862,22 +4862,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5126,22 +5126,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5390,22 +5390,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5654,22 +5654,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5918,22 +5918,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6002,10 +6002,10 @@
         <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD42" t="n">
         <v>0</v>
@@ -6050,22 +6050,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,13 +6086,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6134,10 +6134,10 @@
         <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
         <v>0</v>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6578,7 +6578,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G54" t="n">

--- a/jogos_2025-08-01.xlsx
+++ b/jogos_2025-08-01.xlsx
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rukh Vynnyky</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SK Poltava</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1112,10 +1112,10 @@
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -1166,22 +1166,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Rukh Vynnyky</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mariehamn</t>
+          <t>SK Poltava</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1244,10 +1244,10 @@
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3146,22 +3146,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3278,22 +3278,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.39</v>
+        <v>2.32</v>
       </c>
       <c r="M27" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="N27" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4028,10 +4028,10 @@
         <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
         <v>0</v>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4154,10 +4154,10 @@
         <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
         <v>0</v>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="M30" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N30" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4418,10 +4418,10 @@
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD30" t="n">
         <v>0</v>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,13 +4502,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4556,10 +4556,10 @@
         <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF31" t="n">
         <v>0</v>
@@ -4598,22 +4598,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4862,22 +4862,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5390,22 +5390,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5654,22 +5654,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8030,7 +8030,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G59" t="n">

--- a/jogos_2025-08-01.xlsx
+++ b/jogos_2025-08-01.xlsx
@@ -902,7 +902,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Smorgon</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Dinamo Minsk</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mariehamn</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1166,22 +1166,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rukh Vynnyky</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SK Poltava</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1244,10 +1244,10 @@
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
@@ -1298,22 +1298,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Smorgon</t>
+          <t>Rukh Vynnyky</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dinamo Minsk</t>
+          <t>SK Poltava</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1376,10 +1376,10 @@
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.18</v>
+        <v>1.43</v>
       </c>
       <c r="M11" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="N11" t="n">
-        <v>3.1</v>
+        <v>7.4</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3104,10 +3104,10 @@
         <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -3146,22 +3146,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3278,22 +3278,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4154,10 +4154,10 @@
         <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD28" t="n">
         <v>0</v>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,13 +4238,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.95</v>
+        <v>2.39</v>
       </c>
       <c r="M29" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="N29" t="n">
-        <v>2.29</v>
+        <v>2.6</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4286,16 +4286,16 @@
         <v>0</v>
       </c>
       <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE29" t="n">
         <v>1.7</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>0</v>
       </c>
       <c r="AF29" t="n">
         <v>0</v>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,13 +4502,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4556,10 +4556,10 @@
         <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
         <v>0</v>
@@ -4598,22 +4598,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5390,22 +5390,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5654,22 +5654,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5786,22 +5786,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5918,22 +5918,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6002,10 +6002,10 @@
         <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
         <v>0</v>
@@ -6050,22 +6050,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,13 +6086,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6134,10 +6134,10 @@
         <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD43" t="n">
         <v>0</v>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G57" t="n">

--- a/jogos_2025-08-01.xlsx
+++ b/jogos_2025-08-01.xlsx
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Rukh Vynnyky</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>SK Poltava</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1112,10 +1112,10 @@
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mariehamn</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rukh Vynnyky</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SK Poltava</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1376,10 +1376,10 @@
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4598,22 +4598,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4862,22 +4862,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5654,22 +5654,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5786,22 +5786,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5918,22 +5918,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6002,10 +6002,10 @@
         <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD42" t="n">
         <v>0</v>
@@ -6050,22 +6050,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,13 +6086,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6134,10 +6134,10 @@
         <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
         <v>0</v>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8030,7 +8030,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G59" t="n">

--- a/jogos_2025-08-01.xlsx
+++ b/jogos_2025-08-01.xlsx
@@ -902,22 +902,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Smorgon</t>
+          <t>Rukh Vynnyky</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dinamo Minsk</t>
+          <t>SK Poltava</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -980,10 +980,10 @@
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rukh Vynnyky</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SK Poltava</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1112,10 +1112,10 @@
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Smorgon</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mariehamn</t>
+          <t>Dinamo Minsk</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3146,22 +3146,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3278,22 +3278,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.32</v>
+        <v>2.39</v>
       </c>
       <c r="M27" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="N27" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4028,10 +4028,10 @@
         <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF27" t="n">
         <v>0</v>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.95</v>
+        <v>2.32</v>
       </c>
       <c r="M28" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N28" t="n">
-        <v>2.29</v>
+        <v>2.9</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4154,10 +4154,10 @@
         <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
         <v>0</v>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,13 +4238,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.39</v>
+        <v>2.95</v>
       </c>
       <c r="M29" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="N29" t="n">
-        <v>2.6</v>
+        <v>2.29</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4286,16 +4286,16 @@
         <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
         <v>0</v>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4418,10 +4418,10 @@
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
         <v>0</v>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,13 +4502,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4550,10 +4550,10 @@
         <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD31" t="n">
         <v>0</v>
@@ -4598,22 +4598,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4862,22 +4862,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4994,22 +4994,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5258,22 +5258,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5654,7 +5654,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8030,7 +8030,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G59" t="n">

--- a/jogos_2025-08-01.xlsx
+++ b/jogos_2025-08-01.xlsx
@@ -902,22 +902,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rukh Vynnyky</t>
+          <t>Smorgon</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SK Poltava</t>
+          <t>Dinamo Minsk</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -980,10 +980,10 @@
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1166,22 +1166,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Rukh Vynnyky</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mariehamn</t>
+          <t>SK Poltava</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1244,10 +1244,10 @@
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Smorgon</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dinamo Minsk</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,10 +2702,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3146,22 +3146,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3278,22 +3278,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.32</v>
+        <v>2.95</v>
       </c>
       <c r="M28" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N28" t="n">
-        <v>2.9</v>
+        <v>2.29</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4154,10 +4154,10 @@
         <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD28" t="n">
         <v>0</v>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,13 +4238,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.95</v>
+        <v>2.28</v>
       </c>
       <c r="M29" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="N29" t="n">
-        <v>2.29</v>
+        <v>3.05</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4286,10 +4286,10 @@
         <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.7</v>
+        <v>2.39</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.95</v>
+        <v>1.58</v>
       </c>
       <c r="AD29" t="n">
         <v>0</v>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,13 +4502,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4550,10 +4550,10 @@
         <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
         <v>0</v>
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5258,22 +5258,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5522,22 +5522,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5654,7 +5654,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5918,22 +5918,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6002,10 +6002,10 @@
         <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
         <v>0</v>
@@ -6050,22 +6050,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,13 +6086,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6134,10 +6134,10 @@
         <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD43" t="n">
         <v>0</v>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G57" t="n">

--- a/jogos_2025-08-01.xlsx
+++ b/jogos_2025-08-01.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL62"/>
+  <dimension ref="A1:AL64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -770,22 +770,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -897,12 +897,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Smorgon</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dinamo Minsk</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="AL4" s="3" t="n">
-        <v>45870.5</v>
+        <v>45870.45833333334</v>
       </c>
     </row>
     <row r="5">
@@ -1029,27 +1029,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mariehamn</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1152,7 +1152,7 @@
         </is>
       </c>
       <c r="AL5" s="3" t="n">
-        <v>45870.5</v>
+        <v>45870.45833333334</v>
       </c>
     </row>
     <row r="6">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>BATE</t>
+          <t>Smorgon</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitebsk</t>
+          <t>Dinamo Minsk</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="AL8" s="3" t="n">
-        <v>45870.51041666666</v>
+        <v>45870.5</v>
       </c>
     </row>
     <row r="9">
@@ -1557,27 +1557,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="AL9" s="3" t="n">
-        <v>45870.52083333334</v>
+        <v>45870.5</v>
       </c>
     </row>
     <row r="10">
@@ -1689,27 +1689,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>BATE</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Vitebsk</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="AL10" s="3" t="n">
-        <v>45870.54166666666</v>
+        <v>45870.51041666666</v>
       </c>
     </row>
     <row r="11">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="AL11" s="3" t="n">
-        <v>45870.54166666666</v>
+        <v>45870.52083333334</v>
       </c>
     </row>
     <row r="12">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.43</v>
+        <v>2.18</v>
       </c>
       <c r="M17" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="N17" t="n">
-        <v>7.4</v>
+        <v>3.1</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,10 +2702,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3009,27 +3009,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3104,10 +3104,10 @@
         <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="AL20" s="3" t="n">
-        <v>45870.5625</v>
+        <v>45870.54166666666</v>
       </c>
     </row>
     <row r="21">
@@ -3141,27 +3141,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3264,7 +3264,7 @@
         </is>
       </c>
       <c r="AL21" s="3" t="n">
-        <v>45870.58333333334</v>
+        <v>45870.54166666666</v>
       </c>
     </row>
     <row r="22">
@@ -3273,27 +3273,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3368,10 +3368,10 @@
         <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF22" t="n">
         <v>0</v>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="AL22" s="3" t="n">
-        <v>45870.58333333334</v>
+        <v>45870.5625</v>
       </c>
     </row>
     <row r="23">
@@ -3405,12 +3405,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3528,7 +3528,7 @@
         </is>
       </c>
       <c r="AL23" s="3" t="n">
-        <v>45870.60416666666</v>
+        <v>45870.58333333334</v>
       </c>
     </row>
     <row r="24">
@@ -3537,27 +3537,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3660,7 +3660,7 @@
         </is>
       </c>
       <c r="AL24" s="3" t="n">
-        <v>45870.625</v>
+        <v>45870.58333333334</v>
       </c>
     </row>
     <row r="25">
@@ -3669,12 +3669,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3792,7 +3792,7 @@
         </is>
       </c>
       <c r="AL25" s="3" t="n">
-        <v>45870.625</v>
+        <v>45870.60416666666</v>
       </c>
     </row>
     <row r="26">
@@ -3801,12 +3801,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="AL26" s="3" t="n">
-        <v>45870.63541666666</v>
+        <v>45870.625</v>
       </c>
     </row>
     <row r="27">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4028,10 +4028,10 @@
         <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
         <v>0</v>
@@ -4056,7 +4056,7 @@
         </is>
       </c>
       <c r="AL27" s="3" t="n">
-        <v>45870.64583333334</v>
+        <v>45870.625</v>
       </c>
     </row>
     <row r="28">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4154,10 +4154,10 @@
         <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
         <v>0</v>
@@ -4188,7 +4188,7 @@
         </is>
       </c>
       <c r="AL28" s="3" t="n">
-        <v>45870.64583333334</v>
+        <v>45870.63541666666</v>
       </c>
     </row>
     <row r="29">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.32</v>
+        <v>2.39</v>
       </c>
       <c r="M30" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="N30" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4424,10 +4424,10 @@
         <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF30" t="n">
         <v>0</v>
@@ -4593,27 +4593,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,13 +4634,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4682,10 +4682,10 @@
         <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD32" t="n">
         <v>0</v>
@@ -4716,7 +4716,7 @@
         </is>
       </c>
       <c r="AL32" s="3" t="n">
-        <v>45870.65625</v>
+        <v>45870.64583333334</v>
       </c>
     </row>
     <row r="33">
@@ -4725,27 +4725,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,13 +4766,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4848,7 +4848,7 @@
         </is>
       </c>
       <c r="AL33" s="3" t="n">
-        <v>45870.65625</v>
+        <v>45870.64583333334</v>
       </c>
     </row>
     <row r="34">
@@ -4862,22 +4862,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4994,22 +4994,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5522,22 +5522,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5654,22 +5654,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6036,7 +6036,7 @@
         </is>
       </c>
       <c r="AL42" s="3" t="n">
-        <v>45870.66666666666</v>
+        <v>45870.65625</v>
       </c>
     </row>
     <row r="43">
@@ -6045,27 +6045,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,13 +6086,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6134,10 +6134,10 @@
         <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
         <v>0</v>
@@ -6168,7 +6168,7 @@
         </is>
       </c>
       <c r="AL43" s="3" t="n">
-        <v>45870.66666666666</v>
+        <v>45870.65625</v>
       </c>
     </row>
     <row r="44">
@@ -6177,12 +6177,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6300,7 +6300,7 @@
         </is>
       </c>
       <c r="AL44" s="3" t="n">
-        <v>45870.79166666666</v>
+        <v>45870.66666666666</v>
       </c>
     </row>
     <row r="45">
@@ -6309,27 +6309,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6398,10 +6398,10 @@
         <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD45" t="n">
         <v>0</v>
@@ -6432,7 +6432,7 @@
         </is>
       </c>
       <c r="AL45" s="3" t="n">
-        <v>45870.79166666666</v>
+        <v>45870.66666666666</v>
       </c>
     </row>
     <row r="46">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7238,7 +7238,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7752,7 +7752,7 @@
         </is>
       </c>
       <c r="AL55" s="3" t="n">
-        <v>45870.83333333334</v>
+        <v>45870.79166666666</v>
       </c>
     </row>
     <row r="56">
@@ -7761,12 +7761,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7884,7 +7884,7 @@
         </is>
       </c>
       <c r="AL56" s="3" t="n">
-        <v>45870.875</v>
+        <v>45870.79166666666</v>
       </c>
     </row>
     <row r="57">
@@ -7893,12 +7893,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8016,7 +8016,7 @@
         </is>
       </c>
       <c r="AL57" s="3" t="n">
-        <v>45870.875</v>
+        <v>45870.83333333334</v>
       </c>
     </row>
     <row r="58">
@@ -8025,12 +8025,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8148,7 +8148,7 @@
         </is>
       </c>
       <c r="AL58" s="3" t="n">
-        <v>45870.89583333334</v>
+        <v>45870.875</v>
       </c>
     </row>
     <row r="59">
@@ -8157,12 +8157,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8280,7 +8280,7 @@
         </is>
       </c>
       <c r="AL59" s="3" t="n">
-        <v>45870.89583333334</v>
+        <v>45870.875</v>
       </c>
     </row>
     <row r="60">
@@ -8289,12 +8289,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8412,7 +8412,7 @@
         </is>
       </c>
       <c r="AL60" s="3" t="n">
-        <v>45870.91666666666</v>
+        <v>45870.89583333334</v>
       </c>
     </row>
     <row r="61">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8544,7 +8544,7 @@
         </is>
       </c>
       <c r="AL61" s="3" t="n">
-        <v>45870.95833333334</v>
+        <v>45870.89583333334</v>
       </c>
     </row>
     <row r="62">
@@ -8553,129 +8553,393 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Colorado Springs</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Lexington</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W62" t="n">
+        <v>0</v>
+      </c>
+      <c r="X62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL62" s="3" t="n">
+        <v>45870.91666666666</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Tacoma Defiance</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>LA Galaxy II</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" t="n">
+        <v>0</v>
+      </c>
+      <c r="W63" t="n">
+        <v>0</v>
+      </c>
+      <c r="X63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL63" s="3" t="n">
+        <v>45870.95833333334</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
           <t>23:30</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>Seattle Reign</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>Angel City</t>
         </is>
       </c>
-      <c r="G62" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" t="n">
-        <v>0</v>
-      </c>
-      <c r="K62" t="inlineStr">
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L62" t="n">
-        <v>0</v>
-      </c>
-      <c r="M62" t="n">
-        <v>0</v>
-      </c>
-      <c r="N62" t="n">
-        <v>0</v>
-      </c>
-      <c r="O62" t="n">
-        <v>0</v>
-      </c>
-      <c r="P62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
-      <c r="R62" t="n">
-        <v>0</v>
-      </c>
-      <c r="S62" t="n">
-        <v>0</v>
-      </c>
-      <c r="T62" t="n">
-        <v>0</v>
-      </c>
-      <c r="U62" t="n">
-        <v>0</v>
-      </c>
-      <c r="V62" t="n">
-        <v>0</v>
-      </c>
-      <c r="W62" t="n">
-        <v>0</v>
-      </c>
-      <c r="X62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL62" s="3" t="n">
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" t="n">
+        <v>0</v>
+      </c>
+      <c r="W64" t="n">
+        <v>0</v>
+      </c>
+      <c r="X64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL64" s="3" t="n">
         <v>45870.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-08-01.xlsx
+++ b/jogos_2025-08-01.xlsx
@@ -770,22 +770,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rukh Vynnyky</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SK Poltava</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1244,10 +1244,10 @@
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="AL6" s="3" t="n">
-        <v>45870.5</v>
+        <v>45870.45833333334</v>
       </c>
     </row>
     <row r="7">
@@ -1293,27 +1293,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1416,7 +1416,7 @@
         </is>
       </c>
       <c r="AL7" s="3" t="n">
-        <v>45870.5</v>
+        <v>45870.45833333334</v>
       </c>
     </row>
     <row r="8">
@@ -1425,27 +1425,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Smorgon</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dinamo Minsk</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="AL8" s="3" t="n">
-        <v>45870.5</v>
+        <v>45870.45833333334</v>
       </c>
     </row>
     <row r="9">
@@ -1557,27 +1557,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mariehamn</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="AL9" s="3" t="n">
-        <v>45870.5</v>
+        <v>45870.45833333334</v>
       </c>
     </row>
     <row r="10">
@@ -1689,27 +1689,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BATE</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitebsk</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="AL10" s="3" t="n">
-        <v>45870.51041666666</v>
+        <v>45870.45833333334</v>
       </c>
     </row>
     <row r="11">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="AL11" s="3" t="n">
-        <v>45870.52083333334</v>
+        <v>45870.45833333334</v>
       </c>
     </row>
     <row r="12">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Rukh Vynnyky</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>SK Poltava</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="AL12" s="3" t="n">
-        <v>45870.54166666666</v>
+        <v>45870.5</v>
       </c>
     </row>
     <row r="13">
@@ -2085,27 +2085,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2208,7 +2208,7 @@
         </is>
       </c>
       <c r="AL13" s="3" t="n">
-        <v>45870.54166666666</v>
+        <v>45870.5</v>
       </c>
     </row>
     <row r="14">
@@ -2217,27 +2217,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="AL14" s="3" t="n">
-        <v>45870.54166666666</v>
+        <v>45870.5</v>
       </c>
     </row>
     <row r="15">
@@ -2349,27 +2349,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Smorgon</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Dinamo Minsk</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2472,7 +2472,7 @@
         </is>
       </c>
       <c r="AL15" s="3" t="n">
-        <v>45870.54166666666</v>
+        <v>45870.5</v>
       </c>
     </row>
     <row r="16">
@@ -2481,27 +2481,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>BATE</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Vitebsk</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
         </is>
       </c>
       <c r="AL16" s="3" t="n">
-        <v>45870.54166666666</v>
+        <v>45870.51041666666</v>
       </c>
     </row>
     <row r="17">
@@ -2613,12 +2613,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="AL17" s="3" t="n">
-        <v>45870.54166666666</v>
+        <v>45870.52083333334</v>
       </c>
     </row>
     <row r="18">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3273,27 +3273,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3368,10 +3368,10 @@
         <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
         <v>0</v>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="AL22" s="3" t="n">
-        <v>45870.5625</v>
+        <v>45870.54166666666</v>
       </c>
     </row>
     <row r="23">
@@ -3405,27 +3405,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3500,10 +3500,10 @@
         <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
@@ -3528,7 +3528,7 @@
         </is>
       </c>
       <c r="AL23" s="3" t="n">
-        <v>45870.58333333334</v>
+        <v>45870.5625</v>
       </c>
     </row>
     <row r="24">
@@ -3669,12 +3669,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3792,7 +3792,7 @@
         </is>
       </c>
       <c r="AL25" s="3" t="n">
-        <v>45870.60416666666</v>
+        <v>45870.58333333334</v>
       </c>
     </row>
     <row r="26">
@@ -3801,12 +3801,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="AL26" s="3" t="n">
-        <v>45870.625</v>
+        <v>45870.60416666666</v>
       </c>
     </row>
     <row r="27">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4188,7 +4188,7 @@
         </is>
       </c>
       <c r="AL28" s="3" t="n">
-        <v>45870.63541666666</v>
+        <v>45870.625</v>
       </c>
     </row>
     <row r="29">
@@ -4197,12 +4197,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,13 +4238,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4286,10 +4286,10 @@
         <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
         <v>0</v>
@@ -4320,7 +4320,7 @@
         </is>
       </c>
       <c r="AL29" s="3" t="n">
-        <v>45870.64583333334</v>
+        <v>45870.63541666666</v>
       </c>
     </row>
     <row r="30">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,64 +4370,64 @@
         </is>
       </c>
       <c r="L30" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="M30" t="n">
+        <v>3</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
         <v>2.39</v>
       </c>
-      <c r="M30" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N30" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>0</v>
-      </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
         <v>0</v>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,13 +4634,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.95</v>
+        <v>2.32</v>
       </c>
       <c r="M32" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N32" t="n">
-        <v>2.29</v>
+        <v>2.9</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4682,10 +4682,10 @@
         <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
         <v>0</v>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,13 +4766,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.32</v>
+        <v>2.95</v>
       </c>
       <c r="M33" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N33" t="n">
-        <v>2.9</v>
+        <v>2.29</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4814,10 +4814,10 @@
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD33" t="n">
         <v>0</v>
@@ -4857,12 +4857,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,13 +4898,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4952,10 +4952,10 @@
         <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF34" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         </is>
       </c>
       <c r="AL34" s="3" t="n">
-        <v>45870.65625</v>
+        <v>45870.64583333334</v>
       </c>
     </row>
     <row r="35">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5654,22 +5654,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6050,22 +6050,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6177,27 +6177,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6300,7 +6300,7 @@
         </is>
       </c>
       <c r="AL44" s="3" t="n">
-        <v>45870.66666666666</v>
+        <v>45870.65625</v>
       </c>
     </row>
     <row r="45">
@@ -6441,12 +6441,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6564,7 +6564,7 @@
         </is>
       </c>
       <c r="AL46" s="3" t="n">
-        <v>45870.79166666666</v>
+        <v>45870.66666666666</v>
       </c>
     </row>
     <row r="47">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7893,12 +7893,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8016,7 +8016,7 @@
         </is>
       </c>
       <c r="AL57" s="3" t="n">
-        <v>45870.83333333334</v>
+        <v>45870.79166666666</v>
       </c>
     </row>
     <row r="58">
@@ -8025,12 +8025,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8148,7 +8148,7 @@
         </is>
       </c>
       <c r="AL58" s="3" t="n">
-        <v>45870.875</v>
+        <v>45870.83333333334</v>
       </c>
     </row>
     <row r="59">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8289,12 +8289,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8412,7 +8412,7 @@
         </is>
       </c>
       <c r="AL60" s="3" t="n">
-        <v>45870.89583333334</v>
+        <v>45870.875</v>
       </c>
     </row>
     <row r="61">

--- a/jogos_2025-08-01.xlsx
+++ b/jogos_2025-08-01.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL64"/>
+  <dimension ref="A1:AL65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -674,13 +674,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.44</v>
+        <v>2.59</v>
       </c>
       <c r="M2" t="n">
-        <v>2.85</v>
+        <v>3.45</v>
       </c>
       <c r="N2" t="n">
-        <v>2.95</v>
+        <v>2.54</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -770,22 +770,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1161,27 +1161,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="AL6" s="3" t="n">
-        <v>45870.45833333334</v>
+        <v>45870.5</v>
       </c>
     </row>
     <row r="7">
@@ -1293,27 +1293,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1416,7 +1416,7 @@
         </is>
       </c>
       <c r="AL7" s="3" t="n">
-        <v>45870.45833333334</v>
+        <v>45870.5</v>
       </c>
     </row>
     <row r="8">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Rukh Vynnyky</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>SK Poltava</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.63</v>
+        <v>1.65</v>
       </c>
       <c r="M8" t="n">
-        <v>3.52</v>
+        <v>3.41</v>
       </c>
       <c r="N8" t="n">
-        <v>2.5</v>
+        <v>5.9</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1508,10 +1508,10 @@
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="AL8" s="3" t="n">
-        <v>45870.45833333334</v>
+        <v>45870.5</v>
       </c>
     </row>
     <row r="9">
@@ -1557,27 +1557,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Smorgon</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Dinamo Minsk</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="AL9" s="3" t="n">
-        <v>45870.45833333334</v>
+        <v>45870.5</v>
       </c>
     </row>
     <row r="10">
@@ -1689,27 +1689,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>BATE</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Vitebsk</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="AL10" s="3" t="n">
-        <v>45870.45833333334</v>
+        <v>45870.51041666666</v>
       </c>
     </row>
     <row r="11">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="AL11" s="3" t="n">
-        <v>45870.45833333334</v>
+        <v>45870.52083333334</v>
       </c>
     </row>
     <row r="12">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rukh Vynnyky</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>SK Poltava</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="AL12" s="3" t="n">
-        <v>45870.5</v>
+        <v>45870.54166666666</v>
       </c>
     </row>
     <row r="13">
@@ -2085,27 +2085,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2208,7 +2208,7 @@
         </is>
       </c>
       <c r="AL13" s="3" t="n">
-        <v>45870.5</v>
+        <v>45870.54166666666</v>
       </c>
     </row>
     <row r="14">
@@ -2217,27 +2217,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mariehamn</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="AL14" s="3" t="n">
-        <v>45870.5</v>
+        <v>45870.54166666666</v>
       </c>
     </row>
     <row r="15">
@@ -2349,27 +2349,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Smorgon</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dinamo Minsk</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
         </is>
       </c>
       <c r="AL15" s="3" t="n">
-        <v>45870.5</v>
+        <v>45870.54166666666</v>
       </c>
     </row>
     <row r="16">
@@ -2481,27 +2481,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>BATE</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitebsk</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="M16" t="n">
-        <v>3.28</v>
+        <v>3.35</v>
       </c>
       <c r="N16" t="n">
-        <v>3.46</v>
+        <v>2.85</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
         </is>
       </c>
       <c r="AL16" s="3" t="n">
-        <v>45870.51041666666</v>
+        <v>45870.54166666666</v>
       </c>
     </row>
     <row r="17">
@@ -2613,12 +2613,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,10 +2702,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="AL17" s="3" t="n">
-        <v>45870.52083333334</v>
+        <v>45870.54166666666</v>
       </c>
     </row>
     <row r="18">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.43</v>
+        <v>2.65</v>
       </c>
       <c r="M18" t="n">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="N18" t="n">
-        <v>7.4</v>
+        <v>2.49</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.96</v>
+        <v>1.76</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3273,27 +3273,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3368,10 +3368,10 @@
         <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF22" t="n">
         <v>0</v>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="AL22" s="3" t="n">
-        <v>45870.54166666666</v>
+        <v>45870.5625</v>
       </c>
     </row>
     <row r="23">
@@ -3405,27 +3405,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3500,10 +3500,10 @@
         <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
@@ -3528,7 +3528,7 @@
         </is>
       </c>
       <c r="AL23" s="3" t="n">
-        <v>45870.5625</v>
+        <v>45870.58333333334</v>
       </c>
     </row>
     <row r="24">
@@ -3669,12 +3669,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3792,7 +3792,7 @@
         </is>
       </c>
       <c r="AL25" s="3" t="n">
-        <v>45870.58333333334</v>
+        <v>45870.60416666666</v>
       </c>
     </row>
     <row r="26">
@@ -3801,12 +3801,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="AL26" s="3" t="n">
-        <v>45870.60416666666</v>
+        <v>45870.625</v>
       </c>
     </row>
     <row r="27">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.28</v>
+        <v>2.99</v>
       </c>
       <c r="M30" t="n">
-        <v>3</v>
+        <v>3.21</v>
       </c>
       <c r="N30" t="n">
-        <v>3.05</v>
+        <v>2.36</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4418,16 +4418,16 @@
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF30" t="n">
         <v>0</v>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,13 +4502,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4550,10 +4550,10 @@
         <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD31" t="n">
         <v>0</v>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,13 +4634,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="M32" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="N32" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4682,10 +4682,10 @@
         <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD32" t="n">
         <v>0</v>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,13 +4766,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.95</v>
+        <v>2.27</v>
       </c>
       <c r="M33" t="n">
-        <v>3.3</v>
+        <v>2.99</v>
       </c>
       <c r="N33" t="n">
-        <v>2.29</v>
+        <v>2.9</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4814,10 +4814,10 @@
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
         <v>0</v>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,13 +4898,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4952,10 +4952,10 @@
         <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
         <v>0</v>
@@ -4994,22 +4994,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5210,10 +5210,10 @@
         <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,13 +5558,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5786,22 +5786,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6002,10 +6002,10 @@
         <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD42" t="n">
         <v>0</v>
@@ -6050,22 +6050,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6182,22 +6182,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6218,13 +6218,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6314,22 +6314,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6398,10 +6398,10 @@
         <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
         <v>0</v>
@@ -6446,22 +6446,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6482,13 +6482,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6530,10 +6530,10 @@
         <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD46" t="n">
         <v>0</v>
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7238,7 +7238,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7370,7 +7370,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8246,10 +8246,10 @@
         <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC59" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD59" t="n">
         <v>0</v>
@@ -8330,13 +8330,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8378,10 +8378,10 @@
         <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC60" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD60" t="n">
         <v>0</v>
@@ -8426,7 +8426,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8553,7 +8553,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8594,13 +8594,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8642,10 +8642,10 @@
         <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC62" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AD62" t="n">
         <v>0</v>
@@ -8676,7 +8676,7 @@
         </is>
       </c>
       <c r="AL62" s="3" t="n">
-        <v>45870.91666666666</v>
+        <v>45870.89583333334</v>
       </c>
     </row>
     <row r="63">
@@ -8685,12 +8685,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8726,13 +8726,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8774,10 +8774,10 @@
         <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC63" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD63" t="n">
         <v>0</v>
@@ -8808,7 +8808,7 @@
         </is>
       </c>
       <c r="AL63" s="3" t="n">
-        <v>45870.95833333334</v>
+        <v>45870.91666666666</v>
       </c>
     </row>
     <row r="64">
@@ -8817,129 +8817,261 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Tacoma Defiance</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>LA Galaxy II</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" t="n">
+        <v>0</v>
+      </c>
+      <c r="W64" t="n">
+        <v>0</v>
+      </c>
+      <c r="X64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL64" s="3" t="n">
+        <v>45870.95833333334</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
           <t>23:30</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>Seattle Reign</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>Angel City</t>
         </is>
       </c>
-      <c r="G64" t="n">
-        <v>0</v>
-      </c>
-      <c r="H64" t="n">
-        <v>0</v>
-      </c>
-      <c r="I64" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" t="n">
-        <v>0</v>
-      </c>
-      <c r="K64" t="inlineStr">
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L64" t="n">
-        <v>0</v>
-      </c>
-      <c r="M64" t="n">
-        <v>0</v>
-      </c>
-      <c r="N64" t="n">
-        <v>0</v>
-      </c>
-      <c r="O64" t="n">
-        <v>0</v>
-      </c>
-      <c r="P64" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
-      <c r="R64" t="n">
-        <v>0</v>
-      </c>
-      <c r="S64" t="n">
-        <v>0</v>
-      </c>
-      <c r="T64" t="n">
-        <v>0</v>
-      </c>
-      <c r="U64" t="n">
-        <v>0</v>
-      </c>
-      <c r="V64" t="n">
-        <v>0</v>
-      </c>
-      <c r="W64" t="n">
-        <v>0</v>
-      </c>
-      <c r="X64" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y64" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL64" s="3" t="n">
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
+      </c>
+      <c r="V65" t="n">
+        <v>0</v>
+      </c>
+      <c r="W65" t="n">
+        <v>0</v>
+      </c>
+      <c r="X65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL65" s="3" t="n">
         <v>45870.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-08-01.xlsx
+++ b/jogos_2025-08-01.xlsx
@@ -770,22 +770,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Smorgon</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mariehamn</t>
+          <t>Dinamo Minsk</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Smorgon</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dinamo Minsk</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.78</v>
+        <v>3.8</v>
       </c>
       <c r="M13" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="N13" t="n">
-        <v>3.75</v>
+        <v>1.8</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>9.199999999999999</v>
+        <v>1.78</v>
       </c>
       <c r="M14" t="n">
-        <v>5.6</v>
+        <v>4</v>
       </c>
       <c r="N14" t="n">
-        <v>1.27</v>
+        <v>3.75</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.3</v>
+        <v>1.45</v>
       </c>
       <c r="M16" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="N16" t="n">
-        <v>2.85</v>
+        <v>6.3</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,10 +2702,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.45</v>
+        <v>2.13</v>
       </c>
       <c r="M20" t="n">
-        <v>3.7</v>
+        <v>3.17</v>
       </c>
       <c r="N20" t="n">
-        <v>6.3</v>
+        <v>2.99</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3410,22 +3410,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3542,22 +3542,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.99</v>
+        <v>2.88</v>
       </c>
       <c r="M30" t="n">
-        <v>3.21</v>
+        <v>2.96</v>
       </c>
       <c r="N30" t="n">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4418,16 +4418,16 @@
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
         <v>0</v>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,13 +4502,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.88</v>
+        <v>2.24</v>
       </c>
       <c r="M31" t="n">
         <v>2.96</v>
       </c>
       <c r="N31" t="n">
-        <v>2.31</v>
+        <v>2.98</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4550,10 +4550,10 @@
         <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.7</v>
+        <v>2.39</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.95</v>
+        <v>1.58</v>
       </c>
       <c r="AD31" t="n">
         <v>0</v>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,13 +4634,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.24</v>
+        <v>2.99</v>
       </c>
       <c r="M32" t="n">
-        <v>2.96</v>
+        <v>3.21</v>
       </c>
       <c r="N32" t="n">
-        <v>2.98</v>
+        <v>2.36</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4682,16 +4682,16 @@
         <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF32" t="n">
         <v>0</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5210,10 +5210,10 @@
         <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,13 +5426,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5474,10 +5474,10 @@
         <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5786,22 +5786,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.51</v>
+        <v>2.85</v>
       </c>
       <c r="M42" t="n">
-        <v>3.85</v>
+        <v>3.15</v>
       </c>
       <c r="N42" t="n">
-        <v>5.8</v>
+        <v>2.31</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6002,10 +6002,10 @@
         <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
         <v>0</v>
@@ -6050,22 +6050,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6218,13 +6218,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.85</v>
+        <v>1.51</v>
       </c>
       <c r="M44" t="n">
-        <v>3.15</v>
+        <v>3.85</v>
       </c>
       <c r="N44" t="n">
-        <v>2.31</v>
+        <v>5.8</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6266,10 +6266,10 @@
         <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD44" t="n">
         <v>0</v>
@@ -6314,22 +6314,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6398,10 +6398,10 @@
         <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD45" t="n">
         <v>0</v>
@@ -6446,22 +6446,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6482,13 +6482,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6530,10 +6530,10 @@
         <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
         <v>0</v>
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7370,7 +7370,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="M59" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="N59" t="n">
-        <v>1.84</v>
+        <v>1.52</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8246,10 +8246,10 @@
         <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="AC59" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="AD59" t="n">
         <v>0</v>
@@ -8304,12 +8304,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8330,13 +8330,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="M60" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="N60" t="n">
-        <v>1.52</v>
+        <v>1.84</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8378,10 +8378,10 @@
         <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="AC60" t="n">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="AD60" t="n">
         <v>0</v>
@@ -8426,7 +8426,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8462,13 +8462,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8510,10 +8510,10 @@
         <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC61" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AD61" t="n">
         <v>0</v>
@@ -8558,7 +8558,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8594,13 +8594,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8642,10 +8642,10 @@
         <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AD62" t="n">
         <v>0</v>

--- a/jogos_2025-08-01.xlsx
+++ b/jogos_2025-08-01.xlsx
@@ -770,22 +770,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>9.199999999999999</v>
+        <v>2.3</v>
       </c>
       <c r="M12" t="n">
-        <v>5.6</v>
+        <v>3.35</v>
       </c>
       <c r="N12" t="n">
-        <v>1.27</v>
+        <v>2.85</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>3.85</v>
+        <v>5.6</v>
       </c>
       <c r="N13" t="n">
-        <v>1.8</v>
+        <v>1.27</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.78</v>
+        <v>3.8</v>
       </c>
       <c r="M14" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="N14" t="n">
-        <v>3.75</v>
+        <v>1.8</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.65</v>
+        <v>1.45</v>
       </c>
       <c r="M18" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="N18" t="n">
-        <v>2.49</v>
+        <v>6.3</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3410,22 +3410,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3542,22 +3542,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
       <c r="M30" t="n">
-        <v>2.96</v>
+        <v>3.21</v>
       </c>
       <c r="N30" t="n">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4418,16 +4418,16 @@
         <v>0</v>
       </c>
       <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE30" t="n">
         <v>1.7</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>0</v>
       </c>
       <c r="AF30" t="n">
         <v>0</v>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,13 +4502,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.24</v>
+        <v>2.88</v>
       </c>
       <c r="M31" t="n">
         <v>2.96</v>
       </c>
       <c r="N31" t="n">
-        <v>2.98</v>
+        <v>2.31</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4550,10 +4550,10 @@
         <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.39</v>
+        <v>1.7</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="AD31" t="n">
         <v>0</v>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,13 +4634,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.99</v>
+        <v>2.24</v>
       </c>
       <c r="M32" t="n">
-        <v>3.21</v>
+        <v>2.96</v>
       </c>
       <c r="N32" t="n">
-        <v>2.36</v>
+        <v>2.98</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4682,16 +4682,16 @@
         <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
         <v>0</v>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,13 +4766,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,13 +4898,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4994,22 +4994,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,13 +5030,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5078,10 +5078,10 @@
         <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AD35" t="n">
         <v>0</v>
@@ -5126,22 +5126,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,13 +5426,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5474,10 +5474,10 @@
         <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,13 +5558,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.06</v>
+        <v>1.51</v>
       </c>
       <c r="M39" t="n">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="N39" t="n">
-        <v>3.15</v>
+        <v>5.8</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5606,10 +5606,10 @@
         <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD39" t="n">
         <v>0</v>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,13 +5690,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,13 +5822,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6218,13 +6218,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6266,10 +6266,10 @@
         <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
         <v>0</v>
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8462,13 +8462,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8510,10 +8510,10 @@
         <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AD61" t="n">
         <v>0</v>
@@ -8558,7 +8558,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8594,13 +8594,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8642,10 +8642,10 @@
         <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC62" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AD62" t="n">
         <v>0</v>

--- a/jogos_2025-08-01.xlsx
+++ b/jogos_2025-08-01.xlsx
@@ -902,22 +902,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Smorgon</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Dinamo Minsk</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Smorgon</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dinamo Minsk</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1646,10 +1646,10 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>9.199999999999999</v>
+        <v>2.13</v>
       </c>
       <c r="M13" t="n">
-        <v>5.6</v>
+        <v>3.17</v>
       </c>
       <c r="N13" t="n">
-        <v>1.27</v>
+        <v>2.99</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.8</v>
+        <v>1.45</v>
       </c>
       <c r="M14" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="N14" t="n">
-        <v>1.8</v>
+        <v>6.3</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.45</v>
+        <v>3.8</v>
       </c>
       <c r="M18" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="N18" t="n">
-        <v>6.3</v>
+        <v>1.8</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.13</v>
+        <v>1.78</v>
       </c>
       <c r="M20" t="n">
-        <v>3.17</v>
+        <v>4</v>
       </c>
       <c r="N20" t="n">
-        <v>2.99</v>
+        <v>3.75</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.99</v>
+        <v>2.24</v>
       </c>
       <c r="M30" t="n">
-        <v>3.21</v>
+        <v>2.96</v>
       </c>
       <c r="N30" t="n">
-        <v>2.36</v>
+        <v>2.98</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4418,16 +4418,16 @@
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
         <v>0</v>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,13 +4502,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4550,10 +4550,10 @@
         <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
         <v>0</v>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,13 +4634,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="M32" t="n">
-        <v>2.96</v>
+        <v>2.99</v>
       </c>
       <c r="N32" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4682,10 +4682,10 @@
         <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
         <v>0</v>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,13 +4766,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4814,16 +4814,16 @@
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF33" t="n">
         <v>0</v>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,13 +4898,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.27</v>
+        <v>2.88</v>
       </c>
       <c r="M34" t="n">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="N34" t="n">
-        <v>2.9</v>
+        <v>2.31</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4946,10 +4946,10 @@
         <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD34" t="n">
         <v>0</v>
@@ -5126,22 +5126,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5390,22 +5390,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,13 +5558,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5606,10 +5606,10 @@
         <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
         <v>0</v>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,13 +5822,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.06</v>
+        <v>1.51</v>
       </c>
       <c r="M41" t="n">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="N41" t="n">
-        <v>3.15</v>
+        <v>5.8</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5870,10 +5870,10 @@
         <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD41" t="n">
         <v>0</v>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="M59" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="N59" t="n">
-        <v>1.52</v>
+        <v>1.84</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8246,10 +8246,10 @@
         <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="AC59" t="n">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="AD59" t="n">
         <v>0</v>
@@ -8304,12 +8304,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8330,13 +8330,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="M60" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="N60" t="n">
-        <v>1.84</v>
+        <v>1.52</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8378,10 +8378,10 @@
         <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="AC60" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="AD60" t="n">
         <v>0</v>

--- a/jogos_2025-08-01.xlsx
+++ b/jogos_2025-08-01.xlsx
@@ -1298,22 +1298,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Rukh Vynnyky</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>SK Poltava</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1376,10 +1376,10 @@
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rukh Vynnyky</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SK Poltava</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1508,10 +1508,10 @@
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.13</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>3.17</v>
+        <v>5.6</v>
       </c>
       <c r="N13" t="n">
-        <v>2.99</v>
+        <v>1.27</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.45</v>
+        <v>2.13</v>
       </c>
       <c r="M14" t="n">
-        <v>3.7</v>
+        <v>3.17</v>
       </c>
       <c r="N14" t="n">
-        <v>6.3</v>
+        <v>2.99</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.8</v>
+        <v>1.78</v>
       </c>
       <c r="M18" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="N18" t="n">
-        <v>1.8</v>
+        <v>3.75</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3410,22 +3410,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3494,10 +3494,10 @@
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -3542,22 +3542,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.24</v>
+        <v>2.88</v>
       </c>
       <c r="M30" t="n">
         <v>2.96</v>
       </c>
       <c r="N30" t="n">
-        <v>2.98</v>
+        <v>2.31</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4418,10 +4418,10 @@
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.39</v>
+        <v>1.7</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="AD30" t="n">
         <v>0</v>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,13 +4634,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="M32" t="n">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="N32" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4682,10 +4682,10 @@
         <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD32" t="n">
         <v>0</v>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,13 +4766,13 @@
         </is>
       </c>
       <c r="L33" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="M33" t="n">
         <v>2.99</v>
       </c>
-      <c r="M33" t="n">
-        <v>3.21</v>
-      </c>
       <c r="N33" t="n">
-        <v>2.36</v>
+        <v>2.9</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4814,16 +4814,16 @@
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
         <v>0</v>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,13 +4898,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
       <c r="M34" t="n">
-        <v>2.96</v>
+        <v>3.21</v>
       </c>
       <c r="N34" t="n">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4946,16 +4946,16 @@
         <v>0</v>
       </c>
       <c r="AB34" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE34" t="n">
         <v>1.7</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>0</v>
       </c>
       <c r="AF34" t="n">
         <v>0</v>
@@ -4994,22 +4994,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,13 +5030,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5078,10 +5078,10 @@
         <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
         <v>0</v>
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5258,22 +5258,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5390,22 +5390,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,13 +5426,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,13 +5558,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5606,10 +5606,10 @@
         <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AD39" t="n">
         <v>0</v>
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,10 +5690,10 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="M40" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="N40" t="n">
         <v>3.15</v>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,13 +5822,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5870,10 +5870,10 @@
         <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
         <v>0</v>
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6050,22 +6050,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,13 +6086,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6218,13 +6218,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6266,10 +6266,10 @@
         <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD44" t="n">
         <v>0</v>
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8462,13 +8462,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8510,10 +8510,10 @@
         <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC61" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AD61" t="n">
         <v>0</v>
@@ -8558,7 +8558,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8594,13 +8594,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8642,10 +8642,10 @@
         <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AD62" t="n">
         <v>0</v>

--- a/jogos_2025-08-01.xlsx
+++ b/jogos_2025-08-01.xlsx
@@ -770,22 +770,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -902,22 +902,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Smorgon</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dinamo Minsk</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Smorgon</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mariehamn</t>
+          <t>Dinamo Minsk</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1646,10 +1646,10 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.45</v>
+        <v>1.78</v>
       </c>
       <c r="M12" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="N12" t="n">
-        <v>6.3</v>
+        <v>3.75</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.13</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>3.17</v>
+        <v>5.6</v>
       </c>
       <c r="N14" t="n">
-        <v>2.99</v>
+        <v>1.27</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="M17" t="n">
-        <v>3.85</v>
+        <v>3.35</v>
       </c>
       <c r="N17" t="n">
-        <v>1.8</v>
+        <v>2.85</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.78</v>
+        <v>2.65</v>
       </c>
       <c r="M18" t="n">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="N18" t="n">
-        <v>3.75</v>
+        <v>2.49</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="M19" t="n">
-        <v>3.35</v>
+        <v>3.17</v>
       </c>
       <c r="N19" t="n">
-        <v>2.85</v>
+        <v>2.99</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,13 +4634,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.24</v>
+        <v>2.99</v>
       </c>
       <c r="M32" t="n">
-        <v>2.96</v>
+        <v>3.21</v>
       </c>
       <c r="N32" t="n">
-        <v>2.98</v>
+        <v>2.36</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4682,16 +4682,16 @@
         <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.39</v>
+        <v>1.53</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.58</v>
+        <v>2.35</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF32" t="n">
         <v>0</v>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,13 +4766,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="M33" t="n">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="N33" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4814,10 +4814,10 @@
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD33" t="n">
         <v>0</v>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,13 +4898,13 @@
         </is>
       </c>
       <c r="L34" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="M34" t="n">
         <v>2.99</v>
       </c>
-      <c r="M34" t="n">
-        <v>3.21</v>
-      </c>
       <c r="N34" t="n">
-        <v>2.36</v>
+        <v>2.9</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4946,16 +4946,16 @@
         <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
         <v>0</v>
@@ -4994,22 +4994,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5258,22 +5258,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,13 +5426,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2</v>
+        <v>1.51</v>
       </c>
       <c r="M38" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="N38" t="n">
-        <v>3.15</v>
+        <v>5.8</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5474,10 +5474,10 @@
         <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,13 +5558,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5606,10 +5606,10 @@
         <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
         <v>0</v>
@@ -5654,22 +5654,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,13 +5690,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,13 +5822,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5870,10 +5870,10 @@
         <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AD41" t="n">
         <v>0</v>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6050,22 +6050,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,13 +6086,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6218,13 +6218,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.51</v>
+        <v>2.06</v>
       </c>
       <c r="M44" t="n">
-        <v>3.85</v>
+        <v>3.35</v>
       </c>
       <c r="N44" t="n">
-        <v>5.8</v>
+        <v>3.15</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6266,10 +6266,10 @@
         <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
         <v>0</v>
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7370,7 +7370,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8462,13 +8462,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8510,10 +8510,10 @@
         <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AD61" t="n">
         <v>0</v>
@@ -8558,7 +8558,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8594,13 +8594,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8642,10 +8642,10 @@
         <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC62" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AD62" t="n">
         <v>0</v>

--- a/jogos_2025-08-01.xlsx
+++ b/jogos_2025-08-01.xlsx
@@ -770,22 +770,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Smorgon</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Dinamo Minsk</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mariehamn</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Smorgon</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dinamo Minsk</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1646,10 +1646,10 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.8</v>
+        <v>2.13</v>
       </c>
       <c r="M15" t="n">
-        <v>3.85</v>
+        <v>3.17</v>
       </c>
       <c r="N15" t="n">
-        <v>1.8</v>
+        <v>2.99</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.65</v>
+        <v>1.45</v>
       </c>
       <c r="M18" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="N18" t="n">
-        <v>2.49</v>
+        <v>6.3</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.13</v>
+        <v>3.8</v>
       </c>
       <c r="M19" t="n">
-        <v>3.17</v>
+        <v>3.85</v>
       </c>
       <c r="N19" t="n">
-        <v>2.99</v>
+        <v>1.8</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.45</v>
+        <v>1.78</v>
       </c>
       <c r="M20" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="N20" t="n">
-        <v>6.3</v>
+        <v>3.75</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3410,22 +3410,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3494,10 +3494,10 @@
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -3542,22 +3542,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.88</v>
+        <v>2.27</v>
       </c>
       <c r="M30" t="n">
-        <v>2.96</v>
+        <v>2.99</v>
       </c>
       <c r="N30" t="n">
-        <v>2.31</v>
+        <v>2.9</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4418,10 +4418,10 @@
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
         <v>0</v>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,13 +4502,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4550,16 +4550,16 @@
         <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF31" t="n">
         <v>0</v>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,13 +4634,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4682,16 +4682,16 @@
         <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
         <v>0</v>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,13 +4766,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.24</v>
+        <v>2.88</v>
       </c>
       <c r="M33" t="n">
         <v>2.96</v>
       </c>
       <c r="N33" t="n">
-        <v>2.98</v>
+        <v>2.31</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4814,10 +4814,10 @@
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.39</v>
+        <v>1.7</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="AD33" t="n">
         <v>0</v>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,13 +4898,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="M34" t="n">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="N34" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4946,10 +4946,10 @@
         <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD34" t="n">
         <v>0</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,13 +5030,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5126,22 +5126,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,13 +5426,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5474,10 +5474,10 @@
         <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5654,22 +5654,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,10 +5954,10 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="M42" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="N42" t="n">
         <v>3.15</v>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6218,13 +6218,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.06</v>
+        <v>1.51</v>
       </c>
       <c r="M44" t="n">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="N44" t="n">
-        <v>3.15</v>
+        <v>5.8</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6266,10 +6266,10 @@
         <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD44" t="n">
         <v>0</v>
@@ -6314,22 +6314,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6398,10 +6398,10 @@
         <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
         <v>0</v>
@@ -6446,22 +6446,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6482,13 +6482,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6530,10 +6530,10 @@
         <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD46" t="n">
         <v>0</v>
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7370,7 +7370,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7898,7 +7898,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="M59" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="N59" t="n">
-        <v>1.84</v>
+        <v>1.52</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8246,10 +8246,10 @@
         <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="AC59" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="AD59" t="n">
         <v>0</v>
@@ -8304,12 +8304,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8330,13 +8330,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="M60" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="N60" t="n">
-        <v>1.52</v>
+        <v>1.84</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8378,10 +8378,10 @@
         <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="AC60" t="n">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="AD60" t="n">
         <v>0</v>

--- a/jogos_2025-08-01.xlsx
+++ b/jogos_2025-08-01.xlsx
@@ -196,12 +196,12 @@
     <t>Ukraine Ukrainian Premier League</t>
   </si>
   <si>
+    <t>Switzerland Challenge League</t>
+  </si>
+  <si>
     <t>Uzbekistan Uzbekistan Super League</t>
   </si>
   <si>
-    <t>Switzerland Challenge League</t>
-  </si>
-  <si>
     <t>Finland Veikkausliiga</t>
   </si>
   <si>
@@ -214,30 +214,30 @@
     <t>Romania Liga I</t>
   </si>
   <si>
+    <t>Poland 1. Liga</t>
+  </si>
+  <si>
     <t>Bulgaria First League</t>
   </si>
   <si>
-    <t>Poland 1. Liga</t>
-  </si>
-  <si>
     <t>Austria 2. Liga</t>
   </si>
   <si>
+    <t>Denmark Superliga</t>
+  </si>
+  <si>
     <t>Poland Ekstraklasa</t>
   </si>
   <si>
-    <t>Denmark Superliga</t>
-  </si>
-  <si>
     <t>Estonia Meistriliiga</t>
   </si>
   <si>
+    <t>Sweden Superettan</t>
+  </si>
+  <si>
     <t>Germany 3. Liga</t>
   </si>
   <si>
-    <t>Sweden Superettan</t>
-  </si>
-  <si>
     <t>Hungary NB I</t>
   </si>
   <si>
@@ -253,15 +253,15 @@
     <t>Republic of Ireland First Division</t>
   </si>
   <si>
+    <t>Republic of Ireland Premier Division</t>
+  </si>
+  <si>
+    <t>Scotland Championship</t>
+  </si>
+  <si>
     <t>Belgium Pro League</t>
   </si>
   <si>
-    <t>Republic of Ireland Premier Division</t>
-  </si>
-  <si>
-    <t>Scotland Championship</t>
-  </si>
-  <si>
     <t>England EFL League One</t>
   </si>
   <si>
@@ -292,27 +292,27 @@
     <t>Kolos Kovalivka</t>
   </si>
   <si>
+    <t>Wil</t>
+  </si>
+  <si>
+    <t>Dinamo Samarqand</t>
+  </si>
+  <si>
     <t>Neftchi</t>
   </si>
   <si>
-    <t>Dinamo Samarqand</t>
-  </si>
-  <si>
-    <t>Wil</t>
+    <t>Rukh Vynnyky</t>
   </si>
   <si>
     <t>VPS</t>
   </si>
   <si>
-    <t>Rukh Vynnyky</t>
+    <t>Buxoro</t>
   </si>
   <si>
     <t>Smorgon</t>
   </si>
   <si>
-    <t>Buxoro</t>
-  </si>
-  <si>
     <t>BATE</t>
   </si>
   <si>
@@ -322,141 +322,141 @@
     <t>SSC Farul</t>
   </si>
   <si>
+    <t>Wieczysta Kraków</t>
+  </si>
+  <si>
     <t>Spartak Varna</t>
   </si>
   <si>
-    <t>Wieczysta Kraków</t>
+    <t>Liefering</t>
+  </si>
+  <si>
+    <t>SV Stripfing Weiden</t>
+  </si>
+  <si>
+    <t>Kapfenberger SV</t>
+  </si>
+  <si>
+    <t>Austria Salzburg</t>
+  </si>
+  <si>
+    <t>Fredericia</t>
+  </si>
+  <si>
+    <t>Zagłębie Lubin</t>
   </si>
   <si>
     <t>Amstetten</t>
   </si>
   <si>
-    <t>Zagłębie Lubin</t>
-  </si>
-  <si>
-    <t>Fredericia</t>
-  </si>
-  <si>
-    <t>Liefering</t>
-  </si>
-  <si>
-    <t>SV Stripfing Weiden</t>
-  </si>
-  <si>
-    <t>Austria Salzburg</t>
-  </si>
-  <si>
-    <t>Kapfenberger SV</t>
-  </si>
-  <si>
     <t>Tallinna FC Levadia</t>
   </si>
   <si>
+    <t>Örebro</t>
+  </si>
+  <si>
     <t>Rot-Weiss Essen</t>
   </si>
   <si>
-    <t>Örebro</t>
-  </si>
-  <si>
     <t>Stade Nyonnais</t>
   </si>
   <si>
+    <t>Vejle</t>
+  </si>
+  <si>
     <t>Debrecen</t>
   </si>
   <si>
-    <t>Vejle</t>
-  </si>
-  <si>
     <t>Lokomotiva Zagreb</t>
   </si>
   <si>
     <t>CSKA 1948 Sofia</t>
   </si>
   <si>
+    <t>Wisła Płock</t>
+  </si>
+  <si>
     <t>LASK Linz</t>
   </si>
   <si>
+    <t>Schalke 04</t>
+  </si>
+  <si>
+    <t>ŁKS Łódź</t>
+  </si>
+  <si>
     <t>Petrolul 52</t>
   </si>
   <si>
-    <t>Schalke 04</t>
-  </si>
-  <si>
-    <t>Wisła Płock</t>
-  </si>
-  <si>
-    <t>ŁKS Łódź</t>
+    <t>Wexford</t>
+  </si>
+  <si>
+    <t>Bohemians</t>
   </si>
   <si>
     <t>Bray Wanderers</t>
   </si>
   <si>
+    <t>UCD</t>
+  </si>
+  <si>
+    <t>Kerry</t>
+  </si>
+  <si>
+    <t>Cork City</t>
+  </si>
+  <si>
+    <t>Waterford</t>
+  </si>
+  <si>
+    <t>Cobh Ramblers</t>
+  </si>
+  <si>
+    <t>Arbroath</t>
+  </si>
+  <si>
     <t>KV Mechelen</t>
   </si>
   <si>
-    <t>Cork City</t>
-  </si>
-  <si>
-    <t>Wexford</t>
-  </si>
-  <si>
-    <t>Bohemians</t>
-  </si>
-  <si>
-    <t>Waterford</t>
-  </si>
-  <si>
-    <t>Cobh Ramblers</t>
-  </si>
-  <si>
-    <t>Kerry</t>
-  </si>
-  <si>
-    <t>UCD</t>
-  </si>
-  <si>
-    <t>Arbroath</t>
+    <t>Shamrock Rovers</t>
   </si>
   <si>
     <t>Luton Town</t>
   </si>
   <si>
-    <t>Shamrock Rovers</t>
-  </si>
-  <si>
     <t>Náutico</t>
   </si>
   <si>
     <t>Remo</t>
   </si>
   <si>
+    <t>Maringá</t>
+  </si>
+  <si>
+    <t>Confiança</t>
+  </si>
+  <si>
     <t>São Bernardo</t>
   </si>
   <si>
-    <t>Confiança</t>
+    <t>Ponte Preta</t>
+  </si>
+  <si>
+    <t>Ituano</t>
+  </si>
+  <si>
+    <t>Brusque</t>
+  </si>
+  <si>
+    <t>ABC</t>
+  </si>
+  <si>
+    <t>Ypiranga Erechim</t>
   </si>
   <si>
     <t>CSA</t>
   </si>
   <si>
-    <t>ABC</t>
-  </si>
-  <si>
-    <t>Maringá</t>
-  </si>
-  <si>
-    <t>Ponte Preta</t>
-  </si>
-  <si>
-    <t>Ypiranga Erechim</t>
-  </si>
-  <si>
-    <t>Brusque</t>
-  </si>
-  <si>
-    <t>Ituano</t>
-  </si>
-  <si>
     <t>Audax Italiano</t>
   </si>
   <si>
@@ -466,12 +466,12 @@
     <t>Chicago Red Stars</t>
   </si>
   <si>
+    <t>Tulsa Roughnecks</t>
+  </si>
+  <si>
     <t>Operário PR</t>
   </si>
   <si>
-    <t>Tulsa Roughnecks</t>
-  </si>
-  <si>
     <t>Colorado Springs</t>
   </si>
   <si>
@@ -484,27 +484,27 @@
     <t>Hirnyk</t>
   </si>
   <si>
+    <t>Aarau</t>
+  </si>
+  <si>
+    <t>Navbahor</t>
+  </si>
+  <si>
     <t>Bunyodkor</t>
   </si>
   <si>
-    <t>Navbahor</t>
-  </si>
-  <si>
-    <t>Aarau</t>
+    <t>SK Poltava</t>
   </si>
   <si>
     <t>Mariehamn</t>
   </si>
   <si>
-    <t>SK Poltava</t>
+    <t>AGMK</t>
   </si>
   <si>
     <t>Dinamo Minsk</t>
   </si>
   <si>
-    <t>AGMK</t>
-  </si>
-  <si>
     <t>Vitebsk</t>
   </si>
   <si>
@@ -514,141 +514,141 @@
     <t>Metaloglobus</t>
   </si>
   <si>
+    <t>Znicz Pruszków</t>
+  </si>
+  <si>
     <t>Botev Vratsa</t>
   </si>
   <si>
-    <t>Znicz Pruszków</t>
+    <t>Austria Lustenau</t>
+  </si>
+  <si>
+    <t>First Vienna</t>
+  </si>
+  <si>
+    <t>Admira</t>
+  </si>
+  <si>
+    <t>Austria Klagenfurt</t>
+  </si>
+  <si>
+    <t>København</t>
+  </si>
+  <si>
+    <t>Korona Kielce</t>
   </si>
   <si>
     <t>Sturm Graz II</t>
   </si>
   <si>
-    <t>Korona Kielce</t>
-  </si>
-  <si>
-    <t>København</t>
-  </si>
-  <si>
-    <t>Austria Lustenau</t>
-  </si>
-  <si>
-    <t>First Vienna</t>
-  </si>
-  <si>
-    <t>Austria Klagenfurt</t>
-  </si>
-  <si>
-    <t>Admira</t>
-  </si>
-  <si>
     <t>Kuressaare</t>
   </si>
   <si>
+    <t>Oddevold</t>
+  </si>
+  <si>
     <t>1860 München</t>
   </si>
   <si>
-    <t>Oddevold</t>
-  </si>
-  <si>
     <t>Rapperswil-Jona</t>
   </si>
   <si>
+    <t>OB</t>
+  </si>
+  <si>
     <t>MTK</t>
   </si>
   <si>
-    <t>OB</t>
-  </si>
-  <si>
     <t>HNK Vukovar 1991</t>
   </si>
   <si>
     <t>Septemvri Sofia</t>
   </si>
   <si>
+    <t>Piast Gliwice</t>
+  </si>
+  <si>
     <t>Sturm Graz</t>
   </si>
   <si>
+    <t>Hertha BSC</t>
+  </si>
+  <si>
+    <t>Polonia Bytom</t>
+  </si>
+  <si>
     <t>UTA Arad</t>
   </si>
   <si>
-    <t>Hertha BSC</t>
-  </si>
-  <si>
-    <t>Piast Gliwice</t>
-  </si>
-  <si>
-    <t>Polonia Bytom</t>
+    <t>Finn Harps</t>
+  </si>
+  <si>
+    <t>Drogheda United</t>
   </si>
   <si>
     <t>Treaty United</t>
   </si>
   <si>
+    <t>Dundalk</t>
+  </si>
+  <si>
+    <t>Athlone Town</t>
+  </si>
+  <si>
+    <t>Galway United</t>
+  </si>
+  <si>
+    <t>St Patrick's Athl.</t>
+  </si>
+  <si>
+    <t>Longford Town</t>
+  </si>
+  <si>
+    <t>Ayr United</t>
+  </si>
+  <si>
     <t>Club Brugge</t>
   </si>
   <si>
-    <t>Galway United</t>
-  </si>
-  <si>
-    <t>Finn Harps</t>
-  </si>
-  <si>
-    <t>Drogheda United</t>
-  </si>
-  <si>
-    <t>St Patrick's Athl.</t>
-  </si>
-  <si>
-    <t>Longford Town</t>
-  </si>
-  <si>
-    <t>Athlone Town</t>
-  </si>
-  <si>
-    <t>Dundalk</t>
-  </si>
-  <si>
-    <t>Ayr United</t>
+    <t>Derry City</t>
   </si>
   <si>
     <t>AFC Wimbledon</t>
   </si>
   <si>
-    <t>Derry City</t>
-  </si>
-  <si>
     <t>Retrô</t>
   </si>
   <si>
     <t>Ferroviária</t>
   </si>
   <si>
+    <t>Floresta</t>
+  </si>
+  <si>
+    <t>Anápolis</t>
+  </si>
+  <si>
     <t>Tombense</t>
   </si>
   <si>
-    <t>Anápolis</t>
+    <t>Guarani</t>
+  </si>
+  <si>
+    <t>Londrina</t>
+  </si>
+  <si>
+    <t>Itabaiana</t>
+  </si>
+  <si>
+    <t>Figueirense</t>
+  </si>
+  <si>
+    <t>Caxias</t>
   </si>
   <si>
     <t>Botafogo PB</t>
   </si>
   <si>
-    <t>Figueirense</t>
-  </si>
-  <si>
-    <t>Floresta</t>
-  </si>
-  <si>
-    <t>Guarani</t>
-  </si>
-  <si>
-    <t>Caxias</t>
-  </si>
-  <si>
-    <t>Itabaiana</t>
-  </si>
-  <si>
-    <t>Londrina</t>
-  </si>
-  <si>
     <t>Palestino</t>
   </si>
   <si>
@@ -658,10 +658,10 @@
     <t>Gotham FC</t>
   </si>
   <si>
+    <t>Loudoun United</t>
+  </si>
+  <si>
     <t>Criciúma</t>
-  </si>
-  <si>
-    <t>Loudoun United</t>
   </si>
   <si>
     <t>Lexington</t>
@@ -1286,7 +1286,7 @@
         <v>60</v>
       </c>
       <c r="D3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E3" t="s">
         <v>92</v>
@@ -1310,13 +1310,13 @@
         <v>219</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="M3">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O3">
         <v>0</v>
@@ -1399,7 +1399,7 @@
         <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D4" t="s">
         <v>90</v>
@@ -1518,7 +1518,7 @@
         <v>61</v>
       </c>
       <c r="D5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E5" t="s">
         <v>94</v>
@@ -1542,13 +1542,13 @@
         <v>219</v>
       </c>
       <c r="L5">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="M5">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N5">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O5">
         <v>0</v>
@@ -1631,10 +1631,10 @@
         <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E6" t="s">
         <v>95</v>
@@ -1658,13 +1658,13 @@
         <v>219</v>
       </c>
       <c r="L6">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="M6">
-        <v>4.1</v>
+        <v>3.41</v>
       </c>
       <c r="N6">
-        <v>4.5</v>
+        <v>5.9</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -1700,16 +1700,16 @@
         <v>0</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AB6">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC6">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD6">
         <v>0</v>
@@ -1747,10 +1747,10 @@
         <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E7" t="s">
         <v>96</v>
@@ -1774,13 +1774,13 @@
         <v>219</v>
       </c>
       <c r="L7">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="M7">
-        <v>3.41</v>
+        <v>3.98</v>
       </c>
       <c r="N7">
-        <v>5.9</v>
+        <v>4.33</v>
       </c>
       <c r="O7">
         <v>0</v>
@@ -1816,16 +1816,16 @@
         <v>0</v>
       </c>
       <c r="Z7">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA7">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD7">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>40</v>
       </c>
       <c r="C8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D8" t="s">
         <v>90</v>
@@ -1979,7 +1979,7 @@
         <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D9" t="s">
         <v>90</v>
@@ -2470,13 +2470,13 @@
         <v>219</v>
       </c>
       <c r="L13">
-        <v>2.4</v>
+        <v>1.42</v>
       </c>
       <c r="M13">
-        <v>3.18</v>
+        <v>4.2</v>
       </c>
       <c r="N13">
-        <v>2.9</v>
+        <v>5.6</v>
       </c>
       <c r="O13">
         <v>0</v>
@@ -2586,13 +2586,13 @@
         <v>219</v>
       </c>
       <c r="L14">
-        <v>1.42</v>
+        <v>2.47</v>
       </c>
       <c r="M14">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="N14">
-        <v>5.6</v>
+        <v>2.7</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -2702,13 +2702,13 @@
         <v>219</v>
       </c>
       <c r="L15">
-        <v>1.78</v>
+        <v>2.54</v>
       </c>
       <c r="M15">
-        <v>4</v>
+        <v>3.21</v>
       </c>
       <c r="N15">
-        <v>3.75</v>
+        <v>2.41</v>
       </c>
       <c r="O15">
         <v>0</v>
@@ -2750,10 +2750,10 @@
         <v>0</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD15">
         <v>0</v>
@@ -2791,7 +2791,7 @@
         <v>43</v>
       </c>
       <c r="C16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D16" t="s">
         <v>89</v>
@@ -2818,13 +2818,13 @@
         <v>219</v>
       </c>
       <c r="L16">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="M16">
-        <v>3.17</v>
+        <v>3.21</v>
       </c>
       <c r="N16">
-        <v>2.99</v>
+        <v>2.68</v>
       </c>
       <c r="O16">
         <v>0</v>
@@ -2866,10 +2866,10 @@
         <v>0</v>
       </c>
       <c r="AB16">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC16">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD16">
         <v>0</v>
@@ -2907,7 +2907,7 @@
         <v>43</v>
       </c>
       <c r="C17" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D17" t="s">
         <v>89</v>
@@ -2934,13 +2934,13 @@
         <v>219</v>
       </c>
       <c r="L17">
-        <v>9.199999999999999</v>
+        <v>3.62</v>
       </c>
       <c r="M17">
-        <v>5.6</v>
+        <v>3.7</v>
       </c>
       <c r="N17">
-        <v>1.27</v>
+        <v>1.75</v>
       </c>
       <c r="O17">
         <v>0</v>
@@ -3050,13 +3050,13 @@
         <v>219</v>
       </c>
       <c r="L18">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M18">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N18">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB18">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC18">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD18">
         <v>0</v>
@@ -3139,7 +3139,7 @@
         <v>43</v>
       </c>
       <c r="C19" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D19" t="s">
         <v>89</v>
@@ -3166,13 +3166,13 @@
         <v>219</v>
       </c>
       <c r="L19">
-        <v>2.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M19">
-        <v>3.35</v>
+        <v>5.6</v>
       </c>
       <c r="N19">
-        <v>2.85</v>
+        <v>1.27</v>
       </c>
       <c r="O19">
         <v>0</v>
@@ -3255,7 +3255,7 @@
         <v>43</v>
       </c>
       <c r="C20" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D20" t="s">
         <v>89</v>
@@ -3282,13 +3282,13 @@
         <v>219</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="O20">
         <v>0</v>
@@ -3330,10 +3330,10 @@
         <v>0</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD20">
         <v>0</v>
@@ -3398,13 +3398,13 @@
         <v>219</v>
       </c>
       <c r="L21">
-        <v>3.8</v>
+        <v>1.73</v>
       </c>
       <c r="M21">
-        <v>3.85</v>
+        <v>3.82</v>
       </c>
       <c r="N21">
-        <v>1.8</v>
+        <v>3.57</v>
       </c>
       <c r="O21">
         <v>0</v>
@@ -3606,7 +3606,7 @@
         <v>72</v>
       </c>
       <c r="D23" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E23" t="s">
         <v>112</v>
@@ -3630,13 +3630,13 @@
         <v>219</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M23">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="O23">
         <v>0</v>
@@ -3678,10 +3678,10 @@
         <v>0</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD23">
         <v>0</v>
@@ -3722,7 +3722,7 @@
         <v>73</v>
       </c>
       <c r="D24" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E24" t="s">
         <v>113</v>
@@ -3746,13 +3746,13 @@
         <v>219</v>
       </c>
       <c r="L24">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M24">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="N24">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="O24">
         <v>0</v>
@@ -3794,10 +3794,10 @@
         <v>0</v>
       </c>
       <c r="AB24">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC24">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD24">
         <v>0</v>
@@ -3835,7 +3835,7 @@
         <v>46</v>
       </c>
       <c r="C25" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D25" t="s">
         <v>89</v>
@@ -3951,7 +3951,7 @@
         <v>47</v>
       </c>
       <c r="C26" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D26" t="s">
         <v>89</v>
@@ -3978,13 +3978,13 @@
         <v>219</v>
       </c>
       <c r="L26">
-        <v>1.89</v>
+        <v>2.7</v>
       </c>
       <c r="M26">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="N26">
-        <v>3.5</v>
+        <v>2.41</v>
       </c>
       <c r="O26">
         <v>0</v>
@@ -4067,7 +4067,7 @@
         <v>47</v>
       </c>
       <c r="C27" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D27" t="s">
         <v>89</v>
@@ -4094,13 +4094,13 @@
         <v>219</v>
       </c>
       <c r="L27">
-        <v>2.7</v>
+        <v>1.89</v>
       </c>
       <c r="M27">
+        <v>3.75</v>
+      </c>
+      <c r="N27">
         <v>3.5</v>
-      </c>
-      <c r="N27">
-        <v>2.41</v>
       </c>
       <c r="O27">
         <v>0</v>
@@ -4299,7 +4299,7 @@
         <v>48</v>
       </c>
       <c r="C29" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D29" t="s">
         <v>89</v>
@@ -4415,7 +4415,7 @@
         <v>49</v>
       </c>
       <c r="C30" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D30" t="s">
         <v>89</v>
@@ -4442,13 +4442,13 @@
         <v>219</v>
       </c>
       <c r="L30">
-        <v>2.88</v>
+        <v>2.27</v>
       </c>
       <c r="M30">
-        <v>2.96</v>
+        <v>2.99</v>
       </c>
       <c r="N30">
-        <v>2.31</v>
+        <v>2.9</v>
       </c>
       <c r="O30">
         <v>0</v>
@@ -4490,10 +4490,10 @@
         <v>0</v>
       </c>
       <c r="AB30">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC30">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD30">
         <v>0</v>
@@ -4531,7 +4531,7 @@
         <v>49</v>
       </c>
       <c r="C31" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="D31" t="s">
         <v>89</v>
@@ -4558,13 +4558,13 @@
         <v>219</v>
       </c>
       <c r="L31">
-        <v>2.24</v>
+        <v>2.88</v>
       </c>
       <c r="M31">
         <v>2.96</v>
       </c>
       <c r="N31">
-        <v>2.98</v>
+        <v>2.31</v>
       </c>
       <c r="O31">
         <v>0</v>
@@ -4606,10 +4606,10 @@
         <v>0</v>
       </c>
       <c r="AB31">
-        <v>2.39</v>
+        <v>1.7</v>
       </c>
       <c r="AC31">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="AD31">
         <v>0</v>
@@ -4763,7 +4763,7 @@
         <v>49</v>
       </c>
       <c r="C33" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D33" t="s">
         <v>89</v>
@@ -4790,13 +4790,13 @@
         <v>219</v>
       </c>
       <c r="L33">
-        <v>2.27</v>
+        <v>2.02</v>
       </c>
       <c r="M33">
-        <v>2.99</v>
+        <v>3.13</v>
       </c>
       <c r="N33">
-        <v>2.9</v>
+        <v>3.27</v>
       </c>
       <c r="O33">
         <v>0</v>
@@ -4838,10 +4838,10 @@
         <v>0</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD33">
         <v>0</v>
@@ -4879,7 +4879,7 @@
         <v>49</v>
       </c>
       <c r="C34" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D34" t="s">
         <v>89</v>
@@ -4906,13 +4906,13 @@
         <v>219</v>
       </c>
       <c r="L34">
-        <v>2.02</v>
+        <v>2.24</v>
       </c>
       <c r="M34">
-        <v>3.13</v>
+        <v>2.96</v>
       </c>
       <c r="N34">
-        <v>3.27</v>
+        <v>2.98</v>
       </c>
       <c r="O34">
         <v>0</v>
@@ -4954,10 +4954,10 @@
         <v>0</v>
       </c>
       <c r="AB34">
-        <v>1.95</v>
+        <v>2.39</v>
       </c>
       <c r="AC34">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="AD34">
         <v>0</v>
@@ -5022,13 +5022,13 @@
         <v>219</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M35">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O35">
         <v>0</v>
@@ -5114,7 +5114,7 @@
         <v>79</v>
       </c>
       <c r="D36" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E36" t="s">
         <v>125</v>
@@ -5138,13 +5138,13 @@
         <v>219</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M36">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O36">
         <v>0</v>
@@ -5186,10 +5186,10 @@
         <v>0</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD36">
         <v>0</v>
@@ -5227,7 +5227,7 @@
         <v>50</v>
       </c>
       <c r="C37" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D37" t="s">
         <v>90</v>
@@ -5254,13 +5254,13 @@
         <v>219</v>
       </c>
       <c r="L37">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M37">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N37">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O37">
         <v>0</v>
@@ -5370,13 +5370,13 @@
         <v>219</v>
       </c>
       <c r="L38">
-        <v>2</v>
+        <v>4.3</v>
       </c>
       <c r="M38">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="N38">
-        <v>3.15</v>
+        <v>1.72</v>
       </c>
       <c r="O38">
         <v>0</v>
@@ -5418,10 +5418,10 @@
         <v>0</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AD38">
         <v>0</v>
@@ -5459,7 +5459,7 @@
         <v>50</v>
       </c>
       <c r="C39" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D39" t="s">
         <v>90</v>
@@ -5486,13 +5486,13 @@
         <v>219</v>
       </c>
       <c r="L39">
-        <v>1.51</v>
+        <v>2.06</v>
       </c>
       <c r="M39">
-        <v>3.85</v>
+        <v>3.35</v>
       </c>
       <c r="N39">
-        <v>5.8</v>
+        <v>3.15</v>
       </c>
       <c r="O39">
         <v>0</v>
@@ -5534,10 +5534,10 @@
         <v>0</v>
       </c>
       <c r="AB39">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC39">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD39">
         <v>0</v>
@@ -5575,7 +5575,7 @@
         <v>50</v>
       </c>
       <c r="C40" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D40" t="s">
         <v>90</v>
@@ -5602,13 +5602,13 @@
         <v>219</v>
       </c>
       <c r="L40">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M40">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O40">
         <v>0</v>
@@ -5691,7 +5691,7 @@
         <v>50</v>
       </c>
       <c r="C41" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D41" t="s">
         <v>90</v>
@@ -5834,13 +5834,13 @@
         <v>219</v>
       </c>
       <c r="L42">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M42">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N42">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O42">
         <v>0</v>
@@ -5923,10 +5923,10 @@
         <v>50</v>
       </c>
       <c r="C43" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D43" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E43" t="s">
         <v>132</v>
@@ -5950,13 +5950,13 @@
         <v>219</v>
       </c>
       <c r="L43">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M43">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N43">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="O43">
         <v>0</v>
@@ -5998,10 +5998,10 @@
         <v>0</v>
       </c>
       <c r="AB43">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC43">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AD43">
         <v>0</v>
@@ -6155,10 +6155,10 @@
         <v>51</v>
       </c>
       <c r="C45" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D45" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E45" t="s">
         <v>134</v>
@@ -6182,13 +6182,13 @@
         <v>219</v>
       </c>
       <c r="L45">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M45">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N45">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O45">
         <v>0</v>
@@ -6230,10 +6230,10 @@
         <v>0</v>
       </c>
       <c r="AB45">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC45">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD45">
         <v>0</v>
@@ -6271,10 +6271,10 @@
         <v>51</v>
       </c>
       <c r="C46" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D46" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E46" t="s">
         <v>135</v>
@@ -6298,13 +6298,13 @@
         <v>219</v>
       </c>
       <c r="L46">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M46">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O46">
         <v>0</v>
@@ -6346,10 +6346,10 @@
         <v>0</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC46">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD46">
         <v>0</v>
@@ -8011,7 +8011,7 @@
         <v>55</v>
       </c>
       <c r="C61" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D61" t="s">
         <v>90</v>
@@ -8038,13 +8038,13 @@
         <v>219</v>
       </c>
       <c r="L61">
-        <v>2.16</v>
+        <v>1.86</v>
       </c>
       <c r="M61">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N61">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="O61">
         <v>0</v>
@@ -8080,16 +8080,16 @@
         <v>0</v>
       </c>
       <c r="Z61">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA61">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB61">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC61">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AD61">
         <v>0</v>
@@ -8127,7 +8127,7 @@
         <v>55</v>
       </c>
       <c r="C62" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D62" t="s">
         <v>90</v>
@@ -8154,13 +8154,13 @@
         <v>219</v>
       </c>
       <c r="L62">
-        <v>1.86</v>
+        <v>2.16</v>
       </c>
       <c r="M62">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="N62">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="O62">
         <v>0</v>
@@ -8196,16 +8196,16 @@
         <v>0</v>
       </c>
       <c r="Z62">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA62">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB62">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC62">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AD62">
         <v>0</v>

--- a/jogos_2025-08-01.xlsx
+++ b/jogos_2025-08-01.xlsx
@@ -202,33 +202,33 @@
     <t>Uzbekistan Uzbekistan Super League</t>
   </si>
   <si>
+    <t>Belarus Vysheyshaya Liga</t>
+  </si>
+  <si>
     <t>Finland Veikkausliiga</t>
   </si>
   <si>
-    <t>Belarus Vysheyshaya Liga</t>
-  </si>
-  <si>
     <t>Slovenia PrvaLiga</t>
   </si>
   <si>
+    <t>Poland Ekstraklasa</t>
+  </si>
+  <si>
+    <t>Denmark Superliga</t>
+  </si>
+  <si>
+    <t>Austria 2. Liga</t>
+  </si>
+  <si>
+    <t>Bulgaria First League</t>
+  </si>
+  <si>
     <t>Romania Liga I</t>
   </si>
   <si>
     <t>Poland 1. Liga</t>
   </si>
   <si>
-    <t>Bulgaria First League</t>
-  </si>
-  <si>
-    <t>Austria 2. Liga</t>
-  </si>
-  <si>
-    <t>Denmark Superliga</t>
-  </si>
-  <si>
-    <t>Poland Ekstraklasa</t>
-  </si>
-  <si>
     <t>Estonia Meistriliiga</t>
   </si>
   <si>
@@ -238,12 +238,12 @@
     <t>Germany 3. Liga</t>
   </si>
   <si>
+    <t>Croatia Prva HNL</t>
+  </si>
+  <si>
     <t>Hungary NB I</t>
   </si>
   <si>
-    <t>Croatia Prva HNL</t>
-  </si>
-  <si>
     <t>Austria Bundesliga</t>
   </si>
   <si>
@@ -301,51 +301,51 @@
     <t>Neftchi</t>
   </si>
   <si>
+    <t>Smorgon</t>
+  </si>
+  <si>
+    <t>Buxoro</t>
+  </si>
+  <si>
     <t>Rukh Vynnyky</t>
   </si>
   <si>
     <t>VPS</t>
   </si>
   <si>
-    <t>Buxoro</t>
-  </si>
-  <si>
-    <t>Smorgon</t>
-  </si>
-  <si>
     <t>BATE</t>
   </si>
   <si>
     <t>Radomlje</t>
   </si>
   <si>
+    <t>Zagłębie Lubin</t>
+  </si>
+  <si>
+    <t>Fredericia</t>
+  </si>
+  <si>
+    <t>Liefering</t>
+  </si>
+  <si>
+    <t>Spartak Varna</t>
+  </si>
+  <si>
     <t>SSC Farul</t>
   </si>
   <si>
+    <t>Kapfenberger SV</t>
+  </si>
+  <si>
+    <t>Austria Salzburg</t>
+  </si>
+  <si>
+    <t>SV Stripfing Weiden</t>
+  </si>
+  <si>
     <t>Wieczysta Kraków</t>
   </si>
   <si>
-    <t>Spartak Varna</t>
-  </si>
-  <si>
-    <t>Liefering</t>
-  </si>
-  <si>
-    <t>SV Stripfing Weiden</t>
-  </si>
-  <si>
-    <t>Kapfenberger SV</t>
-  </si>
-  <si>
-    <t>Austria Salzburg</t>
-  </si>
-  <si>
-    <t>Fredericia</t>
-  </si>
-  <si>
-    <t>Zagłębie Lubin</t>
-  </si>
-  <si>
     <t>Amstetten</t>
   </si>
   <si>
@@ -361,60 +361,60 @@
     <t>Stade Nyonnais</t>
   </si>
   <si>
+    <t>Lokomotiva Zagreb</t>
+  </si>
+  <si>
     <t>Vejle</t>
   </si>
   <si>
     <t>Debrecen</t>
   </si>
   <si>
-    <t>Lokomotiva Zagreb</t>
-  </si>
-  <si>
     <t>CSKA 1948 Sofia</t>
   </si>
   <si>
     <t>Wisła Płock</t>
   </si>
   <si>
+    <t>Petrolul 52</t>
+  </si>
+  <si>
+    <t>ŁKS Łódź</t>
+  </si>
+  <si>
     <t>LASK Linz</t>
   </si>
   <si>
     <t>Schalke 04</t>
   </si>
   <si>
-    <t>ŁKS Łódź</t>
-  </si>
-  <si>
-    <t>Petrolul 52</t>
+    <t>Cobh Ramblers</t>
+  </si>
+  <si>
+    <t>UCD</t>
+  </si>
+  <si>
+    <t>Waterford</t>
+  </si>
+  <si>
+    <t>Arbroath</t>
+  </si>
+  <si>
+    <t>Bohemians</t>
+  </si>
+  <si>
+    <t>Cork City</t>
+  </si>
+  <si>
+    <t>Kerry</t>
+  </si>
+  <si>
+    <t>Bray Wanderers</t>
   </si>
   <si>
     <t>Wexford</t>
   </si>
   <si>
-    <t>Bohemians</t>
-  </si>
-  <si>
-    <t>Bray Wanderers</t>
-  </si>
-  <si>
-    <t>UCD</t>
-  </si>
-  <si>
-    <t>Kerry</t>
-  </si>
-  <si>
-    <t>Cork City</t>
-  </si>
-  <si>
-    <t>Waterford</t>
-  </si>
-  <si>
-    <t>Cobh Ramblers</t>
-  </si>
-  <si>
-    <t>Arbroath</t>
-  </si>
-  <si>
     <t>KV Mechelen</t>
   </si>
   <si>
@@ -424,48 +424,48 @@
     <t>Luton Town</t>
   </si>
   <si>
+    <t>Ypiranga Erechim</t>
+  </si>
+  <si>
+    <t>ABC</t>
+  </si>
+  <si>
+    <t>São Bernardo</t>
+  </si>
+  <si>
+    <t>Ponte Preta</t>
+  </si>
+  <si>
+    <t>Maringá</t>
+  </si>
+  <si>
     <t>Náutico</t>
   </si>
   <si>
+    <t>Ituano</t>
+  </si>
+  <si>
     <t>Remo</t>
   </si>
   <si>
-    <t>Maringá</t>
-  </si>
-  <si>
     <t>Confiança</t>
   </si>
   <si>
-    <t>São Bernardo</t>
-  </si>
-  <si>
-    <t>Ponte Preta</t>
-  </si>
-  <si>
-    <t>Ituano</t>
-  </si>
-  <si>
     <t>Brusque</t>
   </si>
   <si>
-    <t>ABC</t>
-  </si>
-  <si>
-    <t>Ypiranga Erechim</t>
-  </si>
-  <si>
     <t>CSA</t>
   </si>
   <si>
     <t>Audax Italiano</t>
   </si>
   <si>
+    <t>Chicago Red Stars</t>
+  </si>
+  <si>
     <t>Racing Louisville</t>
   </si>
   <si>
-    <t>Chicago Red Stars</t>
-  </si>
-  <si>
     <t>Tulsa Roughnecks</t>
   </si>
   <si>
@@ -493,51 +493,51 @@
     <t>Bunyodkor</t>
   </si>
   <si>
+    <t>Dinamo Minsk</t>
+  </si>
+  <si>
+    <t>AGMK</t>
+  </si>
+  <si>
     <t>SK Poltava</t>
   </si>
   <si>
     <t>Mariehamn</t>
   </si>
   <si>
-    <t>AGMK</t>
-  </si>
-  <si>
-    <t>Dinamo Minsk</t>
-  </si>
-  <si>
     <t>Vitebsk</t>
   </si>
   <si>
     <t>Domžale</t>
   </si>
   <si>
+    <t>Korona Kielce</t>
+  </si>
+  <si>
+    <t>København</t>
+  </si>
+  <si>
+    <t>Austria Lustenau</t>
+  </si>
+  <si>
+    <t>Botev Vratsa</t>
+  </si>
+  <si>
     <t>Metaloglobus</t>
   </si>
   <si>
+    <t>Admira</t>
+  </si>
+  <si>
+    <t>Austria Klagenfurt</t>
+  </si>
+  <si>
+    <t>First Vienna</t>
+  </si>
+  <si>
     <t>Znicz Pruszków</t>
   </si>
   <si>
-    <t>Botev Vratsa</t>
-  </si>
-  <si>
-    <t>Austria Lustenau</t>
-  </si>
-  <si>
-    <t>First Vienna</t>
-  </si>
-  <si>
-    <t>Admira</t>
-  </si>
-  <si>
-    <t>Austria Klagenfurt</t>
-  </si>
-  <si>
-    <t>København</t>
-  </si>
-  <si>
-    <t>Korona Kielce</t>
-  </si>
-  <si>
     <t>Sturm Graz II</t>
   </si>
   <si>
@@ -553,60 +553,60 @@
     <t>Rapperswil-Jona</t>
   </si>
   <si>
+    <t>HNK Vukovar 1991</t>
+  </si>
+  <si>
     <t>OB</t>
   </si>
   <si>
     <t>MTK</t>
   </si>
   <si>
-    <t>HNK Vukovar 1991</t>
-  </si>
-  <si>
     <t>Septemvri Sofia</t>
   </si>
   <si>
     <t>Piast Gliwice</t>
   </si>
   <si>
+    <t>UTA Arad</t>
+  </si>
+  <si>
+    <t>Polonia Bytom</t>
+  </si>
+  <si>
     <t>Sturm Graz</t>
   </si>
   <si>
     <t>Hertha BSC</t>
   </si>
   <si>
-    <t>Polonia Bytom</t>
-  </si>
-  <si>
-    <t>UTA Arad</t>
+    <t>Longford Town</t>
+  </si>
+  <si>
+    <t>Dundalk</t>
+  </si>
+  <si>
+    <t>St Patrick's Athl.</t>
+  </si>
+  <si>
+    <t>Ayr United</t>
+  </si>
+  <si>
+    <t>Drogheda United</t>
+  </si>
+  <si>
+    <t>Galway United</t>
+  </si>
+  <si>
+    <t>Athlone Town</t>
+  </si>
+  <si>
+    <t>Treaty United</t>
   </si>
   <si>
     <t>Finn Harps</t>
   </si>
   <si>
-    <t>Drogheda United</t>
-  </si>
-  <si>
-    <t>Treaty United</t>
-  </si>
-  <si>
-    <t>Dundalk</t>
-  </si>
-  <si>
-    <t>Athlone Town</t>
-  </si>
-  <si>
-    <t>Galway United</t>
-  </si>
-  <si>
-    <t>St Patrick's Athl.</t>
-  </si>
-  <si>
-    <t>Longford Town</t>
-  </si>
-  <si>
-    <t>Ayr United</t>
-  </si>
-  <si>
     <t>Club Brugge</t>
   </si>
   <si>
@@ -616,46 +616,46 @@
     <t>AFC Wimbledon</t>
   </si>
   <si>
+    <t>Caxias</t>
+  </si>
+  <si>
+    <t>Figueirense</t>
+  </si>
+  <si>
+    <t>Tombense</t>
+  </si>
+  <si>
+    <t>Guarani</t>
+  </si>
+  <si>
+    <t>Floresta</t>
+  </si>
+  <si>
     <t>Retrô</t>
   </si>
   <si>
+    <t>Londrina</t>
+  </si>
+  <si>
     <t>Ferroviária</t>
   </si>
   <si>
-    <t>Floresta</t>
-  </si>
-  <si>
     <t>Anápolis</t>
   </si>
   <si>
-    <t>Tombense</t>
-  </si>
-  <si>
-    <t>Guarani</t>
-  </si>
-  <si>
-    <t>Londrina</t>
-  </si>
-  <si>
     <t>Itabaiana</t>
   </si>
   <si>
-    <t>Figueirense</t>
-  </si>
-  <si>
-    <t>Caxias</t>
-  </si>
-  <si>
     <t>Botafogo PB</t>
   </si>
   <si>
     <t>Palestino</t>
   </si>
   <si>
+    <t>Gotham FC</t>
+  </si>
+  <si>
     <t>Kansas City</t>
-  </si>
-  <si>
-    <t>Gotham FC</t>
   </si>
   <si>
     <t>Loudoun United</t>
@@ -1631,10 +1631,10 @@
         <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E6" t="s">
         <v>95</v>
@@ -1658,13 +1658,13 @@
         <v>219</v>
       </c>
       <c r="L6">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M6">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N6">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -1700,10 +1700,10 @@
         <v>0</v>
       </c>
       <c r="Z6">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA6">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AB6">
         <v>0</v>
@@ -1747,7 +1747,7 @@
         <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D7" t="s">
         <v>90</v>
@@ -1774,13 +1774,13 @@
         <v>219</v>
       </c>
       <c r="L7">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M7">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="N7">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="O7">
         <v>0</v>
@@ -1822,10 +1822,10 @@
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC7">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD7">
         <v>0</v>
@@ -1863,10 +1863,10 @@
         <v>40</v>
       </c>
       <c r="C8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E8" t="s">
         <v>97</v>
@@ -1890,13 +1890,13 @@
         <v>219</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="O8">
         <v>0</v>
@@ -1932,10 +1932,10 @@
         <v>0</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AB8">
         <v>0</v>
@@ -2006,13 +2006,13 @@
         <v>219</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O9">
         <v>0</v>
@@ -2054,10 +2054,10 @@
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD9">
         <v>0</v>
@@ -2095,7 +2095,7 @@
         <v>41</v>
       </c>
       <c r="C10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D10" t="s">
         <v>90</v>
@@ -2354,13 +2354,13 @@
         <v>219</v>
       </c>
       <c r="L12">
-        <v>1.45</v>
+        <v>2.13</v>
       </c>
       <c r="M12">
-        <v>3.7</v>
+        <v>3.17</v>
       </c>
       <c r="N12">
-        <v>6.3</v>
+        <v>2.99</v>
       </c>
       <c r="O12">
         <v>0</v>
@@ -2402,10 +2402,10 @@
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AC12">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AD12">
         <v>0</v>
@@ -2470,13 +2470,13 @@
         <v>219</v>
       </c>
       <c r="L13">
-        <v>1.42</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M13">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="N13">
-        <v>5.6</v>
+        <v>1.27</v>
       </c>
       <c r="O13">
         <v>0</v>
@@ -2586,13 +2586,13 @@
         <v>219</v>
       </c>
       <c r="L14">
-        <v>2.47</v>
+        <v>2.54</v>
       </c>
       <c r="M14">
-        <v>3.1</v>
+        <v>3.21</v>
       </c>
       <c r="N14">
-        <v>2.7</v>
+        <v>2.41</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -2634,10 +2634,10 @@
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD14">
         <v>0</v>
@@ -2702,13 +2702,13 @@
         <v>219</v>
       </c>
       <c r="L15">
-        <v>2.54</v>
+        <v>2.47</v>
       </c>
       <c r="M15">
-        <v>3.21</v>
+        <v>3.1</v>
       </c>
       <c r="N15">
-        <v>2.41</v>
+        <v>2.7</v>
       </c>
       <c r="O15">
         <v>0</v>
@@ -2750,10 +2750,10 @@
         <v>0</v>
       </c>
       <c r="AB15">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC15">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD15">
         <v>0</v>
@@ -2791,7 +2791,7 @@
         <v>43</v>
       </c>
       <c r="C16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D16" t="s">
         <v>89</v>
@@ -2818,13 +2818,13 @@
         <v>219</v>
       </c>
       <c r="L16">
-        <v>2.3</v>
+        <v>1.45</v>
       </c>
       <c r="M16">
-        <v>3.21</v>
+        <v>3.7</v>
       </c>
       <c r="N16">
-        <v>2.68</v>
+        <v>6.3</v>
       </c>
       <c r="O16">
         <v>0</v>
@@ -2866,10 +2866,10 @@
         <v>0</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD16">
         <v>0</v>
@@ -2907,7 +2907,7 @@
         <v>43</v>
       </c>
       <c r="C17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D17" t="s">
         <v>89</v>
@@ -3023,7 +3023,7 @@
         <v>43</v>
       </c>
       <c r="C18" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D18" t="s">
         <v>89</v>
@@ -3139,7 +3139,7 @@
         <v>43</v>
       </c>
       <c r="C19" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D19" t="s">
         <v>89</v>
@@ -3166,13 +3166,13 @@
         <v>219</v>
       </c>
       <c r="L19">
-        <v>9.199999999999999</v>
+        <v>2.3</v>
       </c>
       <c r="M19">
-        <v>5.6</v>
+        <v>3.21</v>
       </c>
       <c r="N19">
-        <v>1.27</v>
+        <v>2.68</v>
       </c>
       <c r="O19">
         <v>0</v>
@@ -3282,13 +3282,13 @@
         <v>219</v>
       </c>
       <c r="L20">
-        <v>2.13</v>
+        <v>1.42</v>
       </c>
       <c r="M20">
-        <v>3.17</v>
+        <v>4.2</v>
       </c>
       <c r="N20">
-        <v>2.99</v>
+        <v>5.6</v>
       </c>
       <c r="O20">
         <v>0</v>
@@ -3330,10 +3330,10 @@
         <v>0</v>
       </c>
       <c r="AB20">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC20">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD20">
         <v>0</v>
@@ -3371,7 +3371,7 @@
         <v>43</v>
       </c>
       <c r="C21" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D21" t="s">
         <v>89</v>
@@ -3951,7 +3951,7 @@
         <v>47</v>
       </c>
       <c r="C26" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D26" t="s">
         <v>89</v>
@@ -3978,13 +3978,13 @@
         <v>219</v>
       </c>
       <c r="L26">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M26">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N26">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="O26">
         <v>0</v>
@@ -4067,7 +4067,7 @@
         <v>47</v>
       </c>
       <c r="C27" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D27" t="s">
         <v>89</v>
@@ -4094,13 +4094,13 @@
         <v>219</v>
       </c>
       <c r="L27">
-        <v>1.89</v>
+        <v>2.7</v>
       </c>
       <c r="M27">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="N27">
-        <v>3.5</v>
+        <v>2.41</v>
       </c>
       <c r="O27">
         <v>0</v>
@@ -4210,13 +4210,13 @@
         <v>219</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O28">
         <v>0</v>
@@ -4299,7 +4299,7 @@
         <v>48</v>
       </c>
       <c r="C29" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D29" t="s">
         <v>89</v>
@@ -4415,7 +4415,7 @@
         <v>49</v>
       </c>
       <c r="C30" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="D30" t="s">
         <v>89</v>
@@ -4531,7 +4531,7 @@
         <v>49</v>
       </c>
       <c r="C31" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="D31" t="s">
         <v>89</v>
@@ -4558,13 +4558,13 @@
         <v>219</v>
       </c>
       <c r="L31">
-        <v>2.88</v>
+        <v>2.24</v>
       </c>
       <c r="M31">
         <v>2.96</v>
       </c>
       <c r="N31">
-        <v>2.31</v>
+        <v>2.98</v>
       </c>
       <c r="O31">
         <v>0</v>
@@ -4606,10 +4606,10 @@
         <v>0</v>
       </c>
       <c r="AB31">
-        <v>1.7</v>
+        <v>2.39</v>
       </c>
       <c r="AC31">
-        <v>1.95</v>
+        <v>1.58</v>
       </c>
       <c r="AD31">
         <v>0</v>
@@ -4647,7 +4647,7 @@
         <v>49</v>
       </c>
       <c r="C32" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D32" t="s">
         <v>89</v>
@@ -4674,13 +4674,13 @@
         <v>219</v>
       </c>
       <c r="L32">
-        <v>2.99</v>
+        <v>2.02</v>
       </c>
       <c r="M32">
-        <v>3.21</v>
+        <v>3.13</v>
       </c>
       <c r="N32">
-        <v>2.36</v>
+        <v>3.27</v>
       </c>
       <c r="O32">
         <v>0</v>
@@ -4722,16 +4722,16 @@
         <v>0</v>
       </c>
       <c r="AB32">
-        <v>1.53</v>
+        <v>1.95</v>
       </c>
       <c r="AC32">
-        <v>2.35</v>
+        <v>1.75</v>
       </c>
       <c r="AD32">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE32">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF32">
         <v>0</v>
@@ -4763,7 +4763,7 @@
         <v>49</v>
       </c>
       <c r="C33" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="D33" t="s">
         <v>89</v>
@@ -4790,13 +4790,13 @@
         <v>219</v>
       </c>
       <c r="L33">
-        <v>2.02</v>
+        <v>2.88</v>
       </c>
       <c r="M33">
-        <v>3.13</v>
+        <v>2.96</v>
       </c>
       <c r="N33">
-        <v>3.27</v>
+        <v>2.31</v>
       </c>
       <c r="O33">
         <v>0</v>
@@ -4838,10 +4838,10 @@
         <v>0</v>
       </c>
       <c r="AB33">
+        <v>1.7</v>
+      </c>
+      <c r="AC33">
         <v>1.95</v>
-      </c>
-      <c r="AC33">
-        <v>1.75</v>
       </c>
       <c r="AD33">
         <v>0</v>
@@ -4879,7 +4879,7 @@
         <v>49</v>
       </c>
       <c r="C34" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="D34" t="s">
         <v>89</v>
@@ -4906,13 +4906,13 @@
         <v>219</v>
       </c>
       <c r="L34">
-        <v>2.24</v>
+        <v>2.99</v>
       </c>
       <c r="M34">
-        <v>2.96</v>
+        <v>3.21</v>
       </c>
       <c r="N34">
-        <v>2.98</v>
+        <v>2.36</v>
       </c>
       <c r="O34">
         <v>0</v>
@@ -4954,16 +4954,16 @@
         <v>0</v>
       </c>
       <c r="AB34">
-        <v>2.39</v>
+        <v>1.53</v>
       </c>
       <c r="AC34">
-        <v>1.58</v>
+        <v>2.35</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF34">
         <v>0</v>
@@ -5022,13 +5022,13 @@
         <v>219</v>
       </c>
       <c r="L35">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M35">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N35">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O35">
         <v>0</v>
@@ -5111,7 +5111,7 @@
         <v>50</v>
       </c>
       <c r="C36" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D36" t="s">
         <v>90</v>
@@ -5138,13 +5138,13 @@
         <v>219</v>
       </c>
       <c r="L36">
-        <v>1.51</v>
+        <v>4.3</v>
       </c>
       <c r="M36">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="N36">
-        <v>5.8</v>
+        <v>1.72</v>
       </c>
       <c r="O36">
         <v>0</v>
@@ -5186,10 +5186,10 @@
         <v>0</v>
       </c>
       <c r="AB36">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AC36">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="AD36">
         <v>0</v>
@@ -5227,7 +5227,7 @@
         <v>50</v>
       </c>
       <c r="C37" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D37" t="s">
         <v>90</v>
@@ -5343,10 +5343,10 @@
         <v>50</v>
       </c>
       <c r="C38" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D38" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E38" t="s">
         <v>127</v>
@@ -5370,13 +5370,13 @@
         <v>219</v>
       </c>
       <c r="L38">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M38">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N38">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="O38">
         <v>0</v>
@@ -5418,10 +5418,10 @@
         <v>0</v>
       </c>
       <c r="AB38">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC38">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AD38">
         <v>0</v>
@@ -5459,7 +5459,7 @@
         <v>50</v>
       </c>
       <c r="C39" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D39" t="s">
         <v>90</v>
@@ -5486,13 +5486,13 @@
         <v>219</v>
       </c>
       <c r="L39">
-        <v>2.06</v>
+        <v>1.51</v>
       </c>
       <c r="M39">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="N39">
-        <v>3.15</v>
+        <v>5.8</v>
       </c>
       <c r="O39">
         <v>0</v>
@@ -5534,10 +5534,10 @@
         <v>0</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD39">
         <v>0</v>
@@ -5691,7 +5691,7 @@
         <v>50</v>
       </c>
       <c r="C41" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D41" t="s">
         <v>90</v>
@@ -5718,13 +5718,13 @@
         <v>219</v>
       </c>
       <c r="L41">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M41">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O41">
         <v>0</v>
@@ -5923,10 +5923,10 @@
         <v>50</v>
       </c>
       <c r="C43" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D43" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E43" t="s">
         <v>132</v>
@@ -5950,13 +5950,13 @@
         <v>219</v>
       </c>
       <c r="L43">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M43">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O43">
         <v>0</v>
@@ -6503,7 +6503,7 @@
         <v>52</v>
       </c>
       <c r="C48" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D48" t="s">
         <v>90</v>
@@ -6530,13 +6530,13 @@
         <v>219</v>
       </c>
       <c r="L48">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M48">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N48">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O48">
         <v>0</v>
@@ -6578,10 +6578,10 @@
         <v>0</v>
       </c>
       <c r="AB48">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC48">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD48">
         <v>0</v>
@@ -7199,7 +7199,7 @@
         <v>52</v>
       </c>
       <c r="C54" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D54" t="s">
         <v>90</v>
@@ -7226,13 +7226,13 @@
         <v>219</v>
       </c>
       <c r="L54">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M54">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O54">
         <v>0</v>
@@ -7274,10 +7274,10 @@
         <v>0</v>
       </c>
       <c r="AB54">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC54">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD54">
         <v>0</v>
@@ -7806,13 +7806,13 @@
         <v>219</v>
       </c>
       <c r="L59">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="M59">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="N59">
-        <v>1.84</v>
+        <v>1.52</v>
       </c>
       <c r="O59">
         <v>0</v>
@@ -7854,10 +7854,10 @@
         <v>0</v>
       </c>
       <c r="AB59">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="AC59">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="AD59">
         <v>0</v>
@@ -7922,13 +7922,13 @@
         <v>219</v>
       </c>
       <c r="L60">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="M60">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="N60">
-        <v>1.52</v>
+        <v>1.84</v>
       </c>
       <c r="O60">
         <v>0</v>
@@ -7970,10 +7970,10 @@
         <v>0</v>
       </c>
       <c r="AB60">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="AC60">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="AD60">
         <v>0</v>

--- a/jogos_2025-08-01.xlsx
+++ b/jogos_2025-08-01.xlsx
@@ -202,33 +202,33 @@
     <t>Uzbekistan Uzbekistan Super League</t>
   </si>
   <si>
+    <t>Finland Veikkausliiga</t>
+  </si>
+  <si>
     <t>Belarus Vysheyshaya Liga</t>
   </si>
   <si>
-    <t>Finland Veikkausliiga</t>
-  </si>
-  <si>
     <t>Slovenia PrvaLiga</t>
   </si>
   <si>
+    <t>Bulgaria First League</t>
+  </si>
+  <si>
+    <t>Austria 2. Liga</t>
+  </si>
+  <si>
+    <t>Romania Liga I</t>
+  </si>
+  <si>
+    <t>Denmark Superliga</t>
+  </si>
+  <si>
+    <t>Poland 1. Liga</t>
+  </si>
+  <si>
     <t>Poland Ekstraklasa</t>
   </si>
   <si>
-    <t>Denmark Superliga</t>
-  </si>
-  <si>
-    <t>Austria 2. Liga</t>
-  </si>
-  <si>
-    <t>Bulgaria First League</t>
-  </si>
-  <si>
-    <t>Romania Liga I</t>
-  </si>
-  <si>
-    <t>Poland 1. Liga</t>
-  </si>
-  <si>
     <t>Estonia Meistriliiga</t>
   </si>
   <si>
@@ -244,21 +244,21 @@
     <t>Hungary NB I</t>
   </si>
   <si>
+    <t>Germany 2. Bundesliga</t>
+  </si>
+  <si>
     <t>Austria Bundesliga</t>
   </si>
   <si>
-    <t>Germany 2. Bundesliga</t>
+    <t>Scotland Championship</t>
+  </si>
+  <si>
+    <t>Republic of Ireland Premier Division</t>
   </si>
   <si>
     <t>Republic of Ireland First Division</t>
   </si>
   <si>
-    <t>Republic of Ireland Premier Division</t>
-  </si>
-  <si>
-    <t>Scotland Championship</t>
-  </si>
-  <si>
     <t>Belgium Pro League</t>
   </si>
   <si>
@@ -301,54 +301,54 @@
     <t>Neftchi</t>
   </si>
   <si>
+    <t>VPS</t>
+  </si>
+  <si>
+    <t>Buxoro</t>
+  </si>
+  <si>
     <t>Smorgon</t>
   </si>
   <si>
-    <t>Buxoro</t>
-  </si>
-  <si>
     <t>Rukh Vynnyky</t>
   </si>
   <si>
-    <t>VPS</t>
-  </si>
-  <si>
     <t>BATE</t>
   </si>
   <si>
     <t>Radomlje</t>
   </si>
   <si>
+    <t>Spartak Varna</t>
+  </si>
+  <si>
+    <t>Amstetten</t>
+  </si>
+  <si>
+    <t>SSC Farul</t>
+  </si>
+  <si>
+    <t>Austria Salzburg</t>
+  </si>
+  <si>
+    <t>Kapfenberger SV</t>
+  </si>
+  <si>
+    <t>Fredericia</t>
+  </si>
+  <si>
+    <t>Wieczysta Kraków</t>
+  </si>
+  <si>
     <t>Zagłębie Lubin</t>
   </si>
   <si>
-    <t>Fredericia</t>
-  </si>
-  <si>
     <t>Liefering</t>
   </si>
   <si>
-    <t>Spartak Varna</t>
-  </si>
-  <si>
-    <t>SSC Farul</t>
-  </si>
-  <si>
-    <t>Kapfenberger SV</t>
-  </si>
-  <si>
-    <t>Austria Salzburg</t>
-  </si>
-  <si>
     <t>SV Stripfing Weiden</t>
   </si>
   <si>
-    <t>Wieczysta Kraków</t>
-  </si>
-  <si>
-    <t>Amstetten</t>
-  </si>
-  <si>
     <t>Tallinna FC Levadia</t>
   </si>
   <si>
@@ -364,18 +364,21 @@
     <t>Lokomotiva Zagreb</t>
   </si>
   <si>
+    <t>Debrecen</t>
+  </si>
+  <si>
     <t>Vejle</t>
   </si>
   <si>
-    <t>Debrecen</t>
-  </si>
-  <si>
     <t>CSKA 1948 Sofia</t>
   </si>
   <si>
     <t>Wisła Płock</t>
   </si>
   <si>
+    <t>Schalke 04</t>
+  </si>
+  <si>
     <t>Petrolul 52</t>
   </si>
   <si>
@@ -385,87 +388,84 @@
     <t>LASK Linz</t>
   </si>
   <si>
-    <t>Schalke 04</t>
+    <t>Arbroath</t>
+  </si>
+  <si>
+    <t>Waterford</t>
+  </si>
+  <si>
+    <t>Wexford</t>
+  </si>
+  <si>
+    <t>UCD</t>
+  </si>
+  <si>
+    <t>Bray Wanderers</t>
+  </si>
+  <si>
+    <t>Kerry</t>
+  </si>
+  <si>
+    <t>Cork City</t>
   </si>
   <si>
     <t>Cobh Ramblers</t>
   </si>
   <si>
-    <t>UCD</t>
-  </si>
-  <si>
-    <t>Waterford</t>
-  </si>
-  <si>
-    <t>Arbroath</t>
-  </si>
-  <si>
     <t>Bohemians</t>
   </si>
   <si>
-    <t>Cork City</t>
-  </si>
-  <si>
-    <t>Kerry</t>
-  </si>
-  <si>
-    <t>Bray Wanderers</t>
-  </si>
-  <si>
-    <t>Wexford</t>
-  </si>
-  <si>
     <t>KV Mechelen</t>
   </si>
   <si>
+    <t>Luton Town</t>
+  </si>
+  <si>
     <t>Shamrock Rovers</t>
   </si>
   <si>
-    <t>Luton Town</t>
-  </si>
-  <si>
     <t>Ypiranga Erechim</t>
   </si>
   <si>
+    <t>Maringá</t>
+  </si>
+  <si>
+    <t>Ituano</t>
+  </si>
+  <si>
+    <t>Náutico</t>
+  </si>
+  <si>
     <t>ABC</t>
   </si>
   <si>
     <t>São Bernardo</t>
   </si>
   <si>
+    <t>Confiança</t>
+  </si>
+  <si>
+    <t>Remo</t>
+  </si>
+  <si>
+    <t>Brusque</t>
+  </si>
+  <si>
     <t>Ponte Preta</t>
   </si>
   <si>
-    <t>Maringá</t>
-  </si>
-  <si>
-    <t>Náutico</t>
-  </si>
-  <si>
-    <t>Ituano</t>
-  </si>
-  <si>
-    <t>Remo</t>
-  </si>
-  <si>
-    <t>Confiança</t>
-  </si>
-  <si>
-    <t>Brusque</t>
-  </si>
-  <si>
     <t>CSA</t>
   </si>
   <si>
     <t>Audax Italiano</t>
   </si>
   <si>
+    <t>Racing Louisville</t>
+  </si>
+  <si>
     <t>Chicago Red Stars</t>
   </si>
   <si>
-    <t>Racing Louisville</t>
-  </si>
-  <si>
     <t>Tulsa Roughnecks</t>
   </si>
   <si>
@@ -493,54 +493,54 @@
     <t>Bunyodkor</t>
   </si>
   <si>
+    <t>Mariehamn</t>
+  </si>
+  <si>
+    <t>AGMK</t>
+  </si>
+  <si>
     <t>Dinamo Minsk</t>
   </si>
   <si>
-    <t>AGMK</t>
-  </si>
-  <si>
     <t>SK Poltava</t>
   </si>
   <si>
-    <t>Mariehamn</t>
-  </si>
-  <si>
     <t>Vitebsk</t>
   </si>
   <si>
     <t>Domžale</t>
   </si>
   <si>
+    <t>Botev Vratsa</t>
+  </si>
+  <si>
+    <t>Sturm Graz II</t>
+  </si>
+  <si>
+    <t>Metaloglobus</t>
+  </si>
+  <si>
+    <t>Austria Klagenfurt</t>
+  </si>
+  <si>
+    <t>Admira</t>
+  </si>
+  <si>
+    <t>København</t>
+  </si>
+  <si>
+    <t>Znicz Pruszków</t>
+  </si>
+  <si>
     <t>Korona Kielce</t>
   </si>
   <si>
-    <t>København</t>
-  </si>
-  <si>
     <t>Austria Lustenau</t>
   </si>
   <si>
-    <t>Botev Vratsa</t>
-  </si>
-  <si>
-    <t>Metaloglobus</t>
-  </si>
-  <si>
-    <t>Admira</t>
-  </si>
-  <si>
-    <t>Austria Klagenfurt</t>
-  </si>
-  <si>
     <t>First Vienna</t>
   </si>
   <si>
-    <t>Znicz Pruszków</t>
-  </si>
-  <si>
-    <t>Sturm Graz II</t>
-  </si>
-  <si>
     <t>Kuressaare</t>
   </si>
   <si>
@@ -556,18 +556,21 @@
     <t>HNK Vukovar 1991</t>
   </si>
   <si>
+    <t>MTK</t>
+  </si>
+  <si>
     <t>OB</t>
   </si>
   <si>
-    <t>MTK</t>
-  </si>
-  <si>
     <t>Septemvri Sofia</t>
   </si>
   <si>
     <t>Piast Gliwice</t>
   </si>
   <si>
+    <t>Hertha BSC</t>
+  </si>
+  <si>
     <t>UTA Arad</t>
   </si>
   <si>
@@ -577,85 +580,82 @@
     <t>Sturm Graz</t>
   </si>
   <si>
-    <t>Hertha BSC</t>
+    <t>Ayr United</t>
+  </si>
+  <si>
+    <t>St Patrick's Athl.</t>
+  </si>
+  <si>
+    <t>Finn Harps</t>
+  </si>
+  <si>
+    <t>Dundalk</t>
+  </si>
+  <si>
+    <t>Treaty United</t>
+  </si>
+  <si>
+    <t>Athlone Town</t>
+  </si>
+  <si>
+    <t>Galway United</t>
   </si>
   <si>
     <t>Longford Town</t>
   </si>
   <si>
-    <t>Dundalk</t>
-  </si>
-  <si>
-    <t>St Patrick's Athl.</t>
-  </si>
-  <si>
-    <t>Ayr United</t>
-  </si>
-  <si>
     <t>Drogheda United</t>
   </si>
   <si>
-    <t>Galway United</t>
-  </si>
-  <si>
-    <t>Athlone Town</t>
-  </si>
-  <si>
-    <t>Treaty United</t>
-  </si>
-  <si>
-    <t>Finn Harps</t>
-  </si>
-  <si>
     <t>Club Brugge</t>
   </si>
   <si>
+    <t>AFC Wimbledon</t>
+  </si>
+  <si>
     <t>Derry City</t>
   </si>
   <si>
-    <t>AFC Wimbledon</t>
-  </si>
-  <si>
     <t>Caxias</t>
   </si>
   <si>
+    <t>Floresta</t>
+  </si>
+  <si>
+    <t>Londrina</t>
+  </si>
+  <si>
+    <t>Retrô</t>
+  </si>
+  <si>
     <t>Figueirense</t>
   </si>
   <si>
     <t>Tombense</t>
   </si>
   <si>
+    <t>Anápolis</t>
+  </si>
+  <si>
+    <t>Ferroviária</t>
+  </si>
+  <si>
+    <t>Itabaiana</t>
+  </si>
+  <si>
     <t>Guarani</t>
   </si>
   <si>
-    <t>Floresta</t>
-  </si>
-  <si>
-    <t>Retrô</t>
-  </si>
-  <si>
-    <t>Londrina</t>
-  </si>
-  <si>
-    <t>Ferroviária</t>
-  </si>
-  <si>
-    <t>Anápolis</t>
-  </si>
-  <si>
-    <t>Itabaiana</t>
-  </si>
-  <si>
     <t>Botafogo PB</t>
   </si>
   <si>
     <t>Palestino</t>
   </si>
   <si>
+    <t>Kansas City</t>
+  </si>
+  <si>
     <t>Gotham FC</t>
-  </si>
-  <si>
-    <t>Kansas City</t>
   </si>
   <si>
     <t>Loudoun United</t>
@@ -1658,13 +1658,13 @@
         <v>219</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -1706,10 +1706,10 @@
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD6">
         <v>0</v>
@@ -1863,10 +1863,10 @@
         <v>40</v>
       </c>
       <c r="C8" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E8" t="s">
         <v>97</v>
@@ -1890,13 +1890,13 @@
         <v>219</v>
       </c>
       <c r="L8">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M8">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N8">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="O8">
         <v>0</v>
@@ -1932,10 +1932,10 @@
         <v>0</v>
       </c>
       <c r="Z8">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA8">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AB8">
         <v>0</v>
@@ -1979,10 +1979,10 @@
         <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E9" t="s">
         <v>98</v>
@@ -2006,13 +2006,13 @@
         <v>219</v>
       </c>
       <c r="L9">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="M9">
-        <v>3.98</v>
+        <v>3.41</v>
       </c>
       <c r="N9">
-        <v>4.33</v>
+        <v>5.9</v>
       </c>
       <c r="O9">
         <v>0</v>
@@ -2048,16 +2048,16 @@
         <v>0</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AB9">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC9">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD9">
         <v>0</v>
@@ -2095,7 +2095,7 @@
         <v>41</v>
       </c>
       <c r="C10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D10" t="s">
         <v>90</v>
@@ -2354,13 +2354,13 @@
         <v>219</v>
       </c>
       <c r="L12">
-        <v>2.13</v>
+        <v>2.47</v>
       </c>
       <c r="M12">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
       <c r="N12">
-        <v>2.99</v>
+        <v>2.7</v>
       </c>
       <c r="O12">
         <v>0</v>
@@ -2402,10 +2402,10 @@
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC12">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD12">
         <v>0</v>
@@ -2470,13 +2470,13 @@
         <v>219</v>
       </c>
       <c r="L13">
-        <v>9.199999999999999</v>
+        <v>1.73</v>
       </c>
       <c r="M13">
-        <v>5.6</v>
+        <v>3.82</v>
       </c>
       <c r="N13">
-        <v>1.27</v>
+        <v>3.57</v>
       </c>
       <c r="O13">
         <v>0</v>
@@ -2586,13 +2586,13 @@
         <v>219</v>
       </c>
       <c r="L14">
-        <v>2.54</v>
+        <v>1.45</v>
       </c>
       <c r="M14">
-        <v>3.21</v>
+        <v>3.7</v>
       </c>
       <c r="N14">
-        <v>2.41</v>
+        <v>6.3</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -2634,10 +2634,10 @@
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="AC14">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="AD14">
         <v>0</v>
@@ -2675,7 +2675,7 @@
         <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D15" t="s">
         <v>89</v>
@@ -2702,13 +2702,13 @@
         <v>219</v>
       </c>
       <c r="L15">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="M15">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N15">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O15">
         <v>0</v>
@@ -2791,7 +2791,7 @@
         <v>43</v>
       </c>
       <c r="C16" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D16" t="s">
         <v>89</v>
@@ -2818,13 +2818,13 @@
         <v>219</v>
       </c>
       <c r="L16">
-        <v>1.45</v>
+        <v>3.62</v>
       </c>
       <c r="M16">
         <v>3.7</v>
       </c>
       <c r="N16">
-        <v>6.3</v>
+        <v>1.75</v>
       </c>
       <c r="O16">
         <v>0</v>
@@ -2866,10 +2866,10 @@
         <v>0</v>
       </c>
       <c r="AB16">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC16">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD16">
         <v>0</v>
@@ -2907,7 +2907,7 @@
         <v>43</v>
       </c>
       <c r="C17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D17" t="s">
         <v>89</v>
@@ -2934,13 +2934,13 @@
         <v>219</v>
       </c>
       <c r="L17">
-        <v>3.62</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M17">
-        <v>3.7</v>
+        <v>5.6</v>
       </c>
       <c r="N17">
-        <v>1.75</v>
+        <v>1.27</v>
       </c>
       <c r="O17">
         <v>0</v>
@@ -3023,7 +3023,7 @@
         <v>43</v>
       </c>
       <c r="C18" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D18" t="s">
         <v>89</v>
@@ -3050,13 +3050,13 @@
         <v>219</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -3139,7 +3139,7 @@
         <v>43</v>
       </c>
       <c r="C19" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D19" t="s">
         <v>89</v>
@@ -3166,13 +3166,13 @@
         <v>219</v>
       </c>
       <c r="L19">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="M19">
-        <v>3.21</v>
+        <v>3.17</v>
       </c>
       <c r="N19">
-        <v>2.68</v>
+        <v>2.99</v>
       </c>
       <c r="O19">
         <v>0</v>
@@ -3214,10 +3214,10 @@
         <v>0</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD19">
         <v>0</v>
@@ -3255,7 +3255,7 @@
         <v>43</v>
       </c>
       <c r="C20" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D20" t="s">
         <v>89</v>
@@ -3282,13 +3282,13 @@
         <v>219</v>
       </c>
       <c r="L20">
-        <v>1.42</v>
+        <v>2.54</v>
       </c>
       <c r="M20">
-        <v>4.2</v>
+        <v>3.21</v>
       </c>
       <c r="N20">
-        <v>5.6</v>
+        <v>2.41</v>
       </c>
       <c r="O20">
         <v>0</v>
@@ -3330,10 +3330,10 @@
         <v>0</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD20">
         <v>0</v>
@@ -3371,7 +3371,7 @@
         <v>43</v>
       </c>
       <c r="C21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D21" t="s">
         <v>89</v>
@@ -3398,13 +3398,13 @@
         <v>219</v>
       </c>
       <c r="L21">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="M21">
-        <v>3.82</v>
+        <v>3.21</v>
       </c>
       <c r="N21">
-        <v>3.57</v>
+        <v>2.68</v>
       </c>
       <c r="O21">
         <v>0</v>
@@ -3630,13 +3630,13 @@
         <v>219</v>
       </c>
       <c r="L23">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="M23">
-        <v>3.26</v>
+        <v>3.3</v>
       </c>
       <c r="N23">
-        <v>3.09</v>
+        <v>3.15</v>
       </c>
       <c r="O23">
         <v>0</v>
@@ -4067,7 +4067,7 @@
         <v>47</v>
       </c>
       <c r="C27" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="D27" t="s">
         <v>89</v>
@@ -4094,13 +4094,13 @@
         <v>219</v>
       </c>
       <c r="L27">
-        <v>2.7</v>
+        <v>1.89</v>
       </c>
       <c r="M27">
+        <v>3.75</v>
+      </c>
+      <c r="N27">
         <v>3.5</v>
-      </c>
-      <c r="N27">
-        <v>2.41</v>
       </c>
       <c r="O27">
         <v>0</v>
@@ -4183,7 +4183,7 @@
         <v>47</v>
       </c>
       <c r="C28" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="D28" t="s">
         <v>89</v>
@@ -4210,13 +4210,13 @@
         <v>219</v>
       </c>
       <c r="L28">
-        <v>1.89</v>
+        <v>2.7</v>
       </c>
       <c r="M28">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="N28">
-        <v>3.5</v>
+        <v>2.41</v>
       </c>
       <c r="O28">
         <v>0</v>
@@ -4299,7 +4299,7 @@
         <v>48</v>
       </c>
       <c r="C29" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D29" t="s">
         <v>89</v>
@@ -4326,13 +4326,13 @@
         <v>219</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O29">
         <v>0</v>
@@ -4374,10 +4374,10 @@
         <v>0</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD29">
         <v>0</v>
@@ -4415,7 +4415,7 @@
         <v>49</v>
       </c>
       <c r="C30" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D30" t="s">
         <v>89</v>
@@ -4531,7 +4531,7 @@
         <v>49</v>
       </c>
       <c r="C31" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="D31" t="s">
         <v>89</v>
@@ -4558,13 +4558,13 @@
         <v>219</v>
       </c>
       <c r="L31">
-        <v>2.24</v>
+        <v>2.99</v>
       </c>
       <c r="M31">
-        <v>2.96</v>
+        <v>3.21</v>
       </c>
       <c r="N31">
-        <v>2.98</v>
+        <v>2.36</v>
       </c>
       <c r="O31">
         <v>0</v>
@@ -4606,16 +4606,16 @@
         <v>0</v>
       </c>
       <c r="AB31">
-        <v>2.39</v>
+        <v>1.53</v>
       </c>
       <c r="AC31">
-        <v>1.58</v>
+        <v>2.35</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF31">
         <v>0</v>
@@ -4647,7 +4647,7 @@
         <v>49</v>
       </c>
       <c r="C32" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D32" t="s">
         <v>89</v>
@@ -4674,13 +4674,13 @@
         <v>219</v>
       </c>
       <c r="L32">
-        <v>2.02</v>
+        <v>2.24</v>
       </c>
       <c r="M32">
-        <v>3.13</v>
+        <v>2.96</v>
       </c>
       <c r="N32">
-        <v>3.27</v>
+        <v>2.98</v>
       </c>
       <c r="O32">
         <v>0</v>
@@ -4722,10 +4722,10 @@
         <v>0</v>
       </c>
       <c r="AB32">
-        <v>1.95</v>
+        <v>2.39</v>
       </c>
       <c r="AC32">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="AD32">
         <v>0</v>
@@ -4763,7 +4763,7 @@
         <v>49</v>
       </c>
       <c r="C33" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="D33" t="s">
         <v>89</v>
@@ -4790,13 +4790,13 @@
         <v>219</v>
       </c>
       <c r="L33">
-        <v>2.88</v>
+        <v>2.02</v>
       </c>
       <c r="M33">
-        <v>2.96</v>
+        <v>3.13</v>
       </c>
       <c r="N33">
-        <v>2.31</v>
+        <v>3.27</v>
       </c>
       <c r="O33">
         <v>0</v>
@@ -4838,10 +4838,10 @@
         <v>0</v>
       </c>
       <c r="AB33">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AC33">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AD33">
         <v>0</v>
@@ -4906,13 +4906,13 @@
         <v>219</v>
       </c>
       <c r="L34">
-        <v>2.99</v>
+        <v>2.88</v>
       </c>
       <c r="M34">
-        <v>3.21</v>
+        <v>2.96</v>
       </c>
       <c r="N34">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="O34">
         <v>0</v>
@@ -4954,16 +4954,16 @@
         <v>0</v>
       </c>
       <c r="AB34">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AC34">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AD34">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE34">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF34">
         <v>0</v>
@@ -4998,7 +4998,7 @@
         <v>78</v>
       </c>
       <c r="D35" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E35" t="s">
         <v>124</v>
@@ -5022,13 +5022,13 @@
         <v>219</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M35">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O35">
         <v>0</v>
@@ -5070,10 +5070,10 @@
         <v>0</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD35">
         <v>0</v>
@@ -5111,7 +5111,7 @@
         <v>50</v>
       </c>
       <c r="C36" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D36" t="s">
         <v>90</v>
@@ -5138,13 +5138,13 @@
         <v>219</v>
       </c>
       <c r="L36">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M36">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N36">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="O36">
         <v>0</v>
@@ -5186,10 +5186,10 @@
         <v>0</v>
       </c>
       <c r="AB36">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC36">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AD36">
         <v>0</v>
@@ -5227,7 +5227,7 @@
         <v>50</v>
       </c>
       <c r="C37" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D37" t="s">
         <v>90</v>
@@ -5254,13 +5254,13 @@
         <v>219</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M37">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O37">
         <v>0</v>
@@ -5346,7 +5346,7 @@
         <v>80</v>
       </c>
       <c r="D38" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E38" t="s">
         <v>127</v>
@@ -5370,13 +5370,13 @@
         <v>219</v>
       </c>
       <c r="L38">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M38">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O38">
         <v>0</v>
@@ -5418,10 +5418,10 @@
         <v>0</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AD38">
         <v>0</v>
@@ -5459,7 +5459,7 @@
         <v>50</v>
       </c>
       <c r="C39" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D39" t="s">
         <v>90</v>
@@ -5486,13 +5486,13 @@
         <v>219</v>
       </c>
       <c r="L39">
-        <v>1.51</v>
+        <v>2.04</v>
       </c>
       <c r="M39">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="N39">
-        <v>5.8</v>
+        <v>3.15</v>
       </c>
       <c r="O39">
         <v>0</v>
@@ -5534,10 +5534,10 @@
         <v>0</v>
       </c>
       <c r="AB39">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC39">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD39">
         <v>0</v>
@@ -5575,7 +5575,7 @@
         <v>50</v>
       </c>
       <c r="C40" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D40" t="s">
         <v>90</v>
@@ -5602,13 +5602,13 @@
         <v>219</v>
       </c>
       <c r="L40">
-        <v>2.85</v>
+        <v>2.06</v>
       </c>
       <c r="M40">
+        <v>3.35</v>
+      </c>
+      <c r="N40">
         <v>3.15</v>
-      </c>
-      <c r="N40">
-        <v>2.31</v>
       </c>
       <c r="O40">
         <v>0</v>
@@ -5691,7 +5691,7 @@
         <v>50</v>
       </c>
       <c r="C41" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D41" t="s">
         <v>90</v>
@@ -5718,13 +5718,13 @@
         <v>219</v>
       </c>
       <c r="L41">
-        <v>2.06</v>
+        <v>2.85</v>
       </c>
       <c r="M41">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="N41">
-        <v>3.15</v>
+        <v>2.31</v>
       </c>
       <c r="O41">
         <v>0</v>
@@ -5807,7 +5807,7 @@
         <v>50</v>
       </c>
       <c r="C42" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D42" t="s">
         <v>90</v>
@@ -5834,13 +5834,13 @@
         <v>219</v>
       </c>
       <c r="L42">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M42">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="O42">
         <v>0</v>
@@ -5923,7 +5923,7 @@
         <v>50</v>
       </c>
       <c r="C43" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D43" t="s">
         <v>90</v>
@@ -5950,13 +5950,13 @@
         <v>219</v>
       </c>
       <c r="L43">
-        <v>2</v>
+        <v>1.51</v>
       </c>
       <c r="M43">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="N43">
-        <v>3.15</v>
+        <v>5.8</v>
       </c>
       <c r="O43">
         <v>0</v>
@@ -5998,10 +5998,10 @@
         <v>0</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD43">
         <v>0</v>
@@ -6155,10 +6155,10 @@
         <v>51</v>
       </c>
       <c r="C45" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D45" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E45" t="s">
         <v>134</v>
@@ -6182,13 +6182,13 @@
         <v>219</v>
       </c>
       <c r="L45">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M45">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O45">
         <v>0</v>
@@ -6230,10 +6230,10 @@
         <v>0</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC45">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD45">
         <v>0</v>
@@ -6271,10 +6271,10 @@
         <v>51</v>
       </c>
       <c r="C46" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D46" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E46" t="s">
         <v>135</v>
@@ -6298,13 +6298,13 @@
         <v>219</v>
       </c>
       <c r="L46">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M46">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N46">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O46">
         <v>0</v>
@@ -6346,10 +6346,10 @@
         <v>0</v>
       </c>
       <c r="AB46">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC46">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD46">
         <v>0</v>
@@ -7806,13 +7806,13 @@
         <v>219</v>
       </c>
       <c r="L59">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="M59">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="N59">
-        <v>1.52</v>
+        <v>1.84</v>
       </c>
       <c r="O59">
         <v>0</v>
@@ -7854,10 +7854,10 @@
         <v>0</v>
       </c>
       <c r="AB59">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="AC59">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="AD59">
         <v>0</v>
@@ -7922,13 +7922,13 @@
         <v>219</v>
       </c>
       <c r="L60">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="M60">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="N60">
-        <v>1.84</v>
+        <v>1.52</v>
       </c>
       <c r="O60">
         <v>0</v>
@@ -7970,10 +7970,10 @@
         <v>0</v>
       </c>
       <c r="AB60">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="AC60">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="AD60">
         <v>0</v>
@@ -8086,10 +8086,10 @@
         <v>0</v>
       </c>
       <c r="AB61">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="AC61">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AD61">
         <v>0</v>
@@ -8318,10 +8318,10 @@
         <v>0</v>
       </c>
       <c r="AB63">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AC63">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AD63">
         <v>0</v>

--- a/jogos_2025-08-01.xlsx
+++ b/jogos_2025-08-01.xlsx
@@ -196,12 +196,12 @@
     <t>Ukraine Ukrainian Premier League</t>
   </si>
   <si>
+    <t>Uzbekistan Uzbekistan Super League</t>
+  </si>
+  <si>
     <t>Switzerland Challenge League</t>
   </si>
   <si>
-    <t>Uzbekistan Uzbekistan Super League</t>
-  </si>
-  <si>
     <t>Finland Veikkausliiga</t>
   </si>
   <si>
@@ -211,33 +211,33 @@
     <t>Slovenia PrvaLiga</t>
   </si>
   <si>
+    <t>Poland Ekstraklasa</t>
+  </si>
+  <si>
+    <t>Poland 1. Liga</t>
+  </si>
+  <si>
+    <t>Austria 2. Liga</t>
+  </si>
+  <si>
+    <t>Romania Liga I</t>
+  </si>
+  <si>
+    <t>Denmark Superliga</t>
+  </si>
+  <si>
     <t>Bulgaria First League</t>
   </si>
   <si>
-    <t>Austria 2. Liga</t>
-  </si>
-  <si>
-    <t>Romania Liga I</t>
-  </si>
-  <si>
-    <t>Denmark Superliga</t>
-  </si>
-  <si>
-    <t>Poland 1. Liga</t>
-  </si>
-  <si>
-    <t>Poland Ekstraklasa</t>
-  </si>
-  <si>
     <t>Estonia Meistriliiga</t>
   </si>
   <si>
+    <t>Germany 3. Liga</t>
+  </si>
+  <si>
     <t>Sweden Superettan</t>
   </si>
   <si>
-    <t>Germany 3. Liga</t>
-  </si>
-  <si>
     <t>Croatia Prva HNL</t>
   </si>
   <si>
@@ -250,18 +250,18 @@
     <t>Austria Bundesliga</t>
   </si>
   <si>
+    <t>Republic of Ireland First Division</t>
+  </si>
+  <si>
+    <t>Republic of Ireland Premier Division</t>
+  </si>
+  <si>
+    <t>Belgium Pro League</t>
+  </si>
+  <si>
     <t>Scotland Championship</t>
   </si>
   <si>
-    <t>Republic of Ireland Premier Division</t>
-  </si>
-  <si>
-    <t>Republic of Ireland First Division</t>
-  </si>
-  <si>
-    <t>Belgium Pro League</t>
-  </si>
-  <si>
     <t>England EFL League One</t>
   </si>
   <si>
@@ -292,171 +292,171 @@
     <t>Kolos Kovalivka</t>
   </si>
   <si>
+    <t>Neftchi</t>
+  </si>
+  <si>
+    <t>Dinamo Samarqand</t>
+  </si>
+  <si>
     <t>Wil</t>
   </si>
   <si>
-    <t>Dinamo Samarqand</t>
-  </si>
-  <si>
-    <t>Neftchi</t>
+    <t>Rukh Vynnyky</t>
+  </si>
+  <si>
+    <t>Buxoro</t>
   </si>
   <si>
     <t>VPS</t>
   </si>
   <si>
-    <t>Buxoro</t>
-  </si>
-  <si>
     <t>Smorgon</t>
   </si>
   <si>
-    <t>Rukh Vynnyky</t>
-  </si>
-  <si>
     <t>BATE</t>
   </si>
   <si>
     <t>Radomlje</t>
   </si>
   <si>
+    <t>Zagłębie Lubin</t>
+  </si>
+  <si>
+    <t>Wieczysta Kraków</t>
+  </si>
+  <si>
+    <t>Amstetten</t>
+  </si>
+  <si>
+    <t>Kapfenberger SV</t>
+  </si>
+  <si>
+    <t>SSC Farul</t>
+  </si>
+  <si>
+    <t>SV Stripfing Weiden</t>
+  </si>
+  <si>
+    <t>Austria Salzburg</t>
+  </si>
+  <si>
+    <t>Liefering</t>
+  </si>
+  <si>
+    <t>Fredericia</t>
+  </si>
+  <si>
     <t>Spartak Varna</t>
   </si>
   <si>
-    <t>Amstetten</t>
-  </si>
-  <si>
-    <t>SSC Farul</t>
-  </si>
-  <si>
-    <t>Austria Salzburg</t>
-  </si>
-  <si>
-    <t>Kapfenberger SV</t>
-  </si>
-  <si>
-    <t>Fredericia</t>
-  </si>
-  <si>
-    <t>Wieczysta Kraków</t>
-  </si>
-  <si>
-    <t>Zagłębie Lubin</t>
-  </si>
-  <si>
-    <t>Liefering</t>
-  </si>
-  <si>
-    <t>SV Stripfing Weiden</t>
-  </si>
-  <si>
     <t>Tallinna FC Levadia</t>
   </si>
   <si>
+    <t>Rot-Weiss Essen</t>
+  </si>
+  <si>
     <t>Örebro</t>
   </si>
   <si>
-    <t>Rot-Weiss Essen</t>
-  </si>
-  <si>
     <t>Stade Nyonnais</t>
   </si>
   <si>
+    <t>Vejle</t>
+  </si>
+  <si>
     <t>Lokomotiva Zagreb</t>
   </si>
   <si>
     <t>Debrecen</t>
   </si>
   <si>
-    <t>Vejle</t>
-  </si>
-  <si>
     <t>CSKA 1948 Sofia</t>
   </si>
   <si>
+    <t>Schalke 04</t>
+  </si>
+  <si>
+    <t>LASK Linz</t>
+  </si>
+  <si>
+    <t>Petrolul 52</t>
+  </si>
+  <si>
     <t>Wisła Płock</t>
   </si>
   <si>
-    <t>Schalke 04</t>
-  </si>
-  <si>
-    <t>Petrolul 52</t>
-  </si>
-  <si>
     <t>ŁKS Łódź</t>
   </si>
   <si>
-    <t>LASK Linz</t>
+    <t>Bray Wanderers</t>
+  </si>
+  <si>
+    <t>Cork City</t>
+  </si>
+  <si>
+    <t>Wexford</t>
+  </si>
+  <si>
+    <t>Bohemians</t>
+  </si>
+  <si>
+    <t>KV Mechelen</t>
+  </si>
+  <si>
+    <t>UCD</t>
+  </si>
+  <si>
+    <t>Waterford</t>
+  </si>
+  <si>
+    <t>Kerry</t>
   </si>
   <si>
     <t>Arbroath</t>
   </si>
   <si>
-    <t>Waterford</t>
-  </si>
-  <si>
-    <t>Wexford</t>
-  </si>
-  <si>
-    <t>UCD</t>
-  </si>
-  <si>
-    <t>Bray Wanderers</t>
-  </si>
-  <si>
-    <t>Kerry</t>
-  </si>
-  <si>
-    <t>Cork City</t>
-  </si>
-  <si>
     <t>Cobh Ramblers</t>
   </si>
   <si>
-    <t>Bohemians</t>
-  </si>
-  <si>
-    <t>KV Mechelen</t>
+    <t>Shamrock Rovers</t>
   </si>
   <si>
     <t>Luton Town</t>
   </si>
   <si>
-    <t>Shamrock Rovers</t>
+    <t>Confiança</t>
+  </si>
+  <si>
+    <t>Remo</t>
+  </si>
+  <si>
+    <t>Náutico</t>
+  </si>
+  <si>
+    <t>ABC</t>
+  </si>
+  <si>
+    <t>CSA</t>
+  </si>
+  <si>
+    <t>Ponte Preta</t>
+  </si>
+  <si>
+    <t>São Bernardo</t>
+  </si>
+  <si>
+    <t>Ituano</t>
+  </si>
+  <si>
+    <t>Brusque</t>
+  </si>
+  <si>
+    <t>Maringá</t>
   </si>
   <si>
     <t>Ypiranga Erechim</t>
   </si>
   <si>
-    <t>Maringá</t>
-  </si>
-  <si>
-    <t>Ituano</t>
-  </si>
-  <si>
-    <t>Náutico</t>
-  </si>
-  <si>
-    <t>ABC</t>
-  </si>
-  <si>
-    <t>São Bernardo</t>
-  </si>
-  <si>
-    <t>Confiança</t>
-  </si>
-  <si>
-    <t>Remo</t>
-  </si>
-  <si>
-    <t>Brusque</t>
-  </si>
-  <si>
-    <t>Ponte Preta</t>
-  </si>
-  <si>
-    <t>CSA</t>
-  </si>
-  <si>
     <t>Audax Italiano</t>
   </si>
   <si>
@@ -466,12 +466,12 @@
     <t>Chicago Red Stars</t>
   </si>
   <si>
+    <t>Operário PR</t>
+  </si>
+  <si>
     <t>Tulsa Roughnecks</t>
   </si>
   <si>
-    <t>Operário PR</t>
-  </si>
-  <si>
     <t>Colorado Springs</t>
   </si>
   <si>
@@ -484,171 +484,171 @@
     <t>Hirnyk</t>
   </si>
   <si>
+    <t>Bunyodkor</t>
+  </si>
+  <si>
+    <t>Navbahor</t>
+  </si>
+  <si>
     <t>Aarau</t>
   </si>
   <si>
-    <t>Navbahor</t>
-  </si>
-  <si>
-    <t>Bunyodkor</t>
+    <t>SK Poltava</t>
+  </si>
+  <si>
+    <t>AGMK</t>
   </si>
   <si>
     <t>Mariehamn</t>
   </si>
   <si>
-    <t>AGMK</t>
-  </si>
-  <si>
     <t>Dinamo Minsk</t>
   </si>
   <si>
-    <t>SK Poltava</t>
-  </si>
-  <si>
     <t>Vitebsk</t>
   </si>
   <si>
     <t>Domžale</t>
   </si>
   <si>
+    <t>Korona Kielce</t>
+  </si>
+  <si>
+    <t>Znicz Pruszków</t>
+  </si>
+  <si>
+    <t>Sturm Graz II</t>
+  </si>
+  <si>
+    <t>Admira</t>
+  </si>
+  <si>
+    <t>Metaloglobus</t>
+  </si>
+  <si>
+    <t>First Vienna</t>
+  </si>
+  <si>
+    <t>Austria Klagenfurt</t>
+  </si>
+  <si>
+    <t>Austria Lustenau</t>
+  </si>
+  <si>
+    <t>København</t>
+  </si>
+  <si>
     <t>Botev Vratsa</t>
   </si>
   <si>
-    <t>Sturm Graz II</t>
-  </si>
-  <si>
-    <t>Metaloglobus</t>
-  </si>
-  <si>
-    <t>Austria Klagenfurt</t>
-  </si>
-  <si>
-    <t>Admira</t>
-  </si>
-  <si>
-    <t>København</t>
-  </si>
-  <si>
-    <t>Znicz Pruszków</t>
-  </si>
-  <si>
-    <t>Korona Kielce</t>
-  </si>
-  <si>
-    <t>Austria Lustenau</t>
-  </si>
-  <si>
-    <t>First Vienna</t>
-  </si>
-  <si>
     <t>Kuressaare</t>
   </si>
   <si>
+    <t>1860 München</t>
+  </si>
+  <si>
     <t>Oddevold</t>
   </si>
   <si>
-    <t>1860 München</t>
-  </si>
-  <si>
     <t>Rapperswil-Jona</t>
   </si>
   <si>
+    <t>OB</t>
+  </si>
+  <si>
     <t>HNK Vukovar 1991</t>
   </si>
   <si>
     <t>MTK</t>
   </si>
   <si>
-    <t>OB</t>
-  </si>
-  <si>
     <t>Septemvri Sofia</t>
   </si>
   <si>
+    <t>Hertha BSC</t>
+  </si>
+  <si>
+    <t>Sturm Graz</t>
+  </si>
+  <si>
+    <t>UTA Arad</t>
+  </si>
+  <si>
     <t>Piast Gliwice</t>
   </si>
   <si>
-    <t>Hertha BSC</t>
-  </si>
-  <si>
-    <t>UTA Arad</t>
-  </si>
-  <si>
     <t>Polonia Bytom</t>
   </si>
   <si>
-    <t>Sturm Graz</t>
+    <t>Treaty United</t>
+  </si>
+  <si>
+    <t>Galway United</t>
+  </si>
+  <si>
+    <t>Finn Harps</t>
+  </si>
+  <si>
+    <t>Drogheda United</t>
+  </si>
+  <si>
+    <t>Club Brugge</t>
+  </si>
+  <si>
+    <t>Dundalk</t>
+  </si>
+  <si>
+    <t>St Patrick's Athl.</t>
+  </si>
+  <si>
+    <t>Athlone Town</t>
   </si>
   <si>
     <t>Ayr United</t>
   </si>
   <si>
-    <t>St Patrick's Athl.</t>
-  </si>
-  <si>
-    <t>Finn Harps</t>
-  </si>
-  <si>
-    <t>Dundalk</t>
-  </si>
-  <si>
-    <t>Treaty United</t>
-  </si>
-  <si>
-    <t>Athlone Town</t>
-  </si>
-  <si>
-    <t>Galway United</t>
-  </si>
-  <si>
     <t>Longford Town</t>
   </si>
   <si>
-    <t>Drogheda United</t>
-  </si>
-  <si>
-    <t>Club Brugge</t>
+    <t>Derry City</t>
   </si>
   <si>
     <t>AFC Wimbledon</t>
   </si>
   <si>
-    <t>Derry City</t>
+    <t>Anápolis</t>
+  </si>
+  <si>
+    <t>Ferroviária</t>
+  </si>
+  <si>
+    <t>Retrô</t>
+  </si>
+  <si>
+    <t>Figueirense</t>
+  </si>
+  <si>
+    <t>Botafogo PB</t>
+  </si>
+  <si>
+    <t>Guarani</t>
+  </si>
+  <si>
+    <t>Tombense</t>
+  </si>
+  <si>
+    <t>Londrina</t>
+  </si>
+  <si>
+    <t>Itabaiana</t>
+  </si>
+  <si>
+    <t>Floresta</t>
   </si>
   <si>
     <t>Caxias</t>
   </si>
   <si>
-    <t>Floresta</t>
-  </si>
-  <si>
-    <t>Londrina</t>
-  </si>
-  <si>
-    <t>Retrô</t>
-  </si>
-  <si>
-    <t>Figueirense</t>
-  </si>
-  <si>
-    <t>Tombense</t>
-  </si>
-  <si>
-    <t>Anápolis</t>
-  </si>
-  <si>
-    <t>Ferroviária</t>
-  </si>
-  <si>
-    <t>Itabaiana</t>
-  </si>
-  <si>
-    <t>Guarani</t>
-  </si>
-  <si>
-    <t>Botafogo PB</t>
-  </si>
-  <si>
     <t>Palestino</t>
   </si>
   <si>
@@ -658,10 +658,10 @@
     <t>Gotham FC</t>
   </si>
   <si>
+    <t>Criciúma</t>
+  </si>
+  <si>
     <t>Loudoun United</t>
-  </si>
-  <si>
-    <t>Criciúma</t>
   </si>
   <si>
     <t>Lexington</t>
@@ -1286,7 +1286,7 @@
         <v>60</v>
       </c>
       <c r="D3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E3" t="s">
         <v>92</v>
@@ -1310,13 +1310,13 @@
         <v>219</v>
       </c>
       <c r="L3">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="M3">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N3">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O3">
         <v>0</v>
@@ -1399,7 +1399,7 @@
         <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D4" t="s">
         <v>90</v>
@@ -1518,7 +1518,7 @@
         <v>61</v>
       </c>
       <c r="D5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E5" t="s">
         <v>94</v>
@@ -1542,13 +1542,13 @@
         <v>219</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O5">
         <v>0</v>
@@ -1631,10 +1631,10 @@
         <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E6" t="s">
         <v>95</v>
@@ -1658,13 +1658,13 @@
         <v>219</v>
       </c>
       <c r="L6">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="M6">
-        <v>3.98</v>
+        <v>3.41</v>
       </c>
       <c r="N6">
-        <v>4.33</v>
+        <v>5.9</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -1700,16 +1700,16 @@
         <v>0</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AB6">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC6">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD6">
         <v>0</v>
@@ -1747,7 +1747,7 @@
         <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D7" t="s">
         <v>90</v>
@@ -1863,7 +1863,7 @@
         <v>40</v>
       </c>
       <c r="C8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D8" t="s">
         <v>90</v>
@@ -1890,13 +1890,13 @@
         <v>219</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O8">
         <v>0</v>
@@ -1938,10 +1938,10 @@
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD8">
         <v>0</v>
@@ -1979,10 +1979,10 @@
         <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E9" t="s">
         <v>98</v>
@@ -2006,13 +2006,13 @@
         <v>219</v>
       </c>
       <c r="L9">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M9">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N9">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="O9">
         <v>0</v>
@@ -2048,10 +2048,10 @@
         <v>0</v>
       </c>
       <c r="Z9">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA9">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AB9">
         <v>0</v>
@@ -2354,13 +2354,13 @@
         <v>219</v>
       </c>
       <c r="L12">
-        <v>2.47</v>
+        <v>2.13</v>
       </c>
       <c r="M12">
-        <v>3.1</v>
+        <v>3.17</v>
       </c>
       <c r="N12">
-        <v>2.7</v>
+        <v>2.99</v>
       </c>
       <c r="O12">
         <v>0</v>
@@ -2402,10 +2402,10 @@
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD12">
         <v>0</v>
@@ -2470,13 +2470,13 @@
         <v>219</v>
       </c>
       <c r="L13">
-        <v>1.73</v>
+        <v>1.42</v>
       </c>
       <c r="M13">
-        <v>3.82</v>
+        <v>4.2</v>
       </c>
       <c r="N13">
-        <v>3.57</v>
+        <v>5.6</v>
       </c>
       <c r="O13">
         <v>0</v>
@@ -2586,13 +2586,13 @@
         <v>219</v>
       </c>
       <c r="L14">
-        <v>1.45</v>
+        <v>1.73</v>
       </c>
       <c r="M14">
-        <v>3.7</v>
+        <v>3.82</v>
       </c>
       <c r="N14">
-        <v>6.3</v>
+        <v>3.57</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -2634,10 +2634,10 @@
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC14">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD14">
         <v>0</v>
@@ -2675,7 +2675,7 @@
         <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D15" t="s">
         <v>89</v>
@@ -2702,13 +2702,13 @@
         <v>219</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O15">
         <v>0</v>
@@ -2791,7 +2791,7 @@
         <v>43</v>
       </c>
       <c r="C16" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D16" t="s">
         <v>89</v>
@@ -2818,58 +2818,58 @@
         <v>219</v>
       </c>
       <c r="L16">
-        <v>3.62</v>
+        <v>1.45</v>
       </c>
       <c r="M16">
         <v>3.7</v>
       </c>
       <c r="N16">
+        <v>6.3</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>1.95</v>
+      </c>
+      <c r="AC16">
         <v>1.75</v>
-      </c>
-      <c r="O16">
-        <v>0</v>
-      </c>
-      <c r="P16">
-        <v>0</v>
-      </c>
-      <c r="Q16">
-        <v>0</v>
-      </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <v>0</v>
-      </c>
-      <c r="T16">
-        <v>0</v>
-      </c>
-      <c r="U16">
-        <v>0</v>
-      </c>
-      <c r="V16">
-        <v>0</v>
-      </c>
-      <c r="W16">
-        <v>0</v>
-      </c>
-      <c r="X16">
-        <v>0</v>
-      </c>
-      <c r="Y16">
-        <v>0</v>
-      </c>
-      <c r="Z16">
-        <v>0</v>
-      </c>
-      <c r="AA16">
-        <v>0</v>
-      </c>
-      <c r="AB16">
-        <v>0</v>
-      </c>
-      <c r="AC16">
-        <v>0</v>
       </c>
       <c r="AD16">
         <v>0</v>
@@ -2907,7 +2907,7 @@
         <v>43</v>
       </c>
       <c r="C17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D17" t="s">
         <v>89</v>
@@ -2934,13 +2934,13 @@
         <v>219</v>
       </c>
       <c r="L17">
-        <v>9.199999999999999</v>
+        <v>2.3</v>
       </c>
       <c r="M17">
-        <v>5.6</v>
+        <v>3.21</v>
       </c>
       <c r="N17">
-        <v>1.27</v>
+        <v>2.68</v>
       </c>
       <c r="O17">
         <v>0</v>
@@ -3023,7 +3023,7 @@
         <v>43</v>
       </c>
       <c r="C18" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D18" t="s">
         <v>89</v>
@@ -3050,13 +3050,13 @@
         <v>219</v>
       </c>
       <c r="L18">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M18">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N18">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -3139,7 +3139,7 @@
         <v>43</v>
       </c>
       <c r="C19" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D19" t="s">
         <v>89</v>
@@ -3166,13 +3166,13 @@
         <v>219</v>
       </c>
       <c r="L19">
-        <v>2.13</v>
+        <v>2.54</v>
       </c>
       <c r="M19">
-        <v>3.17</v>
+        <v>3.21</v>
       </c>
       <c r="N19">
-        <v>2.99</v>
+        <v>2.41</v>
       </c>
       <c r="O19">
         <v>0</v>
@@ -3214,10 +3214,10 @@
         <v>0</v>
       </c>
       <c r="AB19">
-        <v>1.89</v>
+        <v>1.77</v>
       </c>
       <c r="AC19">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="AD19">
         <v>0</v>
@@ -3255,7 +3255,7 @@
         <v>43</v>
       </c>
       <c r="C20" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D20" t="s">
         <v>89</v>
@@ -3282,13 +3282,13 @@
         <v>219</v>
       </c>
       <c r="L20">
-        <v>2.54</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M20">
-        <v>3.21</v>
+        <v>5.6</v>
       </c>
       <c r="N20">
-        <v>2.41</v>
+        <v>1.27</v>
       </c>
       <c r="O20">
         <v>0</v>
@@ -3330,10 +3330,10 @@
         <v>0</v>
       </c>
       <c r="AB20">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC20">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD20">
         <v>0</v>
@@ -3371,7 +3371,7 @@
         <v>43</v>
       </c>
       <c r="C21" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D21" t="s">
         <v>89</v>
@@ -3398,13 +3398,13 @@
         <v>219</v>
       </c>
       <c r="L21">
-        <v>2.3</v>
+        <v>2.47</v>
       </c>
       <c r="M21">
-        <v>3.21</v>
+        <v>3.1</v>
       </c>
       <c r="N21">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="O21">
         <v>0</v>
@@ -3606,7 +3606,7 @@
         <v>72</v>
       </c>
       <c r="D23" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E23" t="s">
         <v>112</v>
@@ -3630,13 +3630,13 @@
         <v>219</v>
       </c>
       <c r="L23">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M23">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N23">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O23">
         <v>0</v>
@@ -3678,10 +3678,10 @@
         <v>0</v>
       </c>
       <c r="AB23">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC23">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD23">
         <v>0</v>
@@ -3722,7 +3722,7 @@
         <v>73</v>
       </c>
       <c r="D24" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E24" t="s">
         <v>113</v>
@@ -3746,13 +3746,13 @@
         <v>219</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O24">
         <v>0</v>
@@ -3794,10 +3794,10 @@
         <v>0</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD24">
         <v>0</v>
@@ -3835,7 +3835,7 @@
         <v>46</v>
       </c>
       <c r="C25" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D25" t="s">
         <v>89</v>
@@ -3951,7 +3951,7 @@
         <v>47</v>
       </c>
       <c r="C26" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D26" t="s">
         <v>89</v>
@@ -3978,13 +3978,13 @@
         <v>219</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O26">
         <v>0</v>
@@ -4067,7 +4067,7 @@
         <v>47</v>
       </c>
       <c r="C27" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D27" t="s">
         <v>89</v>
@@ -4094,13 +4094,13 @@
         <v>219</v>
       </c>
       <c r="L27">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M27">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N27">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O27">
         <v>0</v>
@@ -4183,7 +4183,7 @@
         <v>47</v>
       </c>
       <c r="C28" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D28" t="s">
         <v>89</v>
@@ -4210,13 +4210,13 @@
         <v>219</v>
       </c>
       <c r="L28">
-        <v>2.7</v>
+        <v>1.89</v>
       </c>
       <c r="M28">
+        <v>3.75</v>
+      </c>
+      <c r="N28">
         <v>3.5</v>
-      </c>
-      <c r="N28">
-        <v>2.41</v>
       </c>
       <c r="O28">
         <v>0</v>
@@ -4299,7 +4299,7 @@
         <v>48</v>
       </c>
       <c r="C29" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D29" t="s">
         <v>89</v>
@@ -4415,7 +4415,7 @@
         <v>49</v>
       </c>
       <c r="C30" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="D30" t="s">
         <v>89</v>
@@ -4442,13 +4442,13 @@
         <v>219</v>
       </c>
       <c r="L30">
-        <v>2.27</v>
+        <v>2.99</v>
       </c>
       <c r="M30">
-        <v>2.99</v>
+        <v>3.21</v>
       </c>
       <c r="N30">
-        <v>2.9</v>
+        <v>2.36</v>
       </c>
       <c r="O30">
         <v>0</v>
@@ -4490,16 +4490,16 @@
         <v>0</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF30">
         <v>0</v>
@@ -4531,7 +4531,7 @@
         <v>49</v>
       </c>
       <c r="C31" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D31" t="s">
         <v>89</v>
@@ -4558,13 +4558,13 @@
         <v>219</v>
       </c>
       <c r="L31">
-        <v>2.99</v>
+        <v>2.88</v>
       </c>
       <c r="M31">
-        <v>3.21</v>
+        <v>2.96</v>
       </c>
       <c r="N31">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="O31">
         <v>0</v>
@@ -4606,16 +4606,16 @@
         <v>0</v>
       </c>
       <c r="AB31">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AC31">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AD31">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE31">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF31">
         <v>0</v>
@@ -4647,7 +4647,7 @@
         <v>49</v>
       </c>
       <c r="C32" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D32" t="s">
         <v>89</v>
@@ -4763,7 +4763,7 @@
         <v>49</v>
       </c>
       <c r="C33" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D33" t="s">
         <v>89</v>
@@ -4790,13 +4790,13 @@
         <v>219</v>
       </c>
       <c r="L33">
-        <v>2.02</v>
+        <v>2.27</v>
       </c>
       <c r="M33">
-        <v>3.13</v>
+        <v>2.99</v>
       </c>
       <c r="N33">
-        <v>3.27</v>
+        <v>2.9</v>
       </c>
       <c r="O33">
         <v>0</v>
@@ -4838,10 +4838,10 @@
         <v>0</v>
       </c>
       <c r="AB33">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC33">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD33">
         <v>0</v>
@@ -4879,7 +4879,7 @@
         <v>49</v>
       </c>
       <c r="C34" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="D34" t="s">
         <v>89</v>
@@ -4906,13 +4906,13 @@
         <v>219</v>
       </c>
       <c r="L34">
-        <v>2.88</v>
+        <v>2.02</v>
       </c>
       <c r="M34">
-        <v>2.96</v>
+        <v>3.13</v>
       </c>
       <c r="N34">
-        <v>2.31</v>
+        <v>3.27</v>
       </c>
       <c r="O34">
         <v>0</v>
@@ -4954,10 +4954,10 @@
         <v>0</v>
       </c>
       <c r="AB34">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AC34">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AD34">
         <v>0</v>
@@ -4998,7 +4998,7 @@
         <v>78</v>
       </c>
       <c r="D35" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E35" t="s">
         <v>124</v>
@@ -5022,13 +5022,13 @@
         <v>219</v>
       </c>
       <c r="L35">
-        <v>3.55</v>
+        <v>2.04</v>
       </c>
       <c r="M35">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="N35">
-        <v>1.89</v>
+        <v>3.15</v>
       </c>
       <c r="O35">
         <v>0</v>
@@ -5070,10 +5070,10 @@
         <v>0</v>
       </c>
       <c r="AB35">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC35">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD35">
         <v>0</v>
@@ -5138,13 +5138,13 @@
         <v>219</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M36">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O36">
         <v>0</v>
@@ -5227,7 +5227,7 @@
         <v>50</v>
       </c>
       <c r="C37" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D37" t="s">
         <v>90</v>
@@ -5343,7 +5343,7 @@
         <v>50</v>
       </c>
       <c r="C38" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D38" t="s">
         <v>90</v>
@@ -5370,13 +5370,13 @@
         <v>219</v>
       </c>
       <c r="L38">
-        <v>4.3</v>
+        <v>1.51</v>
       </c>
       <c r="M38">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="N38">
-        <v>1.72</v>
+        <v>5.8</v>
       </c>
       <c r="O38">
         <v>0</v>
@@ -5418,10 +5418,10 @@
         <v>0</v>
       </c>
       <c r="AB38">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AC38">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="AD38">
         <v>0</v>
@@ -5462,7 +5462,7 @@
         <v>80</v>
       </c>
       <c r="D39" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E39" t="s">
         <v>128</v>
@@ -5486,13 +5486,13 @@
         <v>219</v>
       </c>
       <c r="L39">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M39">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N39">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O39">
         <v>0</v>
@@ -5575,7 +5575,7 @@
         <v>50</v>
       </c>
       <c r="C40" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D40" t="s">
         <v>90</v>
@@ -5602,13 +5602,13 @@
         <v>219</v>
       </c>
       <c r="L40">
-        <v>2.06</v>
+        <v>4.3</v>
       </c>
       <c r="M40">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="N40">
-        <v>3.15</v>
+        <v>1.72</v>
       </c>
       <c r="O40">
         <v>0</v>
@@ -5650,10 +5650,10 @@
         <v>0</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AD40">
         <v>0</v>
@@ -5718,13 +5718,13 @@
         <v>219</v>
       </c>
       <c r="L41">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M41">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N41">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O41">
         <v>0</v>
@@ -5807,7 +5807,7 @@
         <v>50</v>
       </c>
       <c r="C42" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D42" t="s">
         <v>90</v>
@@ -5834,13 +5834,13 @@
         <v>219</v>
       </c>
       <c r="L42">
-        <v>1.35</v>
+        <v>2.06</v>
       </c>
       <c r="M42">
-        <v>4.8</v>
+        <v>3.35</v>
       </c>
       <c r="N42">
-        <v>6.8</v>
+        <v>3.15</v>
       </c>
       <c r="O42">
         <v>0</v>
@@ -5923,10 +5923,10 @@
         <v>50</v>
       </c>
       <c r="C43" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D43" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E43" t="s">
         <v>132</v>
@@ -5950,13 +5950,13 @@
         <v>219</v>
       </c>
       <c r="L43">
-        <v>1.51</v>
+        <v>3.55</v>
       </c>
       <c r="M43">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="N43">
-        <v>5.8</v>
+        <v>1.89</v>
       </c>
       <c r="O43">
         <v>0</v>
@@ -5998,10 +5998,10 @@
         <v>0</v>
       </c>
       <c r="AB43">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AC43">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AD43">
         <v>0</v>
@@ -6039,10 +6039,10 @@
         <v>50</v>
       </c>
       <c r="C44" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D44" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E44" t="s">
         <v>133</v>
@@ -6066,13 +6066,13 @@
         <v>219</v>
       </c>
       <c r="L44">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M44">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -6155,10 +6155,10 @@
         <v>51</v>
       </c>
       <c r="C45" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D45" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E45" t="s">
         <v>134</v>
@@ -6182,13 +6182,13 @@
         <v>219</v>
       </c>
       <c r="L45">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M45">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N45">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O45">
         <v>0</v>
@@ -6230,10 +6230,10 @@
         <v>0</v>
       </c>
       <c r="AB45">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC45">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD45">
         <v>0</v>
@@ -6271,10 +6271,10 @@
         <v>51</v>
       </c>
       <c r="C46" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D46" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E46" t="s">
         <v>135</v>
@@ -6298,13 +6298,13 @@
         <v>219</v>
       </c>
       <c r="L46">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M46">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O46">
         <v>0</v>
@@ -6346,10 +6346,10 @@
         <v>0</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC46">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD46">
         <v>0</v>
@@ -6503,7 +6503,7 @@
         <v>52</v>
       </c>
       <c r="C48" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D48" t="s">
         <v>90</v>
@@ -6530,13 +6530,13 @@
         <v>219</v>
       </c>
       <c r="L48">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M48">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O48">
         <v>0</v>
@@ -6578,10 +6578,10 @@
         <v>0</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC48">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD48">
         <v>0</v>
@@ -7199,7 +7199,7 @@
         <v>52</v>
       </c>
       <c r="C54" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D54" t="s">
         <v>90</v>
@@ -7226,13 +7226,13 @@
         <v>219</v>
       </c>
       <c r="L54">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M54">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N54">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O54">
         <v>0</v>
@@ -7274,10 +7274,10 @@
         <v>0</v>
       </c>
       <c r="AB54">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC54">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD54">
         <v>0</v>
@@ -8011,7 +8011,7 @@
         <v>55</v>
       </c>
       <c r="C61" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D61" t="s">
         <v>90</v>
@@ -8038,13 +8038,13 @@
         <v>219</v>
       </c>
       <c r="L61">
-        <v>1.86</v>
+        <v>2.16</v>
       </c>
       <c r="M61">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="N61">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="O61">
         <v>0</v>
@@ -8080,16 +8080,16 @@
         <v>0</v>
       </c>
       <c r="Z61">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA61">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB61">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC61">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD61">
         <v>0</v>
@@ -8127,7 +8127,7 @@
         <v>55</v>
       </c>
       <c r="C62" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D62" t="s">
         <v>90</v>
@@ -8154,13 +8154,13 @@
         <v>219</v>
       </c>
       <c r="L62">
-        <v>2.16</v>
+        <v>1.86</v>
       </c>
       <c r="M62">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N62">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="O62">
         <v>0</v>
@@ -8196,16 +8196,16 @@
         <v>0</v>
       </c>
       <c r="Z62">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA62">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB62">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC62">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD62">
         <v>0</v>

--- a/jogos_2025-08-01.xlsx
+++ b/jogos_2025-08-01.xlsx
@@ -211,21 +211,21 @@
     <t>Slovenia PrvaLiga</t>
   </si>
   <si>
+    <t>Denmark Superliga</t>
+  </si>
+  <si>
+    <t>Austria 2. Liga</t>
+  </si>
+  <si>
+    <t>Romania Liga I</t>
+  </si>
+  <si>
+    <t>Poland 1. Liga</t>
+  </si>
+  <si>
     <t>Poland Ekstraklasa</t>
   </si>
   <si>
-    <t>Poland 1. Liga</t>
-  </si>
-  <si>
-    <t>Austria 2. Liga</t>
-  </si>
-  <si>
-    <t>Romania Liga I</t>
-  </si>
-  <si>
-    <t>Denmark Superliga</t>
-  </si>
-  <si>
     <t>Bulgaria First League</t>
   </si>
   <si>
@@ -244,24 +244,24 @@
     <t>Hungary NB I</t>
   </si>
   <si>
+    <t>Austria Bundesliga</t>
+  </si>
+  <si>
     <t>Germany 2. Bundesliga</t>
   </si>
   <si>
-    <t>Austria Bundesliga</t>
-  </si>
-  <si>
     <t>Republic of Ireland First Division</t>
   </si>
   <si>
+    <t>Belgium Pro League</t>
+  </si>
+  <si>
+    <t>Scotland Championship</t>
+  </si>
+  <si>
     <t>Republic of Ireland Premier Division</t>
   </si>
   <si>
-    <t>Belgium Pro League</t>
-  </si>
-  <si>
-    <t>Scotland Championship</t>
-  </si>
-  <si>
     <t>England EFL League One</t>
   </si>
   <si>
@@ -295,57 +295,57 @@
     <t>Neftchi</t>
   </si>
   <si>
+    <t>Wil</t>
+  </si>
+  <si>
     <t>Dinamo Samarqand</t>
   </si>
   <si>
-    <t>Wil</t>
+    <t>VPS</t>
+  </si>
+  <si>
+    <t>Buxoro</t>
+  </si>
+  <si>
+    <t>Smorgon</t>
   </si>
   <si>
     <t>Rukh Vynnyky</t>
   </si>
   <si>
-    <t>Buxoro</t>
-  </si>
-  <si>
-    <t>VPS</t>
-  </si>
-  <si>
-    <t>Smorgon</t>
-  </si>
-  <si>
     <t>BATE</t>
   </si>
   <si>
     <t>Radomlje</t>
   </si>
   <si>
+    <t>Fredericia</t>
+  </si>
+  <si>
+    <t>Austria Salzburg</t>
+  </si>
+  <si>
+    <t>SSC Farul</t>
+  </si>
+  <si>
+    <t>Amstetten</t>
+  </si>
+  <si>
+    <t>Liefering</t>
+  </si>
+  <si>
+    <t>Wieczysta Kraków</t>
+  </si>
+  <si>
+    <t>SV Stripfing Weiden</t>
+  </si>
+  <si>
+    <t>Kapfenberger SV</t>
+  </si>
+  <si>
     <t>Zagłębie Lubin</t>
   </si>
   <si>
-    <t>Wieczysta Kraków</t>
-  </si>
-  <si>
-    <t>Amstetten</t>
-  </si>
-  <si>
-    <t>Kapfenberger SV</t>
-  </si>
-  <si>
-    <t>SSC Farul</t>
-  </si>
-  <si>
-    <t>SV Stripfing Weiden</t>
-  </si>
-  <si>
-    <t>Austria Salzburg</t>
-  </si>
-  <si>
-    <t>Liefering</t>
-  </si>
-  <si>
-    <t>Fredericia</t>
-  </si>
-  <si>
     <t>Spartak Varna</t>
   </si>
   <si>
@@ -361,102 +361,102 @@
     <t>Stade Nyonnais</t>
   </si>
   <si>
+    <t>Lokomotiva Zagreb</t>
+  </si>
+  <si>
     <t>Vejle</t>
   </si>
   <si>
-    <t>Lokomotiva Zagreb</t>
-  </si>
-  <si>
     <t>Debrecen</t>
   </si>
   <si>
     <t>CSKA 1948 Sofia</t>
   </si>
   <si>
+    <t>LASK Linz</t>
+  </si>
+  <si>
+    <t>ŁKS Łódź</t>
+  </si>
+  <si>
+    <t>Wisła Płock</t>
+  </si>
+  <si>
+    <t>Petrolul 52</t>
+  </si>
+  <si>
     <t>Schalke 04</t>
   </si>
   <si>
-    <t>LASK Linz</t>
-  </si>
-  <si>
-    <t>Petrolul 52</t>
-  </si>
-  <si>
-    <t>Wisła Płock</t>
-  </si>
-  <si>
-    <t>ŁKS Łódź</t>
+    <t>Cobh Ramblers</t>
+  </si>
+  <si>
+    <t>Kerry</t>
+  </si>
+  <si>
+    <t>UCD</t>
+  </si>
+  <si>
+    <t>Wexford</t>
   </si>
   <si>
     <t>Bray Wanderers</t>
   </si>
   <si>
+    <t>KV Mechelen</t>
+  </si>
+  <si>
+    <t>Arbroath</t>
+  </si>
+  <si>
+    <t>Bohemians</t>
+  </si>
+  <si>
+    <t>Waterford</t>
+  </si>
+  <si>
     <t>Cork City</t>
   </si>
   <si>
-    <t>Wexford</t>
-  </si>
-  <si>
-    <t>Bohemians</t>
-  </si>
-  <si>
-    <t>KV Mechelen</t>
-  </si>
-  <si>
-    <t>UCD</t>
-  </si>
-  <si>
-    <t>Waterford</t>
-  </si>
-  <si>
-    <t>Kerry</t>
-  </si>
-  <si>
-    <t>Arbroath</t>
-  </si>
-  <si>
-    <t>Cobh Ramblers</t>
+    <t>Luton Town</t>
   </si>
   <si>
     <t>Shamrock Rovers</t>
   </si>
   <si>
-    <t>Luton Town</t>
+    <t>ABC</t>
+  </si>
+  <si>
+    <t>Remo</t>
+  </si>
+  <si>
+    <t>Ponte Preta</t>
   </si>
   <si>
     <t>Confiança</t>
   </si>
   <si>
-    <t>Remo</t>
+    <t>Ituano</t>
   </si>
   <si>
     <t>Náutico</t>
   </si>
   <si>
-    <t>ABC</t>
+    <t>Ypiranga Erechim</t>
+  </si>
+  <si>
+    <t>São Bernardo</t>
+  </si>
+  <si>
+    <t>Maringá</t>
+  </si>
+  <si>
+    <t>Brusque</t>
   </si>
   <si>
     <t>CSA</t>
   </si>
   <si>
-    <t>Ponte Preta</t>
-  </si>
-  <si>
-    <t>São Bernardo</t>
-  </si>
-  <si>
-    <t>Ituano</t>
-  </si>
-  <si>
-    <t>Brusque</t>
-  </si>
-  <si>
-    <t>Maringá</t>
-  </si>
-  <si>
-    <t>Ypiranga Erechim</t>
-  </si>
-  <si>
     <t>Audax Italiano</t>
   </si>
   <si>
@@ -487,57 +487,57 @@
     <t>Bunyodkor</t>
   </si>
   <si>
+    <t>Aarau</t>
+  </si>
+  <si>
     <t>Navbahor</t>
   </si>
   <si>
-    <t>Aarau</t>
+    <t>Mariehamn</t>
+  </si>
+  <si>
+    <t>AGMK</t>
+  </si>
+  <si>
+    <t>Dinamo Minsk</t>
   </si>
   <si>
     <t>SK Poltava</t>
   </si>
   <si>
-    <t>AGMK</t>
-  </si>
-  <si>
-    <t>Mariehamn</t>
-  </si>
-  <si>
-    <t>Dinamo Minsk</t>
-  </si>
-  <si>
     <t>Vitebsk</t>
   </si>
   <si>
     <t>Domžale</t>
   </si>
   <si>
+    <t>København</t>
+  </si>
+  <si>
+    <t>Austria Klagenfurt</t>
+  </si>
+  <si>
+    <t>Metaloglobus</t>
+  </si>
+  <si>
+    <t>Sturm Graz II</t>
+  </si>
+  <si>
+    <t>Austria Lustenau</t>
+  </si>
+  <si>
+    <t>Znicz Pruszków</t>
+  </si>
+  <si>
+    <t>First Vienna</t>
+  </si>
+  <si>
+    <t>Admira</t>
+  </si>
+  <si>
     <t>Korona Kielce</t>
   </si>
   <si>
-    <t>Znicz Pruszków</t>
-  </si>
-  <si>
-    <t>Sturm Graz II</t>
-  </si>
-  <si>
-    <t>Admira</t>
-  </si>
-  <si>
-    <t>Metaloglobus</t>
-  </si>
-  <si>
-    <t>First Vienna</t>
-  </si>
-  <si>
-    <t>Austria Klagenfurt</t>
-  </si>
-  <si>
-    <t>Austria Lustenau</t>
-  </si>
-  <si>
-    <t>København</t>
-  </si>
-  <si>
     <t>Botev Vratsa</t>
   </si>
   <si>
@@ -553,100 +553,100 @@
     <t>Rapperswil-Jona</t>
   </si>
   <si>
+    <t>HNK Vukovar 1991</t>
+  </si>
+  <si>
     <t>OB</t>
   </si>
   <si>
-    <t>HNK Vukovar 1991</t>
-  </si>
-  <si>
     <t>MTK</t>
   </si>
   <si>
     <t>Septemvri Sofia</t>
   </si>
   <si>
+    <t>Sturm Graz</t>
+  </si>
+  <si>
+    <t>Polonia Bytom</t>
+  </si>
+  <si>
+    <t>Piast Gliwice</t>
+  </si>
+  <si>
+    <t>UTA Arad</t>
+  </si>
+  <si>
     <t>Hertha BSC</t>
   </si>
   <si>
-    <t>Sturm Graz</t>
-  </si>
-  <si>
-    <t>UTA Arad</t>
-  </si>
-  <si>
-    <t>Piast Gliwice</t>
-  </si>
-  <si>
-    <t>Polonia Bytom</t>
+    <t>Longford Town</t>
+  </si>
+  <si>
+    <t>Athlone Town</t>
+  </si>
+  <si>
+    <t>Dundalk</t>
+  </si>
+  <si>
+    <t>Finn Harps</t>
   </si>
   <si>
     <t>Treaty United</t>
   </si>
   <si>
+    <t>Club Brugge</t>
+  </si>
+  <si>
+    <t>Ayr United</t>
+  </si>
+  <si>
+    <t>Drogheda United</t>
+  </si>
+  <si>
+    <t>St Patrick's Athl.</t>
+  </si>
+  <si>
     <t>Galway United</t>
   </si>
   <si>
-    <t>Finn Harps</t>
-  </si>
-  <si>
-    <t>Drogheda United</t>
-  </si>
-  <si>
-    <t>Club Brugge</t>
-  </si>
-  <si>
-    <t>Dundalk</t>
-  </si>
-  <si>
-    <t>St Patrick's Athl.</t>
-  </si>
-  <si>
-    <t>Athlone Town</t>
-  </si>
-  <si>
-    <t>Ayr United</t>
-  </si>
-  <si>
-    <t>Longford Town</t>
+    <t>AFC Wimbledon</t>
   </si>
   <si>
     <t>Derry City</t>
   </si>
   <si>
-    <t>AFC Wimbledon</t>
+    <t>Figueirense</t>
+  </si>
+  <si>
+    <t>Ferroviária</t>
+  </si>
+  <si>
+    <t>Guarani</t>
   </si>
   <si>
     <t>Anápolis</t>
   </si>
   <si>
-    <t>Ferroviária</t>
+    <t>Londrina</t>
   </si>
   <si>
     <t>Retrô</t>
   </si>
   <si>
-    <t>Figueirense</t>
+    <t>Caxias</t>
+  </si>
+  <si>
+    <t>Tombense</t>
+  </si>
+  <si>
+    <t>Floresta</t>
+  </si>
+  <si>
+    <t>Itabaiana</t>
   </si>
   <si>
     <t>Botafogo PB</t>
-  </si>
-  <si>
-    <t>Guarani</t>
-  </si>
-  <si>
-    <t>Tombense</t>
-  </si>
-  <si>
-    <t>Londrina</t>
-  </si>
-  <si>
-    <t>Itabaiana</t>
-  </si>
-  <si>
-    <t>Floresta</t>
-  </si>
-  <si>
-    <t>Caxias</t>
   </si>
   <si>
     <t>Palestino</t>
@@ -1399,10 +1399,10 @@
         <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E4" t="s">
         <v>93</v>
@@ -1426,13 +1426,13 @@
         <v>219</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O4">
         <v>0</v>
@@ -1515,10 +1515,10 @@
         <v>39</v>
       </c>
       <c r="C5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E5" t="s">
         <v>94</v>
@@ -1542,13 +1542,13 @@
         <v>219</v>
       </c>
       <c r="L5">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="M5">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N5">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O5">
         <v>0</v>
@@ -1631,10 +1631,10 @@
         <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E6" t="s">
         <v>95</v>
@@ -1658,13 +1658,13 @@
         <v>219</v>
       </c>
       <c r="L6">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="M6">
-        <v>3.41</v>
+        <v>3.98</v>
       </c>
       <c r="N6">
-        <v>5.9</v>
+        <v>4.33</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -1700,16 +1700,16 @@
         <v>0</v>
       </c>
       <c r="Z6">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA6">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD6">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>40</v>
       </c>
       <c r="C8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D8" t="s">
         <v>90</v>
@@ -1890,13 +1890,13 @@
         <v>219</v>
       </c>
       <c r="L8">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M8">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="N8">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="O8">
         <v>0</v>
@@ -1938,10 +1938,10 @@
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC8">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD8">
         <v>0</v>
@@ -1979,10 +1979,10 @@
         <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E9" t="s">
         <v>98</v>
@@ -2006,13 +2006,13 @@
         <v>219</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="O9">
         <v>0</v>
@@ -2048,10 +2048,10 @@
         <v>0</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AB9">
         <v>0</v>
@@ -2238,13 +2238,13 @@
         <v>219</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O11">
         <v>0</v>
@@ -2286,10 +2286,10 @@
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD11">
         <v>0</v>
@@ -2354,13 +2354,13 @@
         <v>219</v>
       </c>
       <c r="L12">
-        <v>2.13</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M12">
-        <v>3.17</v>
+        <v>5.6</v>
       </c>
       <c r="N12">
-        <v>2.99</v>
+        <v>1.27</v>
       </c>
       <c r="O12">
         <v>0</v>
@@ -2402,10 +2402,10 @@
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC12">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD12">
         <v>0</v>
@@ -2470,13 +2470,13 @@
         <v>219</v>
       </c>
       <c r="L13">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M13">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N13">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O13">
         <v>0</v>
@@ -2586,13 +2586,13 @@
         <v>219</v>
       </c>
       <c r="L14">
-        <v>1.73</v>
+        <v>1.45</v>
       </c>
       <c r="M14">
-        <v>3.82</v>
+        <v>3.7</v>
       </c>
       <c r="N14">
-        <v>3.57</v>
+        <v>6.3</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -2634,10 +2634,10 @@
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD14">
         <v>0</v>
@@ -2675,7 +2675,7 @@
         <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D15" t="s">
         <v>89</v>
@@ -2702,13 +2702,13 @@
         <v>219</v>
       </c>
       <c r="L15">
-        <v>3.62</v>
+        <v>1.73</v>
       </c>
       <c r="M15">
-        <v>3.7</v>
+        <v>3.82</v>
       </c>
       <c r="N15">
-        <v>1.75</v>
+        <v>3.57</v>
       </c>
       <c r="O15">
         <v>0</v>
@@ -2791,7 +2791,7 @@
         <v>43</v>
       </c>
       <c r="C16" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D16" t="s">
         <v>89</v>
@@ -2818,13 +2818,13 @@
         <v>219</v>
       </c>
       <c r="L16">
-        <v>1.45</v>
+        <v>2.54</v>
       </c>
       <c r="M16">
-        <v>3.7</v>
+        <v>3.21</v>
       </c>
       <c r="N16">
-        <v>6.3</v>
+        <v>2.41</v>
       </c>
       <c r="O16">
         <v>0</v>
@@ -2866,10 +2866,10 @@
         <v>0</v>
       </c>
       <c r="AB16">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="AC16">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="AD16">
         <v>0</v>
@@ -2907,7 +2907,7 @@
         <v>43</v>
       </c>
       <c r="C17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D17" t="s">
         <v>89</v>
@@ -2934,13 +2934,13 @@
         <v>219</v>
       </c>
       <c r="L17">
-        <v>2.3</v>
+        <v>1.42</v>
       </c>
       <c r="M17">
-        <v>3.21</v>
+        <v>4.2</v>
       </c>
       <c r="N17">
-        <v>2.68</v>
+        <v>5.6</v>
       </c>
       <c r="O17">
         <v>0</v>
@@ -3023,7 +3023,7 @@
         <v>43</v>
       </c>
       <c r="C18" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D18" t="s">
         <v>89</v>
@@ -3050,13 +3050,13 @@
         <v>219</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -3139,7 +3139,7 @@
         <v>43</v>
       </c>
       <c r="C19" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D19" t="s">
         <v>89</v>
@@ -3166,13 +3166,13 @@
         <v>219</v>
       </c>
       <c r="L19">
-        <v>2.54</v>
+        <v>3.62</v>
       </c>
       <c r="M19">
-        <v>3.21</v>
+        <v>3.7</v>
       </c>
       <c r="N19">
-        <v>2.41</v>
+        <v>1.75</v>
       </c>
       <c r="O19">
         <v>0</v>
@@ -3214,10 +3214,10 @@
         <v>0</v>
       </c>
       <c r="AB19">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC19">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD19">
         <v>0</v>
@@ -3282,13 +3282,13 @@
         <v>219</v>
       </c>
       <c r="L20">
-        <v>9.199999999999999</v>
+        <v>2.13</v>
       </c>
       <c r="M20">
-        <v>5.6</v>
+        <v>3.17</v>
       </c>
       <c r="N20">
-        <v>1.27</v>
+        <v>2.99</v>
       </c>
       <c r="O20">
         <v>0</v>
@@ -3330,10 +3330,10 @@
         <v>0</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD20">
         <v>0</v>
@@ -3951,7 +3951,7 @@
         <v>47</v>
       </c>
       <c r="C26" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D26" t="s">
         <v>89</v>
@@ -3978,13 +3978,13 @@
         <v>219</v>
       </c>
       <c r="L26">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M26">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N26">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="O26">
         <v>0</v>
@@ -4067,7 +4067,7 @@
         <v>47</v>
       </c>
       <c r="C27" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="D27" t="s">
         <v>89</v>
@@ -4094,13 +4094,13 @@
         <v>219</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O27">
         <v>0</v>
@@ -4374,10 +4374,10 @@
         <v>0</v>
       </c>
       <c r="AB29">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AC29">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AD29">
         <v>0</v>
@@ -4442,13 +4442,13 @@
         <v>219</v>
       </c>
       <c r="L30">
-        <v>2.99</v>
+        <v>2.88</v>
       </c>
       <c r="M30">
-        <v>3.21</v>
+        <v>2.96</v>
       </c>
       <c r="N30">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="O30">
         <v>0</v>
@@ -4490,16 +4490,16 @@
         <v>0</v>
       </c>
       <c r="AB30">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AC30">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AD30">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE30">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF30">
         <v>0</v>
@@ -4531,7 +4531,7 @@
         <v>49</v>
       </c>
       <c r="C31" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D31" t="s">
         <v>89</v>
@@ -4558,13 +4558,13 @@
         <v>219</v>
       </c>
       <c r="L31">
-        <v>2.88</v>
+        <v>2.02</v>
       </c>
       <c r="M31">
-        <v>2.96</v>
+        <v>3.13</v>
       </c>
       <c r="N31">
-        <v>2.31</v>
+        <v>3.27</v>
       </c>
       <c r="O31">
         <v>0</v>
@@ -4606,10 +4606,10 @@
         <v>0</v>
       </c>
       <c r="AB31">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AC31">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AD31">
         <v>0</v>
@@ -4647,7 +4647,7 @@
         <v>49</v>
       </c>
       <c r="C32" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D32" t="s">
         <v>89</v>
@@ -4674,13 +4674,13 @@
         <v>219</v>
       </c>
       <c r="L32">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="M32">
-        <v>2.96</v>
+        <v>2.99</v>
       </c>
       <c r="N32">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="O32">
         <v>0</v>
@@ -4722,10 +4722,10 @@
         <v>0</v>
       </c>
       <c r="AB32">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AC32">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AD32">
         <v>0</v>
@@ -4763,7 +4763,7 @@
         <v>49</v>
       </c>
       <c r="C33" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D33" t="s">
         <v>89</v>
@@ -4790,13 +4790,13 @@
         <v>219</v>
       </c>
       <c r="L33">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="M33">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="N33">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="O33">
         <v>0</v>
@@ -4838,10 +4838,10 @@
         <v>0</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD33">
         <v>0</v>
@@ -4879,7 +4879,7 @@
         <v>49</v>
       </c>
       <c r="C34" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="D34" t="s">
         <v>89</v>
@@ -4906,13 +4906,13 @@
         <v>219</v>
       </c>
       <c r="L34">
-        <v>2.02</v>
+        <v>2.99</v>
       </c>
       <c r="M34">
-        <v>3.13</v>
+        <v>3.21</v>
       </c>
       <c r="N34">
-        <v>3.27</v>
+        <v>2.36</v>
       </c>
       <c r="O34">
         <v>0</v>
@@ -4954,16 +4954,16 @@
         <v>0</v>
       </c>
       <c r="AB34">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="AC34">
-        <v>1.75</v>
+        <v>2.35</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF34">
         <v>0</v>
@@ -5022,13 +5022,13 @@
         <v>219</v>
       </c>
       <c r="L35">
-        <v>2.04</v>
+        <v>1.35</v>
       </c>
       <c r="M35">
-        <v>3.45</v>
+        <v>4.8</v>
       </c>
       <c r="N35">
-        <v>3.15</v>
+        <v>6.8</v>
       </c>
       <c r="O35">
         <v>0</v>
@@ -5111,7 +5111,7 @@
         <v>50</v>
       </c>
       <c r="C36" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D36" t="s">
         <v>90</v>
@@ -5138,13 +5138,13 @@
         <v>219</v>
       </c>
       <c r="L36">
-        <v>2.85</v>
+        <v>2.06</v>
       </c>
       <c r="M36">
+        <v>3.35</v>
+      </c>
+      <c r="N36">
         <v>3.15</v>
-      </c>
-      <c r="N36">
-        <v>2.31</v>
       </c>
       <c r="O36">
         <v>0</v>
@@ -5254,13 +5254,13 @@
         <v>219</v>
       </c>
       <c r="L37">
-        <v>2</v>
+        <v>4.3</v>
       </c>
       <c r="M37">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="N37">
-        <v>3.15</v>
+        <v>1.72</v>
       </c>
       <c r="O37">
         <v>0</v>
@@ -5302,10 +5302,10 @@
         <v>0</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AD37">
         <v>0</v>
@@ -5343,7 +5343,7 @@
         <v>50</v>
       </c>
       <c r="C38" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D38" t="s">
         <v>90</v>
@@ -5370,13 +5370,13 @@
         <v>219</v>
       </c>
       <c r="L38">
-        <v>1.51</v>
+        <v>2</v>
       </c>
       <c r="M38">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="N38">
-        <v>5.8</v>
+        <v>3.15</v>
       </c>
       <c r="O38">
         <v>0</v>
@@ -5418,10 +5418,10 @@
         <v>0</v>
       </c>
       <c r="AB38">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC38">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD38">
         <v>0</v>
@@ -5459,10 +5459,10 @@
         <v>50</v>
       </c>
       <c r="C39" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D39" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E39" t="s">
         <v>128</v>
@@ -5486,13 +5486,13 @@
         <v>219</v>
       </c>
       <c r="L39">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M39">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O39">
         <v>0</v>
@@ -5575,10 +5575,10 @@
         <v>50</v>
       </c>
       <c r="C40" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D40" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E40" t="s">
         <v>129</v>
@@ -5602,13 +5602,13 @@
         <v>219</v>
       </c>
       <c r="L40">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="M40">
-        <v>3.5</v>
+        <v>3.72</v>
       </c>
       <c r="N40">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="O40">
         <v>0</v>
@@ -5650,16 +5650,16 @@
         <v>0</v>
       </c>
       <c r="AB40">
-        <v>1.94</v>
+        <v>1.57</v>
       </c>
       <c r="AC40">
-        <v>1.74</v>
+        <v>2.3</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AF40">
         <v>0</v>
@@ -5691,10 +5691,10 @@
         <v>50</v>
       </c>
       <c r="C41" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D41" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E41" t="s">
         <v>130</v>
@@ -5718,13 +5718,13 @@
         <v>219</v>
       </c>
       <c r="L41">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M41">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O41">
         <v>0</v>
@@ -5766,10 +5766,10 @@
         <v>0</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD41">
         <v>0</v>
@@ -5807,7 +5807,7 @@
         <v>50</v>
       </c>
       <c r="C42" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D42" t="s">
         <v>90</v>
@@ -5834,13 +5834,13 @@
         <v>219</v>
       </c>
       <c r="L42">
-        <v>2.06</v>
+        <v>1.51</v>
       </c>
       <c r="M42">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="N42">
-        <v>3.15</v>
+        <v>5.8</v>
       </c>
       <c r="O42">
         <v>0</v>
@@ -5882,10 +5882,10 @@
         <v>0</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD42">
         <v>0</v>
@@ -5926,7 +5926,7 @@
         <v>81</v>
       </c>
       <c r="D43" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E43" t="s">
         <v>132</v>
@@ -5950,13 +5950,13 @@
         <v>219</v>
       </c>
       <c r="L43">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M43">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N43">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O43">
         <v>0</v>
@@ -5998,10 +5998,10 @@
         <v>0</v>
       </c>
       <c r="AB43">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC43">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD43">
         <v>0</v>
@@ -6039,7 +6039,7 @@
         <v>50</v>
       </c>
       <c r="C44" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D44" t="s">
         <v>90</v>
@@ -6066,13 +6066,13 @@
         <v>219</v>
       </c>
       <c r="L44">
-        <v>1.35</v>
+        <v>2.85</v>
       </c>
       <c r="M44">
-        <v>4.8</v>
+        <v>3.15</v>
       </c>
       <c r="N44">
-        <v>6.8</v>
+        <v>2.31</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -6155,10 +6155,10 @@
         <v>51</v>
       </c>
       <c r="C45" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D45" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E45" t="s">
         <v>134</v>
@@ -6182,13 +6182,13 @@
         <v>219</v>
       </c>
       <c r="L45">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M45">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O45">
         <v>0</v>
@@ -6230,10 +6230,10 @@
         <v>0</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC45">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD45">
         <v>0</v>
@@ -6271,10 +6271,10 @@
         <v>51</v>
       </c>
       <c r="C46" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D46" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E46" t="s">
         <v>135</v>
@@ -6298,13 +6298,13 @@
         <v>219</v>
       </c>
       <c r="L46">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M46">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N46">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O46">
         <v>0</v>
@@ -6346,10 +6346,10 @@
         <v>0</v>
       </c>
       <c r="AB46">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC46">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD46">
         <v>0</v>

--- a/jogos_2025-08-01.xlsx
+++ b/jogos_2025-08-01.xlsx
@@ -211,24 +211,24 @@
     <t>Slovenia PrvaLiga</t>
   </si>
   <si>
+    <t>Romania Liga I</t>
+  </si>
+  <si>
+    <t>Austria 2. Liga</t>
+  </si>
+  <si>
+    <t>Bulgaria First League</t>
+  </si>
+  <si>
+    <t>Poland 1. Liga</t>
+  </si>
+  <si>
+    <t>Poland Ekstraklasa</t>
+  </si>
+  <si>
     <t>Denmark Superliga</t>
   </si>
   <si>
-    <t>Austria 2. Liga</t>
-  </si>
-  <si>
-    <t>Romania Liga I</t>
-  </si>
-  <si>
-    <t>Poland 1. Liga</t>
-  </si>
-  <si>
-    <t>Poland Ekstraklasa</t>
-  </si>
-  <si>
-    <t>Bulgaria First League</t>
-  </si>
-  <si>
     <t>Estonia Meistriliiga</t>
   </si>
   <si>
@@ -265,12 +265,12 @@
     <t>England EFL League One</t>
   </si>
   <si>
+    <t>Brazil Serie B</t>
+  </si>
+  <si>
     <t>Brazil Serie C</t>
   </si>
   <si>
-    <t>Brazil Serie B</t>
-  </si>
-  <si>
     <t>Chile Primera División</t>
   </si>
   <si>
@@ -304,12 +304,12 @@
     <t>VPS</t>
   </si>
   <si>
+    <t>Smorgon</t>
+  </si>
+  <si>
     <t>Buxoro</t>
   </si>
   <si>
-    <t>Smorgon</t>
-  </si>
-  <si>
     <t>Rukh Vynnyky</t>
   </si>
   <si>
@@ -319,36 +319,36 @@
     <t>Radomlje</t>
   </si>
   <si>
+    <t>SSC Farul</t>
+  </si>
+  <si>
+    <t>Kapfenberger SV</t>
+  </si>
+  <si>
+    <t>Spartak Varna</t>
+  </si>
+  <si>
+    <t>Austria Salzburg</t>
+  </si>
+  <si>
+    <t>Wieczysta Kraków</t>
+  </si>
+  <si>
+    <t>Liefering</t>
+  </si>
+  <si>
+    <t>SV Stripfing Weiden</t>
+  </si>
+  <si>
+    <t>Zagłębie Lubin</t>
+  </si>
+  <si>
+    <t>Amstetten</t>
+  </si>
+  <si>
     <t>Fredericia</t>
   </si>
   <si>
-    <t>Austria Salzburg</t>
-  </si>
-  <si>
-    <t>SSC Farul</t>
-  </si>
-  <si>
-    <t>Amstetten</t>
-  </si>
-  <si>
-    <t>Liefering</t>
-  </si>
-  <si>
-    <t>Wieczysta Kraków</t>
-  </si>
-  <si>
-    <t>SV Stripfing Weiden</t>
-  </si>
-  <si>
-    <t>Kapfenberger SV</t>
-  </si>
-  <si>
-    <t>Zagłębie Lubin</t>
-  </si>
-  <si>
-    <t>Spartak Varna</t>
-  </si>
-  <si>
     <t>Tallinna FC Levadia</t>
   </si>
   <si>
@@ -361,111 +361,111 @@
     <t>Stade Nyonnais</t>
   </si>
   <si>
+    <t>Vejle</t>
+  </si>
+  <si>
     <t>Lokomotiva Zagreb</t>
   </si>
   <si>
-    <t>Vejle</t>
-  </si>
-  <si>
     <t>Debrecen</t>
   </si>
   <si>
     <t>CSKA 1948 Sofia</t>
   </si>
   <si>
+    <t>Petrolul 52</t>
+  </si>
+  <si>
+    <t>Wisła Płock</t>
+  </si>
+  <si>
     <t>LASK Linz</t>
   </si>
   <si>
+    <t>Schalke 04</t>
+  </si>
+  <si>
     <t>ŁKS Łódź</t>
   </si>
   <si>
-    <t>Wisła Płock</t>
-  </si>
-  <si>
-    <t>Petrolul 52</t>
-  </si>
-  <si>
-    <t>Schalke 04</t>
-  </si>
-  <si>
     <t>Cobh Ramblers</t>
   </si>
   <si>
+    <t>KV Mechelen</t>
+  </si>
+  <si>
+    <t>Arbroath</t>
+  </si>
+  <si>
+    <t>UCD</t>
+  </si>
+  <si>
+    <t>Bray Wanderers</t>
+  </si>
+  <si>
     <t>Kerry</t>
   </si>
   <si>
-    <t>UCD</t>
-  </si>
-  <si>
     <t>Wexford</t>
   </si>
   <si>
-    <t>Bray Wanderers</t>
-  </si>
-  <si>
-    <t>KV Mechelen</t>
-  </si>
-  <si>
-    <t>Arbroath</t>
+    <t>Waterford</t>
+  </si>
+  <si>
+    <t>Cork City</t>
   </si>
   <si>
     <t>Bohemians</t>
   </si>
   <si>
-    <t>Waterford</t>
-  </si>
-  <si>
-    <t>Cork City</t>
+    <t>Shamrock Rovers</t>
   </si>
   <si>
     <t>Luton Town</t>
   </si>
   <si>
-    <t>Shamrock Rovers</t>
+    <t>Remo</t>
+  </si>
+  <si>
+    <t>Ponte Preta</t>
+  </si>
+  <si>
+    <t>São Bernardo</t>
+  </si>
+  <si>
+    <t>CSA</t>
+  </si>
+  <si>
+    <t>Maringá</t>
+  </si>
+  <si>
+    <t>Náutico</t>
   </si>
   <si>
     <t>ABC</t>
   </si>
   <si>
-    <t>Remo</t>
-  </si>
-  <si>
-    <t>Ponte Preta</t>
-  </si>
-  <si>
     <t>Confiança</t>
   </si>
   <si>
+    <t>Ypiranga Erechim</t>
+  </si>
+  <si>
     <t>Ituano</t>
   </si>
   <si>
-    <t>Náutico</t>
-  </si>
-  <si>
-    <t>Ypiranga Erechim</t>
-  </si>
-  <si>
-    <t>São Bernardo</t>
-  </si>
-  <si>
-    <t>Maringá</t>
-  </si>
-  <si>
     <t>Brusque</t>
   </si>
   <si>
-    <t>CSA</t>
-  </si>
-  <si>
     <t>Audax Italiano</t>
   </si>
   <si>
+    <t>Chicago Red Stars</t>
+  </si>
+  <si>
     <t>Racing Louisville</t>
   </si>
   <si>
-    <t>Chicago Red Stars</t>
-  </si>
-  <si>
     <t>Operário PR</t>
   </si>
   <si>
@@ -496,12 +496,12 @@
     <t>Mariehamn</t>
   </si>
   <si>
+    <t>Dinamo Minsk</t>
+  </si>
+  <si>
     <t>AGMK</t>
   </si>
   <si>
-    <t>Dinamo Minsk</t>
-  </si>
-  <si>
     <t>SK Poltava</t>
   </si>
   <si>
@@ -511,36 +511,36 @@
     <t>Domžale</t>
   </si>
   <si>
+    <t>Metaloglobus</t>
+  </si>
+  <si>
+    <t>Admira</t>
+  </si>
+  <si>
+    <t>Botev Vratsa</t>
+  </si>
+  <si>
+    <t>Austria Klagenfurt</t>
+  </si>
+  <si>
+    <t>Znicz Pruszków</t>
+  </si>
+  <si>
+    <t>Austria Lustenau</t>
+  </si>
+  <si>
+    <t>First Vienna</t>
+  </si>
+  <si>
+    <t>Korona Kielce</t>
+  </si>
+  <si>
+    <t>Sturm Graz II</t>
+  </si>
+  <si>
     <t>København</t>
   </si>
   <si>
-    <t>Austria Klagenfurt</t>
-  </si>
-  <si>
-    <t>Metaloglobus</t>
-  </si>
-  <si>
-    <t>Sturm Graz II</t>
-  </si>
-  <si>
-    <t>Austria Lustenau</t>
-  </si>
-  <si>
-    <t>Znicz Pruszków</t>
-  </si>
-  <si>
-    <t>First Vienna</t>
-  </si>
-  <si>
-    <t>Admira</t>
-  </si>
-  <si>
-    <t>Korona Kielce</t>
-  </si>
-  <si>
-    <t>Botev Vratsa</t>
-  </si>
-  <si>
     <t>Kuressaare</t>
   </si>
   <si>
@@ -553,109 +553,109 @@
     <t>Rapperswil-Jona</t>
   </si>
   <si>
+    <t>OB</t>
+  </si>
+  <si>
     <t>HNK Vukovar 1991</t>
   </si>
   <si>
-    <t>OB</t>
-  </si>
-  <si>
     <t>MTK</t>
   </si>
   <si>
     <t>Septemvri Sofia</t>
   </si>
   <si>
+    <t>UTA Arad</t>
+  </si>
+  <si>
+    <t>Piast Gliwice</t>
+  </si>
+  <si>
     <t>Sturm Graz</t>
   </si>
   <si>
+    <t>Hertha BSC</t>
+  </si>
+  <si>
     <t>Polonia Bytom</t>
   </si>
   <si>
-    <t>Piast Gliwice</t>
-  </si>
-  <si>
-    <t>UTA Arad</t>
-  </si>
-  <si>
-    <t>Hertha BSC</t>
-  </si>
-  <si>
     <t>Longford Town</t>
   </si>
   <si>
+    <t>Club Brugge</t>
+  </si>
+  <si>
+    <t>Ayr United</t>
+  </si>
+  <si>
+    <t>Dundalk</t>
+  </si>
+  <si>
+    <t>Treaty United</t>
+  </si>
+  <si>
     <t>Athlone Town</t>
   </si>
   <si>
-    <t>Dundalk</t>
-  </si>
-  <si>
     <t>Finn Harps</t>
   </si>
   <si>
-    <t>Treaty United</t>
-  </si>
-  <si>
-    <t>Club Brugge</t>
-  </si>
-  <si>
-    <t>Ayr United</t>
+    <t>St Patrick's Athl.</t>
+  </si>
+  <si>
+    <t>Galway United</t>
   </si>
   <si>
     <t>Drogheda United</t>
   </si>
   <si>
-    <t>St Patrick's Athl.</t>
-  </si>
-  <si>
-    <t>Galway United</t>
+    <t>Derry City</t>
   </si>
   <si>
     <t>AFC Wimbledon</t>
   </si>
   <si>
-    <t>Derry City</t>
+    <t>Ferroviária</t>
+  </si>
+  <si>
+    <t>Guarani</t>
+  </si>
+  <si>
+    <t>Tombense</t>
+  </si>
+  <si>
+    <t>Botafogo PB</t>
+  </si>
+  <si>
+    <t>Floresta</t>
+  </si>
+  <si>
+    <t>Retrô</t>
   </si>
   <si>
     <t>Figueirense</t>
   </si>
   <si>
-    <t>Ferroviária</t>
-  </si>
-  <si>
-    <t>Guarani</t>
-  </si>
-  <si>
     <t>Anápolis</t>
   </si>
   <si>
+    <t>Caxias</t>
+  </si>
+  <si>
     <t>Londrina</t>
   </si>
   <si>
-    <t>Retrô</t>
-  </si>
-  <si>
-    <t>Caxias</t>
-  </si>
-  <si>
-    <t>Tombense</t>
-  </si>
-  <si>
-    <t>Floresta</t>
-  </si>
-  <si>
     <t>Itabaiana</t>
   </si>
   <si>
-    <t>Botafogo PB</t>
-  </si>
-  <si>
     <t>Palestino</t>
   </si>
   <si>
+    <t>Gotham FC</t>
+  </si>
+  <si>
     <t>Kansas City</t>
-  </si>
-  <si>
-    <t>Gotham FC</t>
   </si>
   <si>
     <t>Criciúma</t>
@@ -1747,7 +1747,7 @@
         <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D7" t="s">
         <v>90</v>
@@ -1863,7 +1863,7 @@
         <v>40</v>
       </c>
       <c r="C8" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D8" t="s">
         <v>90</v>
@@ -2354,13 +2354,13 @@
         <v>219</v>
       </c>
       <c r="L12">
-        <v>9.199999999999999</v>
+        <v>1.45</v>
       </c>
       <c r="M12">
-        <v>5.6</v>
+        <v>3.7</v>
       </c>
       <c r="N12">
-        <v>1.27</v>
+        <v>6.3</v>
       </c>
       <c r="O12">
         <v>0</v>
@@ -2402,10 +2402,10 @@
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD12">
         <v>0</v>
@@ -2470,13 +2470,13 @@
         <v>219</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O13">
         <v>0</v>
@@ -2586,13 +2586,13 @@
         <v>219</v>
       </c>
       <c r="L14">
-        <v>1.45</v>
+        <v>2.47</v>
       </c>
       <c r="M14">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="N14">
-        <v>6.3</v>
+        <v>2.7</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -2634,10 +2634,10 @@
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC14">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD14">
         <v>0</v>
@@ -2702,13 +2702,13 @@
         <v>219</v>
       </c>
       <c r="L15">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M15">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="N15">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="O15">
         <v>0</v>
@@ -2791,7 +2791,7 @@
         <v>43</v>
       </c>
       <c r="C16" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D16" t="s">
         <v>89</v>
@@ -2818,13 +2818,13 @@
         <v>219</v>
       </c>
       <c r="L16">
-        <v>2.54</v>
+        <v>1.42</v>
       </c>
       <c r="M16">
-        <v>3.21</v>
+        <v>4.2</v>
       </c>
       <c r="N16">
-        <v>2.41</v>
+        <v>5.6</v>
       </c>
       <c r="O16">
         <v>0</v>
@@ -2866,10 +2866,10 @@
         <v>0</v>
       </c>
       <c r="AB16">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC16">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD16">
         <v>0</v>
@@ -2907,7 +2907,7 @@
         <v>43</v>
       </c>
       <c r="C17" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D17" t="s">
         <v>89</v>
@@ -2934,13 +2934,13 @@
         <v>219</v>
       </c>
       <c r="L17">
-        <v>1.42</v>
+        <v>2.54</v>
       </c>
       <c r="M17">
-        <v>4.2</v>
+        <v>3.21</v>
       </c>
       <c r="N17">
-        <v>5.6</v>
+        <v>2.41</v>
       </c>
       <c r="O17">
         <v>0</v>
@@ -2982,10 +2982,10 @@
         <v>0</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD17">
         <v>0</v>
@@ -3139,7 +3139,7 @@
         <v>43</v>
       </c>
       <c r="C19" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D19" t="s">
         <v>89</v>
@@ -3166,13 +3166,13 @@
         <v>219</v>
       </c>
       <c r="L19">
-        <v>3.62</v>
+        <v>2.13</v>
       </c>
       <c r="M19">
-        <v>3.7</v>
+        <v>3.17</v>
       </c>
       <c r="N19">
-        <v>1.75</v>
+        <v>2.99</v>
       </c>
       <c r="O19">
         <v>0</v>
@@ -3214,10 +3214,10 @@
         <v>0</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD19">
         <v>0</v>
@@ -3255,7 +3255,7 @@
         <v>43</v>
       </c>
       <c r="C20" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D20" t="s">
         <v>89</v>
@@ -3282,13 +3282,13 @@
         <v>219</v>
       </c>
       <c r="L20">
-        <v>2.13</v>
+        <v>1.73</v>
       </c>
       <c r="M20">
-        <v>3.17</v>
+        <v>3.82</v>
       </c>
       <c r="N20">
-        <v>2.99</v>
+        <v>3.57</v>
       </c>
       <c r="O20">
         <v>0</v>
@@ -3330,10 +3330,10 @@
         <v>0</v>
       </c>
       <c r="AB20">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC20">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD20">
         <v>0</v>
@@ -3398,13 +3398,13 @@
         <v>219</v>
       </c>
       <c r="L21">
-        <v>2.47</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M21">
-        <v>3.1</v>
+        <v>5.6</v>
       </c>
       <c r="N21">
-        <v>2.7</v>
+        <v>1.27</v>
       </c>
       <c r="O21">
         <v>0</v>
@@ -3794,7 +3794,7 @@
         <v>0</v>
       </c>
       <c r="AB24">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="AC24">
         <v>1.82</v>
@@ -3951,7 +3951,7 @@
         <v>47</v>
       </c>
       <c r="C26" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D26" t="s">
         <v>89</v>
@@ -3978,13 +3978,13 @@
         <v>219</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O26">
         <v>0</v>
@@ -4067,7 +4067,7 @@
         <v>47</v>
       </c>
       <c r="C27" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="D27" t="s">
         <v>89</v>
@@ -4094,13 +4094,13 @@
         <v>219</v>
       </c>
       <c r="L27">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M27">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N27">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="O27">
         <v>0</v>
@@ -4299,7 +4299,7 @@
         <v>48</v>
       </c>
       <c r="C29" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D29" t="s">
         <v>89</v>
@@ -4415,7 +4415,7 @@
         <v>49</v>
       </c>
       <c r="C30" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="D30" t="s">
         <v>89</v>
@@ -4442,13 +4442,13 @@
         <v>219</v>
       </c>
       <c r="L30">
-        <v>2.88</v>
+        <v>2.24</v>
       </c>
       <c r="M30">
         <v>2.96</v>
       </c>
       <c r="N30">
-        <v>2.31</v>
+        <v>2.98</v>
       </c>
       <c r="O30">
         <v>0</v>
@@ -4490,10 +4490,10 @@
         <v>0</v>
       </c>
       <c r="AB30">
-        <v>1.7</v>
+        <v>2.39</v>
       </c>
       <c r="AC30">
-        <v>1.95</v>
+        <v>1.58</v>
       </c>
       <c r="AD30">
         <v>0</v>
@@ -4531,7 +4531,7 @@
         <v>49</v>
       </c>
       <c r="C31" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D31" t="s">
         <v>89</v>
@@ -4558,13 +4558,13 @@
         <v>219</v>
       </c>
       <c r="L31">
-        <v>2.02</v>
+        <v>2.27</v>
       </c>
       <c r="M31">
-        <v>3.13</v>
+        <v>2.99</v>
       </c>
       <c r="N31">
-        <v>3.27</v>
+        <v>2.9</v>
       </c>
       <c r="O31">
         <v>0</v>
@@ -4606,10 +4606,10 @@
         <v>0</v>
       </c>
       <c r="AB31">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC31">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD31">
         <v>0</v>
@@ -4647,7 +4647,7 @@
         <v>49</v>
       </c>
       <c r="C32" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="D32" t="s">
         <v>89</v>
@@ -4674,13 +4674,13 @@
         <v>219</v>
       </c>
       <c r="L32">
-        <v>2.27</v>
+        <v>2.88</v>
       </c>
       <c r="M32">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="N32">
-        <v>2.9</v>
+        <v>2.31</v>
       </c>
       <c r="O32">
         <v>0</v>
@@ -4722,10 +4722,10 @@
         <v>0</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD32">
         <v>0</v>
@@ -4763,7 +4763,7 @@
         <v>49</v>
       </c>
       <c r="C33" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="D33" t="s">
         <v>89</v>
@@ -4790,13 +4790,13 @@
         <v>219</v>
       </c>
       <c r="L33">
-        <v>2.24</v>
+        <v>2.99</v>
       </c>
       <c r="M33">
-        <v>2.96</v>
+        <v>3.21</v>
       </c>
       <c r="N33">
-        <v>2.98</v>
+        <v>2.36</v>
       </c>
       <c r="O33">
         <v>0</v>
@@ -4838,16 +4838,16 @@
         <v>0</v>
       </c>
       <c r="AB33">
-        <v>2.39</v>
+        <v>1.53</v>
       </c>
       <c r="AC33">
-        <v>1.58</v>
+        <v>2.35</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF33">
         <v>0</v>
@@ -4879,7 +4879,7 @@
         <v>49</v>
       </c>
       <c r="C34" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D34" t="s">
         <v>89</v>
@@ -4906,13 +4906,13 @@
         <v>219</v>
       </c>
       <c r="L34">
-        <v>2.99</v>
+        <v>2.02</v>
       </c>
       <c r="M34">
-        <v>3.21</v>
+        <v>3.13</v>
       </c>
       <c r="N34">
-        <v>2.36</v>
+        <v>3.27</v>
       </c>
       <c r="O34">
         <v>0</v>
@@ -4954,16 +4954,16 @@
         <v>0</v>
       </c>
       <c r="AB34">
-        <v>1.53</v>
+        <v>1.95</v>
       </c>
       <c r="AC34">
-        <v>2.35</v>
+        <v>1.75</v>
       </c>
       <c r="AD34">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE34">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF34">
         <v>0</v>
@@ -5111,10 +5111,10 @@
         <v>50</v>
       </c>
       <c r="C36" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D36" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E36" t="s">
         <v>125</v>
@@ -5138,13 +5138,13 @@
         <v>219</v>
       </c>
       <c r="L36">
-        <v>2.06</v>
+        <v>4</v>
       </c>
       <c r="M36">
-        <v>3.35</v>
+        <v>3.72</v>
       </c>
       <c r="N36">
-        <v>3.15</v>
+        <v>1.66</v>
       </c>
       <c r="O36">
         <v>0</v>
@@ -5186,16 +5186,16 @@
         <v>0</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AF36">
         <v>0</v>
@@ -5227,10 +5227,10 @@
         <v>50</v>
       </c>
       <c r="C37" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D37" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E37" t="s">
         <v>126</v>
@@ -5254,13 +5254,13 @@
         <v>219</v>
       </c>
       <c r="L37">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="M37">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="N37">
-        <v>1.72</v>
+        <v>1.89</v>
       </c>
       <c r="O37">
         <v>0</v>
@@ -5302,10 +5302,10 @@
         <v>0</v>
       </c>
       <c r="AB37">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AC37">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="AD37">
         <v>0</v>
@@ -5370,13 +5370,13 @@
         <v>219</v>
       </c>
       <c r="L38">
-        <v>2</v>
+        <v>4.3</v>
       </c>
       <c r="M38">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="N38">
-        <v>3.15</v>
+        <v>1.72</v>
       </c>
       <c r="O38">
         <v>0</v>
@@ -5418,10 +5418,10 @@
         <v>0</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AD38">
         <v>0</v>
@@ -5575,10 +5575,10 @@
         <v>50</v>
       </c>
       <c r="C40" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D40" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E40" t="s">
         <v>129</v>
@@ -5602,13 +5602,13 @@
         <v>219</v>
       </c>
       <c r="L40">
-        <v>4</v>
+        <v>2.06</v>
       </c>
       <c r="M40">
-        <v>3.72</v>
+        <v>3.35</v>
       </c>
       <c r="N40">
-        <v>1.66</v>
+        <v>3.15</v>
       </c>
       <c r="O40">
         <v>0</v>
@@ -5650,16 +5650,16 @@
         <v>0</v>
       </c>
       <c r="AB40">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC40">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD40">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AE40">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AF40">
         <v>0</v>
@@ -5691,10 +5691,10 @@
         <v>50</v>
       </c>
       <c r="C41" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D41" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E41" t="s">
         <v>130</v>
@@ -5718,13 +5718,13 @@
         <v>219</v>
       </c>
       <c r="L41">
+        <v>2</v>
+      </c>
+      <c r="M41">
         <v>3.55</v>
       </c>
-      <c r="M41">
-        <v>3.7</v>
-      </c>
       <c r="N41">
-        <v>1.89</v>
+        <v>3.15</v>
       </c>
       <c r="O41">
         <v>0</v>
@@ -5766,10 +5766,10 @@
         <v>0</v>
       </c>
       <c r="AB41">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC41">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD41">
         <v>0</v>
@@ -5834,13 +5834,13 @@
         <v>219</v>
       </c>
       <c r="L42">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M42">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N42">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O42">
         <v>0</v>
@@ -5882,10 +5882,10 @@
         <v>0</v>
       </c>
       <c r="AB42">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC42">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD42">
         <v>0</v>
@@ -5950,13 +5950,13 @@
         <v>219</v>
       </c>
       <c r="L43">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M43">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O43">
         <v>0</v>
@@ -6066,13 +6066,13 @@
         <v>219</v>
       </c>
       <c r="L44">
-        <v>2.85</v>
+        <v>1.51</v>
       </c>
       <c r="M44">
-        <v>3.15</v>
+        <v>3.85</v>
       </c>
       <c r="N44">
-        <v>2.31</v>
+        <v>5.8</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -6114,10 +6114,10 @@
         <v>0</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC44">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD44">
         <v>0</v>
@@ -6155,10 +6155,10 @@
         <v>51</v>
       </c>
       <c r="C45" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D45" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E45" t="s">
         <v>134</v>
@@ -6182,13 +6182,13 @@
         <v>219</v>
       </c>
       <c r="L45">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M45">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N45">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O45">
         <v>0</v>
@@ -6230,10 +6230,10 @@
         <v>0</v>
       </c>
       <c r="AB45">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC45">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD45">
         <v>0</v>
@@ -6271,10 +6271,10 @@
         <v>51</v>
       </c>
       <c r="C46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D46" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E46" t="s">
         <v>135</v>
@@ -6298,13 +6298,13 @@
         <v>219</v>
       </c>
       <c r="L46">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M46">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O46">
         <v>0</v>
@@ -6346,10 +6346,10 @@
         <v>0</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC46">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD46">
         <v>0</v>
@@ -6414,13 +6414,13 @@
         <v>219</v>
       </c>
       <c r="L47">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M47">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N47">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O47">
         <v>0</v>
@@ -6462,10 +6462,10 @@
         <v>0</v>
       </c>
       <c r="AB47">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC47">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD47">
         <v>0</v>
@@ -6530,13 +6530,13 @@
         <v>219</v>
       </c>
       <c r="L48">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M48">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N48">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O48">
         <v>0</v>
@@ -6578,10 +6578,10 @@
         <v>0</v>
       </c>
       <c r="AB48">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC48">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD48">
         <v>0</v>
@@ -6619,7 +6619,7 @@
         <v>52</v>
       </c>
       <c r="C49" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D49" t="s">
         <v>90</v>
@@ -6735,7 +6735,7 @@
         <v>52</v>
       </c>
       <c r="C50" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D50" t="s">
         <v>90</v>
@@ -6851,7 +6851,7 @@
         <v>52</v>
       </c>
       <c r="C51" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D51" t="s">
         <v>90</v>
@@ -6967,7 +6967,7 @@
         <v>52</v>
       </c>
       <c r="C52" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D52" t="s">
         <v>90</v>
@@ -7083,7 +7083,7 @@
         <v>52</v>
       </c>
       <c r="C53" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D53" t="s">
         <v>90</v>
@@ -7199,7 +7199,7 @@
         <v>52</v>
       </c>
       <c r="C54" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D54" t="s">
         <v>90</v>
@@ -7315,7 +7315,7 @@
         <v>52</v>
       </c>
       <c r="C55" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D55" t="s">
         <v>90</v>
@@ -7431,7 +7431,7 @@
         <v>52</v>
       </c>
       <c r="C56" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D56" t="s">
         <v>90</v>
@@ -7547,7 +7547,7 @@
         <v>52</v>
       </c>
       <c r="C57" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D57" t="s">
         <v>90</v>
@@ -7806,13 +7806,13 @@
         <v>219</v>
       </c>
       <c r="L59">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="M59">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="N59">
-        <v>1.84</v>
+        <v>1.52</v>
       </c>
       <c r="O59">
         <v>0</v>
@@ -7854,10 +7854,10 @@
         <v>0</v>
       </c>
       <c r="AB59">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="AC59">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="AD59">
         <v>0</v>
@@ -7922,13 +7922,13 @@
         <v>219</v>
       </c>
       <c r="L60">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="M60">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="N60">
-        <v>1.52</v>
+        <v>1.84</v>
       </c>
       <c r="O60">
         <v>0</v>
@@ -7970,10 +7970,10 @@
         <v>0</v>
       </c>
       <c r="AB60">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="AC60">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="AD60">
         <v>0</v>
@@ -8011,7 +8011,7 @@
         <v>55</v>
       </c>
       <c r="C61" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D61" t="s">
         <v>90</v>
@@ -8086,10 +8086,10 @@
         <v>2.37</v>
       </c>
       <c r="AB61">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC61">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AD61">
         <v>0</v>

--- a/jogos_2025-08-01.xlsx
+++ b/jogos_2025-08-01.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="229">
   <si>
     <t>Date</t>
   </si>
@@ -157,6 +157,9 @@
     <t>14:30</t>
   </si>
   <si>
+    <t>14:45</t>
+  </si>
+  <si>
     <t>15:00</t>
   </si>
   <si>
@@ -196,16 +199,19 @@
     <t>Ukraine Ukrainian Premier League</t>
   </si>
   <si>
+    <t>Switzerland Challenge League</t>
+  </si>
+  <si>
     <t>Uzbekistan Uzbekistan Super League</t>
   </si>
   <si>
-    <t>Switzerland Challenge League</t>
+    <t>Belarus Vysheyshaya Liga</t>
   </si>
   <si>
     <t>Finland Veikkausliiga</t>
   </si>
   <si>
-    <t>Belarus Vysheyshaya Liga</t>
+    <t>Jordan Jordanian Pro League</t>
   </si>
   <si>
     <t>Slovenia PrvaLiga</t>
@@ -217,18 +223,18 @@
     <t>Austria 2. Liga</t>
   </si>
   <si>
+    <t>Denmark Superliga</t>
+  </si>
+  <si>
+    <t>Poland 1. Liga</t>
+  </si>
+  <si>
+    <t>Poland Ekstraklasa</t>
+  </si>
+  <si>
     <t>Bulgaria First League</t>
   </si>
   <si>
-    <t>Poland 1. Liga</t>
-  </si>
-  <si>
-    <t>Poland Ekstraklasa</t>
-  </si>
-  <si>
-    <t>Denmark Superliga</t>
-  </si>
-  <si>
     <t>Estonia Meistriliiga</t>
   </si>
   <si>
@@ -244,33 +250,33 @@
     <t>Hungary NB I</t>
   </si>
   <si>
+    <t>Germany 2. Bundesliga</t>
+  </si>
+  <si>
     <t>Austria Bundesliga</t>
   </si>
   <si>
-    <t>Germany 2. Bundesliga</t>
+    <t>Republic of Ireland Premier Division</t>
   </si>
   <si>
     <t>Republic of Ireland First Division</t>
   </si>
   <si>
+    <t>Scotland Championship</t>
+  </si>
+  <si>
     <t>Belgium Pro League</t>
   </si>
   <si>
-    <t>Scotland Championship</t>
-  </si>
-  <si>
-    <t>Republic of Ireland Premier Division</t>
-  </si>
-  <si>
     <t>England EFL League One</t>
   </si>
   <si>
+    <t>Brazil Serie C</t>
+  </si>
+  <si>
     <t>Brazil Serie B</t>
   </si>
   <si>
-    <t>Brazil Serie C</t>
-  </si>
-  <si>
     <t>Chile Primera División</t>
   </si>
   <si>
@@ -292,25 +298,31 @@
     <t>Kolos Kovalivka</t>
   </si>
   <si>
+    <t>Wil</t>
+  </si>
+  <si>
     <t>Neftchi</t>
   </si>
   <si>
-    <t>Wil</t>
-  </si>
-  <si>
     <t>Dinamo Samarqand</t>
   </si>
   <si>
+    <t>Buxoro</t>
+  </si>
+  <si>
+    <t>Mash'al</t>
+  </si>
+  <si>
+    <t>Rukh Vynnyky</t>
+  </si>
+  <si>
+    <t>Smorgon</t>
+  </si>
+  <si>
     <t>VPS</t>
   </si>
   <si>
-    <t>Smorgon</t>
-  </si>
-  <si>
-    <t>Buxoro</t>
-  </si>
-  <si>
-    <t>Rukh Vynnyky</t>
+    <t>Al Hussein</t>
   </si>
   <si>
     <t>BATE</t>
@@ -325,30 +337,30 @@
     <t>Kapfenberger SV</t>
   </si>
   <si>
+    <t>Austria Salzburg</t>
+  </si>
+  <si>
+    <t>Fredericia</t>
+  </si>
+  <si>
+    <t>Liefering</t>
+  </si>
+  <si>
+    <t>Wieczysta Kraków</t>
+  </si>
+  <si>
+    <t>SV Stripfing Weiden</t>
+  </si>
+  <si>
+    <t>Amstetten</t>
+  </si>
+  <si>
+    <t>Zagłębie Lubin</t>
+  </si>
+  <si>
     <t>Spartak Varna</t>
   </si>
   <si>
-    <t>Austria Salzburg</t>
-  </si>
-  <si>
-    <t>Wieczysta Kraków</t>
-  </si>
-  <si>
-    <t>Liefering</t>
-  </si>
-  <si>
-    <t>SV Stripfing Weiden</t>
-  </si>
-  <si>
-    <t>Zagłębie Lubin</t>
-  </si>
-  <si>
-    <t>Amstetten</t>
-  </si>
-  <si>
-    <t>Fredericia</t>
-  </si>
-  <si>
     <t>Tallinna FC Levadia</t>
   </si>
   <si>
@@ -361,6 +373,9 @@
     <t>Stade Nyonnais</t>
   </si>
   <si>
+    <t>Al Wihdat</t>
+  </si>
+  <si>
     <t>Vejle</t>
   </si>
   <si>
@@ -376,102 +391,102 @@
     <t>Petrolul 52</t>
   </si>
   <si>
+    <t>ŁKS Łódź</t>
+  </si>
+  <si>
     <t>Wisła Płock</t>
   </si>
   <si>
+    <t>Schalke 04</t>
+  </si>
+  <si>
     <t>LASK Linz</t>
   </si>
   <si>
-    <t>Schalke 04</t>
-  </si>
-  <si>
-    <t>ŁKS Łódź</t>
+    <t>Cork City</t>
+  </si>
+  <si>
+    <t>Wexford</t>
+  </si>
+  <si>
+    <t>Kerry</t>
   </si>
   <si>
     <t>Cobh Ramblers</t>
   </si>
   <si>
+    <t>UCD</t>
+  </si>
+  <si>
+    <t>Bohemians</t>
+  </si>
+  <si>
+    <t>Arbroath</t>
+  </si>
+  <si>
+    <t>Waterford</t>
+  </si>
+  <si>
     <t>KV Mechelen</t>
   </si>
   <si>
-    <t>Arbroath</t>
-  </si>
-  <si>
-    <t>UCD</t>
-  </si>
-  <si>
     <t>Bray Wanderers</t>
   </si>
   <si>
-    <t>Kerry</t>
-  </si>
-  <si>
-    <t>Wexford</t>
-  </si>
-  <si>
-    <t>Waterford</t>
-  </si>
-  <si>
-    <t>Cork City</t>
-  </si>
-  <si>
-    <t>Bohemians</t>
-  </si>
-  <si>
     <t>Shamrock Rovers</t>
   </si>
   <si>
     <t>Luton Town</t>
   </si>
   <si>
+    <t>Ponte Preta</t>
+  </si>
+  <si>
     <t>Remo</t>
   </si>
   <si>
-    <t>Ponte Preta</t>
+    <t>ABC</t>
+  </si>
+  <si>
+    <t>Náutico</t>
+  </si>
+  <si>
+    <t>Brusque</t>
+  </si>
+  <si>
+    <t>Ituano</t>
+  </si>
+  <si>
+    <t>Confiança</t>
   </si>
   <si>
     <t>São Bernardo</t>
   </si>
   <si>
+    <t>Maringá</t>
+  </si>
+  <si>
+    <t>Ypiranga Erechim</t>
+  </si>
+  <si>
     <t>CSA</t>
   </si>
   <si>
-    <t>Maringá</t>
-  </si>
-  <si>
-    <t>Náutico</t>
-  </si>
-  <si>
-    <t>ABC</t>
-  </si>
-  <si>
-    <t>Confiança</t>
-  </si>
-  <si>
-    <t>Ypiranga Erechim</t>
-  </si>
-  <si>
-    <t>Ituano</t>
-  </si>
-  <si>
-    <t>Brusque</t>
-  </si>
-  <si>
     <t>Audax Italiano</t>
   </si>
   <si>
+    <t>Racing Louisville</t>
+  </si>
+  <si>
     <t>Chicago Red Stars</t>
   </si>
   <si>
-    <t>Racing Louisville</t>
+    <t>Tulsa Roughnecks</t>
   </si>
   <si>
     <t>Operário PR</t>
   </si>
   <si>
-    <t>Tulsa Roughnecks</t>
-  </si>
-  <si>
     <t>Colorado Springs</t>
   </si>
   <si>
@@ -484,25 +499,31 @@
     <t>Hirnyk</t>
   </si>
   <si>
+    <t>Aarau</t>
+  </si>
+  <si>
     <t>Bunyodkor</t>
   </si>
   <si>
-    <t>Aarau</t>
-  </si>
-  <si>
     <t>Navbahor</t>
   </si>
   <si>
+    <t>AGMK</t>
+  </si>
+  <si>
+    <t>Pakhtakor</t>
+  </si>
+  <si>
+    <t>SK Poltava</t>
+  </si>
+  <si>
+    <t>Dinamo Minsk</t>
+  </si>
+  <si>
     <t>Mariehamn</t>
   </si>
   <si>
-    <t>Dinamo Minsk</t>
-  </si>
-  <si>
-    <t>AGMK</t>
-  </si>
-  <si>
-    <t>SK Poltava</t>
+    <t>Al Ahli</t>
   </si>
   <si>
     <t>Vitebsk</t>
@@ -517,30 +538,30 @@
     <t>Admira</t>
   </si>
   <si>
+    <t>Austria Klagenfurt</t>
+  </si>
+  <si>
+    <t>København</t>
+  </si>
+  <si>
+    <t>Austria Lustenau</t>
+  </si>
+  <si>
+    <t>Znicz Pruszków</t>
+  </si>
+  <si>
+    <t>First Vienna</t>
+  </si>
+  <si>
+    <t>Sturm Graz II</t>
+  </si>
+  <si>
+    <t>Korona Kielce</t>
+  </si>
+  <si>
     <t>Botev Vratsa</t>
   </si>
   <si>
-    <t>Austria Klagenfurt</t>
-  </si>
-  <si>
-    <t>Znicz Pruszków</t>
-  </si>
-  <si>
-    <t>Austria Lustenau</t>
-  </si>
-  <si>
-    <t>First Vienna</t>
-  </si>
-  <si>
-    <t>Korona Kielce</t>
-  </si>
-  <si>
-    <t>Sturm Graz II</t>
-  </si>
-  <si>
-    <t>København</t>
-  </si>
-  <si>
     <t>Kuressaare</t>
   </si>
   <si>
@@ -553,6 +574,9 @@
     <t>Rapperswil-Jona</t>
   </si>
   <si>
+    <t>Al Ramtha</t>
+  </si>
+  <si>
     <t>OB</t>
   </si>
   <si>
@@ -568,100 +592,100 @@
     <t>UTA Arad</t>
   </si>
   <si>
+    <t>Polonia Bytom</t>
+  </si>
+  <si>
     <t>Piast Gliwice</t>
   </si>
   <si>
+    <t>Hertha BSC</t>
+  </si>
+  <si>
     <t>Sturm Graz</t>
   </si>
   <si>
-    <t>Hertha BSC</t>
-  </si>
-  <si>
-    <t>Polonia Bytom</t>
+    <t>Galway United</t>
+  </si>
+  <si>
+    <t>Finn Harps</t>
+  </si>
+  <si>
+    <t>Athlone Town</t>
   </si>
   <si>
     <t>Longford Town</t>
   </si>
   <si>
+    <t>Dundalk</t>
+  </si>
+  <si>
+    <t>Drogheda United</t>
+  </si>
+  <si>
+    <t>Ayr United</t>
+  </si>
+  <si>
+    <t>St Patrick's Athl.</t>
+  </si>
+  <si>
     <t>Club Brugge</t>
   </si>
   <si>
-    <t>Ayr United</t>
-  </si>
-  <si>
-    <t>Dundalk</t>
-  </si>
-  <si>
     <t>Treaty United</t>
   </si>
   <si>
-    <t>Athlone Town</t>
-  </si>
-  <si>
-    <t>Finn Harps</t>
-  </si>
-  <si>
-    <t>St Patrick's Athl.</t>
-  </si>
-  <si>
-    <t>Galway United</t>
-  </si>
-  <si>
-    <t>Drogheda United</t>
-  </si>
-  <si>
     <t>Derry City</t>
   </si>
   <si>
     <t>AFC Wimbledon</t>
   </si>
   <si>
+    <t>Guarani</t>
+  </si>
+  <si>
     <t>Ferroviária</t>
   </si>
   <si>
-    <t>Guarani</t>
+    <t>Figueirense</t>
+  </si>
+  <si>
+    <t>Retrô</t>
+  </si>
+  <si>
+    <t>Itabaiana</t>
+  </si>
+  <si>
+    <t>Londrina</t>
+  </si>
+  <si>
+    <t>Anápolis</t>
   </si>
   <si>
     <t>Tombense</t>
   </si>
   <si>
+    <t>Floresta</t>
+  </si>
+  <si>
+    <t>Caxias</t>
+  </si>
+  <si>
     <t>Botafogo PB</t>
   </si>
   <si>
-    <t>Floresta</t>
-  </si>
-  <si>
-    <t>Retrô</t>
-  </si>
-  <si>
-    <t>Figueirense</t>
-  </si>
-  <si>
-    <t>Anápolis</t>
-  </si>
-  <si>
-    <t>Caxias</t>
-  </si>
-  <si>
-    <t>Londrina</t>
-  </si>
-  <si>
-    <t>Itabaiana</t>
-  </si>
-  <si>
     <t>Palestino</t>
   </si>
   <si>
+    <t>Kansas City</t>
+  </si>
+  <si>
     <t>Gotham FC</t>
   </si>
   <si>
-    <t>Kansas City</t>
+    <t>Loudoun United</t>
   </si>
   <si>
     <t>Criciúma</t>
-  </si>
-  <si>
-    <t>Loudoun United</t>
   </si>
   <si>
     <t>Lexington</t>
@@ -1040,7 +1064,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AL65"/>
+  <dimension ref="A1:AL68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:38">
@@ -1167,16 +1191,16 @@
         <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F2" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1191,7 +1215,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L2">
         <v>2.59</v>
@@ -1266,10 +1290,10 @@
         <v>0</v>
       </c>
       <c r="AJ2" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK2" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL2" s="3">
         <v>45870.39583333334</v>
@@ -1283,16 +1307,16 @@
         <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F3" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1307,16 +1331,16 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="M3">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O3">
         <v>0</v>
@@ -1382,10 +1406,10 @@
         <v>0</v>
       </c>
       <c r="AJ3" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK3" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL3" s="3">
         <v>45870.45833333334</v>
@@ -1399,16 +1423,16 @@
         <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F4" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1423,16 +1447,16 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L4">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="M4">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N4">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O4">
         <v>0</v>
@@ -1498,10 +1522,10 @@
         <v>0</v>
       </c>
       <c r="AJ4" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK4" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL4" s="3">
         <v>45870.45833333334</v>
@@ -1515,16 +1539,16 @@
         <v>39</v>
       </c>
       <c r="C5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F5" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1539,7 +1563,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -1614,10 +1638,10 @@
         <v>0</v>
       </c>
       <c r="AJ5" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK5" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL5" s="3">
         <v>45870.45833333334</v>
@@ -1634,13 +1658,13 @@
         <v>62</v>
       </c>
       <c r="D6" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E6" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F6" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1655,16 +1679,16 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L6">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M6">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="N6">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -1706,10 +1730,10 @@
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC6">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD6">
         <v>0</v>
@@ -1730,10 +1754,10 @@
         <v>0</v>
       </c>
       <c r="AJ6" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK6" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL6" s="3">
         <v>45870.5</v>
@@ -1747,16 +1771,16 @@
         <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D7" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E7" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F7" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1771,7 +1795,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -1846,10 +1870,10 @@
         <v>0</v>
       </c>
       <c r="AJ7" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK7" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL7" s="3">
         <v>45870.5</v>
@@ -1866,13 +1890,13 @@
         <v>60</v>
       </c>
       <c r="D8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E8" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F8" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1887,16 +1911,16 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="O8">
         <v>0</v>
@@ -1932,10 +1956,10 @@
         <v>0</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AB8">
         <v>0</v>
@@ -1962,10 +1986,10 @@
         <v>0</v>
       </c>
       <c r="AJ8" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK8" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL8" s="3">
         <v>45870.5</v>
@@ -1979,16 +2003,16 @@
         <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D9" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E9" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F9" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2003,16 +2027,16 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L9">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M9">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N9">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="O9">
         <v>0</v>
@@ -2048,10 +2072,10 @@
         <v>0</v>
       </c>
       <c r="Z9">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA9">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AB9">
         <v>0</v>
@@ -2078,10 +2102,10 @@
         <v>0</v>
       </c>
       <c r="AJ9" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK9" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL9" s="3">
         <v>45870.5</v>
@@ -2092,19 +2116,19 @@
         <v>45870</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D10" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E10" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F10" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2119,16 +2143,16 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L10">
-        <v>2.17</v>
+        <v>1.56</v>
       </c>
       <c r="M10">
-        <v>3.28</v>
+        <v>3.98</v>
       </c>
       <c r="N10">
-        <v>3.46</v>
+        <v>4.33</v>
       </c>
       <c r="O10">
         <v>0</v>
@@ -2170,10 +2194,10 @@
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>2.02</v>
+        <v>1.7</v>
       </c>
       <c r="AC10">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="AD10">
         <v>0</v>
@@ -2194,13 +2218,13 @@
         <v>0</v>
       </c>
       <c r="AJ10" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK10" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL10" s="3">
-        <v>45870.51041666666</v>
+        <v>45870.5</v>
       </c>
     </row>
     <row r="11" spans="1:38">
@@ -2208,19 +2232,19 @@
         <v>45870</v>
       </c>
       <c r="B11" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D11" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E11" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F11" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2235,16 +2259,16 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L11">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="M11">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N11">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O11">
         <v>0</v>
@@ -2286,10 +2310,10 @@
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC11">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AD11">
         <v>0</v>
@@ -2310,13 +2334,13 @@
         <v>0</v>
       </c>
       <c r="AJ11" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK11" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL11" s="3">
-        <v>45870.52083333334</v>
+        <v>45870.5</v>
       </c>
     </row>
     <row r="12" spans="1:38">
@@ -2324,19 +2348,19 @@
         <v>45870</v>
       </c>
       <c r="B12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C12" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D12" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E12" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F12" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2351,16 +2375,16 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L12">
-        <v>1.45</v>
+        <v>2.17</v>
       </c>
       <c r="M12">
-        <v>3.7</v>
+        <v>3.28</v>
       </c>
       <c r="N12">
-        <v>6.3</v>
+        <v>3.46</v>
       </c>
       <c r="O12">
         <v>0</v>
@@ -2402,10 +2426,10 @@
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AC12">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AD12">
         <v>0</v>
@@ -2426,13 +2450,13 @@
         <v>0</v>
       </c>
       <c r="AJ12" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK12" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL12" s="3">
-        <v>45870.54166666666</v>
+        <v>45870.51041666666</v>
       </c>
     </row>
     <row r="13" spans="1:38">
@@ -2440,19 +2464,19 @@
         <v>45870</v>
       </c>
       <c r="B13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C13" t="s">
         <v>66</v>
       </c>
       <c r="D13" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E13" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F13" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2467,16 +2491,16 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L13">
-        <v>3.62</v>
+        <v>2.46</v>
       </c>
       <c r="M13">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="N13">
-        <v>1.75</v>
+        <v>2.6</v>
       </c>
       <c r="O13">
         <v>0</v>
@@ -2518,10 +2542,10 @@
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD13">
         <v>0</v>
@@ -2542,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="AJ13" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK13" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL13" s="3">
-        <v>45870.54166666666</v>
+        <v>45870.52083333334</v>
       </c>
     </row>
     <row r="14" spans="1:38">
@@ -2562,13 +2586,13 @@
         <v>67</v>
       </c>
       <c r="D14" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E14" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F14" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2583,16 +2607,16 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L14">
-        <v>2.47</v>
+        <v>1.45</v>
       </c>
       <c r="M14">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="N14">
-        <v>2.7</v>
+        <v>6.3</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -2634,10 +2658,10 @@
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD14">
         <v>0</v>
@@ -2658,10 +2682,10 @@
         <v>0</v>
       </c>
       <c r="AJ14" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK14" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL14" s="3">
         <v>45870.54166666666</v>
@@ -2675,16 +2699,16 @@
         <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D15" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E15" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F15" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2699,16 +2723,16 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O15">
         <v>0</v>
@@ -2774,10 +2798,10 @@
         <v>0</v>
       </c>
       <c r="AJ15" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK15" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL15" s="3">
         <v>45870.54166666666</v>
@@ -2794,13 +2818,13 @@
         <v>68</v>
       </c>
       <c r="D16" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E16" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F16" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2815,16 +2839,16 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L16">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M16">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N16">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O16">
         <v>0</v>
@@ -2890,10 +2914,10 @@
         <v>0</v>
       </c>
       <c r="AJ16" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK16" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL16" s="3">
         <v>45870.54166666666</v>
@@ -2907,16 +2931,16 @@
         <v>43</v>
       </c>
       <c r="C17" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D17" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E17" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F17" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2931,16 +2955,16 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L17">
-        <v>2.54</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M17">
-        <v>3.21</v>
+        <v>5.6</v>
       </c>
       <c r="N17">
-        <v>2.41</v>
+        <v>1.27</v>
       </c>
       <c r="O17">
         <v>0</v>
@@ -2982,10 +3006,10 @@
         <v>0</v>
       </c>
       <c r="AB17">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC17">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD17">
         <v>0</v>
@@ -3006,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="AJ17" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK17" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL17" s="3">
         <v>45870.54166666666</v>
@@ -3023,16 +3047,16 @@
         <v>43</v>
       </c>
       <c r="C18" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D18" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E18" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F18" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -3047,16 +3071,16 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L18">
-        <v>2.3</v>
+        <v>2.54</v>
       </c>
       <c r="M18">
         <v>3.21</v>
       </c>
       <c r="N18">
-        <v>2.68</v>
+        <v>2.41</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -3098,10 +3122,10 @@
         <v>0</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD18">
         <v>0</v>
@@ -3122,10 +3146,10 @@
         <v>0</v>
       </c>
       <c r="AJ18" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK18" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL18" s="3">
         <v>45870.54166666666</v>
@@ -3139,16 +3163,16 @@
         <v>43</v>
       </c>
       <c r="C19" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D19" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E19" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F19" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -3163,16 +3187,16 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L19">
-        <v>2.13</v>
+        <v>1.42</v>
       </c>
       <c r="M19">
-        <v>3.17</v>
+        <v>4.2</v>
       </c>
       <c r="N19">
-        <v>2.99</v>
+        <v>5.6</v>
       </c>
       <c r="O19">
         <v>0</v>
@@ -3214,10 +3238,10 @@
         <v>0</v>
       </c>
       <c r="AB19">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC19">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD19">
         <v>0</v>
@@ -3238,10 +3262,10 @@
         <v>0</v>
       </c>
       <c r="AJ19" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK19" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL19" s="3">
         <v>45870.54166666666</v>
@@ -3255,16 +3279,16 @@
         <v>43</v>
       </c>
       <c r="C20" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D20" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E20" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F20" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -3279,16 +3303,16 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L20">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="M20">
-        <v>3.82</v>
+        <v>3.21</v>
       </c>
       <c r="N20">
-        <v>3.57</v>
+        <v>2.68</v>
       </c>
       <c r="O20">
         <v>0</v>
@@ -3354,10 +3378,10 @@
         <v>0</v>
       </c>
       <c r="AJ20" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK20" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL20" s="3">
         <v>45870.54166666666</v>
@@ -3371,16 +3395,16 @@
         <v>43</v>
       </c>
       <c r="C21" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D21" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E21" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F21" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -3395,16 +3419,16 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L21">
-        <v>9.199999999999999</v>
+        <v>1.73</v>
       </c>
       <c r="M21">
-        <v>5.6</v>
+        <v>3.82</v>
       </c>
       <c r="N21">
-        <v>1.27</v>
+        <v>3.57</v>
       </c>
       <c r="O21">
         <v>0</v>
@@ -3470,10 +3494,10 @@
         <v>0</v>
       </c>
       <c r="AJ21" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK21" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL21" s="3">
         <v>45870.54166666666</v>
@@ -3484,19 +3508,19 @@
         <v>45870</v>
       </c>
       <c r="B22" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C22" t="s">
         <v>71</v>
       </c>
       <c r="D22" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E22" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F22" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3511,16 +3535,16 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L22">
-        <v>1.2</v>
+        <v>2.13</v>
       </c>
       <c r="M22">
-        <v>5.4</v>
+        <v>3.17</v>
       </c>
       <c r="N22">
-        <v>9.800000000000001</v>
+        <v>2.99</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -3562,16 +3586,16 @@
         <v>0</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD22">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE22">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF22">
         <v>0</v>
@@ -3586,13 +3610,13 @@
         <v>0</v>
       </c>
       <c r="AJ22" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK22" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL22" s="3">
-        <v>45870.5625</v>
+        <v>45870.54166666666</v>
       </c>
     </row>
     <row r="23" spans="1:38">
@@ -3600,19 +3624,19 @@
         <v>45870</v>
       </c>
       <c r="B23" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C23" t="s">
         <v>72</v>
       </c>
       <c r="D23" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E23" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F23" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3627,16 +3651,16 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="M23">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O23">
         <v>0</v>
@@ -3702,13 +3726,13 @@
         <v>0</v>
       </c>
       <c r="AJ23" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK23" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL23" s="3">
-        <v>45870.58333333334</v>
+        <v>45870.54166666666</v>
       </c>
     </row>
     <row r="24" spans="1:38">
@@ -3716,19 +3740,19 @@
         <v>45870</v>
       </c>
       <c r="B24" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C24" t="s">
         <v>73</v>
       </c>
       <c r="D24" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E24" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F24" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -3743,16 +3767,16 @@
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L24">
-        <v>2.19</v>
+        <v>1.2</v>
       </c>
       <c r="M24">
-        <v>3.3</v>
+        <v>5.4</v>
       </c>
       <c r="N24">
-        <v>3.15</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O24">
         <v>0</v>
@@ -3794,16 +3818,16 @@
         <v>0</v>
       </c>
       <c r="AB24">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC24">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF24">
         <v>0</v>
@@ -3818,13 +3842,13 @@
         <v>0</v>
       </c>
       <c r="AJ24" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK24" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL24" s="3">
-        <v>45870.58333333334</v>
+        <v>45870.5625</v>
       </c>
     </row>
     <row r="25" spans="1:38">
@@ -3832,19 +3856,19 @@
         <v>45870</v>
       </c>
       <c r="B25" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C25" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="D25" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E25" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F25" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -3859,7 +3883,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -3934,13 +3958,13 @@
         <v>0</v>
       </c>
       <c r="AJ25" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK25" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL25" s="3">
-        <v>45870.60416666666</v>
+        <v>45870.58333333334</v>
       </c>
     </row>
     <row r="26" spans="1:38">
@@ -3948,19 +3972,19 @@
         <v>45870</v>
       </c>
       <c r="B26" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C26" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D26" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E26" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F26" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -3975,16 +3999,16 @@
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L26">
-        <v>2.7</v>
+        <v>2.19</v>
       </c>
       <c r="M26">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N26">
-        <v>2.41</v>
+        <v>3.15</v>
       </c>
       <c r="O26">
         <v>0</v>
@@ -4026,10 +4050,10 @@
         <v>0</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD26">
         <v>0</v>
@@ -4050,13 +4074,13 @@
         <v>0</v>
       </c>
       <c r="AJ26" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK26" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL26" s="3">
-        <v>45870.625</v>
+        <v>45870.58333333334</v>
       </c>
     </row>
     <row r="27" spans="1:38">
@@ -4064,19 +4088,19 @@
         <v>45870</v>
       </c>
       <c r="B27" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C27" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="D27" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E27" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F27" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -4091,7 +4115,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -4166,13 +4190,13 @@
         <v>0</v>
       </c>
       <c r="AJ27" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK27" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL27" s="3">
-        <v>45870.625</v>
+        <v>45870.60416666666</v>
       </c>
     </row>
     <row r="28" spans="1:38">
@@ -4183,16 +4207,16 @@
         <v>47</v>
       </c>
       <c r="C28" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="D28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E28" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F28" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -4207,16 +4231,16 @@
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L28">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M28">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N28">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O28">
         <v>0</v>
@@ -4282,13 +4306,13 @@
         <v>0</v>
       </c>
       <c r="AJ28" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK28" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL28" s="3">
-        <v>45870.625</v>
+        <v>45870.61458333334</v>
       </c>
     </row>
     <row r="29" spans="1:38">
@@ -4299,16 +4323,16 @@
         <v>48</v>
       </c>
       <c r="C29" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D29" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E29" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F29" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -4323,16 +4347,16 @@
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L29">
-        <v>1.52</v>
+        <v>2.7</v>
       </c>
       <c r="M29">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="N29">
-        <v>5.5</v>
+        <v>2.41</v>
       </c>
       <c r="O29">
         <v>0</v>
@@ -4374,10 +4398,10 @@
         <v>0</v>
       </c>
       <c r="AB29">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC29">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD29">
         <v>0</v>
@@ -4398,13 +4422,13 @@
         <v>0</v>
       </c>
       <c r="AJ29" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK29" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL29" s="3">
-        <v>45870.63541666666</v>
+        <v>45870.625</v>
       </c>
     </row>
     <row r="30" spans="1:38">
@@ -4412,19 +4436,19 @@
         <v>45870</v>
       </c>
       <c r="B30" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C30" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="D30" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E30" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F30" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -4439,16 +4463,16 @@
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L30">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="M30">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="N30">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="O30">
         <v>0</v>
@@ -4490,10 +4514,10 @@
         <v>0</v>
       </c>
       <c r="AB30">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AC30">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AD30">
         <v>0</v>
@@ -4514,13 +4538,13 @@
         <v>0</v>
       </c>
       <c r="AJ30" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK30" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL30" s="3">
-        <v>45870.64583333334</v>
+        <v>45870.625</v>
       </c>
     </row>
     <row r="31" spans="1:38">
@@ -4528,19 +4552,19 @@
         <v>45870</v>
       </c>
       <c r="B31" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C31" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="D31" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E31" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F31" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -4555,16 +4579,16 @@
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L31">
-        <v>2.27</v>
+        <v>1.89</v>
       </c>
       <c r="M31">
-        <v>2.99</v>
+        <v>3.75</v>
       </c>
       <c r="N31">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="O31">
         <v>0</v>
@@ -4630,13 +4654,13 @@
         <v>0</v>
       </c>
       <c r="AJ31" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK31" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL31" s="3">
-        <v>45870.64583333334</v>
+        <v>45870.625</v>
       </c>
     </row>
     <row r="32" spans="1:38">
@@ -4647,16 +4671,16 @@
         <v>49</v>
       </c>
       <c r="C32" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D32" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E32" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F32" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -4671,16 +4695,16 @@
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L32">
-        <v>2.88</v>
+        <v>1.52</v>
       </c>
       <c r="M32">
-        <v>2.96</v>
+        <v>3.8</v>
       </c>
       <c r="N32">
-        <v>2.31</v>
+        <v>5.5</v>
       </c>
       <c r="O32">
         <v>0</v>
@@ -4722,10 +4746,10 @@
         <v>0</v>
       </c>
       <c r="AB32">
-        <v>1.7</v>
+        <v>1.92</v>
       </c>
       <c r="AC32">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AD32">
         <v>0</v>
@@ -4746,13 +4770,13 @@
         <v>0</v>
       </c>
       <c r="AJ32" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK32" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL32" s="3">
-        <v>45870.64583333334</v>
+        <v>45870.63541666666</v>
       </c>
     </row>
     <row r="33" spans="1:38">
@@ -4760,19 +4784,19 @@
         <v>45870</v>
       </c>
       <c r="B33" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C33" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="D33" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E33" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F33" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -4787,16 +4811,16 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L33">
-        <v>2.99</v>
+        <v>2.24</v>
       </c>
       <c r="M33">
-        <v>3.21</v>
+        <v>2.96</v>
       </c>
       <c r="N33">
-        <v>2.36</v>
+        <v>2.98</v>
       </c>
       <c r="O33">
         <v>0</v>
@@ -4838,16 +4862,16 @@
         <v>0</v>
       </c>
       <c r="AB33">
-        <v>1.53</v>
+        <v>2.39</v>
       </c>
       <c r="AC33">
-        <v>2.35</v>
+        <v>1.58</v>
       </c>
       <c r="AD33">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE33">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF33">
         <v>0</v>
@@ -4862,10 +4886,10 @@
         <v>0</v>
       </c>
       <c r="AJ33" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK33" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL33" s="3">
         <v>45870.64583333334</v>
@@ -4876,19 +4900,19 @@
         <v>45870</v>
       </c>
       <c r="B34" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C34" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D34" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E34" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F34" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -4903,7 +4927,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L34">
         <v>2.02</v>
@@ -4978,10 +5002,10 @@
         <v>0</v>
       </c>
       <c r="AJ34" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK34" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL34" s="3">
         <v>45870.64583333334</v>
@@ -4995,16 +5019,16 @@
         <v>50</v>
       </c>
       <c r="C35" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D35" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E35" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F35" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -5019,16 +5043,16 @@
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L35">
-        <v>1.35</v>
+        <v>2.27</v>
       </c>
       <c r="M35">
-        <v>4.8</v>
+        <v>2.99</v>
       </c>
       <c r="N35">
-        <v>6.8</v>
+        <v>2.9</v>
       </c>
       <c r="O35">
         <v>0</v>
@@ -5094,13 +5118,13 @@
         <v>0</v>
       </c>
       <c r="AJ35" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK35" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL35" s="3">
-        <v>45870.65625</v>
+        <v>45870.64583333334</v>
       </c>
     </row>
     <row r="36" spans="1:38">
@@ -5111,16 +5135,16 @@
         <v>50</v>
       </c>
       <c r="C36" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D36" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E36" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F36" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -5135,16 +5159,16 @@
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L36">
-        <v>4</v>
+        <v>2.99</v>
       </c>
       <c r="M36">
-        <v>3.72</v>
+        <v>3.21</v>
       </c>
       <c r="N36">
-        <v>1.66</v>
+        <v>2.36</v>
       </c>
       <c r="O36">
         <v>0</v>
@@ -5186,16 +5210,16 @@
         <v>0</v>
       </c>
       <c r="AB36">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AC36">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AD36">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AE36">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AF36">
         <v>0</v>
@@ -5210,13 +5234,13 @@
         <v>0</v>
       </c>
       <c r="AJ36" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK36" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL36" s="3">
-        <v>45870.65625</v>
+        <v>45870.64583333334</v>
       </c>
     </row>
     <row r="37" spans="1:38">
@@ -5227,16 +5251,16 @@
         <v>50</v>
       </c>
       <c r="C37" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D37" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E37" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F37" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -5251,16 +5275,16 @@
         <v>0</v>
       </c>
       <c r="K37" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L37">
-        <v>3.55</v>
+        <v>2.88</v>
       </c>
       <c r="M37">
-        <v>3.7</v>
+        <v>2.96</v>
       </c>
       <c r="N37">
-        <v>1.89</v>
+        <v>2.31</v>
       </c>
       <c r="O37">
         <v>0</v>
@@ -5302,10 +5326,10 @@
         <v>0</v>
       </c>
       <c r="AB37">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AC37">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AD37">
         <v>0</v>
@@ -5326,13 +5350,13 @@
         <v>0</v>
       </c>
       <c r="AJ37" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK37" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL37" s="3">
-        <v>45870.65625</v>
+        <v>45870.64583333334</v>
       </c>
     </row>
     <row r="38" spans="1:38">
@@ -5340,19 +5364,19 @@
         <v>45870</v>
       </c>
       <c r="B38" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C38" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D38" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E38" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F38" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -5367,16 +5391,16 @@
         <v>0</v>
       </c>
       <c r="K38" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L38">
-        <v>4.3</v>
+        <v>2.85</v>
       </c>
       <c r="M38">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="N38">
-        <v>1.72</v>
+        <v>2.31</v>
       </c>
       <c r="O38">
         <v>0</v>
@@ -5418,10 +5442,10 @@
         <v>0</v>
       </c>
       <c r="AB38">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC38">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AD38">
         <v>0</v>
@@ -5442,10 +5466,10 @@
         <v>0</v>
       </c>
       <c r="AJ38" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK38" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL38" s="3">
         <v>45870.65625</v>
@@ -5456,19 +5480,19 @@
         <v>45870</v>
       </c>
       <c r="B39" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C39" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D39" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E39" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F39" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -5483,13 +5507,13 @@
         <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L39">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="M39">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="N39">
         <v>3.15</v>
@@ -5558,10 +5582,10 @@
         <v>0</v>
       </c>
       <c r="AJ39" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK39" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL39" s="3">
         <v>45870.65625</v>
@@ -5572,19 +5596,19 @@
         <v>45870</v>
       </c>
       <c r="B40" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C40" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D40" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E40" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F40" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -5599,7 +5623,7 @@
         <v>0</v>
       </c>
       <c r="K40" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L40">
         <v>2.06</v>
@@ -5674,10 +5698,10 @@
         <v>0</v>
       </c>
       <c r="AJ40" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK40" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL40" s="3">
         <v>45870.65625</v>
@@ -5688,19 +5712,19 @@
         <v>45870</v>
       </c>
       <c r="B41" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C41" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D41" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E41" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F41" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -5715,16 +5739,16 @@
         <v>0</v>
       </c>
       <c r="K41" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L41">
-        <v>2</v>
+        <v>1.35</v>
       </c>
       <c r="M41">
-        <v>3.55</v>
+        <v>4.8</v>
       </c>
       <c r="N41">
-        <v>3.15</v>
+        <v>6.8</v>
       </c>
       <c r="O41">
         <v>0</v>
@@ -5790,10 +5814,10 @@
         <v>0</v>
       </c>
       <c r="AJ41" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK41" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL41" s="3">
         <v>45870.65625</v>
@@ -5804,19 +5828,19 @@
         <v>45870</v>
       </c>
       <c r="B42" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C42" t="s">
         <v>81</v>
       </c>
       <c r="D42" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E42" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F42" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -5831,16 +5855,16 @@
         <v>0</v>
       </c>
       <c r="K42" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L42">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M42">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O42">
         <v>0</v>
@@ -5882,10 +5906,10 @@
         <v>0</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AD42">
         <v>0</v>
@@ -5906,10 +5930,10 @@
         <v>0</v>
       </c>
       <c r="AJ42" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK42" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL42" s="3">
         <v>45870.65625</v>
@@ -5920,19 +5944,19 @@
         <v>45870</v>
       </c>
       <c r="B43" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C43" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D43" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E43" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F43" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -5947,16 +5971,16 @@
         <v>0</v>
       </c>
       <c r="K43" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L43">
-        <v>2.85</v>
+        <v>1.51</v>
       </c>
       <c r="M43">
-        <v>3.15</v>
+        <v>3.85</v>
       </c>
       <c r="N43">
-        <v>2.31</v>
+        <v>5.8</v>
       </c>
       <c r="O43">
         <v>0</v>
@@ -5998,10 +6022,10 @@
         <v>0</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD43">
         <v>0</v>
@@ -6022,10 +6046,10 @@
         <v>0</v>
       </c>
       <c r="AJ43" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK43" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL43" s="3">
         <v>45870.65625</v>
@@ -6036,19 +6060,19 @@
         <v>45870</v>
       </c>
       <c r="B44" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C44" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D44" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E44" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F44" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -6063,16 +6087,16 @@
         <v>0</v>
       </c>
       <c r="K44" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L44">
-        <v>1.51</v>
+        <v>3.55</v>
       </c>
       <c r="M44">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="N44">
-        <v>5.8</v>
+        <v>1.89</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -6114,10 +6138,10 @@
         <v>0</v>
       </c>
       <c r="AB44">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AC44">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AD44">
         <v>0</v>
@@ -6138,10 +6162,10 @@
         <v>0</v>
       </c>
       <c r="AJ44" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK44" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL44" s="3">
         <v>45870.65625</v>
@@ -6155,16 +6179,16 @@
         <v>51</v>
       </c>
       <c r="C45" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D45" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E45" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F45" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -6179,7 +6203,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L45">
         <v>0</v>
@@ -6254,13 +6278,13 @@
         <v>0</v>
       </c>
       <c r="AJ45" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK45" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL45" s="3">
-        <v>45870.66666666666</v>
+        <v>45870.65625</v>
       </c>
     </row>
     <row r="46" spans="1:38">
@@ -6271,16 +6295,16 @@
         <v>51</v>
       </c>
       <c r="C46" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D46" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E46" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F46" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -6295,16 +6319,16 @@
         <v>0</v>
       </c>
       <c r="K46" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L46">
-        <v>1.54</v>
+        <v>4</v>
       </c>
       <c r="M46">
-        <v>3.8</v>
+        <v>3.72</v>
       </c>
       <c r="N46">
-        <v>4.8</v>
+        <v>1.66</v>
       </c>
       <c r="O46">
         <v>0</v>
@@ -6346,16 +6370,16 @@
         <v>0</v>
       </c>
       <c r="AB46">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="AC46">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="AD46">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AE46">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AF46">
         <v>0</v>
@@ -6370,13 +6394,13 @@
         <v>0</v>
       </c>
       <c r="AJ46" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK46" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL46" s="3">
-        <v>45870.66666666666</v>
+        <v>45870.65625</v>
       </c>
     </row>
     <row r="47" spans="1:38">
@@ -6384,19 +6408,19 @@
         <v>45870</v>
       </c>
       <c r="B47" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C47" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D47" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E47" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F47" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -6411,16 +6435,16 @@
         <v>0</v>
       </c>
       <c r="K47" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L47">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="M47">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N47">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="O47">
         <v>0</v>
@@ -6462,10 +6486,10 @@
         <v>0</v>
       </c>
       <c r="AB47">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC47">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD47">
         <v>0</v>
@@ -6486,13 +6510,13 @@
         <v>0</v>
       </c>
       <c r="AJ47" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK47" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL47" s="3">
-        <v>45870.79166666666</v>
+        <v>45870.65625</v>
       </c>
     </row>
     <row r="48" spans="1:38">
@@ -6503,16 +6527,16 @@
         <v>52</v>
       </c>
       <c r="C48" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D48" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E48" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F48" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -6527,7 +6551,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L48">
         <v>0</v>
@@ -6602,13 +6626,13 @@
         <v>0</v>
       </c>
       <c r="AJ48" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK48" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL48" s="3">
-        <v>45870.79166666666</v>
+        <v>45870.66666666666</v>
       </c>
     </row>
     <row r="49" spans="1:38">
@@ -6622,13 +6646,13 @@
         <v>84</v>
       </c>
       <c r="D49" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E49" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F49" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -6643,16 +6667,16 @@
         <v>0</v>
       </c>
       <c r="K49" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L49">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M49">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O49">
         <v>0</v>
@@ -6694,10 +6718,10 @@
         <v>0</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD49">
         <v>0</v>
@@ -6718,13 +6742,13 @@
         <v>0</v>
       </c>
       <c r="AJ49" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK49" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL49" s="3">
-        <v>45870.79166666666</v>
+        <v>45870.66666666666</v>
       </c>
     </row>
     <row r="50" spans="1:38">
@@ -6732,19 +6756,19 @@
         <v>45870</v>
       </c>
       <c r="B50" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C50" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D50" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E50" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F50" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -6759,7 +6783,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L50">
         <v>0</v>
@@ -6834,10 +6858,10 @@
         <v>0</v>
       </c>
       <c r="AJ50" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK50" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL50" s="3">
         <v>45870.79166666666</v>
@@ -6848,19 +6872,19 @@
         <v>45870</v>
       </c>
       <c r="B51" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C51" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E51" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F51" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -6875,16 +6899,16 @@
         <v>0</v>
       </c>
       <c r="K51" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L51">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M51">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O51">
         <v>0</v>
@@ -6926,10 +6950,10 @@
         <v>0</v>
       </c>
       <c r="AB51">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC51">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD51">
         <v>0</v>
@@ -6950,10 +6974,10 @@
         <v>0</v>
       </c>
       <c r="AJ51" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK51" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL51" s="3">
         <v>45870.79166666666</v>
@@ -6964,19 +6988,19 @@
         <v>45870</v>
       </c>
       <c r="B52" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C52" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D52" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E52" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F52" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -6991,7 +7015,7 @@
         <v>0</v>
       </c>
       <c r="K52" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L52">
         <v>0</v>
@@ -7066,10 +7090,10 @@
         <v>0</v>
       </c>
       <c r="AJ52" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK52" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL52" s="3">
         <v>45870.79166666666</v>
@@ -7080,19 +7104,19 @@
         <v>45870</v>
       </c>
       <c r="B53" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C53" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D53" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E53" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F53" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -7107,7 +7131,7 @@
         <v>0</v>
       </c>
       <c r="K53" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L53">
         <v>0</v>
@@ -7182,10 +7206,10 @@
         <v>0</v>
       </c>
       <c r="AJ53" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK53" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL53" s="3">
         <v>45870.79166666666</v>
@@ -7196,19 +7220,19 @@
         <v>45870</v>
       </c>
       <c r="B54" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C54" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D54" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E54" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F54" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -7223,7 +7247,7 @@
         <v>0</v>
       </c>
       <c r="K54" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L54">
         <v>0</v>
@@ -7298,10 +7322,10 @@
         <v>0</v>
       </c>
       <c r="AJ54" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK54" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL54" s="3">
         <v>45870.79166666666</v>
@@ -7312,19 +7336,19 @@
         <v>45870</v>
       </c>
       <c r="B55" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C55" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D55" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E55" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F55" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -7339,7 +7363,7 @@
         <v>0</v>
       </c>
       <c r="K55" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L55">
         <v>0</v>
@@ -7414,10 +7438,10 @@
         <v>0</v>
       </c>
       <c r="AJ55" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK55" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL55" s="3">
         <v>45870.79166666666</v>
@@ -7428,19 +7452,19 @@
         <v>45870</v>
       </c>
       <c r="B56" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C56" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D56" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E56" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F56" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -7455,7 +7479,7 @@
         <v>0</v>
       </c>
       <c r="K56" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L56">
         <v>0</v>
@@ -7530,10 +7554,10 @@
         <v>0</v>
       </c>
       <c r="AJ56" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK56" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL56" s="3">
         <v>45870.79166666666</v>
@@ -7544,19 +7568,19 @@
         <v>45870</v>
       </c>
       <c r="B57" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C57" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D57" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E57" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F57" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -7571,7 +7595,7 @@
         <v>0</v>
       </c>
       <c r="K57" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L57">
         <v>0</v>
@@ -7646,10 +7670,10 @@
         <v>0</v>
       </c>
       <c r="AJ57" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK57" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL57" s="3">
         <v>45870.79166666666</v>
@@ -7666,13 +7690,13 @@
         <v>85</v>
       </c>
       <c r="D58" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E58" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F58" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -7687,7 +7711,7 @@
         <v>0</v>
       </c>
       <c r="K58" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L58">
         <v>0</v>
@@ -7762,13 +7786,13 @@
         <v>0</v>
       </c>
       <c r="AJ58" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK58" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL58" s="3">
-        <v>45870.83333333334</v>
+        <v>45870.79166666666</v>
       </c>
     </row>
     <row r="59" spans="1:38">
@@ -7776,19 +7800,19 @@
         <v>45870</v>
       </c>
       <c r="B59" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C59" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D59" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E59" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F59" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -7803,16 +7827,16 @@
         <v>0</v>
       </c>
       <c r="K59" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L59">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M59">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N59">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="O59">
         <v>0</v>
@@ -7854,10 +7878,10 @@
         <v>0</v>
       </c>
       <c r="AB59">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC59">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD59">
         <v>0</v>
@@ -7878,13 +7902,13 @@
         <v>0</v>
       </c>
       <c r="AJ59" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK59" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL59" s="3">
-        <v>45870.875</v>
+        <v>45870.79166666666</v>
       </c>
     </row>
     <row r="60" spans="1:38">
@@ -7892,19 +7916,19 @@
         <v>45870</v>
       </c>
       <c r="B60" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C60" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D60" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E60" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F60" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -7919,16 +7943,16 @@
         <v>0</v>
       </c>
       <c r="K60" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L60">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M60">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N60">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O60">
         <v>0</v>
@@ -7970,10 +7994,10 @@
         <v>0</v>
       </c>
       <c r="AB60">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC60">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AD60">
         <v>0</v>
@@ -7994,13 +8018,13 @@
         <v>0</v>
       </c>
       <c r="AJ60" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK60" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL60" s="3">
-        <v>45870.875</v>
+        <v>45870.79166666666</v>
       </c>
     </row>
     <row r="61" spans="1:38">
@@ -8008,19 +8032,19 @@
         <v>45870</v>
       </c>
       <c r="B61" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C61" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D61" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E61" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F61" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -8035,16 +8059,16 @@
         <v>0</v>
       </c>
       <c r="K61" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L61">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M61">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N61">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O61">
         <v>0</v>
@@ -8080,16 +8104,16 @@
         <v>0</v>
       </c>
       <c r="Z61">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA61">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB61">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC61">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AD61">
         <v>0</v>
@@ -8110,13 +8134,13 @@
         <v>0</v>
       </c>
       <c r="AJ61" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK61" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL61" s="3">
-        <v>45870.89583333334</v>
+        <v>45870.83333333334</v>
       </c>
     </row>
     <row r="62" spans="1:38">
@@ -8127,16 +8151,16 @@
         <v>55</v>
       </c>
       <c r="C62" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D62" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E62" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F62" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -8151,16 +8175,16 @@
         <v>0</v>
       </c>
       <c r="K62" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L62">
-        <v>1.86</v>
+        <v>3.2</v>
       </c>
       <c r="M62">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="N62">
-        <v>3.6</v>
+        <v>1.84</v>
       </c>
       <c r="O62">
         <v>0</v>
@@ -8202,10 +8226,10 @@
         <v>0</v>
       </c>
       <c r="AB62">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="AC62">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AD62">
         <v>0</v>
@@ -8226,13 +8250,13 @@
         <v>0</v>
       </c>
       <c r="AJ62" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK62" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL62" s="3">
-        <v>45870.89583333334</v>
+        <v>45870.875</v>
       </c>
     </row>
     <row r="63" spans="1:38">
@@ -8240,19 +8264,19 @@
         <v>45870</v>
       </c>
       <c r="B63" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C63" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D63" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E63" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F63" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -8267,16 +8291,16 @@
         <v>0</v>
       </c>
       <c r="K63" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L63">
-        <v>1.61</v>
+        <v>5</v>
       </c>
       <c r="M63">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="N63">
-        <v>4.7</v>
+        <v>1.52</v>
       </c>
       <c r="O63">
         <v>0</v>
@@ -8318,7 +8342,7 @@
         <v>0</v>
       </c>
       <c r="AB63">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="AC63">
         <v>1.9</v>
@@ -8342,13 +8366,13 @@
         <v>0</v>
       </c>
       <c r="AJ63" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK63" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL63" s="3">
-        <v>45870.91666666666</v>
+        <v>45870.875</v>
       </c>
     </row>
     <row r="64" spans="1:38">
@@ -8356,19 +8380,19 @@
         <v>45870</v>
       </c>
       <c r="B64" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C64" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D64" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E64" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F64" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -8383,16 +8407,16 @@
         <v>0</v>
       </c>
       <c r="K64" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L64">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M64">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N64">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O64">
         <v>0</v>
@@ -8434,10 +8458,10 @@
         <v>0</v>
       </c>
       <c r="AB64">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC64">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD64">
         <v>0</v>
@@ -8458,13 +8482,13 @@
         <v>0</v>
       </c>
       <c r="AJ64" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AK64" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AL64" s="3">
-        <v>45870.95833333334</v>
+        <v>45870.89583333334</v>
       </c>
     </row>
     <row r="65" spans="1:38">
@@ -8472,114 +8496,462 @@
         <v>45870</v>
       </c>
       <c r="B65" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C65" t="s">
         <v>86</v>
       </c>
       <c r="D65" t="s">
+        <v>92</v>
+      </c>
+      <c r="E65" t="s">
+        <v>156</v>
+      </c>
+      <c r="F65" t="s">
+        <v>223</v>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0</v>
+      </c>
+      <c r="K65" t="s">
+        <v>227</v>
+      </c>
+      <c r="L65">
+        <v>2.16</v>
+      </c>
+      <c r="M65">
+        <v>3.2</v>
+      </c>
+      <c r="N65">
+        <v>3.3</v>
+      </c>
+      <c r="O65">
+        <v>0</v>
+      </c>
+      <c r="P65">
+        <v>0</v>
+      </c>
+      <c r="Q65">
+        <v>0</v>
+      </c>
+      <c r="R65">
+        <v>0</v>
+      </c>
+      <c r="S65">
+        <v>0</v>
+      </c>
+      <c r="T65">
+        <v>0</v>
+      </c>
+      <c r="U65">
+        <v>0</v>
+      </c>
+      <c r="V65">
+        <v>0</v>
+      </c>
+      <c r="W65">
+        <v>0</v>
+      </c>
+      <c r="X65">
+        <v>0</v>
+      </c>
+      <c r="Y65">
+        <v>0</v>
+      </c>
+      <c r="Z65">
+        <v>1.48</v>
+      </c>
+      <c r="AA65">
+        <v>2.37</v>
+      </c>
+      <c r="AB65">
+        <v>2.5</v>
+      </c>
+      <c r="AC65">
+        <v>1.48</v>
+      </c>
+      <c r="AD65">
+        <v>0</v>
+      </c>
+      <c r="AE65">
+        <v>0</v>
+      </c>
+      <c r="AF65">
+        <v>0</v>
+      </c>
+      <c r="AG65">
+        <v>0</v>
+      </c>
+      <c r="AH65">
+        <v>0</v>
+      </c>
+      <c r="AI65">
+        <v>0</v>
+      </c>
+      <c r="AJ65" t="s">
+        <v>228</v>
+      </c>
+      <c r="AK65" t="s">
+        <v>228</v>
+      </c>
+      <c r="AL65" s="3">
+        <v>45870.89583333334</v>
+      </c>
+    </row>
+    <row r="66" spans="1:38">
+      <c r="A66" s="2">
+        <v>45870</v>
+      </c>
+      <c r="B66" t="s">
+        <v>57</v>
+      </c>
+      <c r="C66" t="s">
+        <v>89</v>
+      </c>
+      <c r="D66" t="s">
+        <v>92</v>
+      </c>
+      <c r="E66" t="s">
+        <v>157</v>
+      </c>
+      <c r="F66" t="s">
+        <v>224</v>
+      </c>
+      <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="H66">
+        <v>0</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>0</v>
+      </c>
+      <c r="K66" t="s">
+        <v>227</v>
+      </c>
+      <c r="L66">
+        <v>1.61</v>
+      </c>
+      <c r="M66">
+        <v>3.75</v>
+      </c>
+      <c r="N66">
+        <v>4.7</v>
+      </c>
+      <c r="O66">
+        <v>0</v>
+      </c>
+      <c r="P66">
+        <v>0</v>
+      </c>
+      <c r="Q66">
+        <v>0</v>
+      </c>
+      <c r="R66">
+        <v>0</v>
+      </c>
+      <c r="S66">
+        <v>0</v>
+      </c>
+      <c r="T66">
+        <v>0</v>
+      </c>
+      <c r="U66">
+        <v>0</v>
+      </c>
+      <c r="V66">
+        <v>0</v>
+      </c>
+      <c r="W66">
+        <v>0</v>
+      </c>
+      <c r="X66">
+        <v>0</v>
+      </c>
+      <c r="Y66">
+        <v>0</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+      <c r="AA66">
+        <v>0</v>
+      </c>
+      <c r="AB66">
+        <v>1.86</v>
+      </c>
+      <c r="AC66">
+        <v>1.9</v>
+      </c>
+      <c r="AD66">
+        <v>0</v>
+      </c>
+      <c r="AE66">
+        <v>0</v>
+      </c>
+      <c r="AF66">
+        <v>0</v>
+      </c>
+      <c r="AG66">
+        <v>0</v>
+      </c>
+      <c r="AH66">
+        <v>0</v>
+      </c>
+      <c r="AI66">
+        <v>0</v>
+      </c>
+      <c r="AJ66" t="s">
+        <v>228</v>
+      </c>
+      <c r="AK66" t="s">
+        <v>228</v>
+      </c>
+      <c r="AL66" s="3">
+        <v>45870.91666666666</v>
+      </c>
+    </row>
+    <row r="67" spans="1:38">
+      <c r="A67" s="2">
+        <v>45870</v>
+      </c>
+      <c r="B67" t="s">
+        <v>58</v>
+      </c>
+      <c r="C67" t="s">
         <v>90</v>
       </c>
-      <c r="E65" t="s">
-        <v>154</v>
-      </c>
-      <c r="F65" t="s">
-        <v>218</v>
-      </c>
-      <c r="G65">
-        <v>0</v>
-      </c>
-      <c r="H65">
-        <v>0</v>
-      </c>
-      <c r="I65">
-        <v>0</v>
-      </c>
-      <c r="J65">
-        <v>0</v>
-      </c>
-      <c r="K65" t="s">
-        <v>219</v>
-      </c>
-      <c r="L65">
-        <v>0</v>
-      </c>
-      <c r="M65">
-        <v>0</v>
-      </c>
-      <c r="N65">
-        <v>0</v>
-      </c>
-      <c r="O65">
-        <v>0</v>
-      </c>
-      <c r="P65">
-        <v>0</v>
-      </c>
-      <c r="Q65">
-        <v>0</v>
-      </c>
-      <c r="R65">
-        <v>0</v>
-      </c>
-      <c r="S65">
-        <v>0</v>
-      </c>
-      <c r="T65">
-        <v>0</v>
-      </c>
-      <c r="U65">
-        <v>0</v>
-      </c>
-      <c r="V65">
-        <v>0</v>
-      </c>
-      <c r="W65">
-        <v>0</v>
-      </c>
-      <c r="X65">
-        <v>0</v>
-      </c>
-      <c r="Y65">
-        <v>0</v>
-      </c>
-      <c r="Z65">
-        <v>0</v>
-      </c>
-      <c r="AA65">
-        <v>0</v>
-      </c>
-      <c r="AB65">
-        <v>0</v>
-      </c>
-      <c r="AC65">
-        <v>0</v>
-      </c>
-      <c r="AD65">
-        <v>0</v>
-      </c>
-      <c r="AE65">
-        <v>0</v>
-      </c>
-      <c r="AF65">
-        <v>0</v>
-      </c>
-      <c r="AG65">
-        <v>0</v>
-      </c>
-      <c r="AH65">
-        <v>0</v>
-      </c>
-      <c r="AI65">
-        <v>0</v>
-      </c>
-      <c r="AJ65" t="s">
-        <v>220</v>
-      </c>
-      <c r="AK65" t="s">
-        <v>220</v>
-      </c>
-      <c r="AL65" s="3">
+      <c r="D67" t="s">
+        <v>92</v>
+      </c>
+      <c r="E67" t="s">
+        <v>158</v>
+      </c>
+      <c r="F67" t="s">
+        <v>225</v>
+      </c>
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
+      <c r="K67" t="s">
+        <v>227</v>
+      </c>
+      <c r="L67">
+        <v>0</v>
+      </c>
+      <c r="M67">
+        <v>0</v>
+      </c>
+      <c r="N67">
+        <v>0</v>
+      </c>
+      <c r="O67">
+        <v>0</v>
+      </c>
+      <c r="P67">
+        <v>0</v>
+      </c>
+      <c r="Q67">
+        <v>0</v>
+      </c>
+      <c r="R67">
+        <v>0</v>
+      </c>
+      <c r="S67">
+        <v>0</v>
+      </c>
+      <c r="T67">
+        <v>0</v>
+      </c>
+      <c r="U67">
+        <v>0</v>
+      </c>
+      <c r="V67">
+        <v>0</v>
+      </c>
+      <c r="W67">
+        <v>0</v>
+      </c>
+      <c r="X67">
+        <v>0</v>
+      </c>
+      <c r="Y67">
+        <v>0</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+      <c r="AA67">
+        <v>0</v>
+      </c>
+      <c r="AB67">
+        <v>0</v>
+      </c>
+      <c r="AC67">
+        <v>0</v>
+      </c>
+      <c r="AD67">
+        <v>0</v>
+      </c>
+      <c r="AE67">
+        <v>0</v>
+      </c>
+      <c r="AF67">
+        <v>0</v>
+      </c>
+      <c r="AG67">
+        <v>0</v>
+      </c>
+      <c r="AH67">
+        <v>0</v>
+      </c>
+      <c r="AI67">
+        <v>0</v>
+      </c>
+      <c r="AJ67" t="s">
+        <v>228</v>
+      </c>
+      <c r="AK67" t="s">
+        <v>228</v>
+      </c>
+      <c r="AL67" s="3">
+        <v>45870.95833333334</v>
+      </c>
+    </row>
+    <row r="68" spans="1:38">
+      <c r="A68" s="2">
+        <v>45870</v>
+      </c>
+      <c r="B68" t="s">
+        <v>59</v>
+      </c>
+      <c r="C68" t="s">
+        <v>88</v>
+      </c>
+      <c r="D68" t="s">
+        <v>92</v>
+      </c>
+      <c r="E68" t="s">
+        <v>159</v>
+      </c>
+      <c r="F68" t="s">
+        <v>226</v>
+      </c>
+      <c r="G68">
+        <v>0</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>0</v>
+      </c>
+      <c r="K68" t="s">
+        <v>227</v>
+      </c>
+      <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="M68">
+        <v>0</v>
+      </c>
+      <c r="N68">
+        <v>0</v>
+      </c>
+      <c r="O68">
+        <v>0</v>
+      </c>
+      <c r="P68">
+        <v>0</v>
+      </c>
+      <c r="Q68">
+        <v>0</v>
+      </c>
+      <c r="R68">
+        <v>0</v>
+      </c>
+      <c r="S68">
+        <v>0</v>
+      </c>
+      <c r="T68">
+        <v>0</v>
+      </c>
+      <c r="U68">
+        <v>0</v>
+      </c>
+      <c r="V68">
+        <v>0</v>
+      </c>
+      <c r="W68">
+        <v>0</v>
+      </c>
+      <c r="X68">
+        <v>0</v>
+      </c>
+      <c r="Y68">
+        <v>0</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+      <c r="AA68">
+        <v>0</v>
+      </c>
+      <c r="AB68">
+        <v>0</v>
+      </c>
+      <c r="AC68">
+        <v>0</v>
+      </c>
+      <c r="AD68">
+        <v>0</v>
+      </c>
+      <c r="AE68">
+        <v>0</v>
+      </c>
+      <c r="AF68">
+        <v>0</v>
+      </c>
+      <c r="AG68">
+        <v>0</v>
+      </c>
+      <c r="AH68">
+        <v>0</v>
+      </c>
+      <c r="AI68">
+        <v>0</v>
+      </c>
+      <c r="AJ68" t="s">
+        <v>228</v>
+      </c>
+      <c r="AK68" t="s">
+        <v>228</v>
+      </c>
+      <c r="AL68" s="3">
         <v>45870.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-08-01.xlsx
+++ b/jogos_2025-08-01.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="231">
   <si>
     <t>Date</t>
   </si>
@@ -199,36 +199,36 @@
     <t>Ukraine Ukrainian Premier League</t>
   </si>
   <si>
+    <t>Austria 2. Liga</t>
+  </si>
+  <si>
     <t>Switzerland Challenge League</t>
   </si>
   <si>
     <t>Uzbekistan Uzbekistan Super League</t>
   </si>
   <si>
+    <t>Jordan Jordanian Pro League</t>
+  </si>
+  <si>
     <t>Belarus Vysheyshaya Liga</t>
   </si>
   <si>
     <t>Finland Veikkausliiga</t>
   </si>
   <si>
-    <t>Jordan Jordanian Pro League</t>
-  </si>
-  <si>
     <t>Slovenia PrvaLiga</t>
   </si>
   <si>
     <t>Romania Liga I</t>
   </si>
   <si>
-    <t>Austria 2. Liga</t>
+    <t>Poland 1. Liga</t>
   </si>
   <si>
     <t>Denmark Superliga</t>
   </si>
   <si>
-    <t>Poland 1. Liga</t>
-  </si>
-  <si>
     <t>Poland Ekstraklasa</t>
   </si>
   <si>
@@ -250,24 +250,24 @@
     <t>Hungary NB I</t>
   </si>
   <si>
+    <t>Austria Bundesliga</t>
+  </si>
+  <si>
     <t>Germany 2. Bundesliga</t>
   </si>
   <si>
-    <t>Austria Bundesliga</t>
+    <t>Republic of Ireland First Division</t>
   </si>
   <si>
     <t>Republic of Ireland Premier Division</t>
   </si>
   <si>
-    <t>Republic of Ireland First Division</t>
+    <t>Belgium Pro League</t>
   </si>
   <si>
     <t>Scotland Championship</t>
   </si>
   <si>
-    <t>Belgium Pro League</t>
-  </si>
-  <si>
     <t>England EFL League One</t>
   </si>
   <si>
@@ -298,6 +298,9 @@
     <t>Kolos Kovalivka</t>
   </si>
   <si>
+    <t>WSPG Wels</t>
+  </si>
+  <si>
     <t>Wil</t>
   </si>
   <si>
@@ -307,60 +310,60 @@
     <t>Dinamo Samarqand</t>
   </si>
   <si>
+    <t>Al Hussein</t>
+  </si>
+  <si>
+    <t>Rukh Vynnyky</t>
+  </si>
+  <si>
+    <t>Smorgon</t>
+  </si>
+  <si>
+    <t>VPS</t>
+  </si>
+  <si>
     <t>Buxoro</t>
   </si>
   <si>
     <t>Mash'al</t>
   </si>
   <si>
-    <t>Rukh Vynnyky</t>
-  </si>
-  <si>
-    <t>Smorgon</t>
-  </si>
-  <si>
-    <t>VPS</t>
-  </si>
-  <si>
-    <t>Al Hussein</t>
-  </si>
-  <si>
     <t>BATE</t>
   </si>
   <si>
     <t>Radomlje</t>
   </si>
   <si>
+    <t>Austria Salzburg</t>
+  </si>
+  <si>
+    <t>Liefering</t>
+  </si>
+  <si>
+    <t>Kapfenberger SV</t>
+  </si>
+  <si>
+    <t>Amstetten</t>
+  </si>
+  <si>
     <t>SSC Farul</t>
   </si>
   <si>
-    <t>Kapfenberger SV</t>
-  </si>
-  <si>
-    <t>Austria Salzburg</t>
+    <t>Wieczysta Kraków</t>
   </si>
   <si>
     <t>Fredericia</t>
   </si>
   <si>
-    <t>Liefering</t>
-  </si>
-  <si>
-    <t>Wieczysta Kraków</t>
+    <t>Zagłębie Lubin</t>
+  </si>
+  <si>
+    <t>Spartak Varna</t>
   </si>
   <si>
     <t>SV Stripfing Weiden</t>
   </si>
   <si>
-    <t>Amstetten</t>
-  </si>
-  <si>
-    <t>Zagłębie Lubin</t>
-  </si>
-  <si>
-    <t>Spartak Varna</t>
-  </si>
-  <si>
     <t>Tallinna FC Levadia</t>
   </si>
   <si>
@@ -376,99 +379,99 @@
     <t>Al Wihdat</t>
   </si>
   <si>
+    <t>Lokomotiva Zagreb</t>
+  </si>
+  <si>
     <t>Vejle</t>
   </si>
   <si>
-    <t>Lokomotiva Zagreb</t>
-  </si>
-  <si>
     <t>Debrecen</t>
   </si>
   <si>
     <t>CSKA 1948 Sofia</t>
   </si>
   <si>
+    <t>LASK Linz</t>
+  </si>
+  <si>
+    <t>Wisła Płock</t>
+  </si>
+  <si>
+    <t>ŁKS Łódź</t>
+  </si>
+  <si>
     <t>Petrolul 52</t>
   </si>
   <si>
-    <t>ŁKS Łódź</t>
-  </si>
-  <si>
-    <t>Wisła Płock</t>
-  </si>
-  <si>
     <t>Schalke 04</t>
   </si>
   <si>
-    <t>LASK Linz</t>
+    <t>Kerry</t>
+  </si>
+  <si>
+    <t>Bohemians</t>
+  </si>
+  <si>
+    <t>Wexford</t>
+  </si>
+  <si>
+    <t>UCD</t>
+  </si>
+  <si>
+    <t>Waterford</t>
+  </si>
+  <si>
+    <t>Bray Wanderers</t>
+  </si>
+  <si>
+    <t>KV Mechelen</t>
   </si>
   <si>
     <t>Cork City</t>
   </si>
   <si>
-    <t>Wexford</t>
-  </si>
-  <si>
-    <t>Kerry</t>
+    <t>Arbroath</t>
   </si>
   <si>
     <t>Cobh Ramblers</t>
   </si>
   <si>
-    <t>UCD</t>
-  </si>
-  <si>
-    <t>Bohemians</t>
-  </si>
-  <si>
-    <t>Arbroath</t>
-  </si>
-  <si>
-    <t>Waterford</t>
-  </si>
-  <si>
-    <t>KV Mechelen</t>
-  </si>
-  <si>
-    <t>Bray Wanderers</t>
+    <t>Luton Town</t>
   </si>
   <si>
     <t>Shamrock Rovers</t>
   </si>
   <si>
-    <t>Luton Town</t>
+    <t>Maringá</t>
+  </si>
+  <si>
+    <t>ABC</t>
+  </si>
+  <si>
+    <t>Remo</t>
+  </si>
+  <si>
+    <t>Ypiranga Erechim</t>
+  </si>
+  <si>
+    <t>Brusque</t>
+  </si>
+  <si>
+    <t>São Bernardo</t>
+  </si>
+  <si>
+    <t>Ituano</t>
+  </si>
+  <si>
+    <t>Náutico</t>
+  </si>
+  <si>
+    <t>Confiança</t>
   </si>
   <si>
     <t>Ponte Preta</t>
   </si>
   <si>
-    <t>Remo</t>
-  </si>
-  <si>
-    <t>ABC</t>
-  </si>
-  <si>
-    <t>Náutico</t>
-  </si>
-  <si>
-    <t>Brusque</t>
-  </si>
-  <si>
-    <t>Ituano</t>
-  </si>
-  <si>
-    <t>Confiança</t>
-  </si>
-  <si>
-    <t>São Bernardo</t>
-  </si>
-  <si>
-    <t>Maringá</t>
-  </si>
-  <si>
-    <t>Ypiranga Erechim</t>
-  </si>
-  <si>
     <t>CSA</t>
   </si>
   <si>
@@ -499,6 +502,9 @@
     <t>Hirnyk</t>
   </si>
   <si>
+    <t>Floridsdorfer AC</t>
+  </si>
+  <si>
     <t>Aarau</t>
   </si>
   <si>
@@ -508,60 +514,60 @@
     <t>Navbahor</t>
   </si>
   <si>
+    <t>Al Ahli</t>
+  </si>
+  <si>
+    <t>SK Poltava</t>
+  </si>
+  <si>
+    <t>Dinamo Minsk</t>
+  </si>
+  <si>
+    <t>Mariehamn</t>
+  </si>
+  <si>
     <t>AGMK</t>
   </si>
   <si>
     <t>Pakhtakor</t>
   </si>
   <si>
-    <t>SK Poltava</t>
-  </si>
-  <si>
-    <t>Dinamo Minsk</t>
-  </si>
-  <si>
-    <t>Mariehamn</t>
-  </si>
-  <si>
-    <t>Al Ahli</t>
-  </si>
-  <si>
     <t>Vitebsk</t>
   </si>
   <si>
     <t>Domžale</t>
   </si>
   <si>
+    <t>Austria Klagenfurt</t>
+  </si>
+  <si>
+    <t>Austria Lustenau</t>
+  </si>
+  <si>
+    <t>Admira</t>
+  </si>
+  <si>
+    <t>Sturm Graz II</t>
+  </si>
+  <si>
     <t>Metaloglobus</t>
   </si>
   <si>
-    <t>Admira</t>
-  </si>
-  <si>
-    <t>Austria Klagenfurt</t>
+    <t>Znicz Pruszków</t>
   </si>
   <si>
     <t>København</t>
   </si>
   <si>
-    <t>Austria Lustenau</t>
-  </si>
-  <si>
-    <t>Znicz Pruszków</t>
+    <t>Korona Kielce</t>
+  </si>
+  <si>
+    <t>Botev Vratsa</t>
   </si>
   <si>
     <t>First Vienna</t>
   </si>
   <si>
-    <t>Sturm Graz II</t>
-  </si>
-  <si>
-    <t>Korona Kielce</t>
-  </si>
-  <si>
-    <t>Botev Vratsa</t>
-  </si>
-  <si>
     <t>Kuressaare</t>
   </si>
   <si>
@@ -577,97 +583,97 @@
     <t>Al Ramtha</t>
   </si>
   <si>
+    <t>HNK Vukovar 1991</t>
+  </si>
+  <si>
     <t>OB</t>
   </si>
   <si>
-    <t>HNK Vukovar 1991</t>
-  </si>
-  <si>
     <t>MTK</t>
   </si>
   <si>
     <t>Septemvri Sofia</t>
   </si>
   <si>
+    <t>Sturm Graz</t>
+  </si>
+  <si>
+    <t>Piast Gliwice</t>
+  </si>
+  <si>
+    <t>Polonia Bytom</t>
+  </si>
+  <si>
     <t>UTA Arad</t>
   </si>
   <si>
-    <t>Polonia Bytom</t>
-  </si>
-  <si>
-    <t>Piast Gliwice</t>
-  </si>
-  <si>
     <t>Hertha BSC</t>
   </si>
   <si>
-    <t>Sturm Graz</t>
+    <t>Athlone Town</t>
+  </si>
+  <si>
+    <t>Drogheda United</t>
+  </si>
+  <si>
+    <t>Finn Harps</t>
+  </si>
+  <si>
+    <t>Dundalk</t>
+  </si>
+  <si>
+    <t>St Patrick's Athl.</t>
+  </si>
+  <si>
+    <t>Treaty United</t>
+  </si>
+  <si>
+    <t>Club Brugge</t>
   </si>
   <si>
     <t>Galway United</t>
   </si>
   <si>
-    <t>Finn Harps</t>
-  </si>
-  <si>
-    <t>Athlone Town</t>
+    <t>Ayr United</t>
   </si>
   <si>
     <t>Longford Town</t>
   </si>
   <si>
-    <t>Dundalk</t>
-  </si>
-  <si>
-    <t>Drogheda United</t>
-  </si>
-  <si>
-    <t>Ayr United</t>
-  </si>
-  <si>
-    <t>St Patrick's Athl.</t>
-  </si>
-  <si>
-    <t>Club Brugge</t>
-  </si>
-  <si>
-    <t>Treaty United</t>
+    <t>AFC Wimbledon</t>
   </si>
   <si>
     <t>Derry City</t>
   </si>
   <si>
-    <t>AFC Wimbledon</t>
+    <t>Floresta</t>
+  </si>
+  <si>
+    <t>Figueirense</t>
+  </si>
+  <si>
+    <t>Ferroviária</t>
+  </si>
+  <si>
+    <t>Caxias</t>
+  </si>
+  <si>
+    <t>Itabaiana</t>
+  </si>
+  <si>
+    <t>Tombense</t>
+  </si>
+  <si>
+    <t>Londrina</t>
+  </si>
+  <si>
+    <t>Retrô</t>
+  </si>
+  <si>
+    <t>Anápolis</t>
   </si>
   <si>
     <t>Guarani</t>
-  </si>
-  <si>
-    <t>Ferroviária</t>
-  </si>
-  <si>
-    <t>Figueirense</t>
-  </si>
-  <si>
-    <t>Retrô</t>
-  </si>
-  <si>
-    <t>Itabaiana</t>
-  </si>
-  <si>
-    <t>Londrina</t>
-  </si>
-  <si>
-    <t>Anápolis</t>
-  </si>
-  <si>
-    <t>Tombense</t>
-  </si>
-  <si>
-    <t>Floresta</t>
-  </si>
-  <si>
-    <t>Caxias</t>
   </si>
   <si>
     <t>Botafogo PB</t>
@@ -1064,7 +1070,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AL68"/>
+  <dimension ref="A1:AL69"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:38">
@@ -1200,7 +1206,7 @@
         <v>93</v>
       </c>
       <c r="F2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1215,7 +1221,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L2">
         <v>2.59</v>
@@ -1290,10 +1296,10 @@
         <v>0</v>
       </c>
       <c r="AJ2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL2" s="3">
         <v>45870.39583333334</v>
@@ -1316,7 +1322,7 @@
         <v>94</v>
       </c>
       <c r="F3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1331,16 +1337,16 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L3">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="M3">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N3">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O3">
         <v>0</v>
@@ -1406,10 +1412,10 @@
         <v>0</v>
       </c>
       <c r="AJ3" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK3" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL3" s="3">
         <v>45870.45833333334</v>
@@ -1426,13 +1432,13 @@
         <v>62</v>
       </c>
       <c r="D4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E4" t="s">
         <v>95</v>
       </c>
       <c r="F4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1447,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O4">
         <v>0</v>
@@ -1498,10 +1504,10 @@
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -1522,10 +1528,10 @@
         <v>0</v>
       </c>
       <c r="AJ4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL4" s="3">
         <v>45870.45833333334</v>
@@ -1539,7 +1545,7 @@
         <v>39</v>
       </c>
       <c r="C5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D5" t="s">
         <v>92</v>
@@ -1548,7 +1554,7 @@
         <v>96</v>
       </c>
       <c r="F5" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1563,7 +1569,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -1638,10 +1644,10 @@
         <v>0</v>
       </c>
       <c r="AJ5" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK5" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL5" s="3">
         <v>45870.45833333334</v>
@@ -1652,10 +1658,10 @@
         <v>45870</v>
       </c>
       <c r="B6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D6" t="s">
         <v>92</v>
@@ -1664,7 +1670,7 @@
         <v>97</v>
       </c>
       <c r="F6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1679,7 +1685,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -1754,13 +1760,13 @@
         <v>0</v>
       </c>
       <c r="AJ6" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK6" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL6" s="3">
-        <v>45870.5</v>
+        <v>45870.45833333334</v>
       </c>
     </row>
     <row r="7" spans="1:38">
@@ -1771,16 +1777,16 @@
         <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E7" t="s">
         <v>98</v>
       </c>
       <c r="F7" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1795,7 +1801,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -1870,10 +1876,10 @@
         <v>0</v>
       </c>
       <c r="AJ7" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK7" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL7" s="3">
         <v>45870.5</v>
@@ -1896,7 +1902,7 @@
         <v>99</v>
       </c>
       <c r="F8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1911,7 +1917,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L8">
         <v>1.65</v>
@@ -1986,10 +1992,10 @@
         <v>0</v>
       </c>
       <c r="AJ8" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK8" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL8" s="3">
         <v>45870.5</v>
@@ -2003,7 +2009,7 @@
         <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D9" t="s">
         <v>92</v>
@@ -2012,7 +2018,7 @@
         <v>100</v>
       </c>
       <c r="F9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2027,7 +2033,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -2102,10 +2108,10 @@
         <v>0</v>
       </c>
       <c r="AJ9" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK9" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL9" s="3">
         <v>45870.5</v>
@@ -2119,7 +2125,7 @@
         <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D10" t="s">
         <v>92</v>
@@ -2128,7 +2134,7 @@
         <v>101</v>
       </c>
       <c r="F10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2143,7 +2149,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L10">
         <v>1.56</v>
@@ -2194,10 +2200,10 @@
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AC10">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AD10">
         <v>0</v>
@@ -2218,10 +2224,10 @@
         <v>0</v>
       </c>
       <c r="AJ10" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK10" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL10" s="3">
         <v>45870.5</v>
@@ -2235,16 +2241,16 @@
         <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E11" t="s">
         <v>102</v>
       </c>
       <c r="F11" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2259,7 +2265,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -2334,10 +2340,10 @@
         <v>0</v>
       </c>
       <c r="AJ11" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK11" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL11" s="3">
         <v>45870.5</v>
@@ -2348,7 +2354,7 @@
         <v>45870</v>
       </c>
       <c r="B12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C12" t="s">
         <v>63</v>
@@ -2360,7 +2366,7 @@
         <v>103</v>
       </c>
       <c r="F12" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2375,16 +2381,16 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L12">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M12">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N12">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="O12">
         <v>0</v>
@@ -2426,10 +2432,10 @@
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC12">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD12">
         <v>0</v>
@@ -2450,13 +2456,13 @@
         <v>0</v>
       </c>
       <c r="AJ12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL12" s="3">
-        <v>45870.51041666666</v>
+        <v>45870.5</v>
       </c>
     </row>
     <row r="13" spans="1:38">
@@ -2464,19 +2470,19 @@
         <v>45870</v>
       </c>
       <c r="B13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E13" t="s">
         <v>104</v>
       </c>
       <c r="F13" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2491,16 +2497,16 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L13">
-        <v>2.46</v>
+        <v>2.17</v>
       </c>
       <c r="M13">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="N13">
-        <v>2.6</v>
+        <v>3.46</v>
       </c>
       <c r="O13">
         <v>0</v>
@@ -2542,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>1.78</v>
+        <v>2.02</v>
       </c>
       <c r="AC13">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="AD13">
         <v>0</v>
@@ -2566,13 +2572,13 @@
         <v>0</v>
       </c>
       <c r="AJ13" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK13" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL13" s="3">
-        <v>45870.52083333334</v>
+        <v>45870.51041666666</v>
       </c>
     </row>
     <row r="14" spans="1:38">
@@ -2580,7 +2586,7 @@
         <v>45870</v>
       </c>
       <c r="B14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C14" t="s">
         <v>67</v>
@@ -2592,7 +2598,7 @@
         <v>105</v>
       </c>
       <c r="F14" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2607,16 +2613,16 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L14">
-        <v>1.45</v>
+        <v>2.46</v>
       </c>
       <c r="M14">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="N14">
-        <v>6.3</v>
+        <v>2.6</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -2658,10 +2664,10 @@
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>1.95</v>
+        <v>1.63</v>
       </c>
       <c r="AC14">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AD14">
         <v>0</v>
@@ -2682,13 +2688,13 @@
         <v>0</v>
       </c>
       <c r="AJ14" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK14" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL14" s="3">
-        <v>45870.54166666666</v>
+        <v>45870.52083333334</v>
       </c>
     </row>
     <row r="15" spans="1:38">
@@ -2699,7 +2705,7 @@
         <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D15" t="s">
         <v>91</v>
@@ -2708,7 +2714,7 @@
         <v>106</v>
       </c>
       <c r="F15" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2723,16 +2729,16 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L15">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="M15">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N15">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O15">
         <v>0</v>
@@ -2798,10 +2804,10 @@
         <v>0</v>
       </c>
       <c r="AJ15" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK15" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL15" s="3">
         <v>45870.54166666666</v>
@@ -2815,7 +2821,7 @@
         <v>43</v>
       </c>
       <c r="C16" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D16" t="s">
         <v>91</v>
@@ -2824,7 +2830,7 @@
         <v>107</v>
       </c>
       <c r="F16" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2839,16 +2845,16 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O16">
         <v>0</v>
@@ -2890,10 +2896,10 @@
         <v>0</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD16">
         <v>0</v>
@@ -2914,10 +2920,10 @@
         <v>0</v>
       </c>
       <c r="AJ16" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK16" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL16" s="3">
         <v>45870.54166666666</v>
@@ -2931,7 +2937,7 @@
         <v>43</v>
       </c>
       <c r="C17" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D17" t="s">
         <v>91</v>
@@ -2940,7 +2946,7 @@
         <v>108</v>
       </c>
       <c r="F17" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2955,16 +2961,16 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L17">
-        <v>9.199999999999999</v>
+        <v>3.62</v>
       </c>
       <c r="M17">
-        <v>5.6</v>
+        <v>3.7</v>
       </c>
       <c r="N17">
-        <v>1.27</v>
+        <v>1.75</v>
       </c>
       <c r="O17">
         <v>0</v>
@@ -3006,10 +3012,10 @@
         <v>0</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AD17">
         <v>0</v>
@@ -3030,10 +3036,10 @@
         <v>0</v>
       </c>
       <c r="AJ17" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK17" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL17" s="3">
         <v>45870.54166666666</v>
@@ -3047,7 +3053,7 @@
         <v>43</v>
       </c>
       <c r="C18" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D18" t="s">
         <v>91</v>
@@ -3056,7 +3062,7 @@
         <v>109</v>
       </c>
       <c r="F18" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -3071,16 +3077,16 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L18">
-        <v>2.54</v>
+        <v>1.73</v>
       </c>
       <c r="M18">
-        <v>3.21</v>
+        <v>3.82</v>
       </c>
       <c r="N18">
-        <v>2.41</v>
+        <v>3.57</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -3122,16 +3128,16 @@
         <v>0</v>
       </c>
       <c r="AB18">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC18">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF18">
         <v>0</v>
@@ -3146,10 +3152,10 @@
         <v>0</v>
       </c>
       <c r="AJ18" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK18" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL18" s="3">
         <v>45870.54166666666</v>
@@ -3163,7 +3169,7 @@
         <v>43</v>
       </c>
       <c r="C19" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D19" t="s">
         <v>91</v>
@@ -3172,7 +3178,7 @@
         <v>110</v>
       </c>
       <c r="F19" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -3187,16 +3193,16 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L19">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="M19">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="N19">
-        <v>5.6</v>
+        <v>6.3</v>
       </c>
       <c r="O19">
         <v>0</v>
@@ -3238,10 +3244,10 @@
         <v>0</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD19">
         <v>0</v>
@@ -3262,10 +3268,10 @@
         <v>0</v>
       </c>
       <c r="AJ19" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK19" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL19" s="3">
         <v>45870.54166666666</v>
@@ -3279,7 +3285,7 @@
         <v>43</v>
       </c>
       <c r="C20" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D20" t="s">
         <v>91</v>
@@ -3288,7 +3294,7 @@
         <v>111</v>
       </c>
       <c r="F20" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -3303,16 +3309,16 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L20">
-        <v>2.3</v>
+        <v>1.42</v>
       </c>
       <c r="M20">
-        <v>3.21</v>
+        <v>4.2</v>
       </c>
       <c r="N20">
-        <v>2.68</v>
+        <v>5.6</v>
       </c>
       <c r="O20">
         <v>0</v>
@@ -3378,10 +3384,10 @@
         <v>0</v>
       </c>
       <c r="AJ20" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK20" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL20" s="3">
         <v>45870.54166666666</v>
@@ -3395,7 +3401,7 @@
         <v>43</v>
       </c>
       <c r="C21" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D21" t="s">
         <v>91</v>
@@ -3404,7 +3410,7 @@
         <v>112</v>
       </c>
       <c r="F21" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -3419,16 +3425,16 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L21">
-        <v>1.73</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M21">
-        <v>3.82</v>
+        <v>5.6</v>
       </c>
       <c r="N21">
-        <v>3.57</v>
+        <v>1.27</v>
       </c>
       <c r="O21">
         <v>0</v>
@@ -3494,10 +3500,10 @@
         <v>0</v>
       </c>
       <c r="AJ21" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK21" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL21" s="3">
         <v>45870.54166666666</v>
@@ -3520,7 +3526,7 @@
         <v>113</v>
       </c>
       <c r="F22" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3535,7 +3541,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L22">
         <v>2.13</v>
@@ -3610,10 +3616,10 @@
         <v>0</v>
       </c>
       <c r="AJ22" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK22" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL22" s="3">
         <v>45870.54166666666</v>
@@ -3636,7 +3642,7 @@
         <v>114</v>
       </c>
       <c r="F23" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3651,7 +3657,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L23">
         <v>2.47</v>
@@ -3702,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AD23">
         <v>0</v>
@@ -3726,10 +3732,10 @@
         <v>0</v>
       </c>
       <c r="AJ23" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK23" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL23" s="3">
         <v>45870.54166666666</v>
@@ -3740,19 +3746,19 @@
         <v>45870</v>
       </c>
       <c r="B24" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C24" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="D24" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E24" t="s">
         <v>115</v>
       </c>
       <c r="F24" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -3767,16 +3773,16 @@
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L24">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="M24">
-        <v>5.4</v>
+        <v>3.21</v>
       </c>
       <c r="N24">
-        <v>9.800000000000001</v>
+        <v>2.68</v>
       </c>
       <c r="O24">
         <v>0</v>
@@ -3818,16 +3824,16 @@
         <v>0</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AD24">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE24">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF24">
         <v>0</v>
@@ -3842,13 +3848,13 @@
         <v>0</v>
       </c>
       <c r="AJ24" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK24" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL24" s="3">
-        <v>45870.5625</v>
+        <v>45870.54166666666</v>
       </c>
     </row>
     <row r="25" spans="1:38">
@@ -3856,19 +3862,19 @@
         <v>45870</v>
       </c>
       <c r="B25" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C25" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E25" t="s">
         <v>116</v>
       </c>
       <c r="F25" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -3883,16 +3889,16 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O25">
         <v>0</v>
@@ -3940,10 +3946,10 @@
         <v>0</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF25">
         <v>0</v>
@@ -3958,13 +3964,13 @@
         <v>0</v>
       </c>
       <c r="AJ25" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK25" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL25" s="3">
-        <v>45870.58333333334</v>
+        <v>45870.5625</v>
       </c>
     </row>
     <row r="26" spans="1:38">
@@ -3975,16 +3981,16 @@
         <v>45</v>
       </c>
       <c r="C26" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D26" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E26" t="s">
         <v>117</v>
       </c>
       <c r="F26" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -3999,16 +4005,16 @@
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L26">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M26">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N26">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O26">
         <v>0</v>
@@ -4050,10 +4056,10 @@
         <v>0</v>
       </c>
       <c r="AB26">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC26">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD26">
         <v>0</v>
@@ -4074,10 +4080,10 @@
         <v>0</v>
       </c>
       <c r="AJ26" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK26" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL26" s="3">
         <v>45870.58333333334</v>
@@ -4088,19 +4094,19 @@
         <v>45870</v>
       </c>
       <c r="B27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C27" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="D27" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E27" t="s">
         <v>118</v>
       </c>
       <c r="F27" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -4115,16 +4121,16 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O27">
         <v>0</v>
@@ -4166,10 +4172,10 @@
         <v>0</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD27">
         <v>0</v>
@@ -4190,13 +4196,13 @@
         <v>0</v>
       </c>
       <c r="AJ27" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK27" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL27" s="3">
-        <v>45870.60416666666</v>
+        <v>45870.58333333334</v>
       </c>
     </row>
     <row r="28" spans="1:38">
@@ -4204,10 +4210,10 @@
         <v>45870</v>
       </c>
       <c r="B28" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C28" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D28" t="s">
         <v>91</v>
@@ -4216,7 +4222,7 @@
         <v>119</v>
       </c>
       <c r="F28" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -4231,7 +4237,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -4306,13 +4312,13 @@
         <v>0</v>
       </c>
       <c r="AJ28" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK28" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL28" s="3">
-        <v>45870.61458333334</v>
+        <v>45870.60416666666</v>
       </c>
     </row>
     <row r="29" spans="1:38">
@@ -4320,10 +4326,10 @@
         <v>45870</v>
       </c>
       <c r="B29" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C29" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D29" t="s">
         <v>91</v>
@@ -4332,7 +4338,7 @@
         <v>120</v>
       </c>
       <c r="F29" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -4347,16 +4353,16 @@
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L29">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M29">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N29">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="O29">
         <v>0</v>
@@ -4422,13 +4428,13 @@
         <v>0</v>
       </c>
       <c r="AJ29" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK29" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL29" s="3">
-        <v>45870.625</v>
+        <v>45870.61458333334</v>
       </c>
     </row>
     <row r="30" spans="1:38">
@@ -4448,7 +4454,7 @@
         <v>121</v>
       </c>
       <c r="F30" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -4463,7 +4469,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -4538,10 +4544,10 @@
         <v>0</v>
       </c>
       <c r="AJ30" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK30" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL30" s="3">
         <v>45870.625</v>
@@ -4555,7 +4561,7 @@
         <v>48</v>
       </c>
       <c r="C31" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D31" t="s">
         <v>91</v>
@@ -4564,7 +4570,7 @@
         <v>122</v>
       </c>
       <c r="F31" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -4579,16 +4585,16 @@
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L31">
-        <v>1.89</v>
+        <v>2.7</v>
       </c>
       <c r="M31">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="N31">
-        <v>3.5</v>
+        <v>2.41</v>
       </c>
       <c r="O31">
         <v>0</v>
@@ -4654,10 +4660,10 @@
         <v>0</v>
       </c>
       <c r="AJ31" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK31" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL31" s="3">
         <v>45870.625</v>
@@ -4668,10 +4674,10 @@
         <v>45870</v>
       </c>
       <c r="B32" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C32" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D32" t="s">
         <v>91</v>
@@ -4680,7 +4686,7 @@
         <v>123</v>
       </c>
       <c r="F32" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -4695,16 +4701,16 @@
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L32">
-        <v>1.52</v>
+        <v>1.81</v>
       </c>
       <c r="M32">
-        <v>3.8</v>
+        <v>3.71</v>
       </c>
       <c r="N32">
-        <v>5.5</v>
+        <v>3.35</v>
       </c>
       <c r="O32">
         <v>0</v>
@@ -4746,16 +4752,16 @@
         <v>0</v>
       </c>
       <c r="AB32">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC32">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF32">
         <v>0</v>
@@ -4770,13 +4776,13 @@
         <v>0</v>
       </c>
       <c r="AJ32" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK32" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL32" s="3">
-        <v>45870.63541666666</v>
+        <v>45870.625</v>
       </c>
     </row>
     <row r="33" spans="1:38">
@@ -4784,10 +4790,10 @@
         <v>45870</v>
       </c>
       <c r="B33" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C33" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D33" t="s">
         <v>91</v>
@@ -4796,7 +4802,7 @@
         <v>124</v>
       </c>
       <c r="F33" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -4811,16 +4817,16 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L33">
-        <v>2.24</v>
+        <v>1.52</v>
       </c>
       <c r="M33">
-        <v>2.96</v>
+        <v>3.8</v>
       </c>
       <c r="N33">
-        <v>2.98</v>
+        <v>5.5</v>
       </c>
       <c r="O33">
         <v>0</v>
@@ -4862,10 +4868,10 @@
         <v>0</v>
       </c>
       <c r="AB33">
-        <v>2.39</v>
+        <v>1.74</v>
       </c>
       <c r="AC33">
-        <v>1.58</v>
+        <v>2.05</v>
       </c>
       <c r="AD33">
         <v>0</v>
@@ -4886,13 +4892,13 @@
         <v>0</v>
       </c>
       <c r="AJ33" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK33" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL33" s="3">
-        <v>45870.64583333334</v>
+        <v>45870.63541666666</v>
       </c>
     </row>
     <row r="34" spans="1:38">
@@ -4903,7 +4909,7 @@
         <v>50</v>
       </c>
       <c r="C34" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D34" t="s">
         <v>91</v>
@@ -4912,7 +4918,7 @@
         <v>125</v>
       </c>
       <c r="F34" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -4927,16 +4933,16 @@
         <v>0</v>
       </c>
       <c r="K34" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L34">
-        <v>2.02</v>
+        <v>2.88</v>
       </c>
       <c r="M34">
-        <v>3.13</v>
+        <v>2.96</v>
       </c>
       <c r="N34">
-        <v>3.27</v>
+        <v>2.31</v>
       </c>
       <c r="O34">
         <v>0</v>
@@ -4978,11 +4984,11 @@
         <v>0</v>
       </c>
       <c r="AB34">
+        <v>1.7</v>
+      </c>
+      <c r="AC34">
         <v>1.95</v>
       </c>
-      <c r="AC34">
-        <v>1.75</v>
-      </c>
       <c r="AD34">
         <v>0</v>
       </c>
@@ -5002,10 +5008,10 @@
         <v>0</v>
       </c>
       <c r="AJ34" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK34" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL34" s="3">
         <v>45870.64583333334</v>
@@ -5028,7 +5034,7 @@
         <v>126</v>
       </c>
       <c r="F35" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -5043,7 +5049,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L35">
         <v>2.27</v>
@@ -5118,10 +5124,10 @@
         <v>0</v>
       </c>
       <c r="AJ35" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK35" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL35" s="3">
         <v>45870.64583333334</v>
@@ -5135,7 +5141,7 @@
         <v>50</v>
       </c>
       <c r="C36" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D36" t="s">
         <v>91</v>
@@ -5144,7 +5150,7 @@
         <v>127</v>
       </c>
       <c r="F36" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -5159,16 +5165,16 @@
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L36">
-        <v>2.99</v>
+        <v>2.02</v>
       </c>
       <c r="M36">
-        <v>3.21</v>
+        <v>3.13</v>
       </c>
       <c r="N36">
-        <v>2.36</v>
+        <v>3.27</v>
       </c>
       <c r="O36">
         <v>0</v>
@@ -5210,16 +5216,16 @@
         <v>0</v>
       </c>
       <c r="AB36">
-        <v>1.53</v>
+        <v>1.95</v>
       </c>
       <c r="AC36">
-        <v>2.35</v>
+        <v>1.75</v>
       </c>
       <c r="AD36">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE36">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF36">
         <v>0</v>
@@ -5234,10 +5240,10 @@
         <v>0</v>
       </c>
       <c r="AJ36" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK36" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL36" s="3">
         <v>45870.64583333334</v>
@@ -5251,7 +5257,7 @@
         <v>50</v>
       </c>
       <c r="C37" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="D37" t="s">
         <v>91</v>
@@ -5260,7 +5266,7 @@
         <v>128</v>
       </c>
       <c r="F37" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -5275,16 +5281,16 @@
         <v>0</v>
       </c>
       <c r="K37" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L37">
-        <v>2.88</v>
+        <v>2.24</v>
       </c>
       <c r="M37">
         <v>2.96</v>
       </c>
       <c r="N37">
-        <v>2.31</v>
+        <v>2.98</v>
       </c>
       <c r="O37">
         <v>0</v>
@@ -5326,10 +5332,10 @@
         <v>0</v>
       </c>
       <c r="AB37">
-        <v>1.7</v>
+        <v>2.39</v>
       </c>
       <c r="AC37">
-        <v>1.95</v>
+        <v>1.58</v>
       </c>
       <c r="AD37">
         <v>0</v>
@@ -5350,10 +5356,10 @@
         <v>0</v>
       </c>
       <c r="AJ37" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK37" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL37" s="3">
         <v>45870.64583333334</v>
@@ -5364,19 +5370,19 @@
         <v>45870</v>
       </c>
       <c r="B38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C38" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D38" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E38" t="s">
         <v>129</v>
       </c>
       <c r="F38" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -5391,16 +5397,16 @@
         <v>0</v>
       </c>
       <c r="K38" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L38">
-        <v>2.85</v>
+        <v>2.99</v>
       </c>
       <c r="M38">
-        <v>3.15</v>
+        <v>3.21</v>
       </c>
       <c r="N38">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="O38">
         <v>0</v>
@@ -5442,16 +5448,16 @@
         <v>0</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF38">
         <v>0</v>
@@ -5466,13 +5472,13 @@
         <v>0</v>
       </c>
       <c r="AJ38" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK38" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL38" s="3">
-        <v>45870.65625</v>
+        <v>45870.64583333334</v>
       </c>
     </row>
     <row r="39" spans="1:38">
@@ -5483,7 +5489,7 @@
         <v>51</v>
       </c>
       <c r="C39" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D39" t="s">
         <v>92</v>
@@ -5492,7 +5498,7 @@
         <v>130</v>
       </c>
       <c r="F39" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -5507,16 +5513,16 @@
         <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L39">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="M39">
-        <v>3.55</v>
+        <v>3.31</v>
       </c>
       <c r="N39">
-        <v>3.15</v>
+        <v>2.7</v>
       </c>
       <c r="O39">
         <v>0</v>
@@ -5558,10 +5564,10 @@
         <v>0</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AD39">
         <v>0</v>
@@ -5582,10 +5588,10 @@
         <v>0</v>
       </c>
       <c r="AJ39" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK39" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL39" s="3">
         <v>45870.65625</v>
@@ -5608,7 +5614,7 @@
         <v>131</v>
       </c>
       <c r="F40" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -5623,16 +5629,16 @@
         <v>0</v>
       </c>
       <c r="K40" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L40">
-        <v>2.06</v>
+        <v>1.48</v>
       </c>
       <c r="M40">
-        <v>3.35</v>
+        <v>3.86</v>
       </c>
       <c r="N40">
-        <v>3.15</v>
+        <v>5.4</v>
       </c>
       <c r="O40">
         <v>0</v>
@@ -5674,10 +5680,10 @@
         <v>0</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD40">
         <v>0</v>
@@ -5698,10 +5704,10 @@
         <v>0</v>
       </c>
       <c r="AJ40" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK40" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL40" s="3">
         <v>45870.65625</v>
@@ -5715,7 +5721,7 @@
         <v>51</v>
       </c>
       <c r="C41" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D41" t="s">
         <v>92</v>
@@ -5724,7 +5730,7 @@
         <v>132</v>
       </c>
       <c r="F41" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -5739,16 +5745,16 @@
         <v>0</v>
       </c>
       <c r="K41" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L41">
-        <v>1.35</v>
+        <v>1.94</v>
       </c>
       <c r="M41">
-        <v>4.8</v>
+        <v>3.45</v>
       </c>
       <c r="N41">
-        <v>6.8</v>
+        <v>3.16</v>
       </c>
       <c r="O41">
         <v>0</v>
@@ -5790,10 +5796,10 @@
         <v>0</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD41">
         <v>0</v>
@@ -5814,10 +5820,10 @@
         <v>0</v>
       </c>
       <c r="AJ41" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK41" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL41" s="3">
         <v>45870.65625</v>
@@ -5831,7 +5837,7 @@
         <v>51</v>
       </c>
       <c r="C42" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D42" t="s">
         <v>92</v>
@@ -5840,7 +5846,7 @@
         <v>133</v>
       </c>
       <c r="F42" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -5855,13 +5861,13 @@
         <v>0</v>
       </c>
       <c r="K42" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L42">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="M42">
-        <v>3.5</v>
+        <v>3.41</v>
       </c>
       <c r="N42">
         <v>1.72</v>
@@ -5906,10 +5912,10 @@
         <v>0</v>
       </c>
       <c r="AB42">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="AC42">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="AD42">
         <v>0</v>
@@ -5930,10 +5936,10 @@
         <v>0</v>
       </c>
       <c r="AJ42" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK42" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL42" s="3">
         <v>45870.65625</v>
@@ -5947,7 +5953,7 @@
         <v>51</v>
       </c>
       <c r="C43" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D43" t="s">
         <v>92</v>
@@ -5956,7 +5962,7 @@
         <v>134</v>
       </c>
       <c r="F43" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -5971,16 +5977,16 @@
         <v>0</v>
       </c>
       <c r="K43" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L43">
-        <v>1.51</v>
+        <v>3.45</v>
       </c>
       <c r="M43">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="N43">
-        <v>5.8</v>
+        <v>1.94</v>
       </c>
       <c r="O43">
         <v>0</v>
@@ -6022,11 +6028,11 @@
         <v>0</v>
       </c>
       <c r="AB43">
+        <v>1.83</v>
+      </c>
+      <c r="AC43">
         <v>1.91</v>
       </c>
-      <c r="AC43">
-        <v>1.77</v>
-      </c>
       <c r="AD43">
         <v>0</v>
       </c>
@@ -6046,10 +6052,10 @@
         <v>0</v>
       </c>
       <c r="AJ43" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK43" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL43" s="3">
         <v>45870.65625</v>
@@ -6063,16 +6069,16 @@
         <v>51</v>
       </c>
       <c r="C44" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D44" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E44" t="s">
         <v>135</v>
       </c>
       <c r="F44" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -6087,16 +6093,16 @@
         <v>0</v>
       </c>
       <c r="K44" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L44">
-        <v>3.55</v>
+        <v>2.12</v>
       </c>
       <c r="M44">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="N44">
-        <v>1.89</v>
+        <v>2.8</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -6138,10 +6144,10 @@
         <v>0</v>
       </c>
       <c r="AB44">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC44">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD44">
         <v>0</v>
@@ -6162,10 +6168,10 @@
         <v>0</v>
       </c>
       <c r="AJ44" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK44" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL44" s="3">
         <v>45870.65625</v>
@@ -6179,16 +6185,16 @@
         <v>51</v>
       </c>
       <c r="C45" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D45" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E45" t="s">
         <v>136</v>
       </c>
       <c r="F45" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -6203,16 +6209,16 @@
         <v>0</v>
       </c>
       <c r="K45" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L45">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M45">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O45">
         <v>0</v>
@@ -6254,16 +6260,16 @@
         <v>0</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC45">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD45">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AE45">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AF45">
         <v>0</v>
@@ -6278,10 +6284,10 @@
         <v>0</v>
       </c>
       <c r="AJ45" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK45" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL45" s="3">
         <v>45870.65625</v>
@@ -6295,16 +6301,16 @@
         <v>51</v>
       </c>
       <c r="C46" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D46" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E46" t="s">
         <v>137</v>
       </c>
       <c r="F46" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -6319,16 +6325,16 @@
         <v>0</v>
       </c>
       <c r="K46" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L46">
-        <v>4</v>
+        <v>2.69</v>
       </c>
       <c r="M46">
-        <v>3.72</v>
+        <v>3.18</v>
       </c>
       <c r="N46">
-        <v>1.66</v>
+        <v>2.31</v>
       </c>
       <c r="O46">
         <v>0</v>
@@ -6370,16 +6376,16 @@
         <v>0</v>
       </c>
       <c r="AB46">
-        <v>1.57</v>
+        <v>1.93</v>
       </c>
       <c r="AC46">
-        <v>2.3</v>
+        <v>1.77</v>
       </c>
       <c r="AD46">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AE46">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AF46">
         <v>0</v>
@@ -6394,10 +6400,10 @@
         <v>0</v>
       </c>
       <c r="AJ46" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK46" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL46" s="3">
         <v>45870.65625</v>
@@ -6411,16 +6417,16 @@
         <v>51</v>
       </c>
       <c r="C47" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D47" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E47" t="s">
         <v>138</v>
       </c>
       <c r="F47" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -6435,16 +6441,16 @@
         <v>0</v>
       </c>
       <c r="K47" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L47">
-        <v>2.04</v>
+        <v>3.55</v>
       </c>
       <c r="M47">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="N47">
-        <v>3.15</v>
+        <v>1.89</v>
       </c>
       <c r="O47">
         <v>0</v>
@@ -6486,10 +6492,10 @@
         <v>0</v>
       </c>
       <c r="AB47">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC47">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD47">
         <v>0</v>
@@ -6510,10 +6516,10 @@
         <v>0</v>
       </c>
       <c r="AJ47" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK47" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL47" s="3">
         <v>45870.65625</v>
@@ -6524,7 +6530,7 @@
         <v>45870</v>
       </c>
       <c r="B48" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C48" t="s">
         <v>80</v>
@@ -6536,7 +6542,7 @@
         <v>139</v>
       </c>
       <c r="F48" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -6551,16 +6557,16 @@
         <v>0</v>
       </c>
       <c r="K48" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L48">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M48">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O48">
         <v>0</v>
@@ -6626,13 +6632,13 @@
         <v>0</v>
       </c>
       <c r="AJ48" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK48" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL48" s="3">
-        <v>45870.66666666666</v>
+        <v>45870.65625</v>
       </c>
     </row>
     <row r="49" spans="1:38">
@@ -6652,7 +6658,7 @@
         <v>140</v>
       </c>
       <c r="F49" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -6667,7 +6673,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L49">
         <v>1.54</v>
@@ -6742,10 +6748,10 @@
         <v>0</v>
       </c>
       <c r="AJ49" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK49" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL49" s="3">
         <v>45870.66666666666</v>
@@ -6756,10 +6762,10 @@
         <v>45870</v>
       </c>
       <c r="B50" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C50" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D50" t="s">
         <v>92</v>
@@ -6768,7 +6774,7 @@
         <v>141</v>
       </c>
       <c r="F50" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -6783,16 +6789,16 @@
         <v>0</v>
       </c>
       <c r="K50" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L50">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M50">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O50">
         <v>0</v>
@@ -6858,13 +6864,13 @@
         <v>0</v>
       </c>
       <c r="AJ50" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK50" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL50" s="3">
-        <v>45870.79166666666</v>
+        <v>45870.66666666666</v>
       </c>
     </row>
     <row r="51" spans="1:38">
@@ -6875,7 +6881,7 @@
         <v>53</v>
       </c>
       <c r="C51" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D51" t="s">
         <v>92</v>
@@ -6884,7 +6890,7 @@
         <v>142</v>
       </c>
       <c r="F51" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -6899,16 +6905,16 @@
         <v>0</v>
       </c>
       <c r="K51" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L51">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M51">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N51">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O51">
         <v>0</v>
@@ -6950,10 +6956,10 @@
         <v>0</v>
       </c>
       <c r="AB51">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC51">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD51">
         <v>0</v>
@@ -6974,10 +6980,10 @@
         <v>0</v>
       </c>
       <c r="AJ51" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK51" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL51" s="3">
         <v>45870.79166666666</v>
@@ -7000,7 +7006,7 @@
         <v>143</v>
       </c>
       <c r="F52" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -7015,7 +7021,7 @@
         <v>0</v>
       </c>
       <c r="K52" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L52">
         <v>0</v>
@@ -7090,10 +7096,10 @@
         <v>0</v>
       </c>
       <c r="AJ52" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK52" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL52" s="3">
         <v>45870.79166666666</v>
@@ -7107,7 +7113,7 @@
         <v>53</v>
       </c>
       <c r="C53" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D53" t="s">
         <v>92</v>
@@ -7116,7 +7122,7 @@
         <v>144</v>
       </c>
       <c r="F53" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -7131,16 +7137,16 @@
         <v>0</v>
       </c>
       <c r="K53" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L53">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M53">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O53">
         <v>0</v>
@@ -7182,10 +7188,10 @@
         <v>0</v>
       </c>
       <c r="AB53">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC53">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD53">
         <v>0</v>
@@ -7206,10 +7212,10 @@
         <v>0</v>
       </c>
       <c r="AJ53" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK53" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL53" s="3">
         <v>45870.79166666666</v>
@@ -7232,7 +7238,7 @@
         <v>145</v>
       </c>
       <c r="F54" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -7247,7 +7253,7 @@
         <v>0</v>
       </c>
       <c r="K54" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L54">
         <v>0</v>
@@ -7322,10 +7328,10 @@
         <v>0</v>
       </c>
       <c r="AJ54" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK54" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL54" s="3">
         <v>45870.79166666666</v>
@@ -7348,7 +7354,7 @@
         <v>146</v>
       </c>
       <c r="F55" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -7363,7 +7369,7 @@
         <v>0</v>
       </c>
       <c r="K55" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L55">
         <v>0</v>
@@ -7438,10 +7444,10 @@
         <v>0</v>
       </c>
       <c r="AJ55" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK55" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL55" s="3">
         <v>45870.79166666666</v>
@@ -7464,7 +7470,7 @@
         <v>147</v>
       </c>
       <c r="F56" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -7479,7 +7485,7 @@
         <v>0</v>
       </c>
       <c r="K56" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L56">
         <v>0</v>
@@ -7554,10 +7560,10 @@
         <v>0</v>
       </c>
       <c r="AJ56" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK56" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL56" s="3">
         <v>45870.79166666666</v>
@@ -7580,7 +7586,7 @@
         <v>148</v>
       </c>
       <c r="F57" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -7595,7 +7601,7 @@
         <v>0</v>
       </c>
       <c r="K57" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L57">
         <v>0</v>
@@ -7670,10 +7676,10 @@
         <v>0</v>
       </c>
       <c r="AJ57" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK57" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL57" s="3">
         <v>45870.79166666666</v>
@@ -7696,7 +7702,7 @@
         <v>149</v>
       </c>
       <c r="F58" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -7711,7 +7717,7 @@
         <v>0</v>
       </c>
       <c r="K58" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L58">
         <v>0</v>
@@ -7786,10 +7792,10 @@
         <v>0</v>
       </c>
       <c r="AJ58" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK58" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL58" s="3">
         <v>45870.79166666666</v>
@@ -7812,7 +7818,7 @@
         <v>150</v>
       </c>
       <c r="F59" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -7827,7 +7833,7 @@
         <v>0</v>
       </c>
       <c r="K59" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L59">
         <v>0</v>
@@ -7902,10 +7908,10 @@
         <v>0</v>
       </c>
       <c r="AJ59" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK59" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL59" s="3">
         <v>45870.79166666666</v>
@@ -7928,7 +7934,7 @@
         <v>151</v>
       </c>
       <c r="F60" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -7943,7 +7949,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L60">
         <v>0</v>
@@ -8018,10 +8024,10 @@
         <v>0</v>
       </c>
       <c r="AJ60" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK60" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL60" s="3">
         <v>45870.79166666666</v>
@@ -8032,10 +8038,10 @@
         <v>45870</v>
       </c>
       <c r="B61" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C61" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D61" t="s">
         <v>92</v>
@@ -8044,7 +8050,7 @@
         <v>152</v>
       </c>
       <c r="F61" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -8059,7 +8065,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L61">
         <v>0</v>
@@ -8134,13 +8140,13 @@
         <v>0</v>
       </c>
       <c r="AJ61" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK61" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL61" s="3">
-        <v>45870.83333333334</v>
+        <v>45870.79166666666</v>
       </c>
     </row>
     <row r="62" spans="1:38">
@@ -8148,10 +8154,10 @@
         <v>45870</v>
       </c>
       <c r="B62" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C62" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D62" t="s">
         <v>92</v>
@@ -8160,7 +8166,7 @@
         <v>153</v>
       </c>
       <c r="F62" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -8175,16 +8181,16 @@
         <v>0</v>
       </c>
       <c r="K62" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L62">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M62">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N62">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O62">
         <v>0</v>
@@ -8226,10 +8232,10 @@
         <v>0</v>
       </c>
       <c r="AB62">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC62">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AD62">
         <v>0</v>
@@ -8250,13 +8256,13 @@
         <v>0</v>
       </c>
       <c r="AJ62" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK62" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL62" s="3">
-        <v>45870.875</v>
+        <v>45870.83333333334</v>
       </c>
     </row>
     <row r="63" spans="1:38">
@@ -8276,7 +8282,7 @@
         <v>154</v>
       </c>
       <c r="F63" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -8291,16 +8297,16 @@
         <v>0</v>
       </c>
       <c r="K63" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L63">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="M63">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="N63">
-        <v>1.52</v>
+        <v>1.84</v>
       </c>
       <c r="O63">
         <v>0</v>
@@ -8342,10 +8348,10 @@
         <v>0</v>
       </c>
       <c r="AB63">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="AC63">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="AD63">
         <v>0</v>
@@ -8366,10 +8372,10 @@
         <v>0</v>
       </c>
       <c r="AJ63" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK63" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL63" s="3">
         <v>45870.875</v>
@@ -8380,10 +8386,10 @@
         <v>45870</v>
       </c>
       <c r="B64" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C64" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D64" t="s">
         <v>92</v>
@@ -8392,7 +8398,7 @@
         <v>155</v>
       </c>
       <c r="F64" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -8407,16 +8413,16 @@
         <v>0</v>
       </c>
       <c r="K64" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L64">
-        <v>1.86</v>
+        <v>5</v>
       </c>
       <c r="M64">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="N64">
-        <v>3.6</v>
+        <v>1.52</v>
       </c>
       <c r="O64">
         <v>0</v>
@@ -8458,10 +8464,10 @@
         <v>0</v>
       </c>
       <c r="AB64">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AC64">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AD64">
         <v>0</v>
@@ -8482,13 +8488,13 @@
         <v>0</v>
       </c>
       <c r="AJ64" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK64" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL64" s="3">
-        <v>45870.89583333334</v>
+        <v>45870.875</v>
       </c>
     </row>
     <row r="65" spans="1:38">
@@ -8499,7 +8505,7 @@
         <v>56</v>
       </c>
       <c r="C65" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D65" t="s">
         <v>92</v>
@@ -8508,7 +8514,7 @@
         <v>156</v>
       </c>
       <c r="F65" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -8523,16 +8529,16 @@
         <v>0</v>
       </c>
       <c r="K65" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L65">
-        <v>2.16</v>
+        <v>1.86</v>
       </c>
       <c r="M65">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N65">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="O65">
         <v>0</v>
@@ -8568,16 +8574,16 @@
         <v>0</v>
       </c>
       <c r="Z65">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA65">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB65">
-        <v>2.5</v>
+        <v>1.84</v>
       </c>
       <c r="AC65">
-        <v>1.48</v>
+        <v>1.92</v>
       </c>
       <c r="AD65">
         <v>0</v>
@@ -8598,10 +8604,10 @@
         <v>0</v>
       </c>
       <c r="AJ65" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK65" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL65" s="3">
         <v>45870.89583333334</v>
@@ -8612,10 +8618,10 @@
         <v>45870</v>
       </c>
       <c r="B66" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C66" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D66" t="s">
         <v>92</v>
@@ -8624,7 +8630,7 @@
         <v>157</v>
       </c>
       <c r="F66" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -8639,16 +8645,16 @@
         <v>0</v>
       </c>
       <c r="K66" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L66">
-        <v>1.61</v>
+        <v>1.87</v>
       </c>
       <c r="M66">
-        <v>3.75</v>
+        <v>3.11</v>
       </c>
       <c r="N66">
-        <v>4.7</v>
+        <v>3.78</v>
       </c>
       <c r="O66">
         <v>0</v>
@@ -8684,16 +8690,16 @@
         <v>0</v>
       </c>
       <c r="Z66">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA66">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB66">
-        <v>1.86</v>
+        <v>2.5</v>
       </c>
       <c r="AC66">
-        <v>1.9</v>
+        <v>1.48</v>
       </c>
       <c r="AD66">
         <v>0</v>
@@ -8714,13 +8720,13 @@
         <v>0</v>
       </c>
       <c r="AJ66" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK66" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL66" s="3">
-        <v>45870.91666666666</v>
+        <v>45870.89583333334</v>
       </c>
     </row>
     <row r="67" spans="1:38">
@@ -8728,10 +8734,10 @@
         <v>45870</v>
       </c>
       <c r="B67" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C67" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D67" t="s">
         <v>92</v>
@@ -8740,7 +8746,7 @@
         <v>158</v>
       </c>
       <c r="F67" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -8755,16 +8761,16 @@
         <v>0</v>
       </c>
       <c r="K67" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L67">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M67">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N67">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O67">
         <v>0</v>
@@ -8806,10 +8812,10 @@
         <v>0</v>
       </c>
       <c r="AB67">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC67">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD67">
         <v>0</v>
@@ -8830,13 +8836,13 @@
         <v>0</v>
       </c>
       <c r="AJ67" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK67" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL67" s="3">
-        <v>45870.95833333334</v>
+        <v>45870.91666666666</v>
       </c>
     </row>
     <row r="68" spans="1:38">
@@ -8844,10 +8850,10 @@
         <v>45870</v>
       </c>
       <c r="B68" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C68" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D68" t="s">
         <v>92</v>
@@ -8856,7 +8862,7 @@
         <v>159</v>
       </c>
       <c r="F68" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -8871,7 +8877,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L68">
         <v>0</v>
@@ -8946,12 +8952,128 @@
         <v>0</v>
       </c>
       <c r="AJ68" t="s">
+        <v>230</v>
+      </c>
+      <c r="AK68" t="s">
+        <v>230</v>
+      </c>
+      <c r="AL68" s="3">
+        <v>45870.95833333334</v>
+      </c>
+    </row>
+    <row r="69" spans="1:38">
+      <c r="A69" s="2">
+        <v>45870</v>
+      </c>
+      <c r="B69" t="s">
+        <v>59</v>
+      </c>
+      <c r="C69" t="s">
+        <v>88</v>
+      </c>
+      <c r="D69" t="s">
+        <v>92</v>
+      </c>
+      <c r="E69" t="s">
+        <v>160</v>
+      </c>
+      <c r="F69" t="s">
         <v>228</v>
       </c>
-      <c r="AK68" t="s">
-        <v>228</v>
-      </c>
-      <c r="AL68" s="3">
+      <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>0</v>
+      </c>
+      <c r="K69" t="s">
+        <v>229</v>
+      </c>
+      <c r="L69">
+        <v>0</v>
+      </c>
+      <c r="M69">
+        <v>0</v>
+      </c>
+      <c r="N69">
+        <v>0</v>
+      </c>
+      <c r="O69">
+        <v>0</v>
+      </c>
+      <c r="P69">
+        <v>0</v>
+      </c>
+      <c r="Q69">
+        <v>0</v>
+      </c>
+      <c r="R69">
+        <v>0</v>
+      </c>
+      <c r="S69">
+        <v>0</v>
+      </c>
+      <c r="T69">
+        <v>0</v>
+      </c>
+      <c r="U69">
+        <v>0</v>
+      </c>
+      <c r="V69">
+        <v>0</v>
+      </c>
+      <c r="W69">
+        <v>0</v>
+      </c>
+      <c r="X69">
+        <v>0</v>
+      </c>
+      <c r="Y69">
+        <v>0</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+      <c r="AA69">
+        <v>0</v>
+      </c>
+      <c r="AB69">
+        <v>0</v>
+      </c>
+      <c r="AC69">
+        <v>0</v>
+      </c>
+      <c r="AD69">
+        <v>0</v>
+      </c>
+      <c r="AE69">
+        <v>0</v>
+      </c>
+      <c r="AF69">
+        <v>0</v>
+      </c>
+      <c r="AG69">
+        <v>0</v>
+      </c>
+      <c r="AH69">
+        <v>0</v>
+      </c>
+      <c r="AI69">
+        <v>0</v>
+      </c>
+      <c r="AJ69" t="s">
+        <v>230</v>
+      </c>
+      <c r="AK69" t="s">
+        <v>230</v>
+      </c>
+      <c r="AL69" s="3">
         <v>45870.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-08-01.xlsx
+++ b/jogos_2025-08-01.xlsx
@@ -770,22 +770,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,13 +806,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -854,10 +854,10 @@
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
         <v>0</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>18.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="M6" t="n">
-        <v>3.76</v>
+        <v>3.3</v>
       </c>
       <c r="N6" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1220,58 +1220,58 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rukh Vynnyky</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SK Poltava</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="M8" t="n">
-        <v>3.41</v>
+        <v>4</v>
       </c>
       <c r="N8" t="n">
-        <v>5.9</v>
+        <v>5</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1484,58 +1484,58 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.52</v>
+        <v>1.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.53</v>
+        <v>4.2</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Smorgon</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dinamo Minsk</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Smorgon</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Dinamo Minsk</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Rukh Vynnyky</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mariehamn</t>
+          <t>SK Poltava</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="M13" t="n">
-        <v>3.98</v>
+        <v>3.41</v>
       </c>
       <c r="N13" t="n">
-        <v>4.33</v>
+        <v>5.9</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2168,16 +2168,16 @@
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2399,43 +2399,43 @@
         <v>2.6</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB15" t="n">
         <v>1.63</v>
@@ -2444,22 +2444,22 @@
         <v>2.15</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.73</v>
+        <v>2.47</v>
       </c>
       <c r="M16" t="n">
-        <v>3.82</v>
+        <v>3.1</v>
       </c>
       <c r="N16" t="n">
-        <v>3.57</v>
+        <v>2.7</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,16 +2570,16 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.3</v>
+        <v>1.42</v>
       </c>
       <c r="M17" t="n">
-        <v>3.21</v>
+        <v>4.2</v>
       </c>
       <c r="N17" t="n">
-        <v>2.68</v>
+        <v>5.6</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,10 +2702,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.62</v>
+        <v>2.13</v>
       </c>
       <c r="M18" t="n">
-        <v>3.7</v>
+        <v>3.17</v>
       </c>
       <c r="N18" t="n">
-        <v>1.75</v>
+        <v>2.99</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.53</v>
+        <v>1.89</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.2</v>
+        <v>1.81</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.02</v>
+        <v>2.3</v>
       </c>
       <c r="M19" t="n">
-        <v>3.45</v>
+        <v>3.21</v>
       </c>
       <c r="N19" t="n">
-        <v>2</v>
+        <v>2.68</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.54</v>
+        <v>3.02</v>
       </c>
       <c r="M20" t="n">
-        <v>3.21</v>
+        <v>3.45</v>
       </c>
       <c r="N20" t="n">
-        <v>2.41</v>
+        <v>2</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>7.7</v>
+        <v>3.62</v>
       </c>
       <c r="M21" t="n">
-        <v>5.2</v>
+        <v>3.7</v>
       </c>
       <c r="N21" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3230,16 +3230,16 @@
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.42</v>
+        <v>2.54</v>
       </c>
       <c r="M22" t="n">
-        <v>4.2</v>
+        <v>3.21</v>
       </c>
       <c r="N22" t="n">
-        <v>5.6</v>
+        <v>2.41</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3362,10 +3362,10 @@
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.47</v>
+        <v>1.45</v>
       </c>
       <c r="M23" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="N23" t="n">
-        <v>2.7</v>
+        <v>6.3</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3494,10 +3494,10 @@
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.45</v>
+        <v>1.73</v>
       </c>
       <c r="M24" t="n">
-        <v>3.7</v>
+        <v>3.82</v>
       </c>
       <c r="N24" t="n">
-        <v>6.3</v>
+        <v>3.57</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.13</v>
+        <v>7.7</v>
       </c>
       <c r="M25" t="n">
-        <v>3.17</v>
+        <v>5.2</v>
       </c>
       <c r="N25" t="n">
-        <v>2.99</v>
+        <v>1.25</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3758,16 +3758,16 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.89</v>
+        <v>1.4</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.81</v>
+        <v>2.75</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF25" t="n">
         <v>0</v>
@@ -3938,22 +3938,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4022,10 +4022,10 @@
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
         <v>0</v>
@@ -4070,22 +4070,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4154,10 +4154,10 @@
         <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD28" t="n">
         <v>0</v>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,13 +4502,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4556,10 +4556,10 @@
         <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF31" t="n">
         <v>0</v>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,13 +4634,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4682,10 +4682,10 @@
         <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
         <v>0</v>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,13 +4766,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.81</v>
+        <v>2.85</v>
       </c>
       <c r="M33" t="n">
-        <v>3.71</v>
+        <v>3.4</v>
       </c>
       <c r="N33" t="n">
-        <v>3.35</v>
+        <v>2.11</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4814,16 +4814,16 @@
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
         <v>0</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,13 +5030,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.99</v>
+        <v>2.24</v>
       </c>
       <c r="M35" t="n">
-        <v>3.21</v>
+        <v>2.96</v>
       </c>
       <c r="N35" t="n">
-        <v>2.36</v>
+        <v>2.98</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5078,16 +5078,16 @@
         <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.53</v>
+        <v>2.39</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.35</v>
+        <v>1.58</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
         <v>0</v>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.24</v>
+        <v>2.02</v>
       </c>
       <c r="M36" t="n">
-        <v>2.96</v>
+        <v>3.13</v>
       </c>
       <c r="N36" t="n">
-        <v>2.98</v>
+        <v>3.27</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5210,10 +5210,10 @@
         <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.39</v>
+        <v>1.95</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.27</v>
+        <v>2.99</v>
       </c>
       <c r="M37" t="n">
-        <v>2.99</v>
+        <v>3.21</v>
       </c>
       <c r="N37" t="n">
-        <v>2.9</v>
+        <v>2.36</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5342,16 +5342,16 @@
         <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF37" t="n">
         <v>0</v>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,13 +5558,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.02</v>
+        <v>2.27</v>
       </c>
       <c r="M39" t="n">
-        <v>3.13</v>
+        <v>2.99</v>
       </c>
       <c r="N39" t="n">
-        <v>3.27</v>
+        <v>2.9</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5606,10 +5606,10 @@
         <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
         <v>0</v>
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,13 +5690,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>4.1</v>
+        <v>1.94</v>
       </c>
       <c r="M40" t="n">
-        <v>3.41</v>
+        <v>3.45</v>
       </c>
       <c r="N40" t="n">
-        <v>1.72</v>
+        <v>3.16</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5738,10 +5738,10 @@
         <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.89</v>
+        <v>1.67</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="AD40" t="n">
         <v>0</v>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,13 +5822,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="M41" t="n">
-        <v>4.33</v>
+        <v>3.86</v>
       </c>
       <c r="N41" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5870,10 +5870,10 @@
         <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.15</v>
+        <v>1.79</v>
       </c>
       <c r="AD41" t="n">
         <v>0</v>
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.94</v>
+        <v>1.39</v>
       </c>
       <c r="M42" t="n">
-        <v>3.45</v>
+        <v>4.33</v>
       </c>
       <c r="N42" t="n">
-        <v>3.16</v>
+        <v>5.8</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6002,10 +6002,10 @@
         <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AC42" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AD42" t="n">
         <v>0</v>
@@ -6314,22 +6314,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.48</v>
+        <v>3.55</v>
       </c>
       <c r="M45" t="n">
-        <v>3.86</v>
+        <v>3.7</v>
       </c>
       <c r="N45" t="n">
-        <v>5.4</v>
+        <v>1.89</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6398,10 +6398,10 @@
         <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AD45" t="n">
         <v>0</v>
@@ -6446,22 +6446,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6482,13 +6482,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.55</v>
+        <v>2.23</v>
       </c>
       <c r="M46" t="n">
-        <v>3.7</v>
+        <v>3.31</v>
       </c>
       <c r="N46" t="n">
-        <v>1.89</v>
+        <v>2.7</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6530,10 +6530,10 @@
         <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.83</v>
+        <v>1.96</v>
       </c>
       <c r="AD46" t="n">
         <v>0</v>
@@ -6578,22 +6578,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,13 +6614,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.23</v>
+        <v>4</v>
       </c>
       <c r="M47" t="n">
-        <v>3.31</v>
+        <v>3.72</v>
       </c>
       <c r="N47" t="n">
-        <v>2.7</v>
+        <v>1.66</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6662,16 +6662,16 @@
         <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.74</v>
+        <v>1.57</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.96</v>
+        <v>2.3</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AF47" t="n">
         <v>0</v>
@@ -6710,22 +6710,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6746,13 +6746,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>4</v>
+        <v>2.12</v>
       </c>
       <c r="M48" t="n">
-        <v>3.72</v>
+        <v>3.45</v>
       </c>
       <c r="N48" t="n">
-        <v>1.66</v>
+        <v>2.8</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6794,16 +6794,16 @@
         <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AC48" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AD48" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
         <v>0</v>
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6878,13 +6878,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.12</v>
+        <v>4.1</v>
       </c>
       <c r="M49" t="n">
-        <v>3.45</v>
+        <v>3.41</v>
       </c>
       <c r="N49" t="n">
-        <v>2.8</v>
+        <v>1.72</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6926,10 +6926,10 @@
         <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.65</v>
+        <v>1.89</v>
       </c>
       <c r="AC49" t="n">
-        <v>2.05</v>
+        <v>1.81</v>
       </c>
       <c r="AD49" t="n">
         <v>0</v>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7274,13 +7274,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7322,10 +7322,10 @@
         <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD52" t="n">
         <v>0</v>
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7670,13 +7670,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7718,10 +7718,10 @@
         <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD55" t="n">
         <v>0</v>
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9096,12 +9096,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9122,13 +9122,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="M66" t="n">
-        <v>3.5</v>
+        <v>3.11</v>
       </c>
       <c r="N66" t="n">
-        <v>3.6</v>
+        <v>3.78</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9164,16 +9164,16 @@
         <v>0</v>
       </c>
       <c r="Z66" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.84</v>
+        <v>2.4</v>
       </c>
       <c r="AC66" t="n">
-        <v>1.92</v>
+        <v>1.5</v>
       </c>
       <c r="AD66" t="n">
         <v>0</v>
@@ -9218,7 +9218,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9254,13 +9254,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="M67" t="n">
-        <v>3.11</v>
+        <v>3.5</v>
       </c>
       <c r="N67" t="n">
-        <v>3.78</v>
+        <v>3.6</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9296,16 +9296,16 @@
         <v>0</v>
       </c>
       <c r="Z67" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>2.4</v>
+        <v>1.84</v>
       </c>
       <c r="AC67" t="n">
-        <v>1.5</v>
+        <v>1.92</v>
       </c>
       <c r="AD67" t="n">
         <v>0</v>

--- a/jogos_2025-08-01.xlsx
+++ b/jogos_2025-08-01.xlsx
@@ -770,22 +770,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,76 +806,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>18.75</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -902,22 +902,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>18.75</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.43</v>
+        <v>2.63</v>
       </c>
       <c r="M5" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="N5" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="O5" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1166,22 +1166,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1298,22 +1298,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Smorgon</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mariehamn</t>
+          <t>Dinamo Minsk</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1484,58 +1484,58 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Rukh Vynnyky</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>SK Poltava</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1772,10 +1772,10 @@
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Smorgon</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dinamo Minsk</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rukh Vynnyky</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SK Poltava</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="M13" t="n">
-        <v>3.41</v>
+        <v>4</v>
       </c>
       <c r="N13" t="n">
-        <v>5.9</v>
+        <v>5</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.52</v>
+        <v>1.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.53</v>
+        <v>4.2</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2267,43 +2267,43 @@
         <v>3.46</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB14" t="n">
         <v>2.02</v>
@@ -2312,22 +2312,22 @@
         <v>1.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.46</v>
+        <v>2.28</v>
       </c>
       <c r="M15" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N15" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="O15" t="n">
         <v>1.93</v>
@@ -2438,10 +2438,10 @@
         <v>4</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AD15" t="n">
         <v>2.6</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.47</v>
+        <v>1.42</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="N16" t="n">
-        <v>2.7</v>
+        <v>5.6</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="M17" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="N17" t="n">
-        <v>5.6</v>
+        <v>6.3</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,10 +2702,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.3</v>
+        <v>2.47</v>
       </c>
       <c r="M19" t="n">
-        <v>3.21</v>
+        <v>3.1</v>
       </c>
       <c r="N19" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC19" t="n">
         <v>1.73</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.91</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.02</v>
+        <v>2.54</v>
       </c>
       <c r="M20" t="n">
-        <v>3.45</v>
+        <v>3.21</v>
       </c>
       <c r="N20" t="n">
-        <v>2</v>
+        <v>2.41</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.62</v>
+        <v>3.02</v>
       </c>
       <c r="M21" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="N21" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3230,10 +3230,10 @@
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.54</v>
+        <v>3.62</v>
       </c>
       <c r="M22" t="n">
-        <v>3.21</v>
+        <v>3.7</v>
       </c>
       <c r="N22" t="n">
-        <v>2.41</v>
+        <v>1.75</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3362,10 +3362,10 @@
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.77</v>
+        <v>1.53</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.45</v>
+        <v>1.73</v>
       </c>
       <c r="M23" t="n">
-        <v>3.7</v>
+        <v>3.82</v>
       </c>
       <c r="N23" t="n">
-        <v>6.3</v>
+        <v>3.57</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3494,16 +3494,16 @@
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.73</v>
+        <v>7.7</v>
       </c>
       <c r="M24" t="n">
-        <v>3.82</v>
+        <v>5.2</v>
       </c>
       <c r="N24" t="n">
-        <v>3.57</v>
+        <v>1.25</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>7.7</v>
+        <v>2.3</v>
       </c>
       <c r="M25" t="n">
-        <v>5.2</v>
+        <v>3.21</v>
       </c>
       <c r="N25" t="n">
-        <v>1.25</v>
+        <v>2.68</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3758,16 +3758,16 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.75</v>
+        <v>1.91</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
         <v>0</v>
@@ -3938,22 +3938,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4022,10 +4022,10 @@
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD27" t="n">
         <v>0</v>
@@ -4070,22 +4070,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4154,10 +4154,10 @@
         <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
         <v>0</v>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,13 +4502,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4556,10 +4556,10 @@
         <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
         <v>0</v>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,13 +4634,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4682,10 +4682,10 @@
         <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD32" t="n">
         <v>0</v>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,13 +4766,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.85</v>
+        <v>1.81</v>
       </c>
       <c r="M33" t="n">
-        <v>3.4</v>
+        <v>3.71</v>
       </c>
       <c r="N33" t="n">
-        <v>2.11</v>
+        <v>3.35</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4814,16 +4814,16 @@
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF33" t="n">
         <v>0</v>
@@ -4946,10 +4946,10 @@
         <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AD34" t="n">
         <v>0</v>
@@ -5078,10 +5078,10 @@
         <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.39</v>
+        <v>2.2</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AD35" t="n">
         <v>0</v>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.02</v>
+        <v>2.88</v>
       </c>
       <c r="M36" t="n">
-        <v>3.13</v>
+        <v>2.96</v>
       </c>
       <c r="N36" t="n">
-        <v>3.27</v>
+        <v>2.31</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5210,10 +5210,10 @@
         <v>0</v>
       </c>
       <c r="AB36" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC36" t="n">
         <v>1.95</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>1.75</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,13 +5426,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.88</v>
+        <v>2.02</v>
       </c>
       <c r="M38" t="n">
-        <v>2.96</v>
+        <v>3.13</v>
       </c>
       <c r="N38" t="n">
-        <v>2.31</v>
+        <v>3.27</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5474,10 +5474,10 @@
         <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,13 +5690,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.94</v>
+        <v>2.12</v>
       </c>
       <c r="M40" t="n">
         <v>3.45</v>
       </c>
       <c r="N40" t="n">
-        <v>3.16</v>
+        <v>2.8</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5738,10 +5738,10 @@
         <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AC40" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AD40" t="n">
         <v>0</v>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,13 +5822,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="M41" t="n">
-        <v>3.86</v>
+        <v>4.33</v>
       </c>
       <c r="N41" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5870,10 +5870,10 @@
         <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.79</v>
+        <v>2.15</v>
       </c>
       <c r="AD41" t="n">
         <v>0</v>
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.39</v>
+        <v>1.94</v>
       </c>
       <c r="M42" t="n">
-        <v>4.33</v>
+        <v>3.45</v>
       </c>
       <c r="N42" t="n">
-        <v>5.8</v>
+        <v>3.16</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6002,10 +6002,10 @@
         <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AD42" t="n">
         <v>0</v>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,13 +6086,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.69</v>
+        <v>4.1</v>
       </c>
       <c r="M43" t="n">
-        <v>3.18</v>
+        <v>3.41</v>
       </c>
       <c r="N43" t="n">
-        <v>2.31</v>
+        <v>1.72</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6134,10 +6134,10 @@
         <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AD43" t="n">
         <v>0</v>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6218,13 +6218,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>3.45</v>
+        <v>2.69</v>
       </c>
       <c r="M44" t="n">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="N44" t="n">
-        <v>1.94</v>
+        <v>2.31</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6266,10 +6266,10 @@
         <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="AD44" t="n">
         <v>0</v>
@@ -6314,22 +6314,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="M45" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="N45" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6398,10 +6398,10 @@
         <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AD45" t="n">
         <v>0</v>
@@ -6446,7 +6446,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6482,13 +6482,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.23</v>
+        <v>1.48</v>
       </c>
       <c r="M46" t="n">
-        <v>3.31</v>
+        <v>3.86</v>
       </c>
       <c r="N46" t="n">
-        <v>2.7</v>
+        <v>5.4</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6530,10 +6530,10 @@
         <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.74</v>
+        <v>1.91</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.96</v>
+        <v>1.79</v>
       </c>
       <c r="AD46" t="n">
         <v>0</v>
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6746,13 +6746,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="M48" t="n">
-        <v>3.45</v>
+        <v>3.31</v>
       </c>
       <c r="N48" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6794,10 +6794,10 @@
         <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AC48" t="n">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="AD48" t="n">
         <v>0</v>
@@ -6842,22 +6842,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6878,13 +6878,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="M49" t="n">
-        <v>3.41</v>
+        <v>3.7</v>
       </c>
       <c r="N49" t="n">
-        <v>1.72</v>
+        <v>1.89</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6926,10 +6926,10 @@
         <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AD49" t="n">
         <v>0</v>
@@ -6974,22 +6974,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7010,13 +7010,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.97</v>
+        <v>1.54</v>
       </c>
       <c r="M50" t="n">
-        <v>2.95</v>
+        <v>3.8</v>
       </c>
       <c r="N50" t="n">
-        <v>3.95</v>
+        <v>4.8</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7058,16 +7058,16 @@
         <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AF50" t="n">
         <v>0</v>
@@ -7106,22 +7106,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7142,13 +7142,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.54</v>
+        <v>1.97</v>
       </c>
       <c r="M51" t="n">
-        <v>3.8</v>
+        <v>2.95</v>
       </c>
       <c r="N51" t="n">
-        <v>4.8</v>
+        <v>3.95</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7190,16 +7190,16 @@
         <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD51" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
         <v>0</v>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7274,13 +7274,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7322,10 +7322,10 @@
         <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
         <v>0</v>
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7802,13 +7802,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7850,10 +7850,10 @@
         <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD56" t="n">
         <v>0</v>
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G62" t="n">

--- a/jogos_2025-08-01.xlsx
+++ b/jogos_2025-08-01.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,76 +806,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.85</v>
+        <v>2.63</v>
       </c>
       <c r="M3" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="N3" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="O3" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>18.75</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -902,22 +902,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.63</v>
+        <v>2.85</v>
       </c>
       <c r="M5" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="N5" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="P5" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC5" t="n">
         <v>2.3</v>
       </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1298,22 +1298,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Smorgon</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dinamo Minsk</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1739,37 +1739,37 @@
         <v>5.9</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="Z10" t="n">
         <v>1.52</v>
@@ -1778,28 +1778,28 @@
         <v>2.53</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Smorgon</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Dinamo Minsk</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mariehamn</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.42</v>
+        <v>3.02</v>
       </c>
       <c r="M16" t="n">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="N16" t="n">
-        <v>5.6</v>
+        <v>2</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.45</v>
+        <v>2.47</v>
       </c>
       <c r="M17" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="N17" t="n">
-        <v>6.3</v>
+        <v>2.7</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2705,7 +2705,7 @@
         <v>1.95</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,76 +2786,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.13</v>
+        <v>1.45</v>
       </c>
       <c r="M18" t="n">
-        <v>3.17</v>
+        <v>3.7</v>
       </c>
       <c r="N18" t="n">
-        <v>2.99</v>
+        <v>6.3</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.47</v>
+        <v>1.73</v>
       </c>
       <c r="M19" t="n">
-        <v>3.1</v>
+        <v>3.82</v>
       </c>
       <c r="N19" t="n">
-        <v>2.7</v>
+        <v>3.57</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,16 +2966,16 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.54</v>
+        <v>2.3</v>
       </c>
       <c r="M20" t="n">
         <v>3.21</v>
       </c>
       <c r="N20" t="n">
-        <v>2.41</v>
+        <v>2.68</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.02</v>
+        <v>2.54</v>
       </c>
       <c r="M21" t="n">
-        <v>3.45</v>
+        <v>3.21</v>
       </c>
       <c r="N21" t="n">
-        <v>2</v>
+        <v>2.41</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3230,10 +3230,10 @@
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.73</v>
+        <v>7.7</v>
       </c>
       <c r="M23" t="n">
-        <v>3.82</v>
+        <v>5.2</v>
       </c>
       <c r="N23" t="n">
-        <v>3.57</v>
+        <v>1.25</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3494,16 +3494,16 @@
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>7.7</v>
+        <v>1.42</v>
       </c>
       <c r="M24" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="N24" t="n">
-        <v>1.25</v>
+        <v>5.6</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="M25" t="n">
-        <v>3.21</v>
+        <v>3.17</v>
       </c>
       <c r="N25" t="n">
-        <v>2.68</v>
+        <v>2.99</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3758,10 +3758,10 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
@@ -3938,22 +3938,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,76 +3974,76 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="M27" t="n">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="N27" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.82</v>
+        <v>2.15</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
@@ -4070,22 +4070,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4154,10 +4154,10 @@
         <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD28" t="n">
         <v>0</v>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,13 +4634,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.85</v>
+        <v>1.81</v>
       </c>
       <c r="M32" t="n">
-        <v>3.4</v>
+        <v>3.71</v>
       </c>
       <c r="N32" t="n">
-        <v>2.11</v>
+        <v>3.35</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4682,16 +4682,16 @@
         <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF32" t="n">
         <v>0</v>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,13 +4766,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.81</v>
+        <v>2.85</v>
       </c>
       <c r="M33" t="n">
-        <v>3.71</v>
+        <v>3.4</v>
       </c>
       <c r="N33" t="n">
-        <v>3.35</v>
+        <v>2.11</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4814,16 +4814,16 @@
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
         <v>0</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,76 +5030,76 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.24</v>
+        <v>2.99</v>
       </c>
       <c r="M35" t="n">
-        <v>2.96</v>
+        <v>3.21</v>
       </c>
       <c r="N35" t="n">
-        <v>2.98</v>
+        <v>2.36</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.57</v>
+        <v>2.35</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.88</v>
+        <v>2.02</v>
       </c>
       <c r="M36" t="n">
-        <v>2.96</v>
+        <v>3.13</v>
       </c>
       <c r="N36" t="n">
-        <v>2.31</v>
+        <v>3.27</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5210,10 +5210,10 @@
         <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="M37" t="n">
         <v>2.99</v>
       </c>
-      <c r="M37" t="n">
-        <v>3.21</v>
-      </c>
       <c r="N37" t="n">
-        <v>2.36</v>
+        <v>2.9</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5342,16 +5342,16 @@
         <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
         <v>0</v>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,40 +5426,40 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.02</v>
+        <v>2.24</v>
       </c>
       <c r="M38" t="n">
-        <v>3.13</v>
+        <v>2.96</v>
       </c>
       <c r="N38" t="n">
-        <v>3.27</v>
+        <v>2.98</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X38" t="n">
         <v>0</v>
@@ -5474,10 +5474,10 @@
         <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -5486,10 +5486,10 @@
         <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH38" t="n">
         <v>0</v>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,76 +5558,76 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.27</v>
+        <v>2.88</v>
       </c>
       <c r="M39" t="n">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="N39" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="O39" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="P39" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V39" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD39" t="n">
         <v>2.9</v>
       </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0</v>
-      </c>
-      <c r="W39" t="n">
-        <v>0</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>0</v>
-      </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,13 +5690,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="M40" t="n">
-        <v>3.45</v>
+        <v>3.31</v>
       </c>
       <c r="N40" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5738,10 +5738,10 @@
         <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="AD40" t="n">
         <v>0</v>
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,13 +5822,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.39</v>
+        <v>2.12</v>
       </c>
       <c r="M41" t="n">
-        <v>4.33</v>
+        <v>3.45</v>
       </c>
       <c r="N41" t="n">
-        <v>5.8</v>
+        <v>2.8</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5870,10 +5870,10 @@
         <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AD41" t="n">
         <v>0</v>
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.94</v>
+        <v>4.1</v>
       </c>
       <c r="M42" t="n">
-        <v>3.45</v>
+        <v>3.41</v>
       </c>
       <c r="N42" t="n">
-        <v>3.16</v>
+        <v>1.72</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6002,10 +6002,10 @@
         <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.67</v>
+        <v>1.89</v>
       </c>
       <c r="AC42" t="n">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="AD42" t="n">
         <v>0</v>
@@ -6050,22 +6050,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,76 +6086,76 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="M43" t="n">
-        <v>3.41</v>
+        <v>3.7</v>
       </c>
       <c r="N43" t="n">
-        <v>1.72</v>
+        <v>1.89</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
@@ -6182,22 +6182,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6218,76 +6218,76 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.69</v>
+        <v>4</v>
       </c>
       <c r="M44" t="n">
-        <v>3.18</v>
+        <v>3.72</v>
       </c>
       <c r="N44" t="n">
-        <v>2.31</v>
+        <v>1.66</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.93</v>
+        <v>1.57</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.77</v>
+        <v>2.3</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6482,13 +6482,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.48</v>
+        <v>1.94</v>
       </c>
       <c r="M46" t="n">
-        <v>3.86</v>
+        <v>3.45</v>
       </c>
       <c r="N46" t="n">
-        <v>5.4</v>
+        <v>3.16</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6530,10 +6530,10 @@
         <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AD46" t="n">
         <v>0</v>
@@ -6578,22 +6578,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,13 +6614,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>4</v>
+        <v>1.39</v>
       </c>
       <c r="M47" t="n">
-        <v>3.72</v>
+        <v>4.33</v>
       </c>
       <c r="N47" t="n">
-        <v>1.66</v>
+        <v>5.8</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6665,13 +6665,13 @@
         <v>1.57</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AD47" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
         <v>0</v>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6746,13 +6746,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.23</v>
+        <v>1.48</v>
       </c>
       <c r="M48" t="n">
-        <v>3.31</v>
+        <v>3.86</v>
       </c>
       <c r="N48" t="n">
-        <v>2.7</v>
+        <v>5.4</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6794,10 +6794,10 @@
         <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.74</v>
+        <v>1.91</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.96</v>
+        <v>1.79</v>
       </c>
       <c r="AD48" t="n">
         <v>0</v>
@@ -6842,22 +6842,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6878,13 +6878,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>3.55</v>
+        <v>2.69</v>
       </c>
       <c r="M49" t="n">
-        <v>3.7</v>
+        <v>3.18</v>
       </c>
       <c r="N49" t="n">
-        <v>1.89</v>
+        <v>2.31</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6926,10 +6926,10 @@
         <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AD49" t="n">
         <v>0</v>
@@ -6974,22 +6974,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7010,13 +7010,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.54</v>
+        <v>1.97</v>
       </c>
       <c r="M50" t="n">
-        <v>3.8</v>
+        <v>2.95</v>
       </c>
       <c r="N50" t="n">
-        <v>4.8</v>
+        <v>3.95</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7058,16 +7058,16 @@
         <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
         <v>0</v>
@@ -7106,22 +7106,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7142,76 +7142,76 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.97</v>
+        <v>1.54</v>
       </c>
       <c r="M51" t="n">
-        <v>2.95</v>
+        <v>3.8</v>
       </c>
       <c r="N51" t="n">
-        <v>3.95</v>
+        <v>4.8</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH51" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI51" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7802,13 +7802,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.96</v>
+        <v>1.8</v>
       </c>
       <c r="M56" t="n">
-        <v>3.3</v>
+        <v>3.11</v>
       </c>
       <c r="N56" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9096,12 +9096,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9122,13 +9122,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="M66" t="n">
-        <v>3.11</v>
+        <v>3.5</v>
       </c>
       <c r="N66" t="n">
-        <v>3.78</v>
+        <v>3.6</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9164,16 +9164,16 @@
         <v>0</v>
       </c>
       <c r="Z66" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>2.4</v>
+        <v>1.84</v>
       </c>
       <c r="AC66" t="n">
-        <v>1.5</v>
+        <v>1.92</v>
       </c>
       <c r="AD66" t="n">
         <v>0</v>
@@ -9218,7 +9218,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9254,13 +9254,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="M67" t="n">
-        <v>3.5</v>
+        <v>3.11</v>
       </c>
       <c r="N67" t="n">
-        <v>3.6</v>
+        <v>3.78</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9296,16 +9296,16 @@
         <v>0</v>
       </c>
       <c r="Z67" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.84</v>
+        <v>2.4</v>
       </c>
       <c r="AC67" t="n">
-        <v>1.92</v>
+        <v>1.5</v>
       </c>
       <c r="AD67" t="n">
         <v>0</v>

--- a/jogos_2025-08-01.xlsx
+++ b/jogos_2025-08-01.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL70"/>
+  <dimension ref="A1:AL54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -770,7 +770,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,76 +806,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.63</v>
+        <v>2.85</v>
       </c>
       <c r="M3" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="N3" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="P3" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC3" t="n">
         <v>2.3</v>
       </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -897,12 +897,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="AL4" s="3" t="n">
-        <v>45870.45833333334</v>
+        <v>45870.5</v>
       </c>
     </row>
     <row r="5">
@@ -1029,27 +1029,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>18.75</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         </is>
       </c>
       <c r="AL5" s="3" t="n">
-        <v>45870.45833333334</v>
+        <v>45870.5</v>
       </c>
     </row>
     <row r="6">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="AL6" s="3" t="n">
-        <v>45870.45833333334</v>
+        <v>45870.5</v>
       </c>
     </row>
     <row r="7">
@@ -1293,12 +1293,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Smorgon</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Dinamo Minsk</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1416,7 +1416,7 @@
         </is>
       </c>
       <c r="AL7" s="3" t="n">
-        <v>45870.45833333334</v>
+        <v>45870.5</v>
       </c>
     </row>
     <row r="8">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Rukh Vynnyky</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>SK Poltava</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1689,27 +1689,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rukh Vynnyky</t>
+          <t>BATE</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SK Poltava</t>
+          <t>Vitebsk</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.65</v>
+        <v>2.17</v>
       </c>
       <c r="M10" t="n">
-        <v>3.41</v>
+        <v>3.28</v>
       </c>
       <c r="N10" t="n">
-        <v>5.9</v>
+        <v>3.46</v>
       </c>
       <c r="O10" t="n">
-        <v>1.44</v>
+        <v>1.77</v>
       </c>
       <c r="P10" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>2.32</v>
       </c>
       <c r="R10" t="n">
-        <v>1.57</v>
+        <v>1.39</v>
       </c>
       <c r="S10" t="n">
-        <v>2.25</v>
+        <v>2.67</v>
       </c>
       <c r="T10" t="n">
-        <v>3.75</v>
+        <v>2.93</v>
       </c>
       <c r="U10" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="V10" t="n">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X10" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>6.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.52</v>
+        <v>1.28</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.53</v>
+        <v>3.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.63</v>
+        <v>2.02</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>5.1</v>
+        <v>3.48</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.63</v>
+        <v>1.78</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.44</v>
+        <v>1.93</v>
       </c>
       <c r="AH10" t="n">
-        <v>8.5</v>
+        <v>7.2</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="AL10" s="3" t="n">
-        <v>45870.5</v>
+        <v>45870.51041666666</v>
       </c>
     </row>
     <row r="11">
@@ -1821,27 +1821,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mariehamn</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.55</v>
+        <v>2.28</v>
       </c>
       <c r="M11" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
-        <v>5</v>
+        <v>2.58</v>
       </c>
       <c r="O11" t="n">
-        <v>1.44</v>
+        <v>1.93</v>
       </c>
       <c r="P11" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.95</v>
+        <v>2.05</v>
       </c>
       <c r="R11" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="S11" t="n">
         <v>3.1</v>
       </c>
       <c r="T11" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="U11" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="V11" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="W11" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
         <v>9</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>4.95</v>
+        <v>4.8</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="AL11" s="3" t="n">
-        <v>45870.5</v>
+        <v>45870.52083333334</v>
       </c>
     </row>
     <row r="12">
@@ -1953,27 +1953,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Smorgon</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dinamo Minsk</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="AL12" s="3" t="n">
-        <v>45870.5</v>
+        <v>45870.54166666666</v>
       </c>
     </row>
     <row r="13">
@@ -2085,27 +2085,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2208,7 +2208,7 @@
         </is>
       </c>
       <c r="AL13" s="3" t="n">
-        <v>45870.5</v>
+        <v>45870.54166666666</v>
       </c>
     </row>
     <row r="14">
@@ -2217,27 +2217,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>BATE</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitebsk</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.17</v>
+        <v>1.45</v>
       </c>
       <c r="M14" t="n">
-        <v>3.28</v>
+        <v>3.7</v>
       </c>
       <c r="N14" t="n">
-        <v>3.46</v>
+        <v>6.3</v>
       </c>
       <c r="O14" t="n">
-        <v>1.77</v>
+        <v>1.28</v>
       </c>
       <c r="P14" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.32</v>
+        <v>3.9</v>
       </c>
       <c r="R14" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="S14" t="n">
-        <v>2.67</v>
+        <v>3.22</v>
       </c>
       <c r="T14" t="n">
-        <v>2.93</v>
+        <v>2.47</v>
       </c>
       <c r="U14" t="n">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="V14" t="n">
-        <v>8.199999999999999</v>
+        <v>5.7</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X14" t="n">
         <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>8.300000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.2</v>
+        <v>3.98</v>
       </c>
       <c r="AB14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AF14" t="n">
         <v>2.02</v>
       </c>
-      <c r="AC14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AG14" t="n">
-        <v>1.93</v>
+        <v>1.71</v>
       </c>
       <c r="AH14" t="n">
-        <v>7.2</v>
+        <v>4.75</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="AL14" s="3" t="n">
-        <v>45870.51041666666</v>
+        <v>45870.54166666666</v>
       </c>
     </row>
     <row r="15">
@@ -2349,12 +2349,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.28</v>
+        <v>1.75</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="N15" t="n">
-        <v>2.58</v>
+        <v>3.81</v>
       </c>
       <c r="O15" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="S15" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="T15" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="U15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AB15" t="n">
         <v>1.5</v>
       </c>
-      <c r="V15" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AC15" t="n">
-        <v>2.05</v>
+        <v>2.39</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.6</v>
+        <v>2.27</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.3</v>
+        <v>2.49</v>
       </c>
       <c r="AH15" t="n">
-        <v>4.8</v>
+        <v>3.75</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         </is>
       </c>
       <c r="AL15" s="3" t="n">
-        <v>45870.52083333334</v>
+        <v>45870.54166666666</v>
       </c>
     </row>
     <row r="16">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,76 +2522,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.02</v>
+        <v>2.81</v>
       </c>
       <c r="M16" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
       <c r="N16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V16" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC16" t="n">
         <v>2</v>
       </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.47</v>
+        <v>2.13</v>
       </c>
       <c r="M17" t="n">
-        <v>3.1</v>
+        <v>3.17</v>
       </c>
       <c r="N17" t="n">
-        <v>2.7</v>
+        <v>2.99</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,10 +2702,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,76 +2786,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.45</v>
+        <v>2.43</v>
       </c>
       <c r="M18" t="n">
         <v>3.7</v>
       </c>
       <c r="N18" t="n">
-        <v>6.3</v>
+        <v>2.51</v>
       </c>
       <c r="O18" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.73</v>
+        <v>2.5</v>
       </c>
       <c r="M19" t="n">
-        <v>3.82</v>
+        <v>3.25</v>
       </c>
       <c r="N19" t="n">
-        <v>3.57</v>
+        <v>2.46</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2936,58 +2936,58 @@
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.3</v>
+        <v>7.7</v>
       </c>
       <c r="M20" t="n">
-        <v>3.21</v>
+        <v>5.2</v>
       </c>
       <c r="N20" t="n">
-        <v>2.68</v>
+        <v>1.25</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,16 +3098,16 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.91</v>
+        <v>2.75</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.54</v>
+        <v>3.62</v>
       </c>
       <c r="M21" t="n">
-        <v>3.21</v>
+        <v>3.7</v>
       </c>
       <c r="N21" t="n">
-        <v>2.41</v>
+        <v>1.75</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3230,10 +3230,10 @@
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.77</v>
+        <v>1.53</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -3273,27 +3273,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.62</v>
+        <v>1.2</v>
       </c>
       <c r="M22" t="n">
-        <v>3.7</v>
+        <v>5.4</v>
       </c>
       <c r="N22" t="n">
-        <v>1.75</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3362,16 +3362,16 @@
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF22" t="n">
         <v>0</v>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="AL22" s="3" t="n">
-        <v>45870.54166666666</v>
+        <v>45870.5625</v>
       </c>
     </row>
     <row r="23">
@@ -3405,27 +3405,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,76 +3446,76 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>7.7</v>
+        <v>2.14</v>
       </c>
       <c r="M23" t="n">
-        <v>5.2</v>
+        <v>3.14</v>
       </c>
       <c r="N23" t="n">
-        <v>1.25</v>
+        <v>3</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.4</v>
+        <v>1.88</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.75</v>
+        <v>1.82</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.85</v>
+        <v>3.35</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.85</v>
+        <v>1.33</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         </is>
       </c>
       <c r="AL23" s="3" t="n">
-        <v>45870.54166666666</v>
+        <v>45870.58333333334</v>
       </c>
     </row>
     <row r="24">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,76 +3578,76 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.42</v>
+        <v>2.2</v>
       </c>
       <c r="M24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="P24" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V24" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AA24" t="n">
         <v>4.2</v>
       </c>
-      <c r="N24" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>0</v>
-      </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
@@ -3660,7 +3660,7 @@
         </is>
       </c>
       <c r="AL24" s="3" t="n">
-        <v>45870.54166666666</v>
+        <v>45870.58333333334</v>
       </c>
     </row>
     <row r="25">
@@ -3669,12 +3669,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3758,10 +3758,10 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
@@ -3792,7 +3792,7 @@
         </is>
       </c>
       <c r="AL25" s="3" t="n">
-        <v>45870.54166666666</v>
+        <v>45870.60416666666</v>
       </c>
     </row>
     <row r="26">
@@ -3801,27 +3801,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3896,10 +3896,10 @@
         <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
         <v>0</v>
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="AL26" s="3" t="n">
-        <v>45870.5625</v>
+        <v>45870.61458333334</v>
       </c>
     </row>
     <row r="27">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,76 +3974,76 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.2</v>
+        <v>2.85</v>
       </c>
       <c r="M27" t="n">
         <v>3.4</v>
       </c>
       <c r="N27" t="n">
-        <v>2.7</v>
+        <v>2.11</v>
       </c>
       <c r="O27" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         </is>
       </c>
       <c r="AL27" s="3" t="n">
-        <v>45870.58333333334</v>
+        <v>45870.625</v>
       </c>
     </row>
     <row r="28">
@@ -4065,27 +4065,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4154,10 +4154,10 @@
         <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
         <v>0</v>
@@ -4188,7 +4188,7 @@
         </is>
       </c>
       <c r="AL28" s="3" t="n">
-        <v>45870.58333333334</v>
+        <v>45870.625</v>
       </c>
     </row>
     <row r="29">
@@ -4197,12 +4197,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,13 +4238,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4292,10 +4292,10 @@
         <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF29" t="n">
         <v>0</v>
@@ -4320,7 +4320,7 @@
         </is>
       </c>
       <c r="AL29" s="3" t="n">
-        <v>45870.60416666666</v>
+        <v>45870.625</v>
       </c>
     </row>
     <row r="30">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4418,10 +4418,10 @@
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD30" t="n">
         <v>0</v>
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="AL30" s="3" t="n">
-        <v>45870.61458333334</v>
+        <v>45870.63541666666</v>
       </c>
     </row>
     <row r="31">
@@ -4461,12 +4461,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,76 +4502,76 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         </is>
       </c>
       <c r="AL31" s="3" t="n">
-        <v>45870.625</v>
+        <v>45870.64583333334</v>
       </c>
     </row>
     <row r="32">
@@ -4593,12 +4593,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,40 +4634,40 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.81</v>
+        <v>2.24</v>
       </c>
       <c r="M32" t="n">
-        <v>3.71</v>
+        <v>2.96</v>
       </c>
       <c r="N32" t="n">
-        <v>3.35</v>
+        <v>2.98</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X32" t="n">
         <v>0</v>
@@ -4682,22 +4682,22 @@
         <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH32" t="n">
         <v>0</v>
@@ -4716,7 +4716,7 @@
         </is>
       </c>
       <c r="AL32" s="3" t="n">
-        <v>45870.625</v>
+        <v>45870.64583333334</v>
       </c>
     </row>
     <row r="33">
@@ -4725,12 +4725,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,13 +4766,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.85</v>
+        <v>2.27</v>
       </c>
       <c r="M33" t="n">
-        <v>3.4</v>
+        <v>2.99</v>
       </c>
       <c r="N33" t="n">
-        <v>2.11</v>
+        <v>2.9</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4814,10 +4814,10 @@
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
         <v>0</v>
@@ -4848,7 +4848,7 @@
         </is>
       </c>
       <c r="AL33" s="3" t="n">
-        <v>45870.625</v>
+        <v>45870.64583333334</v>
       </c>
     </row>
     <row r="34">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,76 +4898,76 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.52</v>
+        <v>2.88</v>
       </c>
       <c r="M34" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="N34" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="O34" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="P34" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V34" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA34" t="n">
         <v>3.8</v>
       </c>
-      <c r="N34" t="n">
+      <c r="AB34" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH34" t="n">
         <v>5.5</v>
       </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" t="n">
-        <v>0</v>
-      </c>
-      <c r="X34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>0</v>
-      </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         </is>
       </c>
       <c r="AL34" s="3" t="n">
-        <v>45870.63541666666</v>
+        <v>45870.64583333334</v>
       </c>
     </row>
     <row r="35">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,76 +5030,76 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.99</v>
+        <v>1.84</v>
       </c>
       <c r="M35" t="n">
-        <v>3.21</v>
+        <v>3.29</v>
       </c>
       <c r="N35" t="n">
-        <v>2.36</v>
+        <v>3.65</v>
       </c>
       <c r="O35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.53</v>
+        <v>1.95</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.35</v>
+        <v>1.75</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
@@ -5121,12 +5121,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,76 +5162,76 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.02</v>
+        <v>3.55</v>
       </c>
       <c r="M36" t="n">
-        <v>3.13</v>
+        <v>3.7</v>
       </c>
       <c r="N36" t="n">
-        <v>3.27</v>
+        <v>1.89</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         </is>
       </c>
       <c r="AL36" s="3" t="n">
-        <v>45870.64583333334</v>
+        <v>45870.65625</v>
       </c>
     </row>
     <row r="37">
@@ -5253,27 +5253,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.27</v>
+        <v>2.12</v>
       </c>
       <c r="M37" t="n">
-        <v>2.99</v>
+        <v>3.45</v>
       </c>
       <c r="N37" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5342,10 +5342,10 @@
         <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
@@ -5376,7 +5376,7 @@
         </is>
       </c>
       <c r="AL37" s="3" t="n">
-        <v>45870.64583333334</v>
+        <v>45870.65625</v>
       </c>
     </row>
     <row r="38">
@@ -5385,27 +5385,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,40 +5426,40 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.24</v>
+        <v>4.1</v>
       </c>
       <c r="M38" t="n">
-        <v>2.96</v>
+        <v>3.41</v>
       </c>
       <c r="N38" t="n">
-        <v>2.98</v>
+        <v>1.72</v>
       </c>
       <c r="O38" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
         <v>0</v>
@@ -5474,10 +5474,10 @@
         <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.2</v>
+        <v>1.89</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -5486,10 +5486,10 @@
         <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
         <v>0</v>
@@ -5508,7 +5508,7 @@
         </is>
       </c>
       <c r="AL38" s="3" t="n">
-        <v>45870.64583333334</v>
+        <v>45870.65625</v>
       </c>
     </row>
     <row r="39">
@@ -5517,27 +5517,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,76 +5558,76 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.88</v>
+        <v>1.39</v>
       </c>
       <c r="M39" t="n">
-        <v>2.96</v>
+        <v>4.33</v>
       </c>
       <c r="N39" t="n">
-        <v>2.31</v>
+        <v>5.8</v>
       </c>
       <c r="O39" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
@@ -5640,7 +5640,7 @@
         </is>
       </c>
       <c r="AL39" s="3" t="n">
-        <v>45870.64583333334</v>
+        <v>45870.65625</v>
       </c>
     </row>
     <row r="40">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,13 +5690,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.23</v>
+        <v>1.94</v>
       </c>
       <c r="M40" t="n">
-        <v>3.31</v>
+        <v>3.45</v>
       </c>
       <c r="N40" t="n">
-        <v>2.7</v>
+        <v>3.16</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5738,10 +5738,10 @@
         <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AD40" t="n">
         <v>0</v>
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,13 +5822,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="M41" t="n">
-        <v>3.45</v>
+        <v>3.31</v>
       </c>
       <c r="N41" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5870,10 +5870,10 @@
         <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="AD41" t="n">
         <v>0</v>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>4.1</v>
+        <v>1.48</v>
       </c>
       <c r="M42" t="n">
-        <v>3.41</v>
+        <v>3.86</v>
       </c>
       <c r="N42" t="n">
-        <v>1.72</v>
+        <v>5.4</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5972,58 +5972,58 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
@@ -6050,22 +6050,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,76 +6086,76 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.55</v>
+        <v>2.69</v>
       </c>
       <c r="M43" t="n">
-        <v>3.7</v>
+        <v>3.18</v>
       </c>
       <c r="N43" t="n">
-        <v>1.89</v>
+        <v>2.31</v>
       </c>
       <c r="O43" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
         <v>1.36</v>
       </c>
       <c r="S43" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="T43" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="U43" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="V43" t="n">
-        <v>6.5</v>
+        <v>6.55</v>
       </c>
       <c r="W43" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X43" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y43" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AA43" t="n">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AD43" t="n">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="AE43" t="n">
         <v>1.28</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AH43" t="n">
-        <v>6.15</v>
+        <v>5.95</v>
       </c>
       <c r="AI43" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
@@ -6309,27 +6309,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,76 +6350,76 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>3.45</v>
+        <v>1.54</v>
       </c>
       <c r="M45" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="N45" t="n">
-        <v>1.94</v>
+        <v>4.8</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI45" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         </is>
       </c>
       <c r="AL45" s="3" t="n">
-        <v>45870.65625</v>
+        <v>45870.66666666666</v>
       </c>
     </row>
     <row r="46">
@@ -6441,12 +6441,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6482,13 +6482,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="M46" t="n">
-        <v>3.45</v>
+        <v>3.11</v>
       </c>
       <c r="N46" t="n">
-        <v>3.16</v>
+        <v>4.1</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6530,10 +6530,10 @@
         <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="AC46" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AD46" t="n">
         <v>0</v>
@@ -6564,7 +6564,7 @@
         </is>
       </c>
       <c r="AL46" s="3" t="n">
-        <v>45870.65625</v>
+        <v>45870.79166666666</v>
       </c>
     </row>
     <row r="47">
@@ -6573,12 +6573,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,76 +6614,76 @@
         </is>
       </c>
       <c r="L47" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M47" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N47" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O47" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="P47" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R47" t="n">
         <v>1.39</v>
       </c>
-      <c r="M47" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="N47" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
-      <c r="R47" t="n">
-        <v>0</v>
-      </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="AI47" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
@@ -6696,7 +6696,7 @@
         </is>
       </c>
       <c r="AL47" s="3" t="n">
-        <v>45870.65625</v>
+        <v>45870.83333333334</v>
       </c>
     </row>
     <row r="48">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6746,13 +6746,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.48</v>
+        <v>3.2</v>
       </c>
       <c r="M48" t="n">
-        <v>3.86</v>
+        <v>3.8</v>
       </c>
       <c r="N48" t="n">
-        <v>5.4</v>
+        <v>1.84</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6828,7 +6828,7 @@
         </is>
       </c>
       <c r="AL48" s="3" t="n">
-        <v>45870.65625</v>
+        <v>45870.875</v>
       </c>
     </row>
     <row r="49">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6878,13 +6878,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.69</v>
+        <v>5</v>
       </c>
       <c r="M49" t="n">
-        <v>3.18</v>
+        <v>3.85</v>
       </c>
       <c r="N49" t="n">
-        <v>2.31</v>
+        <v>1.52</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6926,10 +6926,10 @@
         <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="AD49" t="n">
         <v>0</v>
@@ -6960,7 +6960,7 @@
         </is>
       </c>
       <c r="AL49" s="3" t="n">
-        <v>45870.65625</v>
+        <v>45870.875</v>
       </c>
     </row>
     <row r="50">
@@ -6969,12 +6969,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7010,13 +7010,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="M50" t="n">
-        <v>2.95</v>
+        <v>3.11</v>
       </c>
       <c r="N50" t="n">
-        <v>3.95</v>
+        <v>3.78</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7052,16 +7052,16 @@
         <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD50" t="n">
         <v>0</v>
@@ -7092,7 +7092,7 @@
         </is>
       </c>
       <c r="AL50" s="3" t="n">
-        <v>45870.66666666666</v>
+        <v>45870.89583333334</v>
       </c>
     </row>
     <row r="51">
@@ -7101,27 +7101,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7142,76 +7142,76 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.54</v>
+        <v>1.86</v>
       </c>
       <c r="M51" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="N51" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="O51" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U51" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AD51" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH51" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AI51" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         </is>
       </c>
       <c r="AL51" s="3" t="n">
-        <v>45870.66666666666</v>
+        <v>45870.89583333334</v>
       </c>
     </row>
     <row r="52">
@@ -7233,12 +7233,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7274,13 +7274,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7322,10 +7322,10 @@
         <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD52" t="n">
         <v>0</v>
@@ -7356,7 +7356,7 @@
         </is>
       </c>
       <c r="AL52" s="3" t="n">
-        <v>45870.79166666666</v>
+        <v>45870.91666666666</v>
       </c>
     </row>
     <row r="53">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7488,7 +7488,7 @@
         </is>
       </c>
       <c r="AL53" s="3" t="n">
-        <v>45870.79166666666</v>
+        <v>45870.95833333334</v>
       </c>
     </row>
     <row r="54">
@@ -7497,12 +7497,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7620,2118 +7620,6 @@
         </is>
       </c>
       <c r="AL54" s="3" t="n">
-        <v>45870.79166666666</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="n">
-        <v>45870</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Brazil Serie C</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>ABC</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Figueirense</t>
-        </is>
-      </c>
-      <c r="G55" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L55" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
-      <c r="R55" t="n">
-        <v>0</v>
-      </c>
-      <c r="S55" t="n">
-        <v>0</v>
-      </c>
-      <c r="T55" t="n">
-        <v>0</v>
-      </c>
-      <c r="U55" t="n">
-        <v>0</v>
-      </c>
-      <c r="V55" t="n">
-        <v>0</v>
-      </c>
-      <c r="W55" t="n">
-        <v>0</v>
-      </c>
-      <c r="X55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL55" s="3" t="n">
-        <v>45870.79166666666</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="n">
-        <v>45870</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Remo</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Ferroviária</t>
-        </is>
-      </c>
-      <c r="G56" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L56" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="M56" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="N56" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O56" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" t="n">
-        <v>0</v>
-      </c>
-      <c r="S56" t="n">
-        <v>0</v>
-      </c>
-      <c r="T56" t="n">
-        <v>0</v>
-      </c>
-      <c r="U56" t="n">
-        <v>0</v>
-      </c>
-      <c r="V56" t="n">
-        <v>0</v>
-      </c>
-      <c r="W56" t="n">
-        <v>0</v>
-      </c>
-      <c r="X56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL56" s="3" t="n">
-        <v>45870.79166666666</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="n">
-        <v>45870</v>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Brazil Serie C</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Maringá</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Floresta</t>
-        </is>
-      </c>
-      <c r="G57" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L57" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
-      <c r="R57" t="n">
-        <v>0</v>
-      </c>
-      <c r="S57" t="n">
-        <v>0</v>
-      </c>
-      <c r="T57" t="n">
-        <v>0</v>
-      </c>
-      <c r="U57" t="n">
-        <v>0</v>
-      </c>
-      <c r="V57" t="n">
-        <v>0</v>
-      </c>
-      <c r="W57" t="n">
-        <v>0</v>
-      </c>
-      <c r="X57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL57" s="3" t="n">
-        <v>45870.79166666666</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="n">
-        <v>45870</v>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Brazil Serie C</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Ypiranga Erechim</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Caxias</t>
-        </is>
-      </c>
-      <c r="G58" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" t="n">
-        <v>0</v>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L58" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
-      <c r="R58" t="n">
-        <v>0</v>
-      </c>
-      <c r="S58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T58" t="n">
-        <v>0</v>
-      </c>
-      <c r="U58" t="n">
-        <v>0</v>
-      </c>
-      <c r="V58" t="n">
-        <v>0</v>
-      </c>
-      <c r="W58" t="n">
-        <v>0</v>
-      </c>
-      <c r="X58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL58" s="3" t="n">
-        <v>45870.79166666666</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="n">
-        <v>45870</v>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Brazil Serie C</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Brusque</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Itabaiana</t>
-        </is>
-      </c>
-      <c r="G59" t="n">
-        <v>0</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" t="n">
-        <v>0</v>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L59" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" t="n">
-        <v>0</v>
-      </c>
-      <c r="O59" t="n">
-        <v>0</v>
-      </c>
-      <c r="P59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
-      <c r="R59" t="n">
-        <v>0</v>
-      </c>
-      <c r="S59" t="n">
-        <v>0</v>
-      </c>
-      <c r="T59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U59" t="n">
-        <v>0</v>
-      </c>
-      <c r="V59" t="n">
-        <v>0</v>
-      </c>
-      <c r="W59" t="n">
-        <v>0</v>
-      </c>
-      <c r="X59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL59" s="3" t="n">
-        <v>45870.79166666666</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="n">
-        <v>45870</v>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Brazil Serie C</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>CSA</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Botafogo PB</t>
-        </is>
-      </c>
-      <c r="G60" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" t="n">
-        <v>0</v>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L60" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" t="n">
-        <v>0</v>
-      </c>
-      <c r="O60" t="n">
-        <v>0</v>
-      </c>
-      <c r="P60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
-      <c r="R60" t="n">
-        <v>0</v>
-      </c>
-      <c r="S60" t="n">
-        <v>0</v>
-      </c>
-      <c r="T60" t="n">
-        <v>0</v>
-      </c>
-      <c r="U60" t="n">
-        <v>0</v>
-      </c>
-      <c r="V60" t="n">
-        <v>0</v>
-      </c>
-      <c r="W60" t="n">
-        <v>0</v>
-      </c>
-      <c r="X60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL60" s="3" t="n">
-        <v>45870.79166666666</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="n">
-        <v>45870</v>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Brazil Serie C</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Ituano</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Londrina</t>
-        </is>
-      </c>
-      <c r="G61" t="n">
-        <v>0</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" t="n">
-        <v>0</v>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L61" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" t="n">
-        <v>0</v>
-      </c>
-      <c r="N61" t="n">
-        <v>0</v>
-      </c>
-      <c r="O61" t="n">
-        <v>0</v>
-      </c>
-      <c r="P61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
-      <c r="R61" t="n">
-        <v>0</v>
-      </c>
-      <c r="S61" t="n">
-        <v>0</v>
-      </c>
-      <c r="T61" t="n">
-        <v>0</v>
-      </c>
-      <c r="U61" t="n">
-        <v>0</v>
-      </c>
-      <c r="V61" t="n">
-        <v>0</v>
-      </c>
-      <c r="W61" t="n">
-        <v>0</v>
-      </c>
-      <c r="X61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL61" s="3" t="n">
-        <v>45870.79166666666</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="n">
-        <v>45870</v>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Brazil Serie C</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Ponte Preta</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Guarani</t>
-        </is>
-      </c>
-      <c r="G62" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" t="n">
-        <v>0</v>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L62" t="n">
-        <v>0</v>
-      </c>
-      <c r="M62" t="n">
-        <v>0</v>
-      </c>
-      <c r="N62" t="n">
-        <v>0</v>
-      </c>
-      <c r="O62" t="n">
-        <v>0</v>
-      </c>
-      <c r="P62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
-      <c r="R62" t="n">
-        <v>0</v>
-      </c>
-      <c r="S62" t="n">
-        <v>0</v>
-      </c>
-      <c r="T62" t="n">
-        <v>0</v>
-      </c>
-      <c r="U62" t="n">
-        <v>0</v>
-      </c>
-      <c r="V62" t="n">
-        <v>0</v>
-      </c>
-      <c r="W62" t="n">
-        <v>0</v>
-      </c>
-      <c r="X62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL62" s="3" t="n">
-        <v>45870.79166666666</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="n">
-        <v>45870</v>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Chile Primera División</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Audax Italiano</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Palestino</t>
-        </is>
-      </c>
-      <c r="G63" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L63" t="n">
-        <v>0</v>
-      </c>
-      <c r="M63" t="n">
-        <v>0</v>
-      </c>
-      <c r="N63" t="n">
-        <v>0</v>
-      </c>
-      <c r="O63" t="n">
-        <v>0</v>
-      </c>
-      <c r="P63" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
-      <c r="R63" t="n">
-        <v>0</v>
-      </c>
-      <c r="S63" t="n">
-        <v>0</v>
-      </c>
-      <c r="T63" t="n">
-        <v>0</v>
-      </c>
-      <c r="U63" t="n">
-        <v>0</v>
-      </c>
-      <c r="V63" t="n">
-        <v>0</v>
-      </c>
-      <c r="W63" t="n">
-        <v>0</v>
-      </c>
-      <c r="X63" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y63" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL63" s="3" t="n">
-        <v>45870.83333333334</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="n">
-        <v>45870</v>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Chicago Red Stars</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Gotham FC</t>
-        </is>
-      </c>
-      <c r="G64" t="n">
-        <v>0</v>
-      </c>
-      <c r="H64" t="n">
-        <v>0</v>
-      </c>
-      <c r="I64" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" t="n">
-        <v>0</v>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L64" t="n">
-        <v>5</v>
-      </c>
-      <c r="M64" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="N64" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="O64" t="n">
-        <v>0</v>
-      </c>
-      <c r="P64" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
-      <c r="R64" t="n">
-        <v>0</v>
-      </c>
-      <c r="S64" t="n">
-        <v>0</v>
-      </c>
-      <c r="T64" t="n">
-        <v>0</v>
-      </c>
-      <c r="U64" t="n">
-        <v>0</v>
-      </c>
-      <c r="V64" t="n">
-        <v>0</v>
-      </c>
-      <c r="W64" t="n">
-        <v>0</v>
-      </c>
-      <c r="X64" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y64" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB64" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AC64" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AD64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL64" s="3" t="n">
-        <v>45870.875</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="n">
-        <v>45870</v>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Racing Louisville</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Kansas City</t>
-        </is>
-      </c>
-      <c r="G65" t="n">
-        <v>0</v>
-      </c>
-      <c r="H65" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" t="n">
-        <v>0</v>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L65" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="M65" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N65" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="O65" t="n">
-        <v>0</v>
-      </c>
-      <c r="P65" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
-      <c r="R65" t="n">
-        <v>0</v>
-      </c>
-      <c r="S65" t="n">
-        <v>0</v>
-      </c>
-      <c r="T65" t="n">
-        <v>0</v>
-      </c>
-      <c r="U65" t="n">
-        <v>0</v>
-      </c>
-      <c r="V65" t="n">
-        <v>0</v>
-      </c>
-      <c r="W65" t="n">
-        <v>0</v>
-      </c>
-      <c r="X65" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y65" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB65" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC65" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AD65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL65" s="3" t="n">
-        <v>45870.875</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="n">
-        <v>45870</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Tulsa Roughnecks</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Loudoun United</t>
-        </is>
-      </c>
-      <c r="G66" t="n">
-        <v>0</v>
-      </c>
-      <c r="H66" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" t="n">
-        <v>0</v>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L66" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="M66" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N66" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O66" t="n">
-        <v>0</v>
-      </c>
-      <c r="P66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
-      <c r="R66" t="n">
-        <v>0</v>
-      </c>
-      <c r="S66" t="n">
-        <v>0</v>
-      </c>
-      <c r="T66" t="n">
-        <v>0</v>
-      </c>
-      <c r="U66" t="n">
-        <v>0</v>
-      </c>
-      <c r="V66" t="n">
-        <v>0</v>
-      </c>
-      <c r="W66" t="n">
-        <v>0</v>
-      </c>
-      <c r="X66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB66" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AC66" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AD66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL66" s="3" t="n">
-        <v>45870.89583333334</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="n">
-        <v>45870</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Operário PR</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Criciúma</t>
-        </is>
-      </c>
-      <c r="G67" t="n">
-        <v>0</v>
-      </c>
-      <c r="H67" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" t="n">
-        <v>0</v>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L67" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="M67" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="N67" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="O67" t="n">
-        <v>0</v>
-      </c>
-      <c r="P67" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
-      <c r="R67" t="n">
-        <v>0</v>
-      </c>
-      <c r="S67" t="n">
-        <v>0</v>
-      </c>
-      <c r="T67" t="n">
-        <v>0</v>
-      </c>
-      <c r="U67" t="n">
-        <v>0</v>
-      </c>
-      <c r="V67" t="n">
-        <v>0</v>
-      </c>
-      <c r="W67" t="n">
-        <v>0</v>
-      </c>
-      <c r="X67" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y67" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z67" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AA67" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AB67" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC67" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL67" s="3" t="n">
-        <v>45870.89583333334</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="n">
-        <v>45870</v>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Colorado Springs</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Lexington</t>
-        </is>
-      </c>
-      <c r="G68" t="n">
-        <v>0</v>
-      </c>
-      <c r="H68" t="n">
-        <v>0</v>
-      </c>
-      <c r="I68" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" t="n">
-        <v>0</v>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L68" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="M68" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N68" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="O68" t="n">
-        <v>0</v>
-      </c>
-      <c r="P68" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
-      <c r="R68" t="n">
-        <v>0</v>
-      </c>
-      <c r="S68" t="n">
-        <v>0</v>
-      </c>
-      <c r="T68" t="n">
-        <v>0</v>
-      </c>
-      <c r="U68" t="n">
-        <v>0</v>
-      </c>
-      <c r="V68" t="n">
-        <v>0</v>
-      </c>
-      <c r="W68" t="n">
-        <v>0</v>
-      </c>
-      <c r="X68" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y68" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB68" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AC68" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AD68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL68" s="3" t="n">
-        <v>45870.91666666666</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="n">
-        <v>45870</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>USA MLS Next Pro</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Tacoma Defiance</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>LA Galaxy II</t>
-        </is>
-      </c>
-      <c r="G69" t="n">
-        <v>0</v>
-      </c>
-      <c r="H69" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" t="n">
-        <v>0</v>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L69" t="n">
-        <v>0</v>
-      </c>
-      <c r="M69" t="n">
-        <v>0</v>
-      </c>
-      <c r="N69" t="n">
-        <v>0</v>
-      </c>
-      <c r="O69" t="n">
-        <v>0</v>
-      </c>
-      <c r="P69" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
-      <c r="R69" t="n">
-        <v>0</v>
-      </c>
-      <c r="S69" t="n">
-        <v>0</v>
-      </c>
-      <c r="T69" t="n">
-        <v>0</v>
-      </c>
-      <c r="U69" t="n">
-        <v>0</v>
-      </c>
-      <c r="V69" t="n">
-        <v>0</v>
-      </c>
-      <c r="W69" t="n">
-        <v>0</v>
-      </c>
-      <c r="X69" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y69" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL69" s="3" t="n">
-        <v>45870.95833333334</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="n">
-        <v>45870</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Seattle Reign</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Angel City</t>
-        </is>
-      </c>
-      <c r="G70" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L70" t="n">
-        <v>0</v>
-      </c>
-      <c r="M70" t="n">
-        <v>0</v>
-      </c>
-      <c r="N70" t="n">
-        <v>0</v>
-      </c>
-      <c r="O70" t="n">
-        <v>0</v>
-      </c>
-      <c r="P70" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
-      <c r="R70" t="n">
-        <v>0</v>
-      </c>
-      <c r="S70" t="n">
-        <v>0</v>
-      </c>
-      <c r="T70" t="n">
-        <v>0</v>
-      </c>
-      <c r="U70" t="n">
-        <v>0</v>
-      </c>
-      <c r="V70" t="n">
-        <v>0</v>
-      </c>
-      <c r="W70" t="n">
-        <v>0</v>
-      </c>
-      <c r="X70" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y70" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL70" s="3" t="n">
         <v>45870.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-08-01.xlsx
+++ b/jogos_2025-08-01.xlsx
@@ -722,10 +722,10 @@
         <v>2.31</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AD2" t="n">
         <v>4.35</v>
@@ -806,13 +806,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.85</v>
+        <v>2.77</v>
       </c>
       <c r="M3" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="N3" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="O3" t="n">
         <v>2.08</v>
@@ -824,49 +824,49 @@
         <v>1.72</v>
       </c>
       <c r="R3" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S3" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="T3" t="n">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="U3" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="V3" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="W3" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y3" t="n">
-        <v>14</v>
+        <v>13.8</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.75</v>
+        <v>5.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.39</v>
+        <v>2.2</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AG3" t="n">
         <v>2.5</v>
@@ -875,7 +875,7 @@
         <v>3.7</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>11.3</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>10.9</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Smorgon</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dinamo Minsk</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Rukh Vynnyky</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mariehamn</t>
+          <t>SK Poltava</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="M8" t="n">
-        <v>4</v>
+        <v>3.41</v>
       </c>
       <c r="N8" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="O8" t="n">
         <v>1.44</v>
       </c>
       <c r="P8" t="n">
-        <v>17</v>
+        <v>6.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.95</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="S8" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="T8" t="n">
-        <v>2.38</v>
+        <v>3.75</v>
       </c>
       <c r="U8" t="n">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="V8" t="n">
-        <v>5.5</v>
+        <v>8.5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AI8" t="n">
         <v>1.01</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1.11</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1557,27 +1557,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rukh Vynnyky</t>
+          <t>BATE</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SK Poltava</t>
+          <t>Vitebsk</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.65</v>
+        <v>2.17</v>
       </c>
       <c r="M9" t="n">
-        <v>3.41</v>
+        <v>3.28</v>
       </c>
       <c r="N9" t="n">
-        <v>5.9</v>
+        <v>3.46</v>
       </c>
       <c r="O9" t="n">
-        <v>1.44</v>
+        <v>1.77</v>
       </c>
       <c r="P9" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>4</v>
+        <v>2.32</v>
       </c>
       <c r="R9" t="n">
-        <v>1.57</v>
+        <v>1.39</v>
       </c>
       <c r="S9" t="n">
-        <v>2.25</v>
+        <v>2.67</v>
       </c>
       <c r="T9" t="n">
-        <v>3.75</v>
+        <v>2.93</v>
       </c>
       <c r="U9" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="V9" t="n">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.52</v>
+        <v>1.28</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.53</v>
+        <v>3.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.63</v>
+        <v>2.02</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>5.1</v>
+        <v>3.48</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.63</v>
+        <v>1.78</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.44</v>
+        <v>1.93</v>
       </c>
       <c r="AH9" t="n">
-        <v>8.5</v>
+        <v>7.2</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="AL9" s="3" t="n">
-        <v>45870.5</v>
+        <v>45870.51041666666</v>
       </c>
     </row>
     <row r="10">
@@ -1689,27 +1689,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BATE</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitebsk</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="M10" t="n">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="N10" t="n">
-        <v>3.46</v>
+        <v>2.58</v>
       </c>
       <c r="O10" t="n">
-        <v>1.77</v>
+        <v>1.93</v>
       </c>
       <c r="P10" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.32</v>
+        <v>2.05</v>
       </c>
       <c r="R10" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="S10" t="n">
-        <v>2.67</v>
+        <v>3.1</v>
       </c>
       <c r="T10" t="n">
-        <v>2.93</v>
+        <v>2.4</v>
       </c>
       <c r="U10" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="V10" t="n">
-        <v>8.199999999999999</v>
+        <v>5.6</v>
       </c>
       <c r="W10" t="n">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>8.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.02</v>
+        <v>1.61</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.48</v>
+        <v>2.6</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.24</v>
+        <v>1.45</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.78</v>
+        <v>1.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>7.2</v>
+        <v>4.8</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="AL10" s="3" t="n">
-        <v>45870.51041666666</v>
+        <v>45870.52083333334</v>
       </c>
     </row>
     <row r="11">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4</v>
+        <v>3.21</v>
       </c>
       <c r="N11" t="n">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="O11" t="n">
-        <v>1.93</v>
+        <v>2.07</v>
       </c>
       <c r="P11" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="R11" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="S11" t="n">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="T11" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="U11" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="V11" t="n">
         <v>5.6</v>
       </c>
       <c r="W11" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AA11" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AH11" t="n">
-        <v>4.8</v>
+        <v>4.39</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="AL11" s="3" t="n">
-        <v>45870.52083333334</v>
+        <v>45870.54166666666</v>
       </c>
     </row>
     <row r="12">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.42</v>
+        <v>2.13</v>
       </c>
       <c r="M12" t="n">
-        <v>4.2</v>
+        <v>3.17</v>
       </c>
       <c r="N12" t="n">
-        <v>5.6</v>
+        <v>2.99</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.68</v>
+        <v>1.89</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.05</v>
+        <v>1.81</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N13" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P13" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="T13" t="n">
         <v>2.47</v>
       </c>
-      <c r="M13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N13" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AB13" t="n">
         <v>1.95</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.45</v>
+        <v>3.62</v>
       </c>
       <c r="M14" t="n">
         <v>3.7</v>
       </c>
       <c r="N14" t="n">
-        <v>6.3</v>
+        <v>1.75</v>
       </c>
       <c r="O14" t="n">
-        <v>1.28</v>
+        <v>2.63</v>
       </c>
       <c r="P14" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.9</v>
+        <v>1.5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S14" t="n">
-        <v>3.22</v>
+        <v>3.5</v>
       </c>
       <c r="T14" t="n">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="U14" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="V14" t="n">
-        <v>5.7</v>
+        <v>4.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.02</v>
+        <v>1.67</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.71</v>
+        <v>2.1</v>
       </c>
       <c r="AH14" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2390,22 +2390,22 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="M15" t="n">
-        <v>3.95</v>
+        <v>3.82</v>
       </c>
       <c r="N15" t="n">
-        <v>3.81</v>
+        <v>3.57</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>19.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="R15" t="n">
         <v>1.25</v>
@@ -2420,16 +2420,16 @@
         <v>1.6</v>
       </c>
       <c r="V15" t="n">
-        <v>4.4</v>
+        <v>4.85</v>
       </c>
       <c r="W15" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X15" t="n">
         <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>17</v>
+        <v>14.7</v>
       </c>
       <c r="Z15" t="n">
         <v>1.15</v>
@@ -2441,25 +2441,25 @@
         <v>1.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.49</v>
+        <v>2.44</v>
       </c>
       <c r="AH15" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,40 +2522,40 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.81</v>
+        <v>2.54</v>
       </c>
       <c r="M16" t="n">
-        <v>3.33</v>
+        <v>3.21</v>
       </c>
       <c r="N16" t="n">
-        <v>2.2</v>
+        <v>2.41</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>13.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R16" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S16" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="T16" t="n">
         <v>2.55</v>
       </c>
       <c r="U16" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="V16" t="n">
-        <v>6.25</v>
+        <v>6.55</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X16" t="n">
         <v>1.05</v>
@@ -2564,34 +2564,34 @@
         <v>11</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AC16" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="AH16" t="n">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,76 +2654,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.13</v>
+        <v>2.6</v>
       </c>
       <c r="M17" t="n">
-        <v>3.17</v>
+        <v>3.02</v>
       </c>
       <c r="N17" t="n">
-        <v>2.99</v>
+        <v>2.48</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,76 +2786,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.43</v>
+        <v>1.42</v>
       </c>
       <c r="M18" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="N18" t="n">
-        <v>2.51</v>
+        <v>5.6</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.5</v>
+        <v>7.7</v>
       </c>
       <c r="M19" t="n">
-        <v>3.25</v>
+        <v>5.2</v>
       </c>
       <c r="N19" t="n">
-        <v>2.46</v>
+        <v>1.25</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="R19" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="S19" t="n">
-        <v>2.95</v>
+        <v>3.6</v>
       </c>
       <c r="T19" t="n">
-        <v>2.65</v>
+        <v>2.15</v>
       </c>
       <c r="U19" t="n">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="V19" t="n">
-        <v>6.5</v>
+        <v>4.75</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X19" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>10</v>
+        <v>16.5</v>
       </c>
       <c r="Z19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AI19" t="n">
         <v>1.26</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>1.13</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,40 +3050,40 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>7.7</v>
+        <v>3.02</v>
       </c>
       <c r="M20" t="n">
-        <v>5.2</v>
+        <v>3.45</v>
       </c>
       <c r="N20" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -3098,22 +3098,22 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH20" t="n">
         <v>0</v>
@@ -3141,27 +3141,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,76 +3182,76 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.62</v>
+        <v>1.2</v>
       </c>
       <c r="M21" t="n">
-        <v>3.7</v>
+        <v>5.4</v>
       </c>
       <c r="N21" t="n">
-        <v>1.75</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>18.25</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         </is>
       </c>
       <c r="AL21" s="3" t="n">
-        <v>45870.54166666666</v>
+        <v>45870.5625</v>
       </c>
     </row>
     <row r="22">
@@ -3273,27 +3273,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,76 +3314,76 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="M22" t="n">
-        <v>5.4</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>9.800000000000001</v>
+        <v>2.7</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.9</v>
+        <v>1.45</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="AL22" s="3" t="n">
-        <v>45870.5625</v>
+        <v>45870.58333333334</v>
       </c>
     </row>
     <row r="23">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,76 +3578,76 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
@@ -3660,7 +3660,7 @@
         </is>
       </c>
       <c r="AL24" s="3" t="n">
-        <v>45870.58333333334</v>
+        <v>45870.60416666666</v>
       </c>
     </row>
     <row r="25">
@@ -3669,12 +3669,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,76 +3710,76 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         </is>
       </c>
       <c r="AL25" s="3" t="n">
-        <v>45870.60416666666</v>
+        <v>45870.61458333334</v>
       </c>
     </row>
     <row r="26">
@@ -3801,12 +3801,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,76 +3842,76 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="AL26" s="3" t="n">
-        <v>45870.61458333334</v>
+        <v>45870.625</v>
       </c>
     </row>
     <row r="27">
@@ -3983,43 +3983,43 @@
         <v>2.11</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB27" t="n">
         <v>1.61</v>
@@ -4028,22 +4028,22 @@
         <v>2.05</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,76 +4106,76 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>18.25</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
@@ -4197,12 +4197,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,76 +4238,76 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.81</v>
+        <v>1.39</v>
       </c>
       <c r="M29" t="n">
-        <v>3.71</v>
+        <v>3.82</v>
       </c>
       <c r="N29" t="n">
-        <v>3.35</v>
+        <v>7.2</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.2</v>
+        <v>2.93</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         </is>
       </c>
       <c r="AL29" s="3" t="n">
-        <v>45870.625</v>
+        <v>45870.63541666666</v>
       </c>
     </row>
     <row r="30">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,76 +4370,76 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.52</v>
+        <v>2.99</v>
       </c>
       <c r="M30" t="n">
-        <v>3.8</v>
+        <v>3.21</v>
       </c>
       <c r="N30" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="O30" t="n">
+        <v>2</v>
+      </c>
+      <c r="P30" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V30" t="n">
         <v>5.5</v>
       </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AC30" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="AL30" s="3" t="n">
-        <v>45870.63541666666</v>
+        <v>45870.64583333334</v>
       </c>
     </row>
     <row r="31">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,76 +4502,76 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.99</v>
+        <v>2.02</v>
       </c>
       <c r="M31" t="n">
-        <v>3.21</v>
+        <v>3.13</v>
       </c>
       <c r="N31" t="n">
-        <v>2.36</v>
+        <v>3.27</v>
       </c>
       <c r="O31" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="P31" t="n">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="R31" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="S31" t="n">
-        <v>3.5</v>
+        <v>2.93</v>
       </c>
       <c r="T31" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="U31" t="n">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="V31" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="W31" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X31" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y31" t="n">
         <v>10</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AA31" t="n">
-        <v>4.75</v>
+        <v>3.34</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.53</v>
+        <v>1.95</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.35</v>
+        <v>1.75</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.25</v>
+        <v>3.19</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.53</v>
+        <v>1.32</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AH31" t="n">
-        <v>4.2</v>
+        <v>6.5</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -4775,67 +4775,67 @@
         <v>2.9</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -4989,12 +4989,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,76 +5030,76 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.84</v>
+        <v>4</v>
       </c>
       <c r="M35" t="n">
-        <v>3.29</v>
+        <v>3.72</v>
       </c>
       <c r="N35" t="n">
-        <v>3.65</v>
+        <v>1.66</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="AL35" s="3" t="n">
-        <v>45870.64583333334</v>
+        <v>45870.65625</v>
       </c>
     </row>
     <row r="36">
@@ -5126,22 +5126,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,76 +5162,76 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.55</v>
+        <v>2.12</v>
       </c>
       <c r="M36" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="N36" t="n">
-        <v>1.89</v>
+        <v>2.8</v>
       </c>
       <c r="O36" t="n">
-        <v>2.38</v>
+        <v>1.77</v>
       </c>
       <c r="P36" t="n">
-        <v>12</v>
+        <v>13.75</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.67</v>
+        <v>2.09</v>
       </c>
       <c r="R36" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="S36" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T36" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="U36" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="V36" t="n">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="W36" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y36" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AA36" t="n">
-        <v>3.42</v>
+        <v>3.8</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AD36" t="n">
-        <v>3.08</v>
+        <v>2.62</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.8</v>
+        <v>1.59</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="AH36" t="n">
-        <v>6.15</v>
+        <v>4.5</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,76 +5294,76 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.12</v>
+        <v>1.39</v>
       </c>
       <c r="M37" t="n">
-        <v>3.45</v>
+        <v>4.33</v>
       </c>
       <c r="N37" t="n">
-        <v>2.8</v>
+        <v>5.8</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
@@ -5390,22 +5390,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,76 +5426,76 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="M38" t="n">
-        <v>3.41</v>
+        <v>3.7</v>
       </c>
       <c r="N38" t="n">
-        <v>1.72</v>
+        <v>1.89</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,76 +5558,76 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="M39" t="n">
-        <v>4.33</v>
+        <v>3.86</v>
       </c>
       <c r="N39" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.15</v>
+        <v>1.79</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,76 +5690,76 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.94</v>
+        <v>2.23</v>
       </c>
       <c r="M40" t="n">
-        <v>3.45</v>
+        <v>3.31</v>
       </c>
       <c r="N40" t="n">
-        <v>3.16</v>
+        <v>2.7</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P40" t="n">
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AC40" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,76 +5822,76 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.23</v>
+        <v>1.94</v>
       </c>
       <c r="M41" t="n">
-        <v>3.31</v>
+        <v>3.45</v>
       </c>
       <c r="N41" t="n">
-        <v>2.7</v>
+        <v>3.16</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI41" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,73 +5954,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.48</v>
+        <v>2.69</v>
       </c>
       <c r="M42" t="n">
-        <v>3.86</v>
+        <v>3.18</v>
       </c>
       <c r="N42" t="n">
-        <v>5.4</v>
+        <v>2.31</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="R42" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="S42" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="T42" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="U42" t="n">
         <v>1.39</v>
       </c>
       <c r="V42" t="n">
-        <v>7</v>
+        <v>6.55</v>
       </c>
       <c r="W42" t="n">
         <v>1.08</v>
       </c>
       <c r="X42" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y42" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="Z42" t="n">
         <v>1.27</v>
       </c>
       <c r="AA42" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AD42" t="n">
         <v>3.3</v>
       </c>
-      <c r="AB42" t="n">
+      <c r="AE42" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG42" t="n">
         <v>1.91</v>
       </c>
-      <c r="AC42" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>1.68</v>
-      </c>
       <c r="AH42" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AI42" t="n">
         <v>1.09</v>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,76 +6086,76 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.69</v>
+        <v>4.1</v>
       </c>
       <c r="M43" t="n">
-        <v>3.18</v>
+        <v>3.41</v>
       </c>
       <c r="N43" t="n">
-        <v>2.31</v>
+        <v>1.72</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="R43" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S43" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="T43" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="U43" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="V43" t="n">
-        <v>6.55</v>
+        <v>7.5</v>
       </c>
       <c r="W43" t="n">
         <v>1.08</v>
       </c>
       <c r="X43" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y43" t="n">
-        <v>7.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AA43" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AD43" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AH43" t="n">
-        <v>5.95</v>
+        <v>5.9</v>
       </c>
       <c r="AI43" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
@@ -6177,12 +6177,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6218,76 +6218,76 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>4</v>
+        <v>1.54</v>
       </c>
       <c r="M44" t="n">
-        <v>3.72</v>
+        <v>3.8</v>
       </c>
       <c r="N44" t="n">
-        <v>1.66</v>
+        <v>4.8</v>
       </c>
       <c r="O44" t="n">
-        <v>2.55</v>
+        <v>1.4</v>
       </c>
       <c r="P44" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.57</v>
+        <v>3</v>
       </c>
       <c r="R44" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="S44" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="T44" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="U44" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="V44" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="W44" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X44" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y44" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AA44" t="n">
-        <v>4.75</v>
+        <v>3.9</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.3</v>
+        <v>1.93</v>
       </c>
       <c r="AD44" t="n">
-        <v>2.36</v>
+        <v>2.9</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.59</v>
+        <v>1.37</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="AG44" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AH44" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="AI44" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         </is>
       </c>
       <c r="AL44" s="3" t="n">
-        <v>45870.65625</v>
+        <v>45870.66666666666</v>
       </c>
     </row>
     <row r="45">
@@ -6314,22 +6314,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,76 +6350,76 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.54</v>
+        <v>2.16</v>
       </c>
       <c r="M45" t="n">
-        <v>3.8</v>
+        <v>3.17</v>
       </c>
       <c r="N45" t="n">
-        <v>4.8</v>
+        <v>2.93</v>
       </c>
       <c r="O45" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="S45" t="n">
-        <v>3.25</v>
+        <v>2.35</v>
       </c>
       <c r="T45" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="U45" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="V45" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X45" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y45" t="n">
         <v>6.5</v>
       </c>
-      <c r="W45" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X45" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>10</v>
-      </c>
       <c r="Z45" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AA45" t="n">
-        <v>3.9</v>
+        <v>2.65</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.77</v>
+        <v>2.3</v>
       </c>
       <c r="AC45" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF45" t="n">
         <v>1.93</v>
       </c>
-      <c r="AD45" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AG45" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AH45" t="n">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="AI45" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
@@ -6491,43 +6491,43 @@
         <v>4.1</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AB46" t="n">
         <v>2.3</v>
@@ -6536,22 +6536,22 @@
         <v>1.5</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AI46" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6746,13 +6746,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="M48" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="N48" t="n">
-        <v>1.84</v>
+        <v>1.52</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6764,58 +6764,58 @@
         <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AB48" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF48" t="n">
         <v>1.91</v>
       </c>
-      <c r="AC48" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>0</v>
-      </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI48" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6878,13 +6878,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="M49" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="N49" t="n">
-        <v>1.52</v>
+        <v>1.84</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6896,58 +6896,58 @@
         <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AI49" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7010,76 +7010,76 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="M50" t="n">
-        <v>3.11</v>
+        <v>3.5</v>
       </c>
       <c r="N50" t="n">
-        <v>3.78</v>
+        <v>3.6</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="P50" t="n">
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.48</v>
+        <v>1.22</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.37</v>
+        <v>3.7</v>
       </c>
       <c r="AB50" t="n">
-        <v>2.4</v>
+        <v>1.84</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.5</v>
+        <v>1.92</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AI50" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7142,76 +7142,76 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="M51" t="n">
-        <v>3.5</v>
+        <v>3.11</v>
       </c>
       <c r="N51" t="n">
-        <v>3.6</v>
+        <v>3.78</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.84</v>
+        <v>2.4</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.92</v>
+        <v>1.5</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH51" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AI51" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
@@ -7283,43 +7283,43 @@
         <v>4.7</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AB52" t="n">
         <v>1.86</v>
@@ -7328,22 +7328,22 @@
         <v>1.9</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH52" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AI52" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
@@ -7538,13 +7538,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7556,58 +7556,58 @@
         <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH54" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AI54" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AJ54" t="inlineStr">
         <is>

--- a/jogos_2025-08-01.xlsx
+++ b/jogos_2025-08-01.xlsx
@@ -806,13 +806,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.77</v>
+        <v>2.87</v>
       </c>
       <c r="M3" t="n">
-        <v>3.5</v>
+        <v>3.68</v>
       </c>
       <c r="N3" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="O3" t="n">
         <v>2.08</v>
@@ -827,13 +827,13 @@
         <v>1.25</v>
       </c>
       <c r="S3" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="T3" t="n">
         <v>2.25</v>
       </c>
       <c r="U3" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="V3" t="n">
         <v>5.2</v>
@@ -842,28 +842,28 @@
         <v>1.11</v>
       </c>
       <c r="X3" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>13.8</v>
+        <v>15</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.2</v>
+        <v>5.06</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="AD3" t="n">
         <v>2.2</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AF3" t="n">
         <v>1.5</v>
@@ -875,7 +875,7 @@
         <v>3.7</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -902,22 +902,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.26</v>
+        <v>1.52</v>
       </c>
       <c r="M4" t="n">
-        <v>4.6</v>
+        <v>4.36</v>
       </c>
       <c r="N4" t="n">
-        <v>11.3</v>
+        <v>5.11</v>
       </c>
       <c r="O4" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.75</v>
+        <v>2.95</v>
       </c>
       <c r="R4" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="S4" t="n">
         <v>3.3</v>
       </c>
       <c r="T4" t="n">
-        <v>2.35</v>
+        <v>2.42</v>
       </c>
       <c r="U4" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="V4" t="n">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="W4" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X4" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y4" t="n">
-        <v>10.9</v>
+        <v>9</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.25</v>
+        <v>1.73</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AH4" t="n">
-        <v>4.85</v>
+        <v>4.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mariehamn</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1166,22 +1166,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,76 +1202,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>9.77</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>11.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>10.9</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.3</v>
+        <v>1.42</v>
       </c>
       <c r="M11" t="n">
-        <v>3.21</v>
+        <v>4.2</v>
       </c>
       <c r="N11" t="n">
-        <v>2.68</v>
+        <v>5.6</v>
       </c>
       <c r="O11" t="n">
-        <v>2.07</v>
+        <v>1.44</v>
       </c>
       <c r="P11" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V11" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y11" t="n">
         <v>13</v>
       </c>
-      <c r="Q11" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V11" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>11.5</v>
-      </c>
       <c r="Z11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AI11" t="n">
         <v>1.18</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>1.16</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.13</v>
+        <v>1.75</v>
       </c>
       <c r="M12" t="n">
-        <v>3.17</v>
+        <v>3.7</v>
       </c>
       <c r="N12" t="n">
-        <v>2.99</v>
+        <v>3.6</v>
       </c>
       <c r="O12" t="n">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="P12" t="n">
-        <v>8.5</v>
+        <v>19.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="S12" t="n">
-        <v>2.99</v>
+        <v>3.6</v>
       </c>
       <c r="T12" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="U12" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="V12" t="n">
-        <v>6.5</v>
+        <v>4.8</v>
       </c>
       <c r="W12" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="X12" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>9</v>
+        <v>14.7</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.15</v>
+        <v>4.75</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.89</v>
+        <v>1.53</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.81</v>
+        <v>2.37</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.35</v>
+        <v>2.3</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.24</v>
+        <v>1.57</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.77</v>
+        <v>1.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.95</v>
+        <v>2.49</v>
       </c>
       <c r="AH12" t="n">
-        <v>6.25</v>
+        <v>3.74</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.45</v>
+        <v>2.62</v>
       </c>
       <c r="M13" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="N13" t="n">
-        <v>6.3</v>
+        <v>2.2</v>
       </c>
       <c r="O13" t="n">
-        <v>1.28</v>
+        <v>2.07</v>
       </c>
       <c r="P13" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.9</v>
+        <v>1.84</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S13" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="T13" t="n">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="U13" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="V13" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="W13" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X13" t="n">
         <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>8.9</v>
+        <v>11</v>
       </c>
       <c r="Z13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="AI13" t="n">
         <v>1.17</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1.12</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.62</v>
+        <v>2.1</v>
       </c>
       <c r="M14" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="N14" t="n">
-        <v>1.75</v>
+        <v>3.1</v>
       </c>
       <c r="O14" t="n">
-        <v>2.63</v>
+        <v>1.8</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
       <c r="R14" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="T14" t="n">
-        <v>2.25</v>
+        <v>3.01</v>
       </c>
       <c r="U14" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="V14" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.53</v>
+        <v>2.06</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.73</v>
+        <v>1.45</v>
       </c>
       <c r="M15" t="n">
-        <v>3.82</v>
+        <v>3.7</v>
       </c>
       <c r="N15" t="n">
-        <v>3.57</v>
+        <v>6.3</v>
       </c>
       <c r="O15" t="n">
-        <v>1.58</v>
+        <v>1.28</v>
       </c>
       <c r="P15" t="n">
-        <v>19.25</v>
+        <v>15</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.39</v>
+        <v>3.9</v>
       </c>
       <c r="R15" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S15" t="n">
-        <v>3.6</v>
+        <v>3.22</v>
       </c>
       <c r="T15" t="n">
-        <v>2.2</v>
+        <v>2.47</v>
       </c>
       <c r="U15" t="n">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="V15" t="n">
-        <v>4.85</v>
+        <v>5.7</v>
       </c>
       <c r="W15" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>14.7</v>
+        <v>8.9</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AA15" t="n">
-        <v>4.9</v>
+        <v>3.98</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.5</v>
+        <v>1.95</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.4</v>
+        <v>1.75</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.55</v>
+        <v>1.39</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.51</v>
+        <v>2.02</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.44</v>
+        <v>1.71</v>
       </c>
       <c r="AH15" t="n">
-        <v>3.8</v>
+        <v>4.75</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2522,10 +2522,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.54</v>
+        <v>2.63</v>
       </c>
       <c r="M16" t="n">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
         <v>2.41</v>
@@ -2540,16 +2540,16 @@
         <v>1.91</v>
       </c>
       <c r="R16" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S16" t="n">
-        <v>3.04</v>
+        <v>2.95</v>
       </c>
       <c r="T16" t="n">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="U16" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="V16" t="n">
         <v>6.55</v>
@@ -2558,10 +2558,10 @@
         <v>1.05</v>
       </c>
       <c r="X16" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>11</v>
+        <v>8.5</v>
       </c>
       <c r="Z16" t="n">
         <v>1.22</v>
@@ -2570,13 +2570,13 @@
         <v>3.6</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="AE16" t="n">
         <v>1.32</v>
@@ -2585,13 +2585,13 @@
         <v>1.65</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH16" t="n">
-        <v>5.75</v>
+        <v>5.65</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,76 +2654,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.6</v>
+        <v>6.5</v>
       </c>
       <c r="M17" t="n">
-        <v>3.02</v>
+        <v>5.2</v>
       </c>
       <c r="N17" t="n">
-        <v>2.48</v>
+        <v>1.4</v>
       </c>
       <c r="O17" t="n">
+        <v>3</v>
+      </c>
+      <c r="P17" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V17" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG17" t="n">
         <v>2.1</v>
       </c>
-      <c r="P17" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V17" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.82</v>
-      </c>
       <c r="AH17" t="n">
-        <v>7</v>
+        <v>3.72</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,76 +2786,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.42</v>
+        <v>2.62</v>
       </c>
       <c r="M18" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="N18" t="n">
-        <v>5.6</v>
+        <v>2.55</v>
       </c>
       <c r="O18" t="n">
-        <v>1.44</v>
+        <v>1.83</v>
       </c>
       <c r="P18" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.75</v>
+        <v>2</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S18" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="T18" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="U18" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="V18" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG18" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AH18" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P19" t="n">
         <v>7.7</v>
       </c>
-      <c r="M19" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="N19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="O19" t="n">
-        <v>3</v>
-      </c>
-      <c r="P19" t="n">
-        <v>17</v>
-      </c>
       <c r="Q19" t="n">
-        <v>1.36</v>
+        <v>2.01</v>
       </c>
       <c r="R19" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S19" t="n">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="T19" t="n">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="U19" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="V19" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X19" t="n">
         <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>16.5</v>
+        <v>11</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AA19" t="n">
-        <v>5.3</v>
+        <v>2.87</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.85</v>
+        <v>1.42</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.72</v>
+        <v>4.33</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,40 +3050,40 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.02</v>
+        <v>3.62</v>
       </c>
       <c r="M20" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="N20" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="O20" t="n">
-        <v>1.83</v>
+        <v>2.63</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="R20" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="S20" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="T20" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="U20" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="V20" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3110,10 +3110,10 @@
         <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AH20" t="n">
         <v>0</v>
@@ -3278,22 +3278,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,76 +3314,76 @@
         </is>
       </c>
       <c r="L22" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="P22" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q22" t="n">
         <v>2.2</v>
       </c>
-      <c r="M22" t="n">
+      <c r="R22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V22" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA22" t="n">
         <v>3.4</v>
       </c>
-      <c r="N22" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="P22" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="R22" t="n">
+      <c r="AB22" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AE22" t="n">
         <v>1.33</v>
       </c>
-      <c r="S22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V22" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB22" t="n">
+      <c r="AF22" t="n">
         <v>1.67</v>
       </c>
-      <c r="AC22" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AG22" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AH22" t="n">
-        <v>4.75</v>
+        <v>6.5</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -3410,22 +3410,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,76 +3446,76 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="M23" t="n">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="O23" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="P23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="R23" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S23" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="T23" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="U23" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V23" t="n">
-        <v>7.6</v>
+        <v>5.75</v>
       </c>
       <c r="W23" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X23" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.82</v>
+        <v>2.15</v>
       </c>
       <c r="AD23" t="n">
-        <v>3.35</v>
+        <v>2.7</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AH23" t="n">
-        <v>6.5</v>
+        <v>4.75</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -3710,19 +3710,19 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="M25" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="N25" t="n">
-        <v>6</v>
+        <v>6.79</v>
       </c>
       <c r="O25" t="n">
         <v>1.44</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="Q25" t="n">
         <v>3.1</v>
@@ -3749,7 +3749,7 @@
         <v>1.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="Z25" t="n">
         <v>1.22</v>
@@ -3758,7 +3758,7 @@
         <v>3.8</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC25" t="n">
         <v>2</v>
@@ -3767,10 +3767,10 @@
         <v>2.8</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AG25" t="n">
         <v>1.8</v>
@@ -3779,7 +3779,7 @@
         <v>5.2</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,76 +3842,76 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.73</v>
+        <v>2.75</v>
       </c>
       <c r="M26" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="N26" t="n">
-        <v>4.9</v>
+        <v>2.48</v>
       </c>
       <c r="O26" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="P26" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.75</v>
+        <v>1.83</v>
       </c>
       <c r="R26" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="S26" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="T26" t="n">
-        <v>2.85</v>
+        <v>2.4</v>
       </c>
       <c r="U26" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="V26" t="n">
-        <v>6.95</v>
+        <v>5.5</v>
       </c>
       <c r="W26" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X26" t="n">
         <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AD26" t="n">
-        <v>3.2</v>
+        <v>2.62</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.89</v>
+        <v>1.57</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.83</v>
+        <v>2.37</v>
       </c>
       <c r="AH26" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,76 +3974,76 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.85</v>
+        <v>2.04</v>
       </c>
       <c r="M27" t="n">
-        <v>3.4</v>
+        <v>3.78</v>
       </c>
       <c r="N27" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="P27" t="n">
+        <v>18.25</v>
+      </c>
+      <c r="Q27" t="n">
         <v>2.11</v>
       </c>
-      <c r="O27" t="n">
-        <v>2</v>
-      </c>
-      <c r="P27" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1.83</v>
-      </c>
       <c r="R27" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S27" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="T27" t="n">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="U27" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="V27" t="n">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="W27" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X27" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>12.5</v>
+        <v>18</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AA27" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.61</v>
+        <v>1.42</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="AD27" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AG27" t="n">
         <v>2.67</v>
       </c>
-      <c r="AE27" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>2.37</v>
-      </c>
       <c r="AH27" t="n">
-        <v>4.6</v>
+        <v>3.45</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,76 +4106,76 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="M28" t="n">
-        <v>3.71</v>
+        <v>3.5</v>
       </c>
       <c r="N28" t="n">
-        <v>3.35</v>
+        <v>4.6</v>
       </c>
       <c r="O28" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="P28" t="n">
-        <v>18.25</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.11</v>
+        <v>2.75</v>
       </c>
       <c r="R28" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="S28" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="T28" t="n">
-        <v>2.1</v>
+        <v>2.85</v>
       </c>
       <c r="U28" t="n">
-        <v>1.65</v>
+        <v>1.37</v>
       </c>
       <c r="V28" t="n">
-        <v>4.33</v>
+        <v>6.95</v>
       </c>
       <c r="W28" t="n">
-        <v>1.18</v>
+        <v>1.04</v>
       </c>
       <c r="X28" t="n">
         <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.09</v>
+        <v>1.32</v>
       </c>
       <c r="AA28" t="n">
-        <v>5.5</v>
+        <v>3.2</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.45</v>
+        <v>1.9</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.55</v>
+        <v>1.8</v>
       </c>
       <c r="AD28" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.65</v>
+        <v>1.29</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.42</v>
+        <v>1.9</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.77</v>
+        <v>1.8</v>
       </c>
       <c r="AH28" t="n">
-        <v>3.3</v>
+        <v>6</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.29</v>
+        <v>1.05</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
@@ -4238,13 +4238,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M29" t="n">
-        <v>3.82</v>
+        <v>4.2</v>
       </c>
       <c r="N29" t="n">
-        <v>7.2</v>
+        <v>8.1</v>
       </c>
       <c r="O29" t="n">
         <v>1.36</v>
@@ -4259,16 +4259,16 @@
         <v>1.33</v>
       </c>
       <c r="S29" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="T29" t="n">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="U29" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V29" t="n">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="W29" t="n">
         <v>1.07</v>
@@ -4280,16 +4280,16 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AA29" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.93</v>
+        <v>1.78</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.77</v>
+        <v>1.97</v>
       </c>
       <c r="AD29" t="n">
         <v>2.93</v>
@@ -4301,13 +4301,13 @@
         <v>2</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AH29" t="n">
         <v>5.3</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,76 +4370,76 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.99</v>
+        <v>2</v>
       </c>
       <c r="M30" t="n">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="N30" t="n">
-        <v>2.36</v>
+        <v>3.32</v>
       </c>
       <c r="O30" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P30" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V30" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AG30" t="n">
         <v>2</v>
       </c>
-      <c r="P30" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S30" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V30" t="n">
+      <c r="AH30" t="n">
         <v>5.5</v>
       </c>
-      <c r="W30" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AI30" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,76 +4502,76 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.02</v>
+        <v>2.52</v>
       </c>
       <c r="M31" t="n">
-        <v>3.13</v>
+        <v>3.28</v>
       </c>
       <c r="N31" t="n">
-        <v>3.27</v>
+        <v>2.85</v>
       </c>
       <c r="O31" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="P31" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="R31" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="S31" t="n">
-        <v>2.93</v>
+        <v>2.6</v>
       </c>
       <c r="T31" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="U31" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="V31" t="n">
-        <v>6.8</v>
+        <v>8.25</v>
       </c>
       <c r="W31" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X31" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y31" t="n">
-        <v>10</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.34</v>
+        <v>2.9</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AD31" t="n">
-        <v>3.19</v>
+        <v>3.75</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="AG31" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AH31" t="n">
-        <v>6.5</v>
+        <v>7.8</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,76 +4634,76 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.24</v>
+        <v>2.99</v>
       </c>
       <c r="M32" t="n">
-        <v>2.96</v>
+        <v>3.21</v>
       </c>
       <c r="N32" t="n">
-        <v>2.98</v>
+        <v>2.36</v>
       </c>
       <c r="O32" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T32" t="n">
         <v>2.25</v>
       </c>
-      <c r="R32" t="n">
+      <c r="U32" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V32" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF32" t="n">
         <v>1.5</v>
       </c>
-      <c r="S32" t="n">
+      <c r="AG32" t="n">
         <v>2.5</v>
       </c>
-      <c r="T32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V32" t="n">
-        <v>10</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,76 +4766,76 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.27</v>
+        <v>2.88</v>
       </c>
       <c r="M33" t="n">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="N33" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="O33" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="P33" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V33" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD33" t="n">
         <v>2.9</v>
       </c>
-      <c r="O33" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="P33" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S33" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V33" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X33" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AE33" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.87</v>
+        <v>2.25</v>
       </c>
       <c r="AH33" t="n">
-        <v>7.8</v>
+        <v>5.5</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,76 +4898,76 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.88</v>
+        <v>2.24</v>
       </c>
       <c r="M34" t="n">
         <v>2.96</v>
       </c>
       <c r="N34" t="n">
-        <v>2.31</v>
+        <v>2.98</v>
       </c>
       <c r="O34" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V34" t="n">
         <v>10</v>
       </c>
-      <c r="Q34" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S34" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V34" t="n">
-        <v>6.5</v>
-      </c>
       <c r="W34" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X34" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AH34" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
@@ -4994,22 +4994,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,76 +5030,76 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M35" t="n">
-        <v>3.72</v>
+        <v>3.45</v>
       </c>
       <c r="N35" t="n">
-        <v>1.66</v>
+        <v>3.2</v>
       </c>
       <c r="O35" t="n">
-        <v>2.55</v>
+        <v>1.67</v>
       </c>
       <c r="P35" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.57</v>
+        <v>2.26</v>
       </c>
       <c r="R35" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="S35" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="T35" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="U35" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="V35" t="n">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="W35" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X35" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y35" t="n">
-        <v>11</v>
+        <v>11.4</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AA35" t="n">
-        <v>4.75</v>
+        <v>3.8</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.36</v>
+        <v>2.6</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.59</v>
+        <v>1.4</v>
       </c>
       <c r="AF35" t="n">
         <v>1.57</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH35" t="n">
-        <v>4.2</v>
+        <v>4.95</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,76 +5162,76 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.12</v>
+        <v>1.48</v>
       </c>
       <c r="M36" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="N36" t="n">
-        <v>2.8</v>
+        <v>5.81</v>
       </c>
       <c r="O36" t="n">
-        <v>1.77</v>
+        <v>1.48</v>
       </c>
       <c r="P36" t="n">
-        <v>13.75</v>
+        <v>9</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.09</v>
+        <v>3.25</v>
       </c>
       <c r="R36" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="S36" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="T36" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="U36" t="n">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="V36" t="n">
-        <v>5.75</v>
+        <v>7</v>
       </c>
       <c r="W36" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X36" t="n">
         <v>1.03</v>
       </c>
       <c r="Y36" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AA36" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.65</v>
+        <v>1.97</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.62</v>
+        <v>3.2</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.59</v>
+        <v>2</v>
       </c>
       <c r="AG36" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AH36" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,76 +5294,76 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.39</v>
+        <v>4.2</v>
       </c>
       <c r="M37" t="n">
-        <v>4.33</v>
+        <v>3.45</v>
       </c>
       <c r="N37" t="n">
-        <v>5.8</v>
+        <v>1.78</v>
       </c>
       <c r="O37" t="n">
-        <v>1.35</v>
+        <v>2.79</v>
       </c>
       <c r="P37" t="n">
-        <v>16</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.2</v>
+        <v>1.56</v>
       </c>
       <c r="R37" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="S37" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V37" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD37" t="n">
         <v>3.3</v>
       </c>
-      <c r="T37" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V37" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X37" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AE37" t="n">
-        <v>1.48</v>
+        <v>1.29</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AH37" t="n">
-        <v>4.6</v>
+        <v>5.9</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,76 +5558,76 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="M39" t="n">
-        <v>3.86</v>
+        <v>4.53</v>
       </c>
       <c r="N39" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="O39" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="P39" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="R39" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="S39" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="T39" t="n">
-        <v>2.92</v>
+        <v>2.38</v>
       </c>
       <c r="U39" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="V39" t="n">
-        <v>7</v>
+        <v>5.25</v>
       </c>
       <c r="W39" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X39" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y39" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AA39" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.91</v>
+        <v>1.61</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.79</v>
+        <v>2.2</v>
       </c>
       <c r="AD39" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.98</v>
+        <v>1.73</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="AH39" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
@@ -5654,22 +5654,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,76 +5690,76 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.23</v>
+        <v>4</v>
       </c>
       <c r="M40" t="n">
-        <v>3.31</v>
+        <v>3.72</v>
       </c>
       <c r="N40" t="n">
-        <v>2.7</v>
+        <v>1.66</v>
       </c>
       <c r="O40" t="n">
-        <v>1.83</v>
+        <v>2.55</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="R40" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="S40" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="T40" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="U40" t="n">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="V40" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="W40" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X40" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y40" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AA40" t="n">
-        <v>3.6</v>
+        <v>4.75</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.74</v>
+        <v>1.57</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.96</v>
+        <v>2.3</v>
       </c>
       <c r="AD40" t="n">
-        <v>3</v>
+        <v>2.36</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.36</v>
+        <v>1.59</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="AH40" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,76 +5822,76 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="M41" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="N41" t="n">
-        <v>3.16</v>
+        <v>2.9</v>
       </c>
       <c r="O41" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="P41" t="n">
-        <v>13.5</v>
+        <v>13.75</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.26</v>
+        <v>2.09</v>
       </c>
       <c r="R41" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T41" t="n">
-        <v>2.59</v>
+        <v>2.41</v>
       </c>
       <c r="U41" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="V41" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="W41" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X41" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y41" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AA41" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AC41" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.81</v>
+        <v>2.65</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="AG41" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AH41" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.69</v>
+        <v>2.94</v>
       </c>
       <c r="M42" t="n">
-        <v>3.18</v>
+        <v>3.28</v>
       </c>
       <c r="N42" t="n">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="O42" t="n">
         <v>2.15</v>
@@ -5981,7 +5981,7 @@
         <v>2.75</v>
       </c>
       <c r="U42" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="V42" t="n">
         <v>6.55</v>
@@ -5990,28 +5990,28 @@
         <v>1.08</v>
       </c>
       <c r="X42" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y42" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AA42" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AD42" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AF42" t="n">
         <v>1.73</v>
@@ -6020,10 +6020,10 @@
         <v>1.91</v>
       </c>
       <c r="AH42" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,76 +6086,76 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>4.1</v>
+        <v>2.46</v>
       </c>
       <c r="M43" t="n">
-        <v>3.41</v>
+        <v>3.36</v>
       </c>
       <c r="N43" t="n">
-        <v>1.72</v>
+        <v>2.65</v>
       </c>
       <c r="O43" t="n">
-        <v>2.79</v>
+        <v>1.83</v>
       </c>
       <c r="P43" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.56</v>
+        <v>2.05</v>
       </c>
       <c r="R43" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="S43" t="n">
         <v>2.8</v>
       </c>
       <c r="T43" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="U43" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="V43" t="n">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="W43" t="n">
         <v>1.08</v>
       </c>
       <c r="X43" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y43" t="n">
-        <v>8.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AA43" t="n">
-        <v>3.22</v>
+        <v>3.6</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="AD43" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="AH43" t="n">
-        <v>5.9</v>
+        <v>6.05</v>
       </c>
       <c r="AI43" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="M45" t="n">
-        <v>3.17</v>
+        <v>3.25</v>
       </c>
       <c r="N45" t="n">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6368,7 +6368,7 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="S45" t="n">
         <v>2.35</v>
@@ -6386,16 +6386,16 @@
         <v>1.04</v>
       </c>
       <c r="X45" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y45" t="n">
         <v>6.5</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="AB45" t="n">
         <v>2.3</v>
@@ -6416,7 +6416,7 @@
         <v>1.75</v>
       </c>
       <c r="AH45" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AI45" t="n">
         <v>1.05</v>
@@ -6482,13 +6482,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="M46" t="n">
-        <v>3.11</v>
+        <v>3.15</v>
       </c>
       <c r="N46" t="n">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="O46" t="n">
         <v>1.68</v>
@@ -6500,46 +6500,46 @@
         <v>2.7</v>
       </c>
       <c r="R46" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="S46" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="T46" t="n">
         <v>3.6</v>
       </c>
       <c r="U46" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="V46" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="W46" t="n">
         <v>1.03</v>
       </c>
       <c r="X46" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="Y46" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.26</v>
+        <v>2.45</v>
       </c>
       <c r="AB46" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AD46" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF46" t="n">
         <v>2.25</v>
@@ -6548,10 +6548,10 @@
         <v>1.57</v>
       </c>
       <c r="AH46" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AI46" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6746,13 +6746,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="M48" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="N48" t="n">
-        <v>1.52</v>
+        <v>1.84</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6764,58 +6764,58 @@
         <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="S48" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="T48" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="U48" t="n">
         <v>1.48</v>
       </c>
       <c r="V48" t="n">
-        <v>6.1</v>
+        <v>5.5</v>
       </c>
       <c r="W48" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X48" t="n">
         <v>1.02</v>
       </c>
       <c r="Y48" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AA48" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AD48" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.91</v>
+        <v>1.72</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="AH48" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="AI48" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6878,13 +6878,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="M49" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="N49" t="n">
-        <v>1.84</v>
+        <v>1.43</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6899,55 +6899,55 @@
         <v>1.3</v>
       </c>
       <c r="S49" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="T49" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="U49" t="n">
         <v>1.48</v>
       </c>
       <c r="V49" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X49" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH49" t="n">
         <v>5.5</v>
       </c>
-      <c r="W49" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X49" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>5.75</v>
-      </c>
       <c r="AI49" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
@@ -7010,13 +7010,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="M50" t="n">
-        <v>3.5</v>
+        <v>3.71</v>
       </c>
       <c r="N50" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="O50" t="n">
         <v>1.57</v>
@@ -7028,22 +7028,22 @@
         <v>2.6</v>
       </c>
       <c r="R50" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S50" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="T50" t="n">
         <v>2.5</v>
       </c>
       <c r="U50" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="V50" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="W50" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X50" t="n">
         <v>1.01</v>
@@ -7052,34 +7052,34 @@
         <v>10</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AA50" t="n">
-        <v>3.7</v>
+        <v>3.79</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AD50" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AG50" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH50" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AI50" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
@@ -7142,13 +7142,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.87</v>
+        <v>2.27</v>
       </c>
       <c r="M51" t="n">
-        <v>3.11</v>
+        <v>2.85</v>
       </c>
       <c r="N51" t="n">
-        <v>3.78</v>
+        <v>3.25</v>
       </c>
       <c r="O51" t="n">
         <v>1.72</v>
@@ -7160,16 +7160,16 @@
         <v>2.6</v>
       </c>
       <c r="R51" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="S51" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="T51" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="U51" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="V51" t="n">
         <v>13</v>
@@ -7181,31 +7181,31 @@
         <v>1.12</v>
       </c>
       <c r="Y51" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.37</v>
+        <v>2.2</v>
       </c>
       <c r="AB51" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="AD51" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AF51" t="n">
         <v>2.25</v>
       </c>
       <c r="AG51" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AH51" t="n">
         <v>11</v>
@@ -7274,13 +7274,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="M52" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="N52" t="n">
-        <v>4.7</v>
+        <v>4.33</v>
       </c>
       <c r="O52" t="n">
         <v>1.62</v>
@@ -7316,34 +7316,34 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AA52" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AD52" t="n">
-        <v>2.75</v>
+        <v>2.92</v>
       </c>
       <c r="AE52" t="n">
         <v>1.31</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG52" t="n">
         <v>1.97</v>
       </c>
       <c r="AH52" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="AI52" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
@@ -7538,10 +7538,10 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.41</v>
+        <v>2.48</v>
       </c>
       <c r="M54" t="n">
-        <v>3.23</v>
+        <v>3.2</v>
       </c>
       <c r="N54" t="n">
         <v>2.63</v>
@@ -7559,13 +7559,13 @@
         <v>1.38</v>
       </c>
       <c r="S54" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="T54" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="U54" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="V54" t="n">
         <v>6.5</v>
@@ -7592,13 +7592,13 @@
         <v>1.75</v>
       </c>
       <c r="AD54" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="AE54" t="n">
         <v>1.25</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG54" t="n">
         <v>2</v>

--- a/jogos_2025-08-01.xlsx
+++ b/jogos_2025-08-01.xlsx
@@ -902,7 +902,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mariehamn</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>4.36</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>5.11</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>5.11</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Rukh Vynnyky</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>SK Poltava</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,76 +1202,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.26</v>
+        <v>1.65</v>
       </c>
       <c r="M6" t="n">
-        <v>4.04</v>
+        <v>3.41</v>
       </c>
       <c r="N6" t="n">
-        <v>9.77</v>
+        <v>5.9</v>
       </c>
       <c r="O6" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="P6" t="n">
-        <v>11.25</v>
+        <v>6.4</v>
       </c>
       <c r="Q6" t="n">
+        <v>4</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T6" t="n">
         <v>3.75</v>
       </c>
-      <c r="R6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.6</v>
-      </c>
       <c r="U6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V6" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AC6" t="n">
         <v>1.44</v>
       </c>
-      <c r="V6" t="n">
-        <v>6</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.07</v>
-      </c>
       <c r="AD6" t="n">
-        <v>2.65</v>
+        <v>5.1</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.37</v>
+        <v>1.1</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.19</v>
+        <v>2.63</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AH6" t="n">
-        <v>4.85</v>
+        <v>8.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rukh Vynnyky</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SK Poltava</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.65</v>
+        <v>1.26</v>
       </c>
       <c r="M8" t="n">
-        <v>3.41</v>
+        <v>4.04</v>
       </c>
       <c r="N8" t="n">
-        <v>5.9</v>
+        <v>9.77</v>
       </c>
       <c r="O8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P8" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U8" t="n">
         <v>1.44</v>
       </c>
-      <c r="P8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>4</v>
-      </c>
-      <c r="R8" t="n">
+      <c r="V8" t="n">
+        <v>6</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AG8" t="n">
         <v>1.57</v>
       </c>
-      <c r="S8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V8" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AH8" t="n">
-        <v>8.5</v>
+        <v>4.85</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.42</v>
+        <v>2.62</v>
       </c>
       <c r="M11" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="N11" t="n">
-        <v>5.6</v>
+        <v>2.55</v>
       </c>
       <c r="O11" t="n">
-        <v>1.44</v>
+        <v>1.83</v>
       </c>
       <c r="P11" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.75</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S11" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="T11" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="U11" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="V11" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AC11" t="n">
         <v>2.15</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG11" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AH11" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="M12" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="N12" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="O12" t="n">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="P12" t="n">
-        <v>19.25</v>
+        <v>8.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="R12" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="T12" t="n">
-        <v>2.2</v>
+        <v>3.01</v>
       </c>
       <c r="U12" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="V12" t="n">
-        <v>4.8</v>
+        <v>7.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y12" t="n">
-        <v>14.7</v>
+        <v>9</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.15</v>
+        <v>1.32</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.75</v>
+        <v>3.48</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.53</v>
+        <v>2.06</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.37</v>
+        <v>1.78</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.3</v>
+        <v>3.35</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.5</v>
+        <v>1.77</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.49</v>
+        <v>1.95</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.74</v>
+        <v>6.25</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,37 +2126,37 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.62</v>
+        <v>1.42</v>
       </c>
       <c r="M13" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="N13" t="n">
-        <v>2.2</v>
+        <v>5.6</v>
       </c>
       <c r="O13" t="n">
-        <v>2.07</v>
+        <v>1.44</v>
       </c>
       <c r="P13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.84</v>
+        <v>2.75</v>
       </c>
       <c r="R13" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S13" t="n">
-        <v>3.21</v>
+        <v>3.1</v>
       </c>
       <c r="T13" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="U13" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="V13" t="n">
-        <v>5.6</v>
+        <v>5.25</v>
       </c>
       <c r="W13" t="n">
         <v>1.12</v>
@@ -2165,37 +2165,37 @@
         <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AI13" t="n">
         <v>1.18</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1.17</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="M14" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N14" t="n">
-        <v>3.1</v>
+        <v>2.41</v>
       </c>
       <c r="O14" t="n">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="P14" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V14" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y14" t="n">
         <v>8.5</v>
       </c>
-      <c r="Q14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V14" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>9</v>
-      </c>
       <c r="Z14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AE14" t="n">
         <v>1.32</v>
       </c>
-      <c r="AA14" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AF14" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AH14" t="n">
-        <v>6.25</v>
+        <v>5.65</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.45</v>
+        <v>1.75</v>
       </c>
       <c r="M15" t="n">
         <v>3.7</v>
       </c>
       <c r="N15" t="n">
-        <v>6.3</v>
+        <v>3.6</v>
       </c>
       <c r="O15" t="n">
-        <v>1.28</v>
+        <v>1.58</v>
       </c>
       <c r="P15" t="n">
-        <v>15</v>
+        <v>19.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.9</v>
+        <v>2.39</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S15" t="n">
-        <v>3.22</v>
+        <v>3.6</v>
       </c>
       <c r="T15" t="n">
-        <v>2.47</v>
+        <v>2.2</v>
       </c>
       <c r="U15" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="V15" t="n">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="W15" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>8.9</v>
+        <v>14.7</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.98</v>
+        <v>4.75</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.75</v>
+        <v>2.37</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.39</v>
+        <v>1.57</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.02</v>
+        <v>1.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.71</v>
+        <v>2.49</v>
       </c>
       <c r="AH15" t="n">
-        <v>4.75</v>
+        <v>3.74</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,76 +2522,76 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="O16" t="n">
         <v>2.63</v>
       </c>
-      <c r="M16" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N16" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.98</v>
-      </c>
       <c r="P16" t="n">
-        <v>13.25</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.91</v>
+        <v>1.5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="S16" t="n">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="T16" t="n">
-        <v>2.65</v>
+        <v>2.25</v>
       </c>
       <c r="U16" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="V16" t="n">
-        <v>6.55</v>
+        <v>4.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH16" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,76 +2654,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>6.5</v>
+        <v>2.62</v>
       </c>
       <c r="M17" t="n">
-        <v>5.2</v>
+        <v>3.4</v>
       </c>
       <c r="N17" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="O17" t="n">
-        <v>3</v>
+        <v>2.07</v>
       </c>
       <c r="P17" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.36</v>
+        <v>1.84</v>
       </c>
       <c r="R17" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="S17" t="n">
-        <v>3.6</v>
+        <v>3.21</v>
       </c>
       <c r="T17" t="n">
-        <v>2.09</v>
+        <v>2.4</v>
       </c>
       <c r="U17" t="n">
-        <v>1.73</v>
+        <v>1.51</v>
       </c>
       <c r="V17" t="n">
-        <v>4.75</v>
+        <v>5.6</v>
       </c>
       <c r="W17" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X17" t="n">
         <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AA17" t="n">
-        <v>5.45</v>
+        <v>4.4</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.53</v>
+        <v>2.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.15</v>
+        <v>2.47</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AH17" t="n">
-        <v>3.72</v>
+        <v>4.39</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,76 +2786,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.62</v>
+        <v>1.45</v>
       </c>
       <c r="M18" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="N18" t="n">
-        <v>2.55</v>
+        <v>6.3</v>
       </c>
       <c r="O18" t="n">
-        <v>1.83</v>
+        <v>1.28</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q18" t="n">
-        <v>2</v>
+        <v>3.9</v>
       </c>
       <c r="R18" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S18" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="T18" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="U18" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="V18" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="W18" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.66</v>
+        <v>1.95</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.62</v>
+        <v>2.02</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.2</v>
+        <v>1.71</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="M19" t="n">
-        <v>3.4</v>
+        <v>5.2</v>
       </c>
       <c r="N19" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="O19" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="P19" t="n">
-        <v>7.7</v>
+        <v>17</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.01</v>
+        <v>1.36</v>
       </c>
       <c r="R19" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="S19" t="n">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="T19" t="n">
-        <v>2.6</v>
+        <v>2.09</v>
       </c>
       <c r="U19" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="V19" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="W19" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X19" t="n">
         <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.87</v>
+        <v>5.45</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.62</v>
+        <v>1.43</v>
       </c>
       <c r="AC19" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG19" t="n">
         <v>2.1</v>
       </c>
-      <c r="AD19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AH19" t="n">
-        <v>4.33</v>
+        <v>3.72</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,76 +3050,76 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.62</v>
+        <v>2.5</v>
       </c>
       <c r="M20" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="N20" t="n">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="O20" t="n">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.5</v>
+        <v>2.01</v>
       </c>
       <c r="R20" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S20" t="n">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="T20" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="U20" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="V20" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AC20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG20" t="n">
         <v>2.2</v>
       </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="M21" t="n">
-        <v>5.4</v>
+        <v>5.37</v>
       </c>
       <c r="N21" t="n">
-        <v>9.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="O21" t="n">
         <v>1.22</v>
@@ -3206,7 +3206,7 @@
         <v>4</v>
       </c>
       <c r="T21" t="n">
-        <v>1.77</v>
+        <v>1.88</v>
       </c>
       <c r="U21" t="n">
         <v>1.8</v>
@@ -3236,10 +3236,10 @@
         <v>3</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AF21" t="n">
         <v>1.91</v>
@@ -3251,7 +3251,7 @@
         <v>2.75</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -3278,22 +3278,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,76 +3314,76 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="M22" t="n">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="O22" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="P22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S22" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="T22" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="U22" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V22" t="n">
-        <v>7.6</v>
+        <v>5.75</v>
       </c>
       <c r="W22" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X22" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.82</v>
+        <v>2.15</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.35</v>
+        <v>2.7</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AH22" t="n">
-        <v>6.5</v>
+        <v>4.75</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -3410,22 +3410,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,76 +3446,76 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="P23" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q23" t="n">
         <v>2.2</v>
       </c>
-      <c r="M23" t="n">
+      <c r="R23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V23" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA23" t="n">
         <v>3.4</v>
       </c>
-      <c r="N23" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="P23" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="R23" t="n">
+      <c r="AB23" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AE23" t="n">
         <v>1.33</v>
       </c>
-      <c r="S23" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V23" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB23" t="n">
+      <c r="AF23" t="n">
         <v>1.67</v>
       </c>
-      <c r="AC23" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AG23" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AH23" t="n">
-        <v>4.75</v>
+        <v>6.5</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,76 +3842,76 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.75</v>
+        <v>2.04</v>
       </c>
       <c r="M26" t="n">
-        <v>3.3</v>
+        <v>3.78</v>
       </c>
       <c r="N26" t="n">
-        <v>2.48</v>
+        <v>3.15</v>
       </c>
       <c r="O26" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="P26" t="n">
-        <v>11</v>
+        <v>18.25</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.83</v>
+        <v>2.11</v>
       </c>
       <c r="R26" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S26" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="T26" t="n">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="U26" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="V26" t="n">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="W26" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X26" t="n">
         <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AA26" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="AC26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD26" t="n">
         <v>2.1</v>
       </c>
-      <c r="AD26" t="n">
-        <v>2.62</v>
-      </c>
       <c r="AE26" t="n">
-        <v>1.42</v>
+        <v>1.68</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.37</v>
+        <v>2.67</v>
       </c>
       <c r="AH26" t="n">
-        <v>4.6</v>
+        <v>3.45</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,76 +3974,76 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.04</v>
+        <v>1.73</v>
       </c>
       <c r="M27" t="n">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="N27" t="n">
-        <v>3.15</v>
+        <v>4.6</v>
       </c>
       <c r="O27" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="P27" t="n">
-        <v>18.25</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.11</v>
+        <v>2.75</v>
       </c>
       <c r="R27" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="S27" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="T27" t="n">
-        <v>2.14</v>
+        <v>2.85</v>
       </c>
       <c r="U27" t="n">
-        <v>1.66</v>
+        <v>1.37</v>
       </c>
       <c r="V27" t="n">
-        <v>4.3</v>
+        <v>6.95</v>
       </c>
       <c r="W27" t="n">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="X27" t="n">
         <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>18</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.09</v>
+        <v>1.32</v>
       </c>
       <c r="AA27" t="n">
-        <v>5.3</v>
+        <v>3.2</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.42</v>
+        <v>1.9</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.68</v>
+        <v>1.29</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.38</v>
+        <v>1.9</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.67</v>
+        <v>1.8</v>
       </c>
       <c r="AH27" t="n">
-        <v>3.45</v>
+        <v>6</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,76 +4106,76 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.73</v>
+        <v>2.75</v>
       </c>
       <c r="M28" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N28" t="n">
-        <v>4.6</v>
+        <v>2.48</v>
       </c>
       <c r="O28" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="P28" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.75</v>
+        <v>1.83</v>
       </c>
       <c r="R28" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="S28" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="T28" t="n">
-        <v>2.85</v>
+        <v>2.4</v>
       </c>
       <c r="U28" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="V28" t="n">
-        <v>6.95</v>
+        <v>5.5</v>
       </c>
       <c r="W28" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X28" t="n">
         <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AD28" t="n">
-        <v>3.3</v>
+        <v>2.62</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.9</v>
+        <v>1.57</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.8</v>
+        <v>2.37</v>
       </c>
       <c r="AH28" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,76 +4370,76 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2</v>
+        <v>2.88</v>
       </c>
       <c r="M30" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="N30" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="O30" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="P30" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S30" t="n">
         <v>3.25</v>
       </c>
-      <c r="N30" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="O30" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="P30" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V30" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD30" t="n">
         <v>2.9</v>
       </c>
-      <c r="T30" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U30" t="n">
+      <c r="AE30" t="n">
         <v>1.4</v>
       </c>
-      <c r="V30" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AF30" t="n">
-        <v>1.76</v>
+        <v>1.57</v>
       </c>
       <c r="AG30" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AH30" t="n">
         <v>5.5</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,76 +4502,76 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.52</v>
+        <v>2.99</v>
       </c>
       <c r="M31" t="n">
-        <v>3.28</v>
+        <v>3.21</v>
       </c>
       <c r="N31" t="n">
-        <v>2.85</v>
+        <v>2.36</v>
       </c>
       <c r="O31" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="P31" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="R31" t="n">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="S31" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="T31" t="n">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="U31" t="n">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="V31" t="n">
-        <v>8.25</v>
+        <v>5.5</v>
       </c>
       <c r="W31" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="X31" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y31" t="n">
-        <v>8.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.9</v>
+        <v>4.75</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.12</v>
+        <v>1.53</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.67</v>
+        <v>2.35</v>
       </c>
       <c r="AD31" t="n">
-        <v>3.75</v>
+        <v>2.25</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>7.8</v>
+        <v>4.2</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.02</v>
+        <v>1.22</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,76 +4634,76 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.99</v>
+        <v>2</v>
       </c>
       <c r="M32" t="n">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="N32" t="n">
-        <v>2.36</v>
+        <v>3.32</v>
       </c>
       <c r="O32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P32" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V32" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AG32" t="n">
         <v>2</v>
       </c>
-      <c r="P32" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S32" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V32" t="n">
+      <c r="AH32" t="n">
         <v>5.5</v>
       </c>
-      <c r="W32" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AI32" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,76 +4766,76 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.88</v>
+        <v>2.52</v>
       </c>
       <c r="M33" t="n">
-        <v>2.96</v>
+        <v>3.28</v>
       </c>
       <c r="N33" t="n">
-        <v>2.31</v>
+        <v>2.85</v>
       </c>
       <c r="O33" t="n">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="P33" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="R33" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="S33" t="n">
-        <v>3.25</v>
+        <v>2.6</v>
       </c>
       <c r="T33" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="U33" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="V33" t="n">
-        <v>6.5</v>
+        <v>8.25</v>
       </c>
       <c r="W33" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X33" t="n">
         <v>1.05</v>
       </c>
       <c r="Y33" t="n">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Z33" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AE33" t="n">
         <v>1.25</v>
       </c>
-      <c r="AA33" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AF33" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AH33" t="n">
-        <v>5.5</v>
+        <v>7.8</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,76 +5030,76 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2</v>
+        <v>2.46</v>
       </c>
       <c r="M35" t="n">
-        <v>3.45</v>
+        <v>3.36</v>
       </c>
       <c r="N35" t="n">
-        <v>3.2</v>
+        <v>2.65</v>
       </c>
       <c r="O35" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="P35" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.26</v>
+        <v>2.05</v>
       </c>
       <c r="R35" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="S35" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="T35" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="U35" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="V35" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="W35" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X35" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y35" t="n">
-        <v>11.4</v>
+        <v>9</v>
       </c>
       <c r="Z35" t="n">
         <v>1.25</v>
       </c>
       <c r="AA35" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC35" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH35" t="n">
-        <v>4.95</v>
+        <v>6.05</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,76 +5162,76 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="M36" t="n">
-        <v>4.1</v>
+        <v>4.53</v>
       </c>
       <c r="N36" t="n">
-        <v>5.81</v>
+        <v>6.2</v>
       </c>
       <c r="O36" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="P36" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="R36" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="S36" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="T36" t="n">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="U36" t="n">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="V36" t="n">
-        <v>7</v>
+        <v>5.25</v>
       </c>
       <c r="W36" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X36" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y36" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AA36" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.97</v>
+        <v>1.61</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AD36" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AF36" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AH36" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,76 +5294,76 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>4.2</v>
+        <v>2.15</v>
       </c>
       <c r="M37" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="N37" t="n">
-        <v>1.78</v>
+        <v>2.9</v>
       </c>
       <c r="O37" t="n">
-        <v>2.79</v>
+        <v>1.77</v>
       </c>
       <c r="P37" t="n">
-        <v>8.699999999999999</v>
+        <v>13.75</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.56</v>
+        <v>2.09</v>
       </c>
       <c r="R37" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="S37" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="T37" t="n">
-        <v>2.7</v>
+        <v>2.41</v>
       </c>
       <c r="U37" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V37" t="n">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="W37" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X37" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y37" t="n">
-        <v>8.75</v>
+        <v>12</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AA37" t="n">
-        <v>3.22</v>
+        <v>3.8</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.93</v>
+        <v>1.66</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AD37" t="n">
-        <v>3.3</v>
+        <v>2.65</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.87</v>
+        <v>1.59</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.82</v>
+        <v>2.25</v>
       </c>
       <c r="AH37" t="n">
-        <v>5.9</v>
+        <v>4.5</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
@@ -5390,22 +5390,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,28 +5426,28 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.55</v>
+        <v>2.94</v>
       </c>
       <c r="M38" t="n">
-        <v>3.7</v>
+        <v>3.28</v>
       </c>
       <c r="N38" t="n">
-        <v>1.89</v>
+        <v>2.33</v>
       </c>
       <c r="O38" t="n">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="P38" t="n">
-        <v>12</v>
+        <v>8.5</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.67</v>
+        <v>1.93</v>
       </c>
       <c r="R38" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S38" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="T38" t="n">
         <v>2.75</v>
@@ -5456,46 +5456,46 @@
         <v>1.4</v>
       </c>
       <c r="V38" t="n">
-        <v>6.5</v>
+        <v>6.55</v>
       </c>
       <c r="W38" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X38" t="n">
         <v>1.01</v>
       </c>
       <c r="Y38" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AA38" t="n">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AC38" t="n">
         <v>1.83</v>
       </c>
       <c r="AD38" t="n">
-        <v>3.08</v>
+        <v>3.45</v>
       </c>
       <c r="AE38" t="n">
         <v>1.28</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG38" t="n">
         <v>1.91</v>
       </c>
       <c r="AH38" t="n">
-        <v>6.15</v>
+        <v>6.2</v>
       </c>
       <c r="AI38" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
@@ -5522,22 +5522,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,76 +5558,76 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.35</v>
+        <v>4</v>
       </c>
       <c r="M39" t="n">
-        <v>4.53</v>
+        <v>3.72</v>
       </c>
       <c r="N39" t="n">
-        <v>6.2</v>
+        <v>1.66</v>
       </c>
       <c r="O39" t="n">
-        <v>1.35</v>
+        <v>2.55</v>
       </c>
       <c r="P39" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.2</v>
+        <v>1.57</v>
       </c>
       <c r="R39" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="S39" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="T39" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="U39" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="V39" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="W39" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X39" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y39" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AA39" t="n">
-        <v>4.4</v>
+        <v>4.75</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.6</v>
+        <v>2.36</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.46</v>
+        <v>1.59</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.88</v>
+        <v>2.25</v>
       </c>
       <c r="AH39" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
@@ -5654,22 +5654,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,76 +5690,76 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>4</v>
+        <v>1.48</v>
       </c>
       <c r="M40" t="n">
-        <v>3.72</v>
+        <v>4.1</v>
       </c>
       <c r="N40" t="n">
-        <v>1.66</v>
+        <v>5.81</v>
       </c>
       <c r="O40" t="n">
-        <v>2.55</v>
+        <v>1.48</v>
       </c>
       <c r="P40" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.57</v>
+        <v>3.25</v>
       </c>
       <c r="R40" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="S40" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="T40" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="U40" t="n">
-        <v>1.58</v>
+        <v>1.39</v>
       </c>
       <c r="V40" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W40" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="X40" t="n">
         <v>1.03</v>
       </c>
       <c r="Y40" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AA40" t="n">
-        <v>4.75</v>
+        <v>3.5</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.57</v>
+        <v>1.97</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.36</v>
+        <v>3.2</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.59</v>
+        <v>1.33</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AH40" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
@@ -5786,22 +5786,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,76 +5822,76 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.15</v>
+        <v>3.55</v>
       </c>
       <c r="M41" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="N41" t="n">
-        <v>2.9</v>
+        <v>1.89</v>
       </c>
       <c r="O41" t="n">
-        <v>1.77</v>
+        <v>2.38</v>
       </c>
       <c r="P41" t="n">
-        <v>13.75</v>
+        <v>12</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.09</v>
+        <v>1.67</v>
       </c>
       <c r="R41" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="S41" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="T41" t="n">
-        <v>2.41</v>
+        <v>2.75</v>
       </c>
       <c r="U41" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="V41" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="W41" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X41" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y41" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AA41" t="n">
-        <v>3.8</v>
+        <v>3.42</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.65</v>
+        <v>3.08</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.59</v>
+        <v>1.8</v>
       </c>
       <c r="AG41" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="AH41" t="n">
-        <v>4.5</v>
+        <v>6.15</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,76 +5954,76 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.94</v>
+        <v>2</v>
       </c>
       <c r="M42" t="n">
-        <v>3.28</v>
+        <v>3.45</v>
       </c>
       <c r="N42" t="n">
-        <v>2.33</v>
+        <v>3.2</v>
       </c>
       <c r="O42" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="P42" t="n">
-        <v>8.5</v>
+        <v>13.5</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.93</v>
+        <v>2.26</v>
       </c>
       <c r="R42" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="S42" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="T42" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="U42" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V42" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X42" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AE42" t="n">
         <v>1.4</v>
       </c>
-      <c r="V42" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X42" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AF42" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AH42" t="n">
-        <v>6.2</v>
+        <v>4.95</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,76 +6086,76 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.46</v>
+        <v>4.2</v>
       </c>
       <c r="M43" t="n">
-        <v>3.36</v>
+        <v>3.45</v>
       </c>
       <c r="N43" t="n">
-        <v>2.65</v>
+        <v>1.78</v>
       </c>
       <c r="O43" t="n">
-        <v>1.83</v>
+        <v>2.79</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.05</v>
+        <v>1.56</v>
       </c>
       <c r="R43" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="S43" t="n">
         <v>2.8</v>
       </c>
       <c r="T43" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="U43" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="V43" t="n">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="W43" t="n">
         <v>1.08</v>
       </c>
       <c r="X43" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y43" t="n">
-        <v>9</v>
+        <v>8.75</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AA43" t="n">
-        <v>3.6</v>
+        <v>3.22</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AD43" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AG43" t="n">
-        <v>2.15</v>
+        <v>1.82</v>
       </c>
       <c r="AH43" t="n">
-        <v>6.05</v>
+        <v>5.9</v>
       </c>
       <c r="AI43" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
@@ -6359,13 +6359,13 @@
         <v>3</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="R45" t="n">
         <v>1.45</v>
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6746,13 +6746,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="M48" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="N48" t="n">
-        <v>1.84</v>
+        <v>1.43</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6764,58 +6764,58 @@
         <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="S48" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="T48" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="U48" t="n">
         <v>1.48</v>
       </c>
       <c r="V48" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X48" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH48" t="n">
         <v>5.5</v>
       </c>
-      <c r="W48" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X48" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>5.75</v>
-      </c>
       <c r="AI48" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6878,13 +6878,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="M49" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="N49" t="n">
-        <v>1.43</v>
+        <v>1.84</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6896,58 +6896,58 @@
         <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="S49" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="T49" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="U49" t="n">
         <v>1.48</v>
       </c>
       <c r="V49" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X49" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AH49" t="n">
         <v>5.75</v>
       </c>
-      <c r="W49" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X49" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>5.5</v>
-      </c>
       <c r="AI49" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>

--- a/jogos_2025-08-01.xlsx
+++ b/jogos_2025-08-01.xlsx
@@ -902,22 +902,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Rukh Vynnyky</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>SK Poltava</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mariehamn</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.52</v>
+        <v>1.26</v>
       </c>
       <c r="M5" t="n">
-        <v>4.36</v>
+        <v>4.04</v>
       </c>
       <c r="N5" t="n">
-        <v>5.11</v>
+        <v>9.77</v>
       </c>
       <c r="O5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P5" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U5" t="n">
         <v>1.44</v>
       </c>
-      <c r="P5" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.53</v>
-      </c>
       <c r="V5" t="n">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="W5" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X5" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>9</v>
+        <v>10.9</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.4</v>
+        <v>3.78</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.73</v>
+        <v>2.19</v>
       </c>
       <c r="AG5" t="n">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="AH5" t="n">
-        <v>4.5</v>
+        <v>4.85</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1166,22 +1166,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rukh Vynnyky</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SK Poltava</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,76 +1202,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>5.11</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>9.77</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>11.25</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>10.9</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,40 +1862,40 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.62</v>
+        <v>3.62</v>
       </c>
       <c r="M11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S11" t="n">
         <v>3.5</v>
       </c>
-      <c r="N11" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.25</v>
-      </c>
       <c r="T11" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="U11" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="V11" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -1922,10 +1922,10 @@
         <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AH11" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.63</v>
+        <v>6.5</v>
       </c>
       <c r="M14" t="n">
-        <v>3.25</v>
+        <v>5.2</v>
       </c>
       <c r="N14" t="n">
-        <v>2.41</v>
+        <v>1.4</v>
       </c>
       <c r="O14" t="n">
-        <v>1.98</v>
+        <v>3</v>
       </c>
       <c r="P14" t="n">
-        <v>13.25</v>
+        <v>17</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.91</v>
+        <v>1.36</v>
       </c>
       <c r="R14" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="S14" t="n">
-        <v>2.95</v>
+        <v>3.6</v>
       </c>
       <c r="T14" t="n">
-        <v>2.65</v>
+        <v>2.09</v>
       </c>
       <c r="U14" t="n">
-        <v>1.42</v>
+        <v>1.73</v>
       </c>
       <c r="V14" t="n">
-        <v>6.55</v>
+        <v>4.75</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="X14" t="n">
         <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>8.5</v>
+        <v>16</v>
       </c>
       <c r="Z14" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AI14" t="n">
         <v>1.22</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1.14</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="P15" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V15" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB15" t="n">
         <v>1.75</v>
       </c>
-      <c r="M15" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="N15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="P15" t="n">
-        <v>19.25</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V15" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AC15" t="n">
-        <v>2.37</v>
+        <v>1.98</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.57</v>
+        <v>1.32</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.49</v>
+        <v>2.15</v>
       </c>
       <c r="AH15" t="n">
-        <v>3.74</v>
+        <v>5.65</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,40 +2522,40 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.62</v>
+        <v>2.62</v>
       </c>
       <c r="M16" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="N16" t="n">
-        <v>1.75</v>
+        <v>2.55</v>
       </c>
       <c r="O16" t="n">
-        <v>2.63</v>
+        <v>1.83</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
+        <v>2</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U16" t="n">
         <v>1.5</v>
       </c>
-      <c r="R16" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.57</v>
-      </c>
       <c r="V16" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -2570,22 +2570,22 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AC16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG16" t="n">
         <v>2.2</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2.1</v>
       </c>
       <c r="AH16" t="n">
         <v>0</v>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,37 +2654,37 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="M17" t="n">
         <v>3.4</v>
       </c>
       <c r="N17" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="O17" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="P17" t="n">
-        <v>13</v>
+        <v>7.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.84</v>
+        <v>2.01</v>
       </c>
       <c r="R17" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="S17" t="n">
-        <v>3.21</v>
+        <v>3.28</v>
       </c>
       <c r="T17" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="U17" t="n">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="V17" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="W17" t="n">
         <v>1.12</v>
@@ -2696,34 +2696,34 @@
         <v>11</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.4</v>
+        <v>2.87</v>
       </c>
       <c r="AB17" t="n">
         <v>1.62</v>
       </c>
       <c r="AC17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG17" t="n">
         <v>2.2</v>
       </c>
-      <c r="AD17" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AH17" t="n">
-        <v>4.39</v>
+        <v>4.33</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,22 +2918,22 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>6.5</v>
+        <v>1.75</v>
       </c>
       <c r="M19" t="n">
-        <v>5.2</v>
+        <v>3.7</v>
       </c>
       <c r="N19" t="n">
-        <v>1.4</v>
+        <v>3.6</v>
       </c>
       <c r="O19" t="n">
-        <v>3</v>
+        <v>1.58</v>
       </c>
       <c r="P19" t="n">
-        <v>17</v>
+        <v>19.25</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.36</v>
+        <v>2.39</v>
       </c>
       <c r="R19" t="n">
         <v>1.25</v>
@@ -2942,52 +2942,52 @@
         <v>3.6</v>
       </c>
       <c r="T19" t="n">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="U19" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="V19" t="n">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="W19" t="n">
         <v>1.15</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>16</v>
+        <v>14.7</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AA19" t="n">
-        <v>5.45</v>
+        <v>4.75</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.53</v>
+        <v>2.37</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.1</v>
+        <v>2.49</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.72</v>
+        <v>3.74</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,37 +3050,37 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="M20" t="n">
         <v>3.4</v>
       </c>
       <c r="N20" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="O20" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="P20" t="n">
-        <v>7.7</v>
+        <v>13</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.01</v>
+        <v>1.84</v>
       </c>
       <c r="R20" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="S20" t="n">
-        <v>3.28</v>
+        <v>3.21</v>
       </c>
       <c r="T20" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="U20" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="V20" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="W20" t="n">
         <v>1.12</v>
@@ -3092,34 +3092,34 @@
         <v>11</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.87</v>
+        <v>4.4</v>
       </c>
       <c r="AB20" t="n">
         <v>1.62</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AH20" t="n">
-        <v>4.33</v>
+        <v>4.39</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3278,22 +3278,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,76 +3314,76 @@
         </is>
       </c>
       <c r="L22" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="P22" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q22" t="n">
         <v>2.2</v>
       </c>
-      <c r="M22" t="n">
+      <c r="R22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V22" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA22" t="n">
         <v>3.4</v>
       </c>
-      <c r="N22" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="P22" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="R22" t="n">
+      <c r="AB22" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AE22" t="n">
         <v>1.33</v>
       </c>
-      <c r="S22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V22" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB22" t="n">
+      <c r="AF22" t="n">
         <v>1.67</v>
       </c>
-      <c r="AC22" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AG22" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AH22" t="n">
-        <v>4.75</v>
+        <v>6.5</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -3410,22 +3410,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,76 +3446,76 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="M23" t="n">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="O23" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="P23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="R23" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S23" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="T23" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="U23" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V23" t="n">
-        <v>7.6</v>
+        <v>5.75</v>
       </c>
       <c r="W23" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X23" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.82</v>
+        <v>2.15</v>
       </c>
       <c r="AD23" t="n">
-        <v>3.35</v>
+        <v>2.7</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AH23" t="n">
-        <v>6.5</v>
+        <v>4.75</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,76 +3842,76 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.04</v>
+        <v>1.73</v>
       </c>
       <c r="M26" t="n">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="N26" t="n">
-        <v>3.15</v>
+        <v>4.6</v>
       </c>
       <c r="O26" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="P26" t="n">
-        <v>18.25</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.11</v>
+        <v>2.75</v>
       </c>
       <c r="R26" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="S26" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="T26" t="n">
-        <v>2.14</v>
+        <v>2.85</v>
       </c>
       <c r="U26" t="n">
-        <v>1.66</v>
+        <v>1.37</v>
       </c>
       <c r="V26" t="n">
-        <v>4.3</v>
+        <v>7</v>
       </c>
       <c r="W26" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="X26" t="n">
         <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>18</v>
+        <v>8.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.09</v>
+        <v>1.32</v>
       </c>
       <c r="AA26" t="n">
-        <v>5.3</v>
+        <v>3.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.42</v>
+        <v>2</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.68</v>
+        <v>1.29</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.38</v>
+        <v>1.9</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.67</v>
+        <v>1.85</v>
       </c>
       <c r="AH26" t="n">
-        <v>3.45</v>
+        <v>6</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,76 +3974,76 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.73</v>
+        <v>2.75</v>
       </c>
       <c r="M27" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N27" t="n">
-        <v>4.6</v>
+        <v>2.48</v>
       </c>
       <c r="O27" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="P27" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.75</v>
+        <v>1.83</v>
       </c>
       <c r="R27" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="S27" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="T27" t="n">
-        <v>2.85</v>
+        <v>2.4</v>
       </c>
       <c r="U27" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="V27" t="n">
-        <v>6.95</v>
+        <v>5.5</v>
       </c>
       <c r="W27" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X27" t="n">
         <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AD27" t="n">
-        <v>3.3</v>
+        <v>2.62</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.9</v>
+        <v>1.57</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.8</v>
+        <v>2.37</v>
       </c>
       <c r="AH27" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,76 +4106,76 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.75</v>
+        <v>2.04</v>
       </c>
       <c r="M28" t="n">
-        <v>3.3</v>
+        <v>3.78</v>
       </c>
       <c r="N28" t="n">
-        <v>2.48</v>
+        <v>3.15</v>
       </c>
       <c r="O28" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="P28" t="n">
-        <v>11</v>
+        <v>18.25</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.83</v>
+        <v>2.11</v>
       </c>
       <c r="R28" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S28" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="T28" t="n">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="U28" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="V28" t="n">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="W28" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X28" t="n">
         <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AA28" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="AC28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD28" t="n">
         <v>2.1</v>
       </c>
-      <c r="AD28" t="n">
-        <v>2.62</v>
-      </c>
       <c r="AE28" t="n">
-        <v>1.42</v>
+        <v>1.68</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.37</v>
+        <v>2.67</v>
       </c>
       <c r="AH28" t="n">
-        <v>4.6</v>
+        <v>3.45</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,76 +4370,76 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
       <c r="M30" t="n">
-        <v>2.96</v>
+        <v>3.21</v>
       </c>
       <c r="N30" t="n">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="O30" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="P30" t="n">
         <v>10</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="R30" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="S30" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="T30" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V30" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG30" t="n">
         <v>2.5</v>
       </c>
-      <c r="U30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V30" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AH30" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,76 +4502,76 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.99</v>
+        <v>2.52</v>
       </c>
       <c r="M31" t="n">
-        <v>3.21</v>
+        <v>3.28</v>
       </c>
       <c r="N31" t="n">
-        <v>2.36</v>
+        <v>2.85</v>
       </c>
       <c r="O31" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="P31" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="R31" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="S31" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="T31" t="n">
-        <v>2.25</v>
+        <v>2.9</v>
       </c>
       <c r="U31" t="n">
-        <v>1.57</v>
+        <v>1.32</v>
       </c>
       <c r="V31" t="n">
-        <v>5.5</v>
+        <v>8.25</v>
       </c>
       <c r="W31" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="X31" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y31" t="n">
-        <v>10</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="AA31" t="n">
-        <v>4.75</v>
+        <v>2.9</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.53</v>
+        <v>2.12</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.35</v>
+        <v>1.67</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.25</v>
+        <v>3.75</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="AH31" t="n">
-        <v>4.2</v>
+        <v>7.8</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.22</v>
+        <v>1.02</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,76 +4766,76 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.52</v>
+        <v>2.24</v>
       </c>
       <c r="M33" t="n">
-        <v>3.28</v>
+        <v>2.96</v>
       </c>
       <c r="N33" t="n">
-        <v>2.85</v>
+        <v>2.98</v>
       </c>
       <c r="O33" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="P33" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="R33" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S33" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="T33" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="U33" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="V33" t="n">
-        <v>8.25</v>
+        <v>10</v>
       </c>
       <c r="W33" t="n">
         <v>1.06</v>
       </c>
       <c r="X33" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AD33" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AH33" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,76 +4898,76 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.24</v>
+        <v>2.88</v>
       </c>
       <c r="M34" t="n">
         <v>2.96</v>
       </c>
       <c r="N34" t="n">
-        <v>2.98</v>
+        <v>2.31</v>
       </c>
       <c r="O34" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="P34" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q34" t="n">
         <v>1.83</v>
       </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
+      <c r="R34" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V34" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG34" t="n">
         <v>2.25</v>
       </c>
-      <c r="R34" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T34" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V34" t="n">
-        <v>10</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,76 +5030,76 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.46</v>
+        <v>2</v>
       </c>
       <c r="M35" t="n">
-        <v>3.36</v>
+        <v>3.45</v>
       </c>
       <c r="N35" t="n">
-        <v>2.65</v>
+        <v>3.2</v>
       </c>
       <c r="O35" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.05</v>
+        <v>2.26</v>
       </c>
       <c r="R35" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="S35" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="T35" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="U35" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="V35" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="W35" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X35" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y35" t="n">
-        <v>9</v>
+        <v>11.4</v>
       </c>
       <c r="Z35" t="n">
         <v>1.25</v>
       </c>
       <c r="AA35" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AD35" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH35" t="n">
-        <v>6.05</v>
+        <v>4.95</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
@@ -5126,22 +5126,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,76 +5162,76 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.35</v>
+        <v>4</v>
       </c>
       <c r="M36" t="n">
-        <v>4.53</v>
+        <v>3.72</v>
       </c>
       <c r="N36" t="n">
-        <v>6.2</v>
+        <v>1.66</v>
       </c>
       <c r="O36" t="n">
-        <v>1.35</v>
+        <v>2.55</v>
       </c>
       <c r="P36" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.2</v>
+        <v>1.57</v>
       </c>
       <c r="R36" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="S36" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="T36" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="U36" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="V36" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="W36" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X36" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y36" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AA36" t="n">
-        <v>4.4</v>
+        <v>4.75</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.6</v>
+        <v>2.36</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.46</v>
+        <v>1.59</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.88</v>
+        <v>2.25</v>
       </c>
       <c r="AH36" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,76 +5294,76 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.15</v>
+        <v>4.2</v>
       </c>
       <c r="M37" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="N37" t="n">
-        <v>2.9</v>
+        <v>1.78</v>
       </c>
       <c r="O37" t="n">
-        <v>1.77</v>
+        <v>2.79</v>
       </c>
       <c r="P37" t="n">
-        <v>13.75</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.09</v>
+        <v>1.56</v>
       </c>
       <c r="R37" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="S37" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="T37" t="n">
-        <v>2.41</v>
+        <v>2.7</v>
       </c>
       <c r="U37" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="V37" t="n">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="W37" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X37" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y37" t="n">
-        <v>12</v>
+        <v>8.75</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AA37" t="n">
-        <v>3.8</v>
+        <v>3.22</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.66</v>
+        <v>1.93</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.65</v>
+        <v>3.3</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.59</v>
+        <v>1.87</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.25</v>
+        <v>1.82</v>
       </c>
       <c r="AH37" t="n">
-        <v>4.5</v>
+        <v>5.9</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,73 +5426,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.94</v>
+        <v>1.48</v>
       </c>
       <c r="M38" t="n">
-        <v>3.28</v>
+        <v>4.1</v>
       </c>
       <c r="N38" t="n">
-        <v>2.33</v>
+        <v>5.81</v>
       </c>
       <c r="O38" t="n">
-        <v>2.15</v>
+        <v>1.48</v>
       </c>
       <c r="P38" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.93</v>
+        <v>3.25</v>
       </c>
       <c r="R38" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S38" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="T38" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="U38" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="V38" t="n">
-        <v>6.55</v>
+        <v>7</v>
       </c>
       <c r="W38" t="n">
         <v>1.08</v>
       </c>
       <c r="X38" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y38" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AA38" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AD38" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AH38" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AI38" t="n">
         <v>1.1</v>
@@ -5522,22 +5522,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,76 +5558,76 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>4</v>
+        <v>2.15</v>
       </c>
       <c r="M39" t="n">
-        <v>3.72</v>
+        <v>3.55</v>
       </c>
       <c r="N39" t="n">
-        <v>1.66</v>
+        <v>2.9</v>
       </c>
       <c r="O39" t="n">
-        <v>2.55</v>
+        <v>1.77</v>
       </c>
       <c r="P39" t="n">
-        <v>13</v>
+        <v>13.75</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.57</v>
+        <v>2.09</v>
       </c>
       <c r="R39" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="S39" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="T39" t="n">
-        <v>2.2</v>
+        <v>2.41</v>
       </c>
       <c r="U39" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="V39" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="W39" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X39" t="n">
         <v>1.03</v>
       </c>
       <c r="Y39" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AA39" t="n">
-        <v>4.75</v>
+        <v>3.8</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.36</v>
+        <v>2.65</v>
       </c>
       <c r="AE39" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF39" t="n">
         <v>1.59</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>1.57</v>
       </c>
       <c r="AG39" t="n">
         <v>2.25</v>
       </c>
       <c r="AH39" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,43 +5690,43 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.48</v>
+        <v>2.46</v>
       </c>
       <c r="M40" t="n">
-        <v>4.1</v>
+        <v>3.36</v>
       </c>
       <c r="N40" t="n">
-        <v>5.81</v>
+        <v>2.65</v>
       </c>
       <c r="O40" t="n">
-        <v>1.48</v>
+        <v>1.83</v>
       </c>
       <c r="P40" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.25</v>
+        <v>2.05</v>
       </c>
       <c r="R40" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S40" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="T40" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="U40" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="V40" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="W40" t="n">
         <v>1.08</v>
       </c>
       <c r="X40" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y40" t="n">
         <v>9</v>
@@ -5735,31 +5735,31 @@
         <v>1.25</v>
       </c>
       <c r="AA40" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.97</v>
+        <v>1.75</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AD40" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AE40" t="n">
         <v>1.33</v>
       </c>
       <c r="AF40" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="AH40" t="n">
-        <v>6</v>
+        <v>6.05</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
@@ -5786,22 +5786,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,28 +5822,28 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3.55</v>
+        <v>2.94</v>
       </c>
       <c r="M41" t="n">
-        <v>3.7</v>
+        <v>3.28</v>
       </c>
       <c r="N41" t="n">
-        <v>1.89</v>
+        <v>2.33</v>
       </c>
       <c r="O41" t="n">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="P41" t="n">
-        <v>12</v>
+        <v>8.5</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.67</v>
+        <v>1.93</v>
       </c>
       <c r="R41" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="T41" t="n">
         <v>2.75</v>
@@ -5852,46 +5852,46 @@
         <v>1.4</v>
       </c>
       <c r="V41" t="n">
-        <v>6.5</v>
+        <v>6.55</v>
       </c>
       <c r="W41" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X41" t="n">
         <v>1.01</v>
       </c>
       <c r="Y41" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AA41" t="n">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AC41" t="n">
         <v>1.83</v>
       </c>
       <c r="AD41" t="n">
-        <v>3.08</v>
+        <v>3.45</v>
       </c>
       <c r="AE41" t="n">
         <v>1.28</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG41" t="n">
         <v>1.91</v>
       </c>
       <c r="AH41" t="n">
-        <v>6.15</v>
+        <v>6.2</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,76 +5954,76 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2</v>
+        <v>1.35</v>
       </c>
       <c r="M42" t="n">
-        <v>3.45</v>
+        <v>4.53</v>
       </c>
       <c r="N42" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P42" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q42" t="n">
         <v>3.2</v>
       </c>
-      <c r="O42" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="P42" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>2.26</v>
-      </c>
       <c r="R42" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="S42" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="T42" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="U42" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="V42" t="n">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="W42" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X42" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y42" t="n">
-        <v>11.4</v>
+        <v>12.5</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AA42" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AC42" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AD42" t="n">
         <v>2.6</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AG42" t="n">
-        <v>2.2</v>
+        <v>1.88</v>
       </c>
       <c r="AH42" t="n">
-        <v>4.95</v>
+        <v>4.6</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
@@ -6050,22 +6050,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,76 +6086,76 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="M43" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="N43" t="n">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="O43" t="n">
-        <v>2.79</v>
+        <v>2.38</v>
       </c>
       <c r="P43" t="n">
-        <v>8.699999999999999</v>
+        <v>12</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="R43" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S43" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="T43" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="U43" t="n">
         <v>1.4</v>
       </c>
       <c r="V43" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="W43" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X43" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="AI43" t="n">
         <v>1.06</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>1.1</v>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6746,13 +6746,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="M48" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="N48" t="n">
-        <v>1.43</v>
+        <v>1.84</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6764,58 +6764,58 @@
         <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="S48" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="T48" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="U48" t="n">
         <v>1.48</v>
       </c>
       <c r="V48" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X48" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AH48" t="n">
         <v>5.75</v>
       </c>
-      <c r="W48" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X48" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>5.5</v>
-      </c>
       <c r="AI48" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6878,13 +6878,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="M49" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="N49" t="n">
-        <v>1.84</v>
+        <v>1.43</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6896,58 +6896,58 @@
         <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="S49" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="T49" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="U49" t="n">
         <v>1.48</v>
       </c>
       <c r="V49" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X49" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH49" t="n">
         <v>5.5</v>
       </c>
-      <c r="W49" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X49" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>5.75</v>
-      </c>
       <c r="AI49" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7010,76 +7010,76 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.83</v>
+        <v>2.27</v>
       </c>
       <c r="M50" t="n">
-        <v>3.71</v>
+        <v>2.85</v>
       </c>
       <c r="N50" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="O50" t="n">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q50" t="n">
         <v>2.6</v>
       </c>
       <c r="R50" t="n">
-        <v>1.31</v>
+        <v>1.54</v>
       </c>
       <c r="S50" t="n">
-        <v>3.14</v>
+        <v>2.15</v>
       </c>
       <c r="T50" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="U50" t="n">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
       <c r="V50" t="n">
+        <v>13</v>
+      </c>
+      <c r="W50" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X50" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Y50" t="n">
         <v>5.5</v>
       </c>
-      <c r="W50" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>10</v>
-      </c>
       <c r="Z50" t="n">
-        <v>1.24</v>
+        <v>1.6</v>
       </c>
       <c r="AA50" t="n">
-        <v>3.79</v>
+        <v>2.2</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.73</v>
+        <v>2.75</v>
       </c>
       <c r="AC50" t="n">
-        <v>2</v>
+        <v>1.39</v>
       </c>
       <c r="AD50" t="n">
-        <v>2.83</v>
+        <v>6</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.38</v>
+        <v>1.12</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.6</v>
+        <v>2.25</v>
       </c>
       <c r="AG50" t="n">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="AH50" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AI50" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7142,76 +7142,76 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.27</v>
+        <v>1.83</v>
       </c>
       <c r="M51" t="n">
-        <v>2.85</v>
+        <v>3.71</v>
       </c>
       <c r="N51" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="O51" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="P51" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
         <v>2.6</v>
       </c>
       <c r="R51" t="n">
-        <v>1.54</v>
+        <v>1.31</v>
       </c>
       <c r="S51" t="n">
-        <v>2.15</v>
+        <v>3.14</v>
       </c>
       <c r="T51" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="U51" t="n">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
       <c r="V51" t="n">
-        <v>13</v>
+        <v>5.5</v>
       </c>
       <c r="W51" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="X51" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="Y51" t="n">
-        <v>5.5</v>
+        <v>10</v>
       </c>
       <c r="Z51" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF51" t="n">
         <v>1.6</v>
       </c>
-      <c r="AA51" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AG51" t="n">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="AH51" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AI51" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="AJ51" t="inlineStr">
         <is>

--- a/jogos_2025-08-01.xlsx
+++ b/jogos_2025-08-01.xlsx
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.26</v>
+        <v>1.52</v>
       </c>
       <c r="M5" t="n">
-        <v>4.04</v>
+        <v>4.36</v>
       </c>
       <c r="N5" t="n">
-        <v>9.77</v>
+        <v>5.11</v>
       </c>
       <c r="O5" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="P5" t="n">
-        <v>11.25</v>
+        <v>17</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.75</v>
+        <v>2.95</v>
       </c>
       <c r="R5" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="T5" t="n">
-        <v>2.6</v>
+        <v>2.42</v>
       </c>
       <c r="U5" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="V5" t="n">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="W5" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X5" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>10.9</v>
+        <v>9</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.78</v>
+        <v>4.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.19</v>
+        <v>1.73</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AH5" t="n">
-        <v>4.85</v>
+        <v>4.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1166,22 +1166,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,76 +1202,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>9.77</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>11.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>10.9</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mariehamn</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>4.36</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>5.11</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="M9" t="n">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="N9" t="n">
-        <v>3.46</v>
+        <v>3.1</v>
       </c>
       <c r="O9" t="n">
         <v>1.77</v>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.62</v>
+        <v>2.5</v>
       </c>
       <c r="M11" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="O11" t="n">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.5</v>
+        <v>2.01</v>
       </c>
       <c r="R11" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S11" t="n">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="T11" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="U11" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="V11" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AC11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG11" t="n">
         <v>2.2</v>
       </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.1</v>
+        <v>2.62</v>
       </c>
       <c r="M12" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="N12" t="n">
-        <v>3.1</v>
+        <v>2.55</v>
       </c>
       <c r="O12" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="P12" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S12" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="T12" t="n">
-        <v>3.01</v>
+        <v>2.5</v>
       </c>
       <c r="U12" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V12" t="n">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X12" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.06</v>
+        <v>1.66</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.78</v>
+        <v>2.15</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AH12" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.42</v>
+        <v>2.1</v>
       </c>
       <c r="M13" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="N13" t="n">
-        <v>5.6</v>
+        <v>3.1</v>
       </c>
       <c r="O13" t="n">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="P13" t="n">
-        <v>12</v>
+        <v>8.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="R13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V13" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AE13" t="n">
         <v>1.3</v>
       </c>
-      <c r="S13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V13" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.46</v>
-      </c>
       <c r="AF13" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AG13" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH13" t="n">
-        <v>4.75</v>
+        <v>6.25</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>6.5</v>
+        <v>1.42</v>
       </c>
       <c r="M14" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="N14" t="n">
-        <v>1.4</v>
+        <v>5.6</v>
       </c>
       <c r="O14" t="n">
-        <v>3</v>
+        <v>1.44</v>
       </c>
       <c r="P14" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.36</v>
+        <v>2.75</v>
       </c>
       <c r="R14" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S14" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="T14" t="n">
-        <v>2.09</v>
+        <v>2.45</v>
       </c>
       <c r="U14" t="n">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="V14" t="n">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X14" t="n">
         <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.45</v>
+        <v>4.33</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.43</v>
+        <v>1.68</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.53</v>
+        <v>2.05</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.15</v>
+        <v>2.52</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH14" t="n">
-        <v>3.72</v>
+        <v>4.55</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.63</v>
+        <v>1.75</v>
       </c>
       <c r="M15" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="N15" t="n">
-        <v>2.41</v>
+        <v>3.6</v>
       </c>
       <c r="O15" t="n">
-        <v>1.98</v>
+        <v>1.58</v>
       </c>
       <c r="P15" t="n">
-        <v>13.25</v>
+        <v>19.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.91</v>
+        <v>2.39</v>
       </c>
       <c r="R15" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="S15" t="n">
-        <v>2.95</v>
+        <v>3.6</v>
       </c>
       <c r="T15" t="n">
-        <v>2.65</v>
+        <v>2.2</v>
       </c>
       <c r="U15" t="n">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="V15" t="n">
-        <v>6.55</v>
+        <v>4.8</v>
       </c>
       <c r="W15" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>8.5</v>
+        <v>14.7</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.6</v>
+        <v>4.75</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.98</v>
+        <v>2.37</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.15</v>
+        <v>2.49</v>
       </c>
       <c r="AH15" t="n">
-        <v>5.65</v>
+        <v>3.74</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2525,73 +2525,73 @@
         <v>2.62</v>
       </c>
       <c r="M16" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N16" t="n">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="O16" t="n">
-        <v>1.83</v>
+        <v>2.07</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="R16" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S16" t="n">
-        <v>3.25</v>
+        <v>3.21</v>
       </c>
       <c r="T16" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="U16" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="V16" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="W16" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,76 +2654,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="M17" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N17" t="n">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="O17" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="P17" t="n">
-        <v>7.7</v>
+        <v>13.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="R17" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="S17" t="n">
-        <v>3.28</v>
+        <v>2.95</v>
       </c>
       <c r="T17" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="U17" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="V17" t="n">
-        <v>5</v>
+        <v>6.55</v>
       </c>
       <c r="W17" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X17" t="n">
         <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>11</v>
+        <v>8.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.87</v>
+        <v>3.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH17" t="n">
-        <v>4.33</v>
+        <v>5.65</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,76 +2786,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.45</v>
+        <v>6.5</v>
       </c>
       <c r="M18" t="n">
-        <v>3.7</v>
+        <v>5.2</v>
       </c>
       <c r="N18" t="n">
-        <v>6.3</v>
+        <v>1.4</v>
       </c>
       <c r="O18" t="n">
-        <v>1.28</v>
+        <v>3</v>
       </c>
       <c r="P18" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.9</v>
+        <v>1.36</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S18" t="n">
-        <v>3.22</v>
+        <v>3.6</v>
       </c>
       <c r="T18" t="n">
-        <v>2.47</v>
+        <v>2.09</v>
       </c>
       <c r="U18" t="n">
-        <v>1.48</v>
+        <v>1.73</v>
       </c>
       <c r="V18" t="n">
-        <v>5.7</v>
+        <v>4.75</v>
       </c>
       <c r="W18" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>8.9</v>
+        <v>16</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.98</v>
+        <v>5.45</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.95</v>
+        <v>1.43</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.75</v>
+        <v>2.53</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.39</v>
+        <v>1.7</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.02</v>
+        <v>1.7</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.71</v>
+        <v>2.1</v>
       </c>
       <c r="AH18" t="n">
-        <v>4.75</v>
+        <v>3.72</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.75</v>
+        <v>1.45</v>
       </c>
       <c r="M19" t="n">
         <v>3.7</v>
       </c>
       <c r="N19" t="n">
-        <v>3.6</v>
+        <v>6.3</v>
       </c>
       <c r="O19" t="n">
-        <v>1.58</v>
+        <v>1.28</v>
       </c>
       <c r="P19" t="n">
-        <v>19.25</v>
+        <v>15</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.39</v>
+        <v>3.9</v>
       </c>
       <c r="R19" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S19" t="n">
-        <v>3.6</v>
+        <v>3.22</v>
       </c>
       <c r="T19" t="n">
-        <v>2.2</v>
+        <v>2.47</v>
       </c>
       <c r="U19" t="n">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="V19" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="W19" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>14.7</v>
+        <v>8.9</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AA19" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AH19" t="n">
         <v>4.75</v>
       </c>
-      <c r="AB19" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>3.74</v>
-      </c>
       <c r="AI19" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,76 +3050,76 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.62</v>
+        <v>3.62</v>
       </c>
       <c r="M20" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="N20" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="O20" t="n">
-        <v>2.07</v>
+        <v>2.63</v>
       </c>
       <c r="P20" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.84</v>
+        <v>1.5</v>
       </c>
       <c r="R20" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="S20" t="n">
-        <v>3.21</v>
+        <v>3.5</v>
       </c>
       <c r="T20" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="U20" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="V20" t="n">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AC20" t="n">
         <v>2.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AH20" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3278,22 +3278,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,76 +3314,76 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="M22" t="n">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="O22" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="P22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S22" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="T22" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="U22" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V22" t="n">
-        <v>7.6</v>
+        <v>5.75</v>
       </c>
       <c r="W22" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X22" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.82</v>
+        <v>2.15</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.35</v>
+        <v>2.7</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AH22" t="n">
-        <v>6.5</v>
+        <v>4.75</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -3410,22 +3410,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,76 +3446,76 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="P23" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q23" t="n">
         <v>2.2</v>
       </c>
-      <c r="M23" t="n">
+      <c r="R23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V23" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA23" t="n">
         <v>3.4</v>
       </c>
-      <c r="N23" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="P23" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="R23" t="n">
+      <c r="AB23" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AE23" t="n">
         <v>1.33</v>
       </c>
-      <c r="S23" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V23" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB23" t="n">
+      <c r="AF23" t="n">
         <v>1.67</v>
       </c>
-      <c r="AC23" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AG23" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AH23" t="n">
-        <v>4.75</v>
+        <v>6.5</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,76 +3974,76 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.75</v>
+        <v>2.04</v>
       </c>
       <c r="M27" t="n">
-        <v>3.3</v>
+        <v>3.78</v>
       </c>
       <c r="N27" t="n">
-        <v>2.48</v>
+        <v>3.15</v>
       </c>
       <c r="O27" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="P27" t="n">
-        <v>11</v>
+        <v>18.25</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.83</v>
+        <v>2.11</v>
       </c>
       <c r="R27" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S27" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="T27" t="n">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="U27" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="V27" t="n">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="W27" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X27" t="n">
         <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AA27" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="AC27" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD27" t="n">
         <v>2.1</v>
       </c>
-      <c r="AD27" t="n">
-        <v>2.62</v>
-      </c>
       <c r="AE27" t="n">
-        <v>1.42</v>
+        <v>1.68</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.37</v>
+        <v>2.67</v>
       </c>
       <c r="AH27" t="n">
-        <v>4.6</v>
+        <v>3.45</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,76 +4106,76 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.04</v>
+        <v>2.75</v>
       </c>
       <c r="M28" t="n">
-        <v>3.78</v>
+        <v>3.3</v>
       </c>
       <c r="N28" t="n">
-        <v>3.15</v>
+        <v>2.48</v>
       </c>
       <c r="O28" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="P28" t="n">
-        <v>18.25</v>
+        <v>11</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.11</v>
+        <v>1.83</v>
       </c>
       <c r="R28" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S28" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="T28" t="n">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="U28" t="n">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="V28" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="W28" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X28" t="n">
         <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="AA28" t="n">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="AB28" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AE28" t="n">
         <v>1.42</v>
       </c>
-      <c r="AC28" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.68</v>
-      </c>
       <c r="AF28" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.67</v>
+        <v>2.37</v>
       </c>
       <c r="AH28" t="n">
-        <v>3.45</v>
+        <v>4.6</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,76 +4370,76 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.99</v>
+        <v>2.24</v>
       </c>
       <c r="M30" t="n">
-        <v>3.21</v>
+        <v>2.96</v>
       </c>
       <c r="N30" t="n">
-        <v>2.36</v>
+        <v>2.98</v>
       </c>
       <c r="O30" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V30" t="n">
         <v>10</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="W30" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG30" t="n">
         <v>1.8</v>
       </c>
-      <c r="R30" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S30" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V30" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AH30" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,76 +4502,76 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.52</v>
+        <v>2.99</v>
       </c>
       <c r="M31" t="n">
-        <v>3.28</v>
+        <v>3.21</v>
       </c>
       <c r="N31" t="n">
-        <v>2.85</v>
+        <v>2.36</v>
       </c>
       <c r="O31" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="P31" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="R31" t="n">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="S31" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="T31" t="n">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="U31" t="n">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="V31" t="n">
-        <v>8.25</v>
+        <v>5.5</v>
       </c>
       <c r="W31" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="X31" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y31" t="n">
-        <v>8.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.9</v>
+        <v>4.75</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.12</v>
+        <v>1.53</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.67</v>
+        <v>2.35</v>
       </c>
       <c r="AD31" t="n">
-        <v>3.75</v>
+        <v>2.25</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>7.8</v>
+        <v>4.2</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.02</v>
+        <v>1.22</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,76 +4634,76 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2</v>
+        <v>2.88</v>
       </c>
       <c r="M32" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="N32" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="O32" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="P32" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S32" t="n">
         <v>3.25</v>
       </c>
-      <c r="N32" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="O32" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="P32" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S32" t="n">
+      <c r="T32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V32" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD32" t="n">
         <v>2.9</v>
       </c>
-      <c r="T32" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U32" t="n">
+      <c r="AE32" t="n">
         <v>1.4</v>
       </c>
-      <c r="V32" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AF32" t="n">
-        <v>1.76</v>
+        <v>1.57</v>
       </c>
       <c r="AG32" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AH32" t="n">
         <v>5.5</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,76 +4766,76 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.24</v>
+        <v>2.52</v>
       </c>
       <c r="M33" t="n">
-        <v>2.96</v>
+        <v>3.28</v>
       </c>
       <c r="N33" t="n">
-        <v>2.98</v>
+        <v>2.85</v>
       </c>
       <c r="O33" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="R33" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S33" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="T33" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="U33" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="V33" t="n">
-        <v>10</v>
+        <v>8.25</v>
       </c>
       <c r="W33" t="n">
         <v>1.06</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,76 +4898,76 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.88</v>
+        <v>2.02</v>
       </c>
       <c r="M34" t="n">
-        <v>2.96</v>
+        <v>3.13</v>
       </c>
       <c r="N34" t="n">
-        <v>2.31</v>
+        <v>3.27</v>
       </c>
       <c r="O34" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="P34" t="n">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="R34" t="n">
         <v>1.33</v>
       </c>
       <c r="S34" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="T34" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="U34" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="V34" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="W34" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X34" t="n">
         <v>1.05</v>
       </c>
       <c r="Y34" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AA34" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AH34" t="n">
         <v>5.5</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,76 +5030,76 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2</v>
+        <v>1.35</v>
       </c>
       <c r="M35" t="n">
-        <v>3.45</v>
+        <v>4.53</v>
       </c>
       <c r="N35" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P35" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q35" t="n">
         <v>3.2</v>
       </c>
-      <c r="O35" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="P35" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>2.26</v>
-      </c>
       <c r="R35" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="S35" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="T35" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="U35" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="V35" t="n">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="W35" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X35" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y35" t="n">
-        <v>11.4</v>
+        <v>12.5</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AA35" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AC35" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AD35" t="n">
         <v>2.6</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.2</v>
+        <v>1.88</v>
       </c>
       <c r="AH35" t="n">
-        <v>4.95</v>
+        <v>4.6</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
@@ -5126,22 +5126,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,76 +5162,76 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="M36" t="n">
-        <v>3.72</v>
+        <v>3.45</v>
       </c>
       <c r="N36" t="n">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="O36" t="n">
-        <v>2.55</v>
+        <v>2.79</v>
       </c>
       <c r="P36" t="n">
-        <v>13</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="R36" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="S36" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="T36" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="U36" t="n">
-        <v>1.58</v>
+        <v>1.4</v>
       </c>
       <c r="V36" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="W36" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="X36" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y36" t="n">
-        <v>11</v>
+        <v>8.75</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AA36" t="n">
-        <v>4.75</v>
+        <v>3.22</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.57</v>
+        <v>1.93</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.36</v>
+        <v>3.3</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.59</v>
+        <v>1.29</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.57</v>
+        <v>1.87</v>
       </c>
       <c r="AG36" t="n">
-        <v>2.25</v>
+        <v>1.82</v>
       </c>
       <c r="AH36" t="n">
-        <v>4.2</v>
+        <v>5.9</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,76 +5294,76 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>4.2</v>
+        <v>2.15</v>
       </c>
       <c r="M37" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="N37" t="n">
-        <v>1.78</v>
+        <v>2.9</v>
       </c>
       <c r="O37" t="n">
-        <v>2.79</v>
+        <v>1.77</v>
       </c>
       <c r="P37" t="n">
-        <v>8.699999999999999</v>
+        <v>13.75</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.56</v>
+        <v>2.09</v>
       </c>
       <c r="R37" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="S37" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="T37" t="n">
-        <v>2.7</v>
+        <v>2.41</v>
       </c>
       <c r="U37" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V37" t="n">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="W37" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X37" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y37" t="n">
-        <v>8.75</v>
+        <v>12</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AA37" t="n">
-        <v>3.22</v>
+        <v>3.8</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.93</v>
+        <v>1.66</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AD37" t="n">
-        <v>3.3</v>
+        <v>2.65</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.87</v>
+        <v>1.59</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.82</v>
+        <v>2.25</v>
       </c>
       <c r="AH37" t="n">
-        <v>5.9</v>
+        <v>4.5</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,76 +5426,76 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.48</v>
+        <v>2</v>
       </c>
       <c r="M38" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="N38" t="n">
-        <v>5.81</v>
+        <v>3.2</v>
       </c>
       <c r="O38" t="n">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
       <c r="P38" t="n">
-        <v>9</v>
+        <v>13.5</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.25</v>
+        <v>2.26</v>
       </c>
       <c r="R38" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="S38" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="T38" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="U38" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="V38" t="n">
-        <v>7</v>
+        <v>5.75</v>
       </c>
       <c r="W38" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X38" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y38" t="n">
-        <v>9</v>
+        <v>11.4</v>
       </c>
       <c r="Z38" t="n">
         <v>1.25</v>
       </c>
       <c r="AA38" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.97</v>
+        <v>1.73</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AD38" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AF38" t="n">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AH38" t="n">
-        <v>6</v>
+        <v>4.95</v>
       </c>
       <c r="AI38" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,76 +5558,76 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.15</v>
+        <v>2.46</v>
       </c>
       <c r="M39" t="n">
-        <v>3.55</v>
+        <v>3.36</v>
       </c>
       <c r="N39" t="n">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="O39" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="P39" t="n">
-        <v>13.75</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="R39" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="S39" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="T39" t="n">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="U39" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="V39" t="n">
         <v>5.5</v>
       </c>
       <c r="W39" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X39" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y39" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AA39" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH39" t="n">
-        <v>4.5</v>
+        <v>6.05</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
@@ -5654,22 +5654,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,76 +5690,76 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.46</v>
+        <v>3.55</v>
       </c>
       <c r="M40" t="n">
-        <v>3.36</v>
+        <v>3.7</v>
       </c>
       <c r="N40" t="n">
-        <v>2.65</v>
+        <v>1.89</v>
       </c>
       <c r="O40" t="n">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="R40" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S40" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="T40" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="U40" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="V40" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="W40" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X40" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y40" t="n">
         <v>9</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AA40" t="n">
-        <v>3.6</v>
+        <v>3.42</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AD40" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="AH40" t="n">
-        <v>6.05</v>
+        <v>6.15</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,76 +5954,76 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="M42" t="n">
-        <v>4.53</v>
+        <v>4.1</v>
       </c>
       <c r="N42" t="n">
-        <v>6.2</v>
+        <v>5.81</v>
       </c>
       <c r="O42" t="n">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="P42" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="Q42" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S42" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V42" t="n">
+        <v>7</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X42" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD42" t="n">
         <v>3.2</v>
       </c>
-      <c r="R42" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S42" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T42" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V42" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X42" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AE42" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AH42" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,76 +6086,76 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="M43" t="n">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="N43" t="n">
-        <v>1.89</v>
+        <v>1.66</v>
       </c>
       <c r="O43" t="n">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="P43" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="R43" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="S43" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="T43" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="U43" t="n">
-        <v>1.4</v>
+        <v>1.58</v>
       </c>
       <c r="V43" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="W43" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X43" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y43" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AA43" t="n">
-        <v>3.42</v>
+        <v>4.75</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="AD43" t="n">
-        <v>3.08</v>
+        <v>2.36</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.28</v>
+        <v>1.59</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="AH43" t="n">
-        <v>6.15</v>
+        <v>4.2</v>
       </c>
       <c r="AI43" t="n">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
@@ -6482,13 +6482,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="M46" t="n">
-        <v>3.15</v>
+        <v>3.11</v>
       </c>
       <c r="N46" t="n">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="O46" t="n">
         <v>1.68</v>
@@ -6500,22 +6500,22 @@
         <v>2.7</v>
       </c>
       <c r="R46" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="S46" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="T46" t="n">
         <v>3.6</v>
       </c>
       <c r="U46" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="V46" t="n">
         <v>9</v>
       </c>
       <c r="W46" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X46" t="n">
         <v>1.05</v>
@@ -6524,19 +6524,19 @@
         <v>6.2</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="AB46" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AD46" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AE46" t="n">
         <v>1.12</v>
@@ -6545,10 +6545,10 @@
         <v>2.25</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AH46" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="AI46" t="n">
         <v>1.04</v>
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6746,13 +6746,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="M48" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="N48" t="n">
-        <v>1.84</v>
+        <v>1.43</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6764,58 +6764,58 @@
         <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="S48" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="T48" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="U48" t="n">
         <v>1.48</v>
       </c>
       <c r="V48" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X48" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH48" t="n">
         <v>5.5</v>
       </c>
-      <c r="W48" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X48" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>5.75</v>
-      </c>
       <c r="AI48" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6878,13 +6878,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="M49" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="N49" t="n">
-        <v>1.43</v>
+        <v>1.84</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6896,58 +6896,58 @@
         <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="S49" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="T49" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="U49" t="n">
         <v>1.48</v>
       </c>
       <c r="V49" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X49" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AH49" t="n">
         <v>5.75</v>
       </c>
-      <c r="W49" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X49" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>5.5</v>
-      </c>
       <c r="AI49" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
@@ -7010,13 +7010,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.27</v>
+        <v>1.87</v>
       </c>
       <c r="M50" t="n">
-        <v>2.85</v>
+        <v>3.11</v>
       </c>
       <c r="N50" t="n">
-        <v>3.25</v>
+        <v>3.78</v>
       </c>
       <c r="O50" t="n">
         <v>1.72</v>
@@ -7028,13 +7028,13 @@
         <v>2.6</v>
       </c>
       <c r="R50" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="S50" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="T50" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="U50" t="n">
         <v>1.22</v>
@@ -7046,34 +7046,34 @@
         <v>1.02</v>
       </c>
       <c r="X50" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Y50" t="n">
         <v>5.5</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.2</v>
+        <v>2.37</v>
       </c>
       <c r="AB50" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="AD50" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="AE50" t="n">
         <v>1.12</v>
       </c>
       <c r="AF50" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AH50" t="n">
         <v>11</v>
@@ -7142,13 +7142,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="M51" t="n">
-        <v>3.71</v>
+        <v>3.5</v>
       </c>
       <c r="N51" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="O51" t="n">
         <v>1.57</v>
@@ -7160,16 +7160,16 @@
         <v>2.6</v>
       </c>
       <c r="R51" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S51" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="T51" t="n">
         <v>2.5</v>
       </c>
       <c r="U51" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="V51" t="n">
         <v>5.5</v>
@@ -7184,22 +7184,22 @@
         <v>10</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AA51" t="n">
-        <v>3.79</v>
+        <v>3.9</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="AC51" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AD51" t="n">
         <v>2.83</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AF51" t="n">
         <v>1.6</v>
@@ -7211,7 +7211,7 @@
         <v>5</v>
       </c>
       <c r="AI51" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
@@ -7274,13 +7274,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="M52" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="N52" t="n">
-        <v>4.33</v>
+        <v>4.7</v>
       </c>
       <c r="O52" t="n">
         <v>1.62</v>
@@ -7301,13 +7301,13 @@
         <v>2.48</v>
       </c>
       <c r="U52" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="V52" t="n">
         <v>6</v>
       </c>
       <c r="W52" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X52" t="n">
         <v>1</v>
@@ -7322,28 +7322,28 @@
         <v>3.5</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AD52" t="n">
         <v>2.92</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG52" t="n">
         <v>1.97</v>
       </c>
       <c r="AH52" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AI52" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AJ52" t="inlineStr">
         <is>

--- a/jogos_2025-08-01.xlsx
+++ b/jogos_2025-08-01.xlsx
@@ -806,13 +806,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.87</v>
+        <v>2.93</v>
       </c>
       <c r="M3" t="n">
-        <v>3.68</v>
+        <v>3.75</v>
       </c>
       <c r="N3" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="O3" t="n">
         <v>2.08</v>
@@ -827,55 +827,55 @@
         <v>1.25</v>
       </c>
       <c r="S3" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="T3" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="U3" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="V3" t="n">
         <v>5.2</v>
       </c>
       <c r="W3" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X3" t="n">
         <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.06</v>
+        <v>4.6</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AG3" t="n">
         <v>2.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.7</v>
+        <v>3.92</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -902,22 +902,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rukh Vynnyky</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SK Poltava</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="M4" t="n">
-        <v>3.41</v>
+        <v>3.9</v>
       </c>
       <c r="N4" t="n">
-        <v>5.9</v>
+        <v>4.9</v>
       </c>
       <c r="O4" t="n">
         <v>1.44</v>
       </c>
       <c r="P4" t="n">
-        <v>6.4</v>
+        <v>17</v>
       </c>
       <c r="Q4" t="n">
-        <v>4</v>
+        <v>2.95</v>
       </c>
       <c r="R4" t="n">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="S4" t="n">
-        <v>2.25</v>
+        <v>3.3</v>
       </c>
       <c r="T4" t="n">
-        <v>3.75</v>
+        <v>2.42</v>
       </c>
       <c r="U4" t="n">
-        <v>1.25</v>
+        <v>1.51</v>
       </c>
       <c r="V4" t="n">
-        <v>8.5</v>
+        <v>5.3</v>
       </c>
       <c r="W4" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X4" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.4</v>
+        <v>12</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.5</v>
+        <v>1.21</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.3</v>
+        <v>4.33</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.63</v>
+        <v>1.68</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.44</v>
+        <v>2.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>5.1</v>
+        <v>2.62</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.1</v>
+        <v>1.45</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.63</v>
+        <v>1.73</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.44</v>
+        <v>2.05</v>
       </c>
       <c r="AH4" t="n">
-        <v>8.5</v>
+        <v>4.6</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Rukh Vynnyky</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mariehamn</t>
+          <t>SK Poltava</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="M5" t="n">
-        <v>4.36</v>
+        <v>3.41</v>
       </c>
       <c r="N5" t="n">
-        <v>5.11</v>
+        <v>5.9</v>
       </c>
       <c r="O5" t="n">
         <v>1.44</v>
       </c>
       <c r="P5" t="n">
-        <v>17</v>
+        <v>6.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.95</v>
+        <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="S5" t="n">
-        <v>3.3</v>
+        <v>2.25</v>
       </c>
       <c r="T5" t="n">
-        <v>2.42</v>
+        <v>3.75</v>
       </c>
       <c r="U5" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="V5" t="n">
-        <v>5.25</v>
+        <v>8.5</v>
       </c>
       <c r="W5" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X5" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y5" t="n">
-        <v>9</v>
+        <v>6.4</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.16</v>
+        <v>1.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.62</v>
+        <v>2.65</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.15</v>
+        <v>1.42</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.62</v>
+        <v>5.1</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.45</v>
+        <v>1.1</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.73</v>
+        <v>2.63</v>
       </c>
       <c r="AG5" t="n">
-        <v>2</v>
+        <v>1.44</v>
       </c>
       <c r="AH5" t="n">
-        <v>4.5</v>
+        <v>8.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1166,22 +1166,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,76 +1202,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.26</v>
+        <v>3.5</v>
       </c>
       <c r="M6" t="n">
-        <v>4.04</v>
+        <v>2.95</v>
       </c>
       <c r="N6" t="n">
-        <v>9.77</v>
+        <v>2.1</v>
       </c>
       <c r="O6" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="P6" t="n">
-        <v>11.25</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.75</v>
+        <v>1.8</v>
       </c>
       <c r="R6" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U6" t="n">
         <v>1.33</v>
       </c>
-      <c r="S6" t="n">
+      <c r="V6" t="n">
+        <v>8</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA6" t="n">
         <v>3</v>
       </c>
-      <c r="T6" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V6" t="n">
-        <v>6</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>3.78</v>
-      </c>
       <c r="AB6" t="n">
-        <v>1.72</v>
+        <v>2.1</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.07</v>
+        <v>1.65</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.65</v>
+        <v>3.8</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.19</v>
+        <v>1.87</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AH6" t="n">
-        <v>4.85</v>
+        <v>7.1</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>11.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>8.23</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>11.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.05</v>
+        <v>2.56</v>
       </c>
       <c r="M9" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="N9" t="n">
-        <v>3.1</v>
+        <v>2.57</v>
       </c>
       <c r="O9" t="n">
         <v>1.77</v>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.5</v>
+        <v>2.81</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="O11" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="P11" t="n">
-        <v>7.7</v>
+        <v>13.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="R11" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="S11" t="n">
-        <v>3.28</v>
+        <v>3.04</v>
       </c>
       <c r="T11" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="U11" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V11" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.87</v>
+        <v>3.7</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH11" t="n">
-        <v>4.33</v>
+        <v>5.25</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.62</v>
+        <v>2.49</v>
       </c>
       <c r="M12" t="n">
         <v>3.5</v>
       </c>
       <c r="N12" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="O12" t="n">
         <v>1.83</v>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="M13" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="N13" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="O13" t="n">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="P13" t="n">
-        <v>8.5</v>
+        <v>19.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="S13" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="T13" t="n">
-        <v>3.01</v>
+        <v>2.2</v>
       </c>
       <c r="U13" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="V13" t="n">
-        <v>7.5</v>
+        <v>4.75</v>
       </c>
       <c r="W13" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="X13" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>9</v>
+        <v>14.7</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.32</v>
+        <v>1.12</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.48</v>
+        <v>5.2</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.06</v>
+        <v>1.51</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.78</v>
+        <v>2.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>3.35</v>
+        <v>2.2</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.77</v>
+        <v>1.45</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="AH13" t="n">
-        <v>6.25</v>
+        <v>3.74</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.42</v>
+        <v>3.62</v>
       </c>
       <c r="M14" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="N14" t="n">
-        <v>5.6</v>
+        <v>1.75</v>
       </c>
       <c r="O14" t="n">
-        <v>1.44</v>
+        <v>2.63</v>
       </c>
       <c r="P14" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.75</v>
+        <v>1.5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S14" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="T14" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="U14" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="V14" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG14" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH14" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.75</v>
+        <v>5.7</v>
       </c>
       <c r="M15" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="N15" t="n">
-        <v>3.6</v>
+        <v>1.43</v>
       </c>
       <c r="O15" t="n">
-        <v>1.58</v>
+        <v>3</v>
       </c>
       <c r="P15" t="n">
-        <v>19.25</v>
+        <v>17</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.39</v>
+        <v>1.36</v>
       </c>
       <c r="R15" t="n">
         <v>1.25</v>
       </c>
       <c r="S15" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="T15" t="n">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="U15" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="V15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AA15" t="n">
         <v>4.8</v>
       </c>
-      <c r="W15" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>4.75</v>
-      </c>
       <c r="AB15" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.49</v>
+        <v>1.98</v>
       </c>
       <c r="AH15" t="n">
-        <v>3.74</v>
+        <v>4.25</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,76 +2522,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.62</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="N16" t="n">
-        <v>2.2</v>
+        <v>3.15</v>
       </c>
       <c r="O16" t="n">
-        <v>2.07</v>
+        <v>1.8</v>
       </c>
       <c r="P16" t="n">
-        <v>13</v>
+        <v>8.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.84</v>
+        <v>2.25</v>
       </c>
       <c r="R16" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="S16" t="n">
-        <v>3.21</v>
+        <v>2.7</v>
       </c>
       <c r="T16" t="n">
-        <v>2.4</v>
+        <v>2.89</v>
       </c>
       <c r="U16" t="n">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="V16" t="n">
-        <v>5.6</v>
+        <v>6.25</v>
       </c>
       <c r="W16" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AA16" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.62</v>
+        <v>2.02</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.47</v>
+        <v>3.6</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.48</v>
+        <v>1.29</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.38</v>
+        <v>1.95</v>
       </c>
       <c r="AH16" t="n">
-        <v>4.39</v>
+        <v>6.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,76 +2654,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.63</v>
+        <v>2.78</v>
       </c>
       <c r="M17" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="N17" t="n">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="O17" t="n">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="P17" t="n">
-        <v>13.25</v>
+        <v>13</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="R17" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="S17" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="T17" t="n">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="U17" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="V17" t="n">
-        <v>6.55</v>
+        <v>5.6</v>
       </c>
       <c r="W17" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>8.5</v>
+        <v>11</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.88</v>
+        <v>2.47</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.32</v>
+        <v>1.48</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>5.65</v>
+        <v>4.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,76 +2786,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>6.5</v>
+        <v>1.42</v>
       </c>
       <c r="M18" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="N18" t="n">
-        <v>1.4</v>
+        <v>5.6</v>
       </c>
       <c r="O18" t="n">
-        <v>3</v>
+        <v>1.44</v>
       </c>
       <c r="P18" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.36</v>
+        <v>2.75</v>
       </c>
       <c r="R18" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S18" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="T18" t="n">
-        <v>2.09</v>
+        <v>2.3</v>
       </c>
       <c r="U18" t="n">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="V18" t="n">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>5.45</v>
+        <v>4</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.53</v>
+        <v>2.13</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.15</v>
+        <v>2.62</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.7</v>
+        <v>1.47</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.72</v>
+        <v>4.55</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.45</v>
+        <v>2.6</v>
       </c>
       <c r="M19" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>6.3</v>
+        <v>2.3</v>
       </c>
       <c r="O19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P19" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="R19" t="n">
         <v>1.28</v>
       </c>
-      <c r="P19" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.3</v>
-      </c>
       <c r="S19" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="T19" t="n">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="U19" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="V19" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="W19" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>8.9</v>
+        <v>13</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.95</v>
+        <v>1.66</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.02</v>
+        <v>1.58</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.71</v>
+        <v>2.32</v>
       </c>
       <c r="AH19" t="n">
-        <v>4.75</v>
+        <v>5.6</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,76 +3050,76 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.62</v>
+        <v>1.45</v>
       </c>
       <c r="M20" t="n">
         <v>3.7</v>
       </c>
       <c r="N20" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P20" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V20" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC20" t="n">
         <v>1.75</v>
       </c>
-      <c r="O20" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.67</v>
+        <v>2.02</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.1</v>
+        <v>1.71</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="M21" t="n">
-        <v>5.37</v>
+        <v>6.8</v>
       </c>
       <c r="N21" t="n">
-        <v>13</v>
+        <v>11.95</v>
       </c>
       <c r="O21" t="n">
         <v>1.22</v>
@@ -3203,55 +3203,55 @@
         <v>1.21</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="T21" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="U21" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="V21" t="n">
         <v>3.6</v>
       </c>
       <c r="W21" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>16.5</v>
+        <v>26</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AA21" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AC21" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AH21" t="n">
         <v>2.75</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -3278,22 +3278,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,76 +3314,76 @@
         </is>
       </c>
       <c r="L22" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="P22" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q22" t="n">
         <v>2.2</v>
       </c>
-      <c r="M22" t="n">
+      <c r="R22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V22" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA22" t="n">
         <v>3.4</v>
       </c>
-      <c r="N22" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="P22" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="R22" t="n">
+      <c r="AB22" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AE22" t="n">
         <v>1.33</v>
       </c>
-      <c r="S22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V22" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB22" t="n">
+      <c r="AF22" t="n">
         <v>1.67</v>
       </c>
-      <c r="AC22" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AG22" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AH22" t="n">
-        <v>4.75</v>
+        <v>6.5</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -3410,22 +3410,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,76 +3446,76 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="M23" t="n">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="O23" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="P23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="R23" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S23" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="T23" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="U23" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V23" t="n">
-        <v>7.6</v>
+        <v>5.75</v>
       </c>
       <c r="W23" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X23" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.82</v>
+        <v>2.15</v>
       </c>
       <c r="AD23" t="n">
-        <v>3.35</v>
+        <v>2.7</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AH23" t="n">
-        <v>6.5</v>
+        <v>4.75</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -3578,40 +3578,40 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>
@@ -3638,10 +3638,10 @@
         <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH24" t="n">
         <v>0</v>
@@ -3716,7 +3716,7 @@
         <v>3.75</v>
       </c>
       <c r="N25" t="n">
-        <v>6.79</v>
+        <v>6.5</v>
       </c>
       <c r="O25" t="n">
         <v>1.44</v>
@@ -3728,16 +3728,16 @@
         <v>3.1</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S25" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="T25" t="n">
         <v>2.62</v>
       </c>
       <c r="U25" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="V25" t="n">
         <v>6</v>
@@ -3749,25 +3749,25 @@
         <v>1.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC25" t="n">
         <v>2</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AF25" t="n">
         <v>1.91</v>
@@ -3779,7 +3779,7 @@
         <v>5.2</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>2.75</v>
       </c>
       <c r="R26" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S26" t="n">
         <v>2.8</v>
@@ -3869,31 +3869,31 @@
         <v>2.85</v>
       </c>
       <c r="U26" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="V26" t="n">
-        <v>7</v>
+        <v>6.95</v>
       </c>
       <c r="W26" t="n">
         <v>1.08</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y26" t="n">
-        <v>8.5</v>
+        <v>8.75</v>
       </c>
       <c r="Z26" t="n">
         <v>1.32</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AB26" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AD26" t="n">
         <v>3.5</v>
@@ -3905,13 +3905,13 @@
         <v>1.9</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AH26" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,76 +3974,76 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.04</v>
+        <v>2.7</v>
       </c>
       <c r="M27" t="n">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="N27" t="n">
-        <v>3.15</v>
+        <v>2.4</v>
       </c>
       <c r="O27" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="P27" t="n">
-        <v>18.25</v>
+        <v>11</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.11</v>
+        <v>1.83</v>
       </c>
       <c r="R27" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="S27" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="T27" t="n">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="U27" t="n">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="V27" t="n">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="W27" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X27" t="n">
         <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>18</v>
+        <v>12.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="AA27" t="n">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.42</v>
+        <v>1.7</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.6</v>
+        <v>2.08</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.1</v>
+        <v>2.67</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.68</v>
+        <v>1.44</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.67</v>
+        <v>2.37</v>
       </c>
       <c r="AH27" t="n">
-        <v>3.45</v>
+        <v>4.6</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,76 +4106,76 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.75</v>
+        <v>1.92</v>
       </c>
       <c r="M28" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="N28" t="n">
-        <v>2.48</v>
+        <v>3.1</v>
       </c>
       <c r="O28" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="P28" t="n">
-        <v>11</v>
+        <v>18.25</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.83</v>
+        <v>2.11</v>
       </c>
       <c r="R28" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="S28" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="T28" t="n">
-        <v>2.4</v>
+        <v>2.09</v>
       </c>
       <c r="U28" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="V28" t="n">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="W28" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X28" t="n">
         <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AA28" t="n">
-        <v>4</v>
+        <v>5.68</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.1</v>
+        <v>2.62</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.62</v>
+        <v>2.04</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.42</v>
+        <v>1.68</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.37</v>
+        <v>2.7</v>
       </c>
       <c r="AH28" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
@@ -4241,10 +4241,10 @@
         <v>1.38</v>
       </c>
       <c r="M29" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="N29" t="n">
-        <v>8.1</v>
+        <v>6.7</v>
       </c>
       <c r="O29" t="n">
         <v>1.36</v>
@@ -4259,16 +4259,16 @@
         <v>1.33</v>
       </c>
       <c r="S29" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="T29" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="U29" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="V29" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="W29" t="n">
         <v>1.07</v>
@@ -4277,25 +4277,25 @@
         <v>1</v>
       </c>
       <c r="Y29" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="Z29" t="n">
         <v>1.25</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.6</v>
+        <v>3.52</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AD29" t="n">
         <v>2.93</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AF29" t="n">
         <v>2</v>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,76 +4370,76 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.24</v>
+        <v>2.41</v>
       </c>
       <c r="M30" t="n">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="N30" t="n">
-        <v>2.98</v>
+        <v>2.84</v>
       </c>
       <c r="O30" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="R30" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S30" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="T30" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="U30" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="V30" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="W30" t="n">
         <v>1.06</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB30" t="n">
         <v>2.2</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,76 +4502,76 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.99</v>
+        <v>2.88</v>
       </c>
       <c r="M31" t="n">
-        <v>3.21</v>
+        <v>2.96</v>
       </c>
       <c r="N31" t="n">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="O31" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="P31" t="n">
         <v>10</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="R31" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="S31" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="T31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V31" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG31" t="n">
         <v>2.25</v>
       </c>
-      <c r="U31" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V31" t="n">
+      <c r="AH31" t="n">
         <v>5.5</v>
       </c>
-      <c r="W31" t="n">
+      <c r="AI31" t="n">
         <v>1.14</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>1.22</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,76 +4634,76 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.88</v>
+        <v>2.07</v>
       </c>
       <c r="M32" t="n">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="N32" t="n">
-        <v>2.31</v>
+        <v>3</v>
       </c>
       <c r="O32" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="P32" t="n">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="R32" t="n">
         <v>1.33</v>
       </c>
       <c r="S32" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="T32" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="U32" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="V32" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="W32" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X32" t="n">
         <v>1.05</v>
       </c>
       <c r="Y32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z32" t="n">
         <v>1.25</v>
       </c>
       <c r="AA32" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AH32" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,76 +4766,76 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.52</v>
+        <v>2.24</v>
       </c>
       <c r="M33" t="n">
-        <v>3.28</v>
+        <v>2.96</v>
       </c>
       <c r="N33" t="n">
-        <v>2.85</v>
+        <v>2.98</v>
       </c>
       <c r="O33" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="P33" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="R33" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S33" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="T33" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="U33" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="V33" t="n">
-        <v>8.25</v>
+        <v>10</v>
       </c>
       <c r="W33" t="n">
         <v>1.06</v>
       </c>
       <c r="X33" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AD33" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AH33" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,76 +4898,76 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.02</v>
+        <v>2.99</v>
       </c>
       <c r="M34" t="n">
-        <v>3.13</v>
+        <v>3.21</v>
       </c>
       <c r="N34" t="n">
-        <v>3.27</v>
+        <v>2.36</v>
       </c>
       <c r="O34" t="n">
+        <v>2</v>
+      </c>
+      <c r="P34" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q34" t="n">
         <v>1.8</v>
       </c>
-      <c r="P34" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>2.2</v>
-      </c>
       <c r="R34" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="S34" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="T34" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="U34" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="V34" t="n">
-        <v>6.8</v>
+        <v>5.5</v>
       </c>
       <c r="W34" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X34" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y34" t="n">
         <v>10</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AA34" t="n">
-        <v>3.3</v>
+        <v>4.75</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.95</v>
+        <v>1.56</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.75</v>
+        <v>2.27</v>
       </c>
       <c r="AD34" t="n">
-        <v>3.3</v>
+        <v>2.25</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="AH34" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,76 +5030,76 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.35</v>
+        <v>4.32</v>
       </c>
       <c r="M35" t="n">
-        <v>4.53</v>
+        <v>3.45</v>
       </c>
       <c r="N35" t="n">
-        <v>6.2</v>
+        <v>1.79</v>
       </c>
       <c r="O35" t="n">
-        <v>1.35</v>
+        <v>2.79</v>
       </c>
       <c r="P35" t="n">
-        <v>16</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.2</v>
+        <v>1.56</v>
       </c>
       <c r="R35" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="S35" t="n">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="T35" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="U35" t="n">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="V35" t="n">
-        <v>5.25</v>
+        <v>6.5</v>
       </c>
       <c r="W35" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X35" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y35" t="n">
-        <v>12.5</v>
+        <v>9</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="AA35" t="n">
-        <v>4.4</v>
+        <v>3.22</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.61</v>
+        <v>2.02</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.6</v>
+        <v>3.27</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AG35" t="n">
         <v>1.88</v>
       </c>
       <c r="AH35" t="n">
-        <v>4.6</v>
+        <v>6.25</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,76 +5162,76 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="M36" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="N36" t="n">
-        <v>1.78</v>
+        <v>2.38</v>
       </c>
       <c r="O36" t="n">
-        <v>2.79</v>
+        <v>2.15</v>
       </c>
       <c r="P36" t="n">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.56</v>
+        <v>1.93</v>
       </c>
       <c r="R36" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="S36" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="T36" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="U36" t="n">
         <v>1.4</v>
       </c>
       <c r="V36" t="n">
-        <v>7.5</v>
+        <v>6.4</v>
       </c>
       <c r="W36" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X36" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y36" t="n">
-        <v>8.75</v>
+        <v>9</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AA36" t="n">
-        <v>3.22</v>
+        <v>3.5</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AD36" t="n">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="AE36" t="n">
         <v>1.29</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AH36" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="M37" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="N37" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="O37" t="n">
         <v>1.77</v>
@@ -5318,10 +5318,10 @@
         <v>3.1</v>
       </c>
       <c r="T37" t="n">
-        <v>2.41</v>
+        <v>2.51</v>
       </c>
       <c r="U37" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="V37" t="n">
         <v>5.5</v>
@@ -5330,40 +5330,40 @@
         <v>1.11</v>
       </c>
       <c r="X37" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y37" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z37" t="n">
         <v>1.2</v>
       </c>
       <c r="AA37" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AB37" t="n">
         <v>1.66</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="AG37" t="n">
         <v>2.25</v>
       </c>
       <c r="AH37" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
@@ -5426,13 +5426,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="M38" t="n">
         <v>3.45</v>
       </c>
       <c r="N38" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="O38" t="n">
         <v>1.67</v>
@@ -5450,10 +5450,10 @@
         <v>3.1</v>
       </c>
       <c r="T38" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="U38" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="V38" t="n">
         <v>5.75</v>
@@ -5462,10 +5462,10 @@
         <v>1.11</v>
       </c>
       <c r="X38" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y38" t="n">
-        <v>11.4</v>
+        <v>12</v>
       </c>
       <c r="Z38" t="n">
         <v>1.25</v>
@@ -5474,28 +5474,28 @@
         <v>3.8</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC38" t="n">
         <v>2</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH38" t="n">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="AI38" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,76 +5558,76 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.46</v>
+        <v>1.36</v>
       </c>
       <c r="M39" t="n">
-        <v>3.36</v>
+        <v>4.6</v>
       </c>
       <c r="N39" t="n">
-        <v>2.65</v>
+        <v>5.75</v>
       </c>
       <c r="O39" t="n">
-        <v>1.83</v>
+        <v>1.35</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.05</v>
+        <v>3.2</v>
       </c>
       <c r="R39" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="S39" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="T39" t="n">
-        <v>2.6</v>
+        <v>2.39</v>
       </c>
       <c r="U39" t="n">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="V39" t="n">
         <v>5.5</v>
       </c>
       <c r="W39" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X39" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y39" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AA39" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AD39" t="n">
-        <v>3</v>
+        <v>2.46</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AH39" t="n">
-        <v>6.05</v>
+        <v>4.4</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
@@ -5786,22 +5786,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,76 +5822,76 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.94</v>
+        <v>4</v>
       </c>
       <c r="M41" t="n">
-        <v>3.28</v>
+        <v>3.72</v>
       </c>
       <c r="N41" t="n">
-        <v>2.33</v>
+        <v>1.66</v>
       </c>
       <c r="O41" t="n">
-        <v>2.15</v>
+        <v>2.55</v>
       </c>
       <c r="P41" t="n">
-        <v>8.5</v>
+        <v>13</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.93</v>
+        <v>1.57</v>
       </c>
       <c r="R41" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="S41" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="T41" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="U41" t="n">
-        <v>1.4</v>
+        <v>1.58</v>
       </c>
       <c r="V41" t="n">
-        <v>6.55</v>
+        <v>5</v>
       </c>
       <c r="W41" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="X41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y41" t="n">
-        <v>8.5</v>
+        <v>11</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AA41" t="n">
-        <v>3.3</v>
+        <v>4.75</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.91</v>
+        <v>1.52</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.83</v>
+        <v>2.35</v>
       </c>
       <c r="AD41" t="n">
-        <v>3.45</v>
+        <v>2.36</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.28</v>
+        <v>1.59</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="AH41" t="n">
-        <v>6.2</v>
+        <v>4.2</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="M42" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="N42" t="n">
-        <v>5.81</v>
+        <v>5.83</v>
       </c>
       <c r="O42" t="n">
         <v>1.48</v>
@@ -5972,13 +5972,13 @@
         <v>3.25</v>
       </c>
       <c r="R42" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S42" t="n">
         <v>2.88</v>
       </c>
       <c r="T42" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="U42" t="n">
         <v>1.39</v>
@@ -5987,43 +5987,43 @@
         <v>7</v>
       </c>
       <c r="W42" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X42" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y42" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AA42" t="n">
         <v>3.5</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AD42" t="n">
         <v>3.2</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AF42" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AH42" t="n">
-        <v>6</v>
+        <v>6.57</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
@@ -6050,22 +6050,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,76 +6086,76 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>4</v>
+        <v>2.49</v>
       </c>
       <c r="M43" t="n">
-        <v>3.72</v>
+        <v>3.25</v>
       </c>
       <c r="N43" t="n">
-        <v>1.66</v>
+        <v>2.65</v>
       </c>
       <c r="O43" t="n">
-        <v>2.55</v>
+        <v>1.83</v>
       </c>
       <c r="P43" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.57</v>
+        <v>2.05</v>
       </c>
       <c r="R43" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="S43" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="T43" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="U43" t="n">
-        <v>1.58</v>
+        <v>1.42</v>
       </c>
       <c r="V43" t="n">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="W43" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="X43" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y43" t="n">
         <v>11</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AA43" t="n">
-        <v>4.75</v>
+        <v>3.6</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.3</v>
+        <v>1.89</v>
       </c>
       <c r="AD43" t="n">
-        <v>2.36</v>
+        <v>3.04</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.59</v>
+        <v>1.33</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AG43" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH43" t="n">
-        <v>4.2</v>
+        <v>5.91</v>
       </c>
       <c r="AI43" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
@@ -6350,10 +6350,10 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.19</v>
+        <v>2.4</v>
       </c>
       <c r="M45" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="N45" t="n">
         <v>3</v>
@@ -6368,58 +6368,58 @@
         <v>2.24</v>
       </c>
       <c r="R45" t="n">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="S45" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="T45" t="n">
-        <v>3.1</v>
+        <v>3.56</v>
       </c>
       <c r="U45" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="V45" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="W45" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X45" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Y45" t="n">
         <v>6.5</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.66</v>
+        <v>2.4</v>
       </c>
       <c r="AB45" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="AD45" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AH45" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="AI45" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
@@ -6482,13 +6482,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="M46" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="N46" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="O46" t="n">
         <v>1.68</v>
@@ -6500,19 +6500,19 @@
         <v>2.7</v>
       </c>
       <c r="R46" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="S46" t="n">
         <v>2.3</v>
       </c>
       <c r="T46" t="n">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="U46" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="V46" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="W46" t="n">
         <v>1.04</v>
@@ -6521,37 +6521,37 @@
         <v>1.05</v>
       </c>
       <c r="Y46" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.36</v>
+        <v>2.7</v>
       </c>
       <c r="AB46" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AD46" t="n">
-        <v>4.75</v>
+        <v>4.3</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AF46" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AH46" t="n">
-        <v>9.1</v>
+        <v>8.4</v>
       </c>
       <c r="AI46" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6746,73 +6746,73 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="M48" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="N48" t="n">
-        <v>1.43</v>
+        <v>1.84</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P48" t="n">
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="R48" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="S48" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="T48" t="n">
-        <v>2.58</v>
+        <v>2.61</v>
       </c>
       <c r="U48" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="V48" t="n">
-        <v>5.75</v>
+        <v>5.8</v>
       </c>
       <c r="W48" t="n">
         <v>1.1</v>
       </c>
       <c r="X48" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y48" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AA48" t="n">
         <v>3.8</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AD48" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AH48" t="n">
-        <v>5.5</v>
+        <v>5.95</v>
       </c>
       <c r="AI48" t="n">
         <v>1.14</v>
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6878,13 +6878,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="M49" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="N49" t="n">
-        <v>1.84</v>
+        <v>1.47</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6896,58 +6896,58 @@
         <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="S49" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="T49" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="U49" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="V49" t="n">
-        <v>5.5</v>
+        <v>6.1</v>
       </c>
       <c r="W49" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X49" t="n">
         <v>1.02</v>
       </c>
       <c r="Y49" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AA49" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC49" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AD49" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.72</v>
+        <v>1.88</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.97</v>
+        <v>1.78</v>
       </c>
       <c r="AH49" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="AI49" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7010,76 +7010,76 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="M50" t="n">
-        <v>3.11</v>
+        <v>3.75</v>
       </c>
       <c r="N50" t="n">
-        <v>3.78</v>
+        <v>4</v>
       </c>
       <c r="O50" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="P50" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
         <v>2.6</v>
       </c>
       <c r="R50" t="n">
-        <v>1.58</v>
+        <v>1.3</v>
       </c>
       <c r="S50" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V50" t="n">
+        <v>6</v>
+      </c>
+      <c r="W50" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X50" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG50" t="n">
         <v>2.1</v>
       </c>
-      <c r="T50" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="U50" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V50" t="n">
-        <v>13</v>
-      </c>
-      <c r="W50" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X50" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AH50" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AI50" t="n">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7142,76 +7142,76 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.86</v>
+        <v>2.25</v>
       </c>
       <c r="M51" t="n">
-        <v>3.5</v>
+        <v>2.84</v>
       </c>
       <c r="N51" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="O51" t="n">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q51" t="n">
         <v>2.6</v>
       </c>
       <c r="R51" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="S51" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="T51" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="U51" t="n">
-        <v>1.42</v>
+        <v>1.22</v>
       </c>
       <c r="V51" t="n">
+        <v>10</v>
+      </c>
+      <c r="W51" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X51" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Y51" t="n">
         <v>5.5</v>
       </c>
-      <c r="W51" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X51" t="n">
+      <c r="Z51" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI51" t="n">
         <v>1.01</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>5</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>1.14</v>
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
@@ -7274,13 +7274,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="M52" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="N52" t="n">
-        <v>4.7</v>
+        <v>4.25</v>
       </c>
       <c r="O52" t="n">
         <v>1.62</v>
@@ -7298,49 +7298,49 @@
         <v>2.95</v>
       </c>
       <c r="T52" t="n">
-        <v>2.48</v>
+        <v>2.65</v>
       </c>
       <c r="U52" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="V52" t="n">
         <v>6</v>
       </c>
       <c r="W52" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X52" t="n">
         <v>1</v>
       </c>
       <c r="Y52" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AA52" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AD52" t="n">
         <v>2.92</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG52" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AH52" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AI52" t="n">
         <v>1.09</v>
@@ -7406,40 +7406,40 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P53" t="n">
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X53" t="n">
         <v>0</v>
@@ -7448,34 +7448,34 @@
         <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH53" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AI53" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
@@ -7538,13 +7538,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="M54" t="n">
-        <v>3.2</v>
+        <v>3.23</v>
       </c>
       <c r="N54" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7559,16 +7559,16 @@
         <v>1.38</v>
       </c>
       <c r="S54" t="n">
-        <v>2.65</v>
+        <v>2.76</v>
       </c>
       <c r="T54" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="U54" t="n">
         <v>1.35</v>
       </c>
       <c r="V54" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="W54" t="n">
         <v>1.08</v>
@@ -7580,16 +7580,16 @@
         <v>9</v>
       </c>
       <c r="Z54" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AA54" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AC54" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AD54" t="n">
         <v>3.3</v>
@@ -7598,16 +7598,16 @@
         <v>1.25</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AG54" t="n">
         <v>2</v>
       </c>
       <c r="AH54" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="AI54" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AJ54" t="inlineStr">
         <is>

--- a/jogos_2025-08-01.xlsx
+++ b/jogos_2025-08-01.xlsx
@@ -902,7 +902,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mariehamn</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.59</v>
+        <v>3.5</v>
       </c>
       <c r="M4" t="n">
-        <v>3.9</v>
+        <v>2.95</v>
       </c>
       <c r="N4" t="n">
-        <v>4.9</v>
+        <v>2.1</v>
       </c>
       <c r="O4" t="n">
-        <v>1.44</v>
+        <v>2.5</v>
       </c>
       <c r="P4" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T4" t="n">
         <v>2.95</v>
       </c>
-      <c r="R4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.42</v>
-      </c>
       <c r="U4" t="n">
-        <v>1.51</v>
+        <v>1.33</v>
       </c>
       <c r="V4" t="n">
-        <v>5.3</v>
+        <v>8</v>
       </c>
       <c r="W4" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X4" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.33</v>
+        <v>3</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.68</v>
+        <v>2.1</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.1</v>
+        <v>1.65</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.62</v>
+        <v>3.8</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AH4" t="n">
-        <v>4.6</v>
+        <v>7.1</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,76 +1202,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.5</v>
+        <v>6.3</v>
       </c>
       <c r="M6" t="n">
-        <v>2.95</v>
+        <v>3.78</v>
       </c>
       <c r="N6" t="n">
-        <v>2.1</v>
+        <v>1.42</v>
       </c>
       <c r="O6" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>11.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="R6" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="S6" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="T6" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="U6" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V6" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE6" t="n">
         <v>1.33</v>
       </c>
-      <c r="V6" t="n">
-        <v>8</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AF6" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AH6" t="n">
-        <v>7.1</v>
+        <v>5</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>6.3</v>
+        <v>1.59</v>
       </c>
       <c r="M7" t="n">
-        <v>3.78</v>
+        <v>3.9</v>
       </c>
       <c r="N7" t="n">
-        <v>1.42</v>
+        <v>4.9</v>
       </c>
       <c r="O7" t="n">
-        <v>3.2</v>
+        <v>1.44</v>
       </c>
       <c r="P7" t="n">
-        <v>11.25</v>
+        <v>17</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.44</v>
+        <v>2.95</v>
       </c>
       <c r="R7" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="S7" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="T7" t="n">
-        <v>2.75</v>
+        <v>2.42</v>
       </c>
       <c r="U7" t="n">
-        <v>1.37</v>
+        <v>1.51</v>
       </c>
       <c r="V7" t="n">
-        <v>6.5</v>
+        <v>5.3</v>
       </c>
       <c r="W7" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.34</v>
+        <v>4.33</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.97</v>
+        <v>1.73</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="AH7" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="M8" t="n">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="N8" t="n">
-        <v>8.23</v>
+        <v>8.5</v>
       </c>
       <c r="O8" t="n">
         <v>1.3</v>
@@ -1514,7 +1514,7 @@
         <v>3.85</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC8" t="n">
         <v>2</v>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.81</v>
+        <v>1.82</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="N11" t="n">
-        <v>2.3</v>
+        <v>3.35</v>
       </c>
       <c r="O11" t="n">
-        <v>1.98</v>
+        <v>1.58</v>
       </c>
       <c r="P11" t="n">
-        <v>13.25</v>
+        <v>19.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.91</v>
+        <v>2.39</v>
       </c>
       <c r="R11" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="S11" t="n">
-        <v>3.04</v>
+        <v>3.6</v>
       </c>
       <c r="T11" t="n">
-        <v>2.67</v>
+        <v>2.2</v>
       </c>
       <c r="U11" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="V11" t="n">
-        <v>6.5</v>
+        <v>4.75</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>10.5</v>
+        <v>14.7</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.7</v>
+        <v>5.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.8</v>
+        <v>1.51</v>
       </c>
       <c r="AC11" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.65</v>
+        <v>1.45</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="AH11" t="n">
-        <v>5.25</v>
+        <v>3.74</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.82</v>
+        <v>1.45</v>
       </c>
       <c r="M13" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N13" t="n">
-        <v>3.35</v>
+        <v>6.3</v>
       </c>
       <c r="O13" t="n">
-        <v>1.58</v>
+        <v>1.28</v>
       </c>
       <c r="P13" t="n">
-        <v>19.25</v>
+        <v>15</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.39</v>
+        <v>3.9</v>
       </c>
       <c r="R13" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="S13" t="n">
-        <v>3.6</v>
+        <v>3.22</v>
       </c>
       <c r="T13" t="n">
-        <v>2.2</v>
+        <v>2.47</v>
       </c>
       <c r="U13" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="V13" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AH13" t="n">
         <v>4.75</v>
       </c>
-      <c r="W13" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="Z13" t="n">
+      <c r="AI13" t="n">
         <v>1.12</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1.22</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.62</v>
+        <v>1.42</v>
       </c>
       <c r="M14" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="N14" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P14" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AF14" t="n">
         <v>1.75</v>
       </c>
-      <c r="O14" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AG14" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5.7</v>
+        <v>3.62</v>
       </c>
       <c r="M15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V15" t="n">
         <v>4.5</v>
       </c>
-      <c r="N15" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="O15" t="n">
-        <v>3</v>
-      </c>
-      <c r="P15" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V15" t="n">
-        <v>4.6</v>
-      </c>
       <c r="W15" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
         <v>1.67</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AH15" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,76 +2522,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>2.78</v>
       </c>
       <c r="M16" t="n">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="N16" t="n">
-        <v>3.15</v>
+        <v>2.3</v>
       </c>
       <c r="O16" t="n">
-        <v>1.8</v>
+        <v>2.07</v>
       </c>
       <c r="P16" t="n">
-        <v>8.5</v>
+        <v>13</v>
       </c>
       <c r="Q16" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V16" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AG16" t="n">
         <v>2.25</v>
       </c>
-      <c r="R16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V16" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AH16" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,76 +2654,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="M17" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N17" t="n">
         <v>2.3</v>
       </c>
       <c r="O17" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="P17" t="n">
-        <v>13</v>
+        <v>7.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.84</v>
+        <v>2.01</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S17" t="n">
         <v>3.1</v>
       </c>
       <c r="T17" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="U17" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="V17" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="W17" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AC17" t="n">
         <v>2.15</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AH17" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,76 +2786,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.42</v>
+        <v>5.7</v>
       </c>
       <c r="M18" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="N18" t="n">
-        <v>5.6</v>
+        <v>1.43</v>
       </c>
       <c r="O18" t="n">
-        <v>1.44</v>
+        <v>3</v>
       </c>
       <c r="P18" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.75</v>
+        <v>1.36</v>
       </c>
       <c r="R18" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="S18" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="T18" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="U18" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="V18" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="W18" t="n">
         <v>1.13</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AA18" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.47</v>
+        <v>1.7</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG18" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AH18" t="n">
-        <v>4.55</v>
+        <v>4.25</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.6</v>
+        <v>2.81</v>
       </c>
       <c r="M19" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="N19" t="n">
         <v>2.3</v>
       </c>
       <c r="O19" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="P19" t="n">
-        <v>7.7</v>
+        <v>13.25</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="R19" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="S19" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="T19" t="n">
-        <v>2.55</v>
+        <v>2.67</v>
       </c>
       <c r="U19" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="V19" t="n">
-        <v>5.2</v>
+        <v>6.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AA19" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AC19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG19" t="n">
         <v>2.15</v>
       </c>
-      <c r="AD19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.32</v>
-      </c>
       <c r="AH19" t="n">
-        <v>5.6</v>
+        <v>5.25</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,76 +3050,76 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.45</v>
+        <v>2</v>
       </c>
       <c r="M20" t="n">
-        <v>3.7</v>
+        <v>3.42</v>
       </c>
       <c r="N20" t="n">
-        <v>6.3</v>
+        <v>3.15</v>
       </c>
       <c r="O20" t="n">
-        <v>1.28</v>
+        <v>1.8</v>
       </c>
       <c r="P20" t="n">
-        <v>15</v>
+        <v>8.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.9</v>
+        <v>2.25</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="S20" t="n">
-        <v>3.22</v>
+        <v>2.7</v>
       </c>
       <c r="T20" t="n">
-        <v>2.47</v>
+        <v>2.89</v>
       </c>
       <c r="U20" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="V20" t="n">
-        <v>5.7</v>
+        <v>6.25</v>
       </c>
       <c r="W20" t="n">
         <v>1.08</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y20" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.98</v>
+        <v>3.1</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AC20" t="n">
         <v>1.75</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.02</v>
+        <v>1.77</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.71</v>
+        <v>1.95</v>
       </c>
       <c r="AH20" t="n">
-        <v>4.75</v>
+        <v>6.5</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="M25" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="N25" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="O25" t="n">
         <v>1.44</v>
@@ -3758,10 +3758,10 @@
         <v>3.9</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AC25" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AD25" t="n">
         <v>2.74</v>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,76 +3842,76 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.73</v>
+        <v>2.7</v>
       </c>
       <c r="M26" t="n">
         <v>3.5</v>
       </c>
       <c r="N26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O26" t="n">
+        <v>2</v>
+      </c>
+      <c r="P26" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V26" t="n">
+        <v>6</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AH26" t="n">
         <v>4.6</v>
       </c>
-      <c r="O26" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="P26" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V26" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>6.5</v>
-      </c>
       <c r="AI26" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,76 +3974,76 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.7</v>
+        <v>1.92</v>
       </c>
       <c r="M27" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N27" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="O27" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="P27" t="n">
-        <v>11</v>
+        <v>18.25</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.83</v>
+        <v>2.11</v>
       </c>
       <c r="R27" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="S27" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="T27" t="n">
-        <v>2.4</v>
+        <v>2.09</v>
       </c>
       <c r="U27" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="V27" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="W27" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X27" t="n">
         <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AA27" t="n">
-        <v>4</v>
+        <v>5.68</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.08</v>
+        <v>2.62</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.67</v>
+        <v>2.04</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.44</v>
+        <v>1.68</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.37</v>
+        <v>2.7</v>
       </c>
       <c r="AH27" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,76 +4106,76 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.92</v>
+        <v>1.73</v>
       </c>
       <c r="M28" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N28" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="O28" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="P28" t="n">
-        <v>18.25</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.11</v>
+        <v>2.75</v>
       </c>
       <c r="R28" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="S28" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="T28" t="n">
-        <v>2.09</v>
+        <v>2.85</v>
       </c>
       <c r="U28" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="V28" t="n">
-        <v>4.4</v>
+        <v>6.95</v>
       </c>
       <c r="W28" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="X28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y28" t="n">
-        <v>11</v>
+        <v>8.75</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.08</v>
+        <v>1.32</v>
       </c>
       <c r="AA28" t="n">
-        <v>5.68</v>
+        <v>3.3</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.44</v>
+        <v>2.02</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.62</v>
+        <v>1.75</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.04</v>
+        <v>3.5</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.68</v>
+        <v>1.29</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.38</v>
+        <v>1.9</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="AH28" t="n">
-        <v>3.4</v>
+        <v>6.5</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.3</v>
+        <v>1.09</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,76 +4370,76 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.41</v>
+        <v>2.07</v>
       </c>
       <c r="M30" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P30" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V30" t="n">
+        <v>6</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD30" t="n">
         <v>3.2</v>
       </c>
-      <c r="N30" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="O30" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="P30" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T30" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V30" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>3.82</v>
-      </c>
       <c r="AE30" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AH30" t="n">
-        <v>7.5</v>
+        <v>6.2</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,76 +4502,76 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
       <c r="M31" t="n">
-        <v>2.96</v>
+        <v>3.21</v>
       </c>
       <c r="N31" t="n">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="O31" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="P31" t="n">
         <v>10</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="R31" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="S31" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="T31" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V31" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG31" t="n">
         <v>2.5</v>
       </c>
-      <c r="U31" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V31" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AH31" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,76 +4634,76 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.07</v>
+        <v>2.41</v>
       </c>
       <c r="M32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N32" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="P32" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T32" t="n">
         <v>3.25</v>
       </c>
-      <c r="N32" t="n">
-        <v>3</v>
-      </c>
-      <c r="O32" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="P32" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Q32" t="n">
+      <c r="U32" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V32" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB32" t="n">
         <v>2.2</v>
       </c>
-      <c r="R32" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V32" t="n">
-        <v>6</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB32" t="n">
+      <c r="AC32" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG32" t="n">
         <v>1.85</v>
       </c>
-      <c r="AC32" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>2</v>
-      </c>
       <c r="AH32" t="n">
-        <v>6.2</v>
+        <v>7.5</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,76 +4898,76 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.99</v>
+        <v>2.88</v>
       </c>
       <c r="M34" t="n">
-        <v>3.21</v>
+        <v>2.96</v>
       </c>
       <c r="N34" t="n">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="O34" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="P34" t="n">
         <v>10</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="R34" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="S34" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="T34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V34" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG34" t="n">
         <v>2.25</v>
       </c>
-      <c r="U34" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V34" t="n">
+      <c r="AH34" t="n">
         <v>5.5</v>
       </c>
-      <c r="W34" t="n">
+      <c r="AI34" t="n">
         <v>1.14</v>
-      </c>
-      <c r="X34" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>1.22</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
@@ -4994,22 +4994,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,76 +5030,76 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>4.32</v>
+        <v>4</v>
       </c>
       <c r="M35" t="n">
-        <v>3.45</v>
+        <v>3.72</v>
       </c>
       <c r="N35" t="n">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="O35" t="n">
-        <v>2.79</v>
+        <v>2.55</v>
       </c>
       <c r="P35" t="n">
-        <v>8.699999999999999</v>
+        <v>13</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="R35" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="S35" t="n">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="T35" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="U35" t="n">
-        <v>1.39</v>
+        <v>1.58</v>
       </c>
       <c r="V35" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="W35" t="n">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="X35" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y35" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AA35" t="n">
-        <v>3.22</v>
+        <v>4.75</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.02</v>
+        <v>1.52</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.8</v>
+        <v>2.35</v>
       </c>
       <c r="AD35" t="n">
-        <v>3.27</v>
+        <v>2.36</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.32</v>
+        <v>1.59</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.81</v>
+        <v>1.57</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.88</v>
+        <v>2.25</v>
       </c>
       <c r="AH35" t="n">
-        <v>6.25</v>
+        <v>4.2</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,76 +5162,76 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.8</v>
+        <v>1.57</v>
       </c>
       <c r="M36" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="N36" t="n">
-        <v>2.38</v>
+        <v>5.83</v>
       </c>
       <c r="O36" t="n">
-        <v>2.15</v>
+        <v>1.48</v>
       </c>
       <c r="P36" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.93</v>
+        <v>3.25</v>
       </c>
       <c r="R36" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="S36" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="T36" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="U36" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="V36" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="W36" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X36" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y36" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AA36" t="n">
         <v>3.5</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AD36" t="n">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AG36" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AH36" t="n">
-        <v>6</v>
+        <v>6.57</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,76 +5294,76 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.18</v>
+        <v>4.32</v>
       </c>
       <c r="M37" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N37" t="n">
-        <v>2.92</v>
+        <v>1.79</v>
       </c>
       <c r="O37" t="n">
-        <v>1.77</v>
+        <v>2.79</v>
       </c>
       <c r="P37" t="n">
-        <v>13.75</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.09</v>
+        <v>1.56</v>
       </c>
       <c r="R37" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="S37" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="T37" t="n">
-        <v>2.51</v>
+        <v>2.75</v>
       </c>
       <c r="U37" t="n">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="V37" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="W37" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X37" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y37" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AA37" t="n">
-        <v>3.9</v>
+        <v>3.22</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.66</v>
+        <v>2.02</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.75</v>
+        <v>3.27</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.64</v>
+        <v>1.81</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.25</v>
+        <v>1.88</v>
       </c>
       <c r="AH37" t="n">
-        <v>4.75</v>
+        <v>6.25</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
@@ -5522,22 +5522,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,76 +5558,76 @@
         </is>
       </c>
       <c r="L39" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="M39" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N39" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="O39" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P39" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R39" t="n">
         <v>1.36</v>
       </c>
-      <c r="M39" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="N39" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="O39" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="P39" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.29</v>
-      </c>
       <c r="S39" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="T39" t="n">
-        <v>2.39</v>
+        <v>2.75</v>
       </c>
       <c r="U39" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="V39" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="W39" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X39" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y39" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AA39" t="n">
-        <v>4.6</v>
+        <v>3.42</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.46</v>
+        <v>3.08</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.46</v>
+        <v>1.28</v>
       </c>
       <c r="AF39" t="n">
         <v>1.8</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AH39" t="n">
-        <v>4.4</v>
+        <v>6.15</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
@@ -5654,22 +5654,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,76 +5690,76 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.55</v>
+        <v>2.8</v>
       </c>
       <c r="M40" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="N40" t="n">
-        <v>1.89</v>
+        <v>2.38</v>
       </c>
       <c r="O40" t="n">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="P40" t="n">
-        <v>12</v>
+        <v>8.5</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.67</v>
+        <v>1.93</v>
       </c>
       <c r="R40" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S40" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="T40" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="U40" t="n">
         <v>1.4</v>
       </c>
       <c r="V40" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="W40" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X40" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y40" t="n">
         <v>9</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AA40" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AD40" t="n">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AH40" t="n">
-        <v>6.15</v>
+        <v>6</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
@@ -5786,22 +5786,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,76 +5822,76 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>4</v>
+        <v>2.49</v>
       </c>
       <c r="M41" t="n">
-        <v>3.72</v>
+        <v>3.25</v>
       </c>
       <c r="N41" t="n">
-        <v>1.66</v>
+        <v>2.65</v>
       </c>
       <c r="O41" t="n">
-        <v>2.55</v>
+        <v>1.83</v>
       </c>
       <c r="P41" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.57</v>
+        <v>2.05</v>
       </c>
       <c r="R41" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="S41" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="T41" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="U41" t="n">
-        <v>1.58</v>
+        <v>1.42</v>
       </c>
       <c r="V41" t="n">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="W41" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="X41" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y41" t="n">
         <v>11</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AA41" t="n">
-        <v>4.75</v>
+        <v>3.6</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.52</v>
+        <v>1.77</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.35</v>
+        <v>1.89</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.36</v>
+        <v>3.04</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.59</v>
+        <v>1.33</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AG41" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH41" t="n">
-        <v>4.2</v>
+        <v>5.91</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,76 +5954,76 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.57</v>
+        <v>2.18</v>
       </c>
       <c r="M42" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="N42" t="n">
-        <v>5.83</v>
+        <v>2.92</v>
       </c>
       <c r="O42" t="n">
-        <v>1.48</v>
+        <v>1.77</v>
       </c>
       <c r="P42" t="n">
-        <v>9</v>
+        <v>13.75</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.25</v>
+        <v>2.09</v>
       </c>
       <c r="R42" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="S42" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="T42" t="n">
-        <v>2.75</v>
+        <v>2.51</v>
       </c>
       <c r="U42" t="n">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="V42" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="W42" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X42" t="n">
         <v>1.02</v>
       </c>
       <c r="Y42" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AA42" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.95</v>
+        <v>1.66</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AD42" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.95</v>
+        <v>1.64</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="AH42" t="n">
-        <v>6.57</v>
+        <v>4.75</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,76 +6086,76 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.49</v>
+        <v>1.36</v>
       </c>
       <c r="M43" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N43" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="O43" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P43" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S43" t="n">
         <v>3.25</v>
       </c>
-      <c r="N43" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="O43" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="P43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="R43" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S43" t="n">
-        <v>3</v>
-      </c>
       <c r="T43" t="n">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="U43" t="n">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="V43" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="W43" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X43" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y43" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AA43" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="AD43" t="n">
-        <v>3.04</v>
+        <v>2.46</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AG43" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AH43" t="n">
-        <v>5.91</v>
+        <v>4.4</v>
       </c>
       <c r="AI43" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
@@ -6182,22 +6182,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6218,76 +6218,76 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.54</v>
+        <v>2.4</v>
       </c>
       <c r="M44" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="N44" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="O44" t="n">
-        <v>1.4</v>
+        <v>1.85</v>
       </c>
       <c r="P44" t="n">
-        <v>11</v>
+        <v>7.7</v>
       </c>
       <c r="Q44" t="n">
-        <v>3</v>
+        <v>2.24</v>
       </c>
       <c r="R44" t="n">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="S44" t="n">
-        <v>3.25</v>
+        <v>2.3</v>
       </c>
       <c r="T44" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="V44" t="n">
+        <v>10</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X44" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB44" t="n">
         <v>2.5</v>
       </c>
-      <c r="U44" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V44" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X44" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y44" t="n">
+      <c r="AC44" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH44" t="n">
         <v>10</v>
       </c>
-      <c r="Z44" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>5.5</v>
-      </c>
       <c r="AI44" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
@@ -6314,22 +6314,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,76 +6350,76 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.4</v>
+        <v>1.54</v>
       </c>
       <c r="M45" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N45" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O45" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P45" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>3</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S45" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V45" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X45" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AD45" t="n">
         <v>2.9</v>
       </c>
-      <c r="N45" t="n">
-        <v>3</v>
-      </c>
-      <c r="O45" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="P45" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="R45" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S45" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T45" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="U45" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="V45" t="n">
-        <v>10</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X45" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>4.6</v>
-      </c>
       <c r="AE45" t="n">
-        <v>1.12</v>
+        <v>1.37</v>
       </c>
       <c r="AF45" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AH45" t="n">
-        <v>10</v>
+        <v>5.5</v>
       </c>
       <c r="AI45" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>

--- a/jogos_2025-08-01.xlsx
+++ b/jogos_2025-08-01.xlsx
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.5</v>
+        <v>6.3</v>
       </c>
       <c r="M4" t="n">
-        <v>2.95</v>
+        <v>3.78</v>
       </c>
       <c r="N4" t="n">
-        <v>2.1</v>
+        <v>1.42</v>
       </c>
       <c r="O4" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>11.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="R4" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="S4" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="T4" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="U4" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE4" t="n">
         <v>1.33</v>
       </c>
-      <c r="V4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AF4" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AH4" t="n">
-        <v>7.1</v>
+        <v>5</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,76 +1202,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>6.3</v>
+        <v>3.5</v>
       </c>
       <c r="M6" t="n">
-        <v>3.78</v>
+        <v>2.95</v>
       </c>
       <c r="N6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R6" t="n">
         <v>1.42</v>
       </c>
-      <c r="O6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P6" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.37</v>
-      </c>
       <c r="S6" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="T6" t="n">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="U6" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="V6" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="W6" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.34</v>
+        <v>3</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AD6" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AH6" t="n">
-        <v>5</v>
+        <v>7.1</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1646,10 +1646,10 @@
         <v>3.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AD9" t="n">
         <v>3.48</v>
@@ -1778,10 +1778,10 @@
         <v>4</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.61</v>
+        <v>1.77</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AD10" t="n">
         <v>2.6</v>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.82</v>
+        <v>2.81</v>
       </c>
       <c r="M11" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>3.35</v>
+        <v>2.3</v>
       </c>
       <c r="O11" t="n">
-        <v>1.58</v>
+        <v>1.98</v>
       </c>
       <c r="P11" t="n">
-        <v>19.25</v>
+        <v>13.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.39</v>
+        <v>1.91</v>
       </c>
       <c r="R11" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="S11" t="n">
-        <v>3.6</v>
+        <v>3.04</v>
       </c>
       <c r="T11" t="n">
-        <v>2.2</v>
+        <v>2.67</v>
       </c>
       <c r="U11" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="V11" t="n">
-        <v>4.75</v>
+        <v>6.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>14.7</v>
+        <v>10.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.2</v>
+        <v>3.7</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.51</v>
+        <v>1.8</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.45</v>
+        <v>1.65</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.74</v>
+        <v>5.25</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.49</v>
+        <v>2</v>
       </c>
       <c r="M12" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="N12" t="n">
-        <v>2.5</v>
+        <v>3.15</v>
       </c>
       <c r="O12" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="R12" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="T12" t="n">
-        <v>2.5</v>
+        <v>2.89</v>
       </c>
       <c r="U12" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="V12" t="n">
-        <v>5.5</v>
+        <v>6.25</v>
       </c>
       <c r="W12" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.66</v>
+        <v>2.02</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.45</v>
+        <v>2.6</v>
       </c>
       <c r="M13" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="N13" t="n">
-        <v>6.3</v>
+        <v>2.3</v>
       </c>
       <c r="O13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P13" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="R13" t="n">
         <v>1.28</v>
       </c>
-      <c r="P13" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.3</v>
-      </c>
       <c r="S13" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="T13" t="n">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="U13" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="V13" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="W13" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>8.9</v>
+        <v>13</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.95</v>
+        <v>1.66</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.02</v>
+        <v>1.58</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.71</v>
+        <v>2.32</v>
       </c>
       <c r="AH13" t="n">
-        <v>4.75</v>
+        <v>5.6</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.42</v>
+        <v>2.78</v>
       </c>
       <c r="M14" t="n">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="N14" t="n">
-        <v>5.6</v>
+        <v>2.3</v>
       </c>
       <c r="O14" t="n">
-        <v>1.44</v>
+        <v>2.07</v>
       </c>
       <c r="P14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.75</v>
+        <v>1.84</v>
       </c>
       <c r="R14" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S14" t="n">
         <v>3.1</v>
       </c>
       <c r="T14" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="U14" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="V14" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="W14" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AA14" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AB14" t="n">
         <v>1.6</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.62</v>
+        <v>2.47</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AG14" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AH14" t="n">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.62</v>
+        <v>1.45</v>
       </c>
       <c r="M15" t="n">
         <v>3.7</v>
       </c>
       <c r="N15" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P15" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V15" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC15" t="n">
         <v>1.75</v>
       </c>
-      <c r="O15" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.67</v>
+        <v>2.02</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.1</v>
+        <v>1.71</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,76 +2522,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.78</v>
+        <v>1.82</v>
       </c>
       <c r="M16" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="N16" t="n">
-        <v>2.3</v>
+        <v>3.35</v>
       </c>
       <c r="O16" t="n">
-        <v>2.07</v>
+        <v>1.58</v>
       </c>
       <c r="P16" t="n">
-        <v>13</v>
+        <v>19.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.84</v>
+        <v>2.39</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="S16" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="T16" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="U16" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="V16" t="n">
-        <v>5.6</v>
+        <v>4.75</v>
       </c>
       <c r="W16" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X16" t="n">
         <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>11</v>
+        <v>14.7</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AA16" t="n">
-        <v>4.33</v>
+        <v>5.2</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.47</v>
+        <v>2.2</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AH16" t="n">
-        <v>4.5</v>
+        <v>3.74</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,22 +2654,22 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.6</v>
+        <v>1.42</v>
       </c>
       <c r="M17" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="N17" t="n">
-        <v>2.3</v>
+        <v>5.6</v>
       </c>
       <c r="O17" t="n">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="P17" t="n">
-        <v>7.7</v>
+        <v>12</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.01</v>
+        <v>2.75</v>
       </c>
       <c r="R17" t="n">
         <v>1.28</v>
@@ -2678,22 +2678,22 @@
         <v>3.1</v>
       </c>
       <c r="T17" t="n">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="U17" t="n">
         <v>1.52</v>
       </c>
       <c r="V17" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Z17" t="n">
         <v>1.2</v>
@@ -2702,28 +2702,28 @@
         <v>4</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.32</v>
+        <v>2</v>
       </c>
       <c r="AH17" t="n">
-        <v>5.6</v>
+        <v>4.55</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.81</v>
+        <v>2.49</v>
       </c>
       <c r="M19" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="O19" t="n">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="P19" t="n">
-        <v>13.25</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="R19" t="n">
         <v>1.33</v>
       </c>
       <c r="S19" t="n">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="T19" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="U19" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="V19" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="X19" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AC19" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH19" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,76 +3050,76 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2</v>
+        <v>3.62</v>
       </c>
       <c r="M20" t="n">
-        <v>3.42</v>
+        <v>3.7</v>
       </c>
       <c r="N20" t="n">
-        <v>3.15</v>
+        <v>1.75</v>
       </c>
       <c r="O20" t="n">
-        <v>1.8</v>
+        <v>2.63</v>
       </c>
       <c r="P20" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T20" t="n">
         <v>2.25</v>
       </c>
-      <c r="R20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.89</v>
-      </c>
       <c r="U20" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="V20" t="n">
-        <v>6.25</v>
+        <v>4.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="X20" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.02</v>
+        <v>1.53</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AH20" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3278,22 +3278,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,76 +3314,76 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="M22" t="n">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="O22" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="P22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S22" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="T22" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="U22" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V22" t="n">
-        <v>7.6</v>
+        <v>5.75</v>
       </c>
       <c r="W22" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X22" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.82</v>
+        <v>2.15</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.35</v>
+        <v>2.7</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AH22" t="n">
-        <v>6.5</v>
+        <v>4.75</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -3410,22 +3410,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,76 +3446,76 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="P23" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q23" t="n">
         <v>2.2</v>
       </c>
-      <c r="M23" t="n">
+      <c r="R23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V23" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA23" t="n">
         <v>3.4</v>
       </c>
-      <c r="N23" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="P23" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="R23" t="n">
+      <c r="AB23" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AE23" t="n">
         <v>1.33</v>
       </c>
-      <c r="S23" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V23" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB23" t="n">
+      <c r="AF23" t="n">
         <v>1.67</v>
       </c>
-      <c r="AC23" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AG23" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AH23" t="n">
-        <v>4.75</v>
+        <v>6.5</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,76 +3842,76 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.7</v>
+        <v>1.92</v>
       </c>
       <c r="M26" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N26" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="O26" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="P26" t="n">
-        <v>11</v>
+        <v>18.25</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.83</v>
+        <v>2.11</v>
       </c>
       <c r="R26" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="S26" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="T26" t="n">
-        <v>2.4</v>
+        <v>2.09</v>
       </c>
       <c r="U26" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="V26" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="W26" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X26" t="n">
         <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AA26" t="n">
-        <v>4</v>
+        <v>5.68</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.08</v>
+        <v>2.62</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.67</v>
+        <v>2.04</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.44</v>
+        <v>1.68</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.37</v>
+        <v>2.7</v>
       </c>
       <c r="AH26" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,76 +3974,76 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.92</v>
+        <v>2.7</v>
       </c>
       <c r="M27" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N27" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O27" t="n">
+        <v>2</v>
+      </c>
+      <c r="P27" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S27" t="n">
         <v>3.1</v>
       </c>
-      <c r="O27" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="P27" t="n">
-        <v>18.25</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S27" t="n">
-        <v>3.6</v>
-      </c>
       <c r="T27" t="n">
-        <v>2.09</v>
+        <v>2.4</v>
       </c>
       <c r="U27" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="V27" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="W27" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X27" t="n">
         <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AA27" t="n">
-        <v>5.68</v>
+        <v>4</v>
       </c>
       <c r="AB27" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AE27" t="n">
         <v>1.44</v>
       </c>
-      <c r="AC27" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.68</v>
-      </c>
       <c r="AF27" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.7</v>
+        <v>2.37</v>
       </c>
       <c r="AH27" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="M28" t="n">
         <v>3.5</v>
       </c>
       <c r="N28" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O28" t="n">
         <v>1.57</v>
@@ -4133,7 +4133,7 @@
         <v>2.85</v>
       </c>
       <c r="U28" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="V28" t="n">
         <v>6.95</v>
@@ -4142,22 +4142,22 @@
         <v>1.08</v>
       </c>
       <c r="X28" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y28" t="n">
-        <v>8.75</v>
+        <v>9.5</v>
       </c>
       <c r="Z28" t="n">
         <v>1.32</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AD28" t="n">
         <v>3.5</v>
@@ -4166,16 +4166,16 @@
         <v>1.29</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AH28" t="n">
         <v>6.5</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,76 +4370,76 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.07</v>
+        <v>2.99</v>
       </c>
       <c r="M30" t="n">
-        <v>3.25</v>
+        <v>3.21</v>
       </c>
       <c r="N30" t="n">
-        <v>3</v>
+        <v>2.36</v>
       </c>
       <c r="O30" t="n">
+        <v>2</v>
+      </c>
+      <c r="P30" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q30" t="n">
         <v>1.8</v>
       </c>
-      <c r="P30" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>2.2</v>
-      </c>
       <c r="R30" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="S30" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="T30" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="U30" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="V30" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="W30" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X30" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y30" t="n">
         <v>10</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.5</v>
+        <v>4.75</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.85</v>
+        <v>1.56</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.85</v>
+        <v>2.27</v>
       </c>
       <c r="AD30" t="n">
-        <v>3.2</v>
+        <v>2.25</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AG30" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>6.2</v>
+        <v>4.2</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,76 +4502,76 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.99</v>
+        <v>2.41</v>
       </c>
       <c r="M31" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="N31" t="n">
-        <v>2.36</v>
+        <v>2.84</v>
       </c>
       <c r="O31" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="P31" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="R31" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="S31" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="T31" t="n">
-        <v>2.25</v>
+        <v>3.25</v>
       </c>
       <c r="U31" t="n">
-        <v>1.57</v>
+        <v>1.34</v>
       </c>
       <c r="V31" t="n">
-        <v>5.5</v>
+        <v>8.4</v>
       </c>
       <c r="W31" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="X31" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y31" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AA31" t="n">
-        <v>4.75</v>
+        <v>2.9</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.56</v>
+        <v>2.2</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.27</v>
+        <v>1.68</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.25</v>
+        <v>3.82</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="AH31" t="n">
-        <v>4.2</v>
+        <v>7.5</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,76 +4634,76 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.41</v>
+        <v>2.07</v>
       </c>
       <c r="M32" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N32" t="n">
+        <v>3</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P32" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V32" t="n">
+        <v>6</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD32" t="n">
         <v>3.2</v>
       </c>
-      <c r="N32" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="O32" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="P32" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T32" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V32" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>3.82</v>
-      </c>
       <c r="AE32" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AH32" t="n">
-        <v>7.5</v>
+        <v>6.2</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
@@ -4994,22 +4994,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,76 +5030,76 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>4</v>
+        <v>1.36</v>
       </c>
       <c r="M35" t="n">
-        <v>3.72</v>
+        <v>4.6</v>
       </c>
       <c r="N35" t="n">
-        <v>1.66</v>
+        <v>5.75</v>
       </c>
       <c r="O35" t="n">
-        <v>2.55</v>
+        <v>1.35</v>
       </c>
       <c r="P35" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.57</v>
+        <v>3.2</v>
       </c>
       <c r="R35" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="S35" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="T35" t="n">
-        <v>2.2</v>
+        <v>2.39</v>
       </c>
       <c r="U35" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="V35" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="W35" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X35" t="n">
         <v>1.03</v>
       </c>
       <c r="Y35" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z35" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AI35" t="n">
         <v>1.18</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>1.22</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
@@ -5126,22 +5126,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,76 +5162,76 @@
         </is>
       </c>
       <c r="L36" t="n">
+        <v>4</v>
+      </c>
+      <c r="M36" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="N36" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="O36" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="P36" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q36" t="n">
         <v>1.57</v>
       </c>
-      <c r="M36" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N36" t="n">
-        <v>5.83</v>
-      </c>
-      <c r="O36" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="P36" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>3.25</v>
-      </c>
       <c r="R36" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="S36" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="T36" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="U36" t="n">
-        <v>1.39</v>
+        <v>1.58</v>
       </c>
       <c r="V36" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W36" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="X36" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y36" t="n">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AA36" t="n">
-        <v>3.5</v>
+        <v>4.75</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.95</v>
+        <v>1.52</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.83</v>
+        <v>2.35</v>
       </c>
       <c r="AD36" t="n">
-        <v>3.2</v>
+        <v>2.36</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.3</v>
+        <v>1.59</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="AH36" t="n">
-        <v>6.57</v>
+        <v>4.2</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
@@ -5258,22 +5258,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,76 +5294,76 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>4.32</v>
+        <v>3.55</v>
       </c>
       <c r="M37" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="N37" t="n">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="O37" t="n">
-        <v>2.79</v>
+        <v>2.38</v>
       </c>
       <c r="P37" t="n">
-        <v>8.699999999999999</v>
+        <v>12</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="R37" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S37" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="T37" t="n">
         <v>2.75</v>
       </c>
       <c r="U37" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="V37" t="n">
         <v>6.5</v>
       </c>
       <c r="W37" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X37" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y37" t="n">
         <v>9</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AA37" t="n">
-        <v>3.22</v>
+        <v>3.42</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="AC37" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF37" t="n">
         <v>1.8</v>
       </c>
-      <c r="AD37" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>1.81</v>
-      </c>
       <c r="AG37" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AH37" t="n">
-        <v>6.25</v>
+        <v>6.15</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,76 +5426,76 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.06</v>
+        <v>2.49</v>
       </c>
       <c r="M38" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="N38" t="n">
-        <v>3.1</v>
+        <v>2.65</v>
       </c>
       <c r="O38" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="P38" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.26</v>
+        <v>2.05</v>
       </c>
       <c r="R38" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S38" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="T38" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="U38" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="V38" t="n">
         <v>5.75</v>
       </c>
       <c r="W38" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X38" t="n">
         <v>1.05</v>
       </c>
       <c r="Y38" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AA38" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC38" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.7</v>
+        <v>3.04</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH38" t="n">
-        <v>5</v>
+        <v>5.91</v>
       </c>
       <c r="AI38" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
@@ -5522,22 +5522,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,76 +5558,76 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.55</v>
+        <v>2.18</v>
       </c>
       <c r="M39" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="N39" t="n">
-        <v>1.89</v>
+        <v>2.92</v>
       </c>
       <c r="O39" t="n">
-        <v>2.38</v>
+        <v>1.77</v>
       </c>
       <c r="P39" t="n">
-        <v>12</v>
+        <v>13.75</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.67</v>
+        <v>2.09</v>
       </c>
       <c r="R39" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="S39" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T39" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V39" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD39" t="n">
         <v>2.75</v>
       </c>
-      <c r="U39" t="n">
+      <c r="AE39" t="n">
         <v>1.4</v>
       </c>
-      <c r="V39" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X39" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AF39" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="AH39" t="n">
-        <v>6.15</v>
+        <v>4.75</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,73 +5822,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.49</v>
+        <v>4.32</v>
       </c>
       <c r="M41" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="N41" t="n">
-        <v>2.65</v>
+        <v>1.79</v>
       </c>
       <c r="O41" t="n">
-        <v>1.83</v>
+        <v>2.79</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.05</v>
+        <v>1.56</v>
       </c>
       <c r="R41" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="T41" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="U41" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="V41" t="n">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="W41" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X41" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y41" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AA41" t="n">
-        <v>3.6</v>
+        <v>3.22</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.77</v>
+        <v>2.02</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AD41" t="n">
-        <v>3.04</v>
+        <v>3.27</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.65</v>
+        <v>1.81</v>
       </c>
       <c r="AG41" t="n">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="AH41" t="n">
-        <v>5.91</v>
+        <v>6.25</v>
       </c>
       <c r="AI41" t="n">
         <v>1.1</v>
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,76 +5954,76 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="M42" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N42" t="n">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="O42" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="P42" t="n">
-        <v>13.75</v>
+        <v>13.5</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.09</v>
+        <v>2.26</v>
       </c>
       <c r="R42" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S42" t="n">
         <v>3.1</v>
       </c>
       <c r="T42" t="n">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="U42" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="V42" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="W42" t="n">
         <v>1.11</v>
       </c>
       <c r="X42" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y42" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AA42" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AG42" t="n">
         <v>2.25</v>
       </c>
       <c r="AH42" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,76 +6086,76 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="M43" t="n">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="N43" t="n">
-        <v>5.75</v>
+        <v>5.83</v>
       </c>
       <c r="O43" t="n">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="P43" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="Q43" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S43" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V43" t="n">
+        <v>7</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X43" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD43" t="n">
         <v>3.2</v>
       </c>
-      <c r="R43" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S43" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T43" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="U43" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V43" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W43" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X43" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>2.46</v>
-      </c>
       <c r="AE43" t="n">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AH43" t="n">
-        <v>4.4</v>
+        <v>6.57</v>
       </c>
       <c r="AI43" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
@@ -7424,58 +7424,58 @@
         <v>1.8</v>
       </c>
       <c r="R53" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="S53" t="n">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="T53" t="n">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="U53" t="n">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="V53" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="W53" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC53" t="n">
         <v>3.5</v>
       </c>
-      <c r="W53" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>2.9</v>
-      </c>
       <c r="AD53" t="n">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AG53" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AH53" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="AI53" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AJ53" t="inlineStr">
         <is>

--- a/jogos_2025-08-01.xlsx
+++ b/jogos_2025-08-01.xlsx
@@ -902,7 +902,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>6.3</v>
+        <v>1.59</v>
       </c>
       <c r="M4" t="n">
-        <v>3.78</v>
+        <v>3.9</v>
       </c>
       <c r="N4" t="n">
-        <v>1.42</v>
+        <v>4.9</v>
       </c>
       <c r="O4" t="n">
-        <v>3.2</v>
+        <v>1.44</v>
       </c>
       <c r="P4" t="n">
-        <v>11.25</v>
+        <v>17</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.44</v>
+        <v>2.95</v>
       </c>
       <c r="R4" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="S4" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="T4" t="n">
-        <v>2.75</v>
+        <v>2.42</v>
       </c>
       <c r="U4" t="n">
-        <v>1.37</v>
+        <v>1.51</v>
       </c>
       <c r="V4" t="n">
-        <v>6.5</v>
+        <v>5.3</v>
       </c>
       <c r="W4" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X4" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.34</v>
+        <v>4.33</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.97</v>
+        <v>1.73</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="AH4" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rukh Vynnyky</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SK Poltava</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.65</v>
+        <v>6.96</v>
       </c>
       <c r="M5" t="n">
-        <v>3.41</v>
+        <v>4</v>
       </c>
       <c r="N5" t="n">
-        <v>5.9</v>
+        <v>1.45</v>
       </c>
       <c r="O5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P5" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="Q5" t="n">
         <v>1.44</v>
       </c>
-      <c r="P5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>4</v>
-      </c>
       <c r="R5" t="n">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="S5" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="T5" t="n">
-        <v>3.75</v>
+        <v>2.65</v>
       </c>
       <c r="U5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V5" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z5" t="n">
         <v>1.25</v>
       </c>
-      <c r="V5" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AA5" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.65</v>
+        <v>1.83</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.42</v>
+        <v>1.85</v>
       </c>
       <c r="AD5" t="n">
-        <v>5.1</v>
+        <v>2.95</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.1</v>
+        <v>1.35</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.63</v>
+        <v>2</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="AH5" t="n">
-        <v>8.5</v>
+        <v>5</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.5</v>
+        <v>4.02</v>
       </c>
       <c r="M6" t="n">
-        <v>2.95</v>
+        <v>3.46</v>
       </c>
       <c r="N6" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="O6" t="n">
         <v>2.5</v>
@@ -1220,28 +1220,28 @@
         <v>1.8</v>
       </c>
       <c r="R6" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S6" t="n">
         <v>2.6</v>
       </c>
       <c r="T6" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="U6" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V6" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X6" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y6" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="Z6" t="n">
         <v>1.33</v>
@@ -1250,28 +1250,28 @@
         <v>3</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AE6" t="n">
         <v>1.22</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AH6" t="n">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1298,22 +1298,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mariehamn</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,73 +1334,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.59</v>
+        <v>1.28</v>
       </c>
       <c r="M7" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="N7" t="n">
-        <v>4.9</v>
+        <v>8.5</v>
       </c>
       <c r="O7" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="P7" t="n">
-        <v>17</v>
+        <v>11.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.95</v>
+        <v>3.75</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="S7" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="T7" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="U7" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="V7" t="n">
-        <v>5.3</v>
+        <v>5.75</v>
       </c>
       <c r="W7" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.33</v>
+        <v>3.85</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AD7" t="n">
         <v>2.62</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.05</v>
+        <v>1.6</v>
       </c>
       <c r="AH7" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AI7" t="n">
         <v>1.14</v>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Rukh Vynnyky</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>SK Poltava</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.28</v>
+        <v>1.65</v>
       </c>
       <c r="M8" t="n">
-        <v>4.8</v>
+        <v>3.41</v>
       </c>
       <c r="N8" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V8" t="n">
         <v>8.5</v>
       </c>
-      <c r="O8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P8" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U8" t="n">
+      <c r="W8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Z8" t="n">
         <v>1.5</v>
       </c>
-      <c r="V8" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="W8" t="n">
+      <c r="AA8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AE8" t="n">
         <v>1.1</v>
       </c>
-      <c r="X8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AF8" t="n">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AH8" t="n">
-        <v>4.8</v>
+        <v>8.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.81</v>
+        <v>1.45</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="N11" t="n">
-        <v>2.3</v>
+        <v>6.3</v>
       </c>
       <c r="O11" t="n">
-        <v>1.98</v>
+        <v>1.28</v>
       </c>
       <c r="P11" t="n">
-        <v>13.25</v>
+        <v>15</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.91</v>
+        <v>3.9</v>
       </c>
       <c r="R11" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>3.04</v>
+        <v>3.22</v>
       </c>
       <c r="T11" t="n">
-        <v>2.67</v>
+        <v>2.47</v>
       </c>
       <c r="U11" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="V11" t="n">
-        <v>6.5</v>
+        <v>5.7</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>10.5</v>
+        <v>8.9</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.7</v>
+        <v>3.98</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AC11" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.65</v>
+        <v>2.02</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.15</v>
+        <v>1.71</v>
       </c>
       <c r="AH11" t="n">
-        <v>5.25</v>
+        <v>4.75</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P12" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG12" t="n">
         <v>2</v>
       </c>
-      <c r="M12" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="N12" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="P12" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V12" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AH12" t="n">
-        <v>6.5</v>
+        <v>4.55</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,55 +2126,55 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="M13" t="n">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="N13" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="O13" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="P13" t="n">
-        <v>7.7</v>
+        <v>13</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.01</v>
+        <v>1.84</v>
       </c>
       <c r="R13" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S13" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="T13" t="n">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="U13" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="V13" t="n">
-        <v>5.2</v>
+        <v>5.65</v>
       </c>
       <c r="W13" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AA13" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AC13" t="n">
         <v>2.15</v>
@@ -2183,19 +2183,19 @@
         <v>2.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>5.6</v>
+        <v>4.55</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="M14" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N14" t="n">
         <v>2.3</v>
       </c>
       <c r="O14" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="P14" t="n">
-        <v>13</v>
+        <v>7.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.84</v>
+        <v>2.01</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S14" t="n">
         <v>3.1</v>
       </c>
       <c r="T14" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="U14" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="V14" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="W14" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AC14" t="n">
         <v>2.15</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AH14" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.45</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
-        <v>3.7</v>
+        <v>3.44</v>
       </c>
       <c r="N15" t="n">
-        <v>6.3</v>
+        <v>3.25</v>
       </c>
       <c r="O15" t="n">
-        <v>1.28</v>
+        <v>1.8</v>
       </c>
       <c r="P15" t="n">
-        <v>15</v>
+        <v>8.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.9</v>
+        <v>2.25</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="S15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V15" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AA15" t="n">
         <v>3.22</v>
       </c>
-      <c r="T15" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V15" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>3.98</v>
-      </c>
       <c r="AB15" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.02</v>
+        <v>1.82</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.71</v>
+        <v>2.07</v>
       </c>
       <c r="AH15" t="n">
-        <v>4.75</v>
+        <v>6.2</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="M16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N16" t="n">
         <v>3.6</v>
-      </c>
-      <c r="N16" t="n">
-        <v>3.35</v>
       </c>
       <c r="O16" t="n">
         <v>1.58</v>
@@ -2543,43 +2543,43 @@
         <v>1.26</v>
       </c>
       <c r="S16" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="T16" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="U16" t="n">
         <v>1.62</v>
       </c>
       <c r="V16" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>14.7</v>
+        <v>17</v>
       </c>
       <c r="Z16" t="n">
         <v>1.12</v>
       </c>
       <c r="AA16" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AB16" t="n">
         <v>1.51</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AF16" t="n">
         <v>1.45</v>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,76 +2654,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.42</v>
+        <v>4.5</v>
       </c>
       <c r="M17" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="N17" t="n">
-        <v>5.6</v>
+        <v>1.66</v>
       </c>
       <c r="O17" t="n">
-        <v>1.44</v>
+        <v>2.63</v>
       </c>
       <c r="P17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.75</v>
+        <v>1.5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S17" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="T17" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="U17" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="V17" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG17" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH17" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="M19" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="N19" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="O19" t="n">
         <v>1.83</v>
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,76 +3050,76 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.62</v>
+        <v>2.81</v>
       </c>
       <c r="M20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="P20" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V20" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AA20" t="n">
         <v>3.7</v>
       </c>
-      <c r="N20" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="O20" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0</v>
-      </c>
       <c r="AB20" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.2</v>
+        <v>2.01</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3278,22 +3278,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,76 +3314,76 @@
         </is>
       </c>
       <c r="L22" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="P22" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q22" t="n">
         <v>2.2</v>
       </c>
-      <c r="M22" t="n">
+      <c r="R22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V22" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA22" t="n">
         <v>3.4</v>
       </c>
-      <c r="N22" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="P22" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="R22" t="n">
+      <c r="AB22" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AE22" t="n">
         <v>1.33</v>
       </c>
-      <c r="S22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V22" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB22" t="n">
+      <c r="AF22" t="n">
         <v>1.67</v>
       </c>
-      <c r="AC22" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AG22" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AH22" t="n">
-        <v>4.75</v>
+        <v>6.5</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -3410,22 +3410,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,76 +3446,76 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="M23" t="n">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="O23" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="P23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="R23" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S23" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="T23" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="U23" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V23" t="n">
-        <v>7.6</v>
+        <v>5.75</v>
       </c>
       <c r="W23" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X23" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.82</v>
+        <v>2.15</v>
       </c>
       <c r="AD23" t="n">
-        <v>3.35</v>
+        <v>2.7</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AH23" t="n">
-        <v>6.5</v>
+        <v>4.75</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,76 +3974,76 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.7</v>
+        <v>1.75</v>
       </c>
       <c r="M27" t="n">
         <v>3.5</v>
       </c>
       <c r="N27" t="n">
-        <v>2.4</v>
+        <v>4.7</v>
       </c>
       <c r="O27" t="n">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="P27" t="n">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.83</v>
+        <v>2.75</v>
       </c>
       <c r="R27" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V27" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Z27" t="n">
         <v>1.32</v>
       </c>
-      <c r="S27" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V27" t="n">
-        <v>6</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AA27" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.7</v>
+        <v>2.03</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.08</v>
+        <v>1.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.67</v>
+        <v>3.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.57</v>
+        <v>1.98</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.37</v>
+        <v>1.81</v>
       </c>
       <c r="AH27" t="n">
-        <v>4.6</v>
+        <v>6.5</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,76 +4106,76 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.75</v>
+        <v>2.7</v>
       </c>
       <c r="M28" t="n">
         <v>3.5</v>
       </c>
       <c r="N28" t="n">
-        <v>4.7</v>
+        <v>2.4</v>
       </c>
       <c r="O28" t="n">
+        <v>2</v>
+      </c>
+      <c r="P28" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V28" t="n">
+        <v>6</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF28" t="n">
         <v>1.57</v>
       </c>
-      <c r="P28" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V28" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.98</v>
-      </c>
       <c r="AG28" t="n">
-        <v>1.81</v>
+        <v>2.37</v>
       </c>
       <c r="AH28" t="n">
-        <v>6.5</v>
+        <v>4.6</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,76 +4370,76 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.99</v>
+        <v>2.5</v>
       </c>
       <c r="M30" t="n">
-        <v>3.21</v>
+        <v>3.15</v>
       </c>
       <c r="N30" t="n">
-        <v>2.36</v>
+        <v>2.8</v>
       </c>
       <c r="O30" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="P30" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="R30" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="S30" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="T30" t="n">
-        <v>2.25</v>
+        <v>2.85</v>
       </c>
       <c r="U30" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="V30" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="W30" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="X30" t="n">
         <v>1.04</v>
       </c>
       <c r="Y30" t="n">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AA30" t="n">
-        <v>4.75</v>
+        <v>2.9</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.56</v>
+        <v>2.2</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.27</v>
+        <v>1.67</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.25</v>
+        <v>3.6</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.53</v>
+        <v>1.27</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="AH30" t="n">
-        <v>4.2</v>
+        <v>7.5</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,76 +4502,76 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.41</v>
+        <v>2.07</v>
       </c>
       <c r="M31" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N31" t="n">
+        <v>3</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P31" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V31" t="n">
+        <v>6</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD31" t="n">
         <v>3.2</v>
       </c>
-      <c r="N31" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="O31" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="P31" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T31" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V31" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>3.82</v>
-      </c>
       <c r="AE31" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AH31" t="n">
-        <v>7.5</v>
+        <v>6.2</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,76 +4634,76 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.07</v>
+        <v>2.24</v>
       </c>
       <c r="M32" t="n">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="N32" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="O32" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V32" t="n">
+        <v>10</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG32" t="n">
         <v>1.8</v>
       </c>
-      <c r="P32" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V32" t="n">
-        <v>6</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>2</v>
-      </c>
       <c r="AH32" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,76 +4766,76 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.24</v>
+        <v>2.99</v>
       </c>
       <c r="M33" t="n">
-        <v>2.96</v>
+        <v>3.21</v>
       </c>
       <c r="N33" t="n">
-        <v>2.98</v>
+        <v>2.36</v>
       </c>
       <c r="O33" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q33" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T33" t="n">
         <v>2.25</v>
       </c>
-      <c r="R33" t="n">
+      <c r="U33" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V33" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF33" t="n">
         <v>1.5</v>
       </c>
-      <c r="S33" t="n">
+      <c r="AG33" t="n">
         <v>2.5</v>
       </c>
-      <c r="T33" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V33" t="n">
-        <v>10</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,76 +5030,76 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.36</v>
+        <v>4.32</v>
       </c>
       <c r="M35" t="n">
-        <v>4.6</v>
+        <v>3.45</v>
       </c>
       <c r="N35" t="n">
-        <v>5.75</v>
+        <v>1.79</v>
       </c>
       <c r="O35" t="n">
-        <v>1.35</v>
+        <v>2.79</v>
       </c>
       <c r="P35" t="n">
-        <v>16</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.2</v>
+        <v>1.56</v>
       </c>
       <c r="R35" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="S35" t="n">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="T35" t="n">
-        <v>2.39</v>
+        <v>2.75</v>
       </c>
       <c r="U35" t="n">
-        <v>1.52</v>
+        <v>1.39</v>
       </c>
       <c r="V35" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="W35" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X35" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y35" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AA35" t="n">
-        <v>4.6</v>
+        <v>3.22</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.65</v>
+        <v>2.02</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.46</v>
+        <v>3.27</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AH35" t="n">
-        <v>4.4</v>
+        <v>6.25</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
@@ -5126,22 +5126,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,76 +5162,76 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="M36" t="n">
-        <v>3.72</v>
+        <v>3</v>
       </c>
       <c r="N36" t="n">
-        <v>1.66</v>
+        <v>2.38</v>
       </c>
       <c r="O36" t="n">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="P36" t="n">
-        <v>13</v>
+        <v>8.5</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.57</v>
+        <v>1.93</v>
       </c>
       <c r="R36" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V36" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z36" t="n">
         <v>1.27</v>
       </c>
-      <c r="S36" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T36" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V36" t="n">
-        <v>5</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X36" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AA36" t="n">
-        <v>4.75</v>
+        <v>3.5</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.52</v>
+        <v>1.96</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.35</v>
+        <v>1.81</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.36</v>
+        <v>3.12</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.59</v>
+        <v>1.29</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AG36" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AH36" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
@@ -5258,22 +5258,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,76 +5294,76 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.55</v>
+        <v>2.18</v>
       </c>
       <c r="M37" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="N37" t="n">
-        <v>1.89</v>
+        <v>2.92</v>
       </c>
       <c r="O37" t="n">
-        <v>2.38</v>
+        <v>1.77</v>
       </c>
       <c r="P37" t="n">
-        <v>12</v>
+        <v>13.75</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.67</v>
+        <v>2.09</v>
       </c>
       <c r="R37" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="S37" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T37" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V37" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD37" t="n">
         <v>2.75</v>
       </c>
-      <c r="U37" t="n">
+      <c r="AE37" t="n">
         <v>1.4</v>
       </c>
-      <c r="V37" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X37" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AF37" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="AH37" t="n">
-        <v>6.15</v>
+        <v>4.75</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,76 +5426,76 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.49</v>
+        <v>1.57</v>
       </c>
       <c r="M38" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N38" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P38" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q38" t="n">
         <v>3.25</v>
       </c>
-      <c r="N38" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="O38" t="n">
+      <c r="R38" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V38" t="n">
+        <v>7</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC38" t="n">
         <v>1.83</v>
       </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S38" t="n">
-        <v>3</v>
-      </c>
-      <c r="T38" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V38" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X38" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.89</v>
-      </c>
       <c r="AD38" t="n">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="AH38" t="n">
-        <v>5.91</v>
+        <v>6.57</v>
       </c>
       <c r="AI38" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
@@ -5522,22 +5522,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,76 +5558,76 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.18</v>
+        <v>4</v>
       </c>
       <c r="M39" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="N39" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="O39" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="P39" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S39" t="n">
         <v>3.4</v>
       </c>
-      <c r="N39" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="O39" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="P39" t="n">
-        <v>13.75</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S39" t="n">
-        <v>3.1</v>
-      </c>
       <c r="T39" t="n">
-        <v>2.51</v>
+        <v>2.2</v>
       </c>
       <c r="U39" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="V39" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="W39" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X39" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y39" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AA39" t="n">
-        <v>3.9</v>
+        <v>4.75</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.75</v>
+        <v>2.36</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.4</v>
+        <v>1.59</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AG39" t="n">
         <v>2.25</v>
       </c>
       <c r="AH39" t="n">
-        <v>4.75</v>
+        <v>4.2</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,76 +5690,76 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.8</v>
+        <v>2.49</v>
       </c>
       <c r="M40" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N40" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S40" t="n">
         <v>3</v>
       </c>
-      <c r="N40" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="O40" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="P40" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S40" t="n">
-        <v>2.9</v>
-      </c>
       <c r="T40" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="U40" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="V40" t="n">
-        <v>6.4</v>
+        <v>5.75</v>
       </c>
       <c r="W40" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X40" t="n">
         <v>1.05</v>
       </c>
       <c r="Y40" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AA40" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.96</v>
+        <v>1.77</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="AD40" t="n">
-        <v>3.12</v>
+        <v>3.04</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AG40" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AH40" t="n">
-        <v>6</v>
+        <v>5.91</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
@@ -5786,22 +5786,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>UCD</